--- a/04_结果/示例审批/外部数据新版式示例.xlsx
+++ b/04_结果/示例审批/外部数据新版式示例.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -490,21 +490,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. VIX/TNX 按 ETF 格式展示：第14行=名称，第15行=Open/High/Low/Close/Adj Close/Volume/回报。</t>
+          <t>1. VIX/TNX 原始数据按 ETF 格式展示：第14行=名称，第15行=Open/High/Low/Close/Adj Close/Volume。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2. 派生外部列：第14行=指标名称，第15行=计算公式（谁减谁），数据区为 Excel 公式。</t>
+          <t>2. VIX/TNX 回报与变化指标集中放一起，第15行直接写名称（如 VIX回报、VIX_Chg%、TNX_ChgBp），后面用空列分隔。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3. ETF 回报、VIX/TNX 回报、派生指标均用公式计算，回报率保留4位小数。</t>
+          <t>3. 其他派生外部列：第14行=指标名称，第15行=计算公式（谁减谁），数据区为 Excel 公式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4. ETF 回报、VIX/TNX 回报、派生指标均用公式计算，回报率保留4位小数。</t>
         </is>
       </c>
     </row>
@@ -519,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A14:CV42"/>
+  <dimension ref="A14:CW42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -622,6 +629,7 @@
     <col width="14" customWidth="1" min="98" max="98"/>
     <col width="14" customWidth="1" min="99" max="99"/>
     <col width="14" customWidth="1" min="100" max="100"/>
+    <col width="14" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="14" ht="30" customHeight="1">
@@ -751,68 +759,53 @@
       <c r="CB14" s="2" t="n"/>
       <c r="CC14" s="2" t="n"/>
       <c r="CD14" s="2" t="n"/>
-      <c r="CE14" s="2" t="n"/>
-      <c r="CF14" s="2" t="inlineStr">
+      <c r="CE14" s="2" t="inlineStr">
         <is>
           <t>TNX</t>
         </is>
       </c>
+      <c r="CF14" s="2" t="n"/>
       <c r="CG14" s="2" t="n"/>
       <c r="CH14" s="2" t="n"/>
       <c r="CI14" s="2" t="n"/>
       <c r="CJ14" s="2" t="n"/>
       <c r="CK14" s="2" t="n"/>
-      <c r="CL14" s="2" t="inlineStr">
-        <is>
-          <t>VIX_Chg%</t>
-        </is>
-      </c>
-      <c r="CM14" s="2" t="inlineStr">
-        <is>
-          <t>TNX_ChgBp</t>
-        </is>
-      </c>
-      <c r="CN14" s="2" t="inlineStr">
-        <is>
-          <t>VIX_5dChg</t>
-        </is>
-      </c>
-      <c r="CO14" s="2" t="inlineStr">
-        <is>
-          <t>VIX_20dVol</t>
-        </is>
-      </c>
-      <c r="CP14" s="2" t="inlineStr">
+      <c r="CL14" s="2" t="n"/>
+      <c r="CM14" s="2" t="n"/>
+      <c r="CN14" s="2" t="n"/>
+      <c r="CO14" s="2" t="n"/>
+      <c r="CP14" s="2" t="n"/>
+      <c r="CQ14" s="2" t="inlineStr">
         <is>
           <t>CreditSpread</t>
         </is>
       </c>
-      <c r="CQ14" s="2" t="inlineStr">
+      <c r="CR14" s="2" t="inlineStr">
         <is>
           <t>JNKSpread</t>
         </is>
       </c>
-      <c r="CR14" s="2" t="inlineStr">
+      <c r="CS14" s="2" t="inlineStr">
         <is>
           <t>StkBonCorr</t>
         </is>
       </c>
-      <c r="CS14" s="2" t="inlineStr">
+      <c r="CT14" s="2" t="inlineStr">
         <is>
           <t>USDGoldRatio</t>
         </is>
       </c>
-      <c r="CT14" s="2" t="inlineStr">
+      <c r="CU14" s="2" t="inlineStr">
         <is>
           <t>SectRotation</t>
         </is>
       </c>
-      <c r="CU14" s="2" t="inlineStr">
+      <c r="CV14" s="2" t="inlineStr">
         <is>
           <t>VIX_TNX_Ratio</t>
         </is>
       </c>
-      <c r="CV14" s="2" t="inlineStr">
+      <c r="CW14" s="2" t="inlineStr">
         <is>
           <t>YldCurveProxy</t>
         </is>
@@ -1178,99 +1171,100 @@
           <t>Volume</t>
         </is>
       </c>
-      <c r="CB15" s="2" t="inlineStr">
-        <is>
-          <t>回报</t>
-        </is>
-      </c>
-      <c r="CC15" s="2" t="n"/>
+      <c r="CB15" s="2" t="n"/>
+      <c r="CC15" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
       <c r="CD15" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>High</t>
         </is>
       </c>
       <c r="CE15" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="CF15" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="CG15" s="2" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Adj Close</t>
         </is>
       </c>
       <c r="CH15" s="2" t="inlineStr">
         <is>
-          <t>Adj Close</t>
-        </is>
-      </c>
-      <c r="CI15" s="2" t="inlineStr">
-        <is>
           <t>Volume</t>
         </is>
       </c>
+      <c r="CI15" s="2" t="n"/>
       <c r="CJ15" s="2" t="inlineStr">
         <is>
-          <t>回报</t>
-        </is>
-      </c>
-      <c r="CK15" s="2" t="n"/>
+          <t>VIX回报</t>
+        </is>
+      </c>
+      <c r="CK15" s="2" t="inlineStr">
+        <is>
+          <t>VIX_Chg%</t>
+        </is>
+      </c>
       <c r="CL15" s="2" t="inlineStr">
         <is>
-          <t>VIX_close/昨VIX_close-1</t>
+          <t>VIX_5dChg</t>
         </is>
       </c>
       <c r="CM15" s="2" t="inlineStr">
         <is>
-          <t>(TNX_close-昨TNX_close)*100</t>
+          <t>VIX_20dVol</t>
         </is>
       </c>
       <c r="CN15" s="2" t="inlineStr">
         <is>
-          <t>VIX_close/5日前VIX_close-1</t>
+          <t>TNX回报</t>
         </is>
       </c>
       <c r="CO15" s="2" t="inlineStr">
         <is>
-          <t>STDEV(VIX日变化,近20日)</t>
-        </is>
-      </c>
-      <c r="CP15" s="2" t="inlineStr">
+          <t>TNX_ChgBp</t>
+        </is>
+      </c>
+      <c r="CP15" s="2" t="n"/>
+      <c r="CQ15" s="2" t="inlineStr">
         <is>
           <t>HYG-TLT</t>
         </is>
       </c>
-      <c r="CQ15" s="2" t="inlineStr">
+      <c r="CR15" s="2" t="inlineStr">
         <is>
           <t>JNK-TLT</t>
         </is>
       </c>
-      <c r="CR15" s="2" t="inlineStr">
+      <c r="CS15" s="2" t="inlineStr">
         <is>
           <t>CORREL(SPY,TLT,近20日)</t>
         </is>
       </c>
-      <c r="CS15" s="2" t="inlineStr">
+      <c r="CT15" s="2" t="inlineStr">
         <is>
           <t>UUP-GLD</t>
         </is>
       </c>
-      <c r="CT15" s="2" t="inlineStr">
+      <c r="CU15" s="2" t="inlineStr">
         <is>
           <t>XLK-XLF</t>
         </is>
       </c>
-      <c r="CU15" s="2" t="inlineStr">
+      <c r="CV15" s="2" t="inlineStr">
         <is>
           <t>VIX_close/TNX_close</t>
         </is>
       </c>
-      <c r="CV15" s="2" t="inlineStr">
+      <c r="CW15" s="2" t="inlineStr">
         <is>
           <t>TLT-TIP</t>
         </is>
@@ -1399,75 +1393,76 @@
       <c r="CA16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB16" s="4">
-        <f>IF(COUNT(BY16:BY17)=2,ROUND((BY16/BY17-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC16" s="3" t="n"/>
+      <c r="CB16" s="3" t="n"/>
+      <c r="CC16" s="3" t="n">
+        <v>4.692</v>
+      </c>
       <c r="CD16" s="3" t="n">
-        <v>4.692</v>
+        <v>4.703</v>
       </c>
       <c r="CE16" s="3" t="n">
-        <v>4.703</v>
+        <v>4.668</v>
       </c>
       <c r="CF16" s="3" t="n">
-        <v>4.668</v>
+        <v>4.684</v>
       </c>
       <c r="CG16" s="3" t="n">
         <v>4.684</v>
       </c>
       <c r="CH16" s="3" t="n">
-        <v>4.684</v>
-      </c>
-      <c r="CI16" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI16" s="3" t="n"/>
       <c r="CJ16" s="4">
-        <f>IF(COUNT(CG16:CG17)=2,ROUND((CG16/CG17-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK16" s="3" t="n"/>
+        <f>IF(COUNT(BY16:BY17)=2,ROUND((BY16/BY17-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK16" s="4">
+        <f>IF(COUNT(BY16:BY17)=2,ROUND((BY16/BY17-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL16" s="4">
-        <f>IF(COUNT(BY16:BY17)=2,ROUND((BY16/BY17-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM16" s="5">
-        <f>IF(COUNT(CG16:CG17)=2,(CG16-CG17)*100,"")</f>
+        <f>IF(COUNT(BY16:BY21)=6,ROUND((BY16/BY21-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM16" s="4">
+        <f>IF(COUNT(CK16:CK35)=20,IFERROR(ROUND(STDEV(CK16:CK35),4),""),"")</f>
         <v/>
       </c>
       <c r="CN16" s="4">
-        <f>IF(COUNT(BY16:BY21)=6,ROUND((BY16/BY21-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO16" s="4">
-        <f>IF(COUNT(CL16:CL35)=20,ROUND(STDEV(CL16:CL35),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP16" s="4">
+        <f>IF(COUNT(CF16:CF17)=2,ROUND((CF16/CF17-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO16" s="5">
+        <f>IF(COUNT(CF16:CF17)=2,(CF16-CF17)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP16" s="3" t="n"/>
+      <c r="CQ16" s="4">
         <f>X16-P16</f>
         <v/>
       </c>
-      <c r="CQ16" s="4">
+      <c r="CR16" s="4">
         <f>AF16-P16</f>
         <v/>
       </c>
-      <c r="CR16" s="6">
-        <f>IF(COUNT(H16:H35)=20,CORREL(H16:H35,P16:P35),"")</f>
-        <v/>
-      </c>
-      <c r="CS16" s="4">
+      <c r="CS16" s="6">
+        <f>IF(COUNT(H16:H35)=20,IFERROR(CORREL(H16:H35,P16:P35),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT16" s="4">
         <f>AN16-AV16</f>
         <v/>
       </c>
-      <c r="CT16" s="4">
+      <c r="CU16" s="4">
         <f>BD16-BL16</f>
         <v/>
       </c>
-      <c r="CU16" s="6">
-        <f>BY16/CG16</f>
-        <v/>
-      </c>
-      <c r="CV16" s="4">
+      <c r="CV16" s="6">
+        <f>BY16/CF16</f>
+        <v/>
+      </c>
+      <c r="CW16" s="4">
         <f>P16-BT16</f>
         <v/>
       </c>
@@ -1595,75 +1590,76 @@
       <c r="CA17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB17" s="4">
-        <f>IF(COUNT(BY17:BY18)=2,ROUND((BY17/BY18-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC17" s="3" t="n"/>
+      <c r="CB17" s="3" t="n"/>
+      <c r="CC17" s="3" t="n">
+        <v>4.662</v>
+      </c>
       <c r="CD17" s="3" t="n">
+        <v>4.703</v>
+      </c>
+      <c r="CE17" s="3" t="n">
         <v>4.662</v>
       </c>
-      <c r="CE17" s="3" t="n">
-        <v>4.703</v>
-      </c>
       <c r="CF17" s="3" t="n">
-        <v>4.662</v>
+        <v>4.699</v>
       </c>
       <c r="CG17" s="3" t="n">
         <v>4.699</v>
       </c>
       <c r="CH17" s="3" t="n">
-        <v>4.699</v>
-      </c>
-      <c r="CI17" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI17" s="3" t="n"/>
       <c r="CJ17" s="4">
-        <f>IF(COUNT(CG17:CG18)=2,ROUND((CG17/CG18-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK17" s="3" t="n"/>
+        <f>IF(COUNT(BY17:BY18)=2,ROUND((BY17/BY18-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK17" s="4">
+        <f>IF(COUNT(BY17:BY18)=2,ROUND((BY17/BY18-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL17" s="4">
-        <f>IF(COUNT(BY17:BY18)=2,ROUND((BY17/BY18-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM17" s="5">
-        <f>IF(COUNT(CG17:CG18)=2,(CG17-CG18)*100,"")</f>
+        <f>IF(COUNT(BY17:BY22)=6,ROUND((BY17/BY22-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM17" s="4">
+        <f>IF(COUNT(CK17:CK36)=20,IFERROR(ROUND(STDEV(CK17:CK36),4),""),"")</f>
         <v/>
       </c>
       <c r="CN17" s="4">
-        <f>IF(COUNT(BY17:BY22)=6,ROUND((BY17/BY22-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO17" s="4">
-        <f>IF(COUNT(CL17:CL36)=20,ROUND(STDEV(CL17:CL36),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP17" s="4">
+        <f>IF(COUNT(CF17:CF18)=2,ROUND((CF17/CF18-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO17" s="5">
+        <f>IF(COUNT(CF17:CF18)=2,(CF17-CF18)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP17" s="3" t="n"/>
+      <c r="CQ17" s="4">
         <f>X17-P17</f>
         <v/>
       </c>
-      <c r="CQ17" s="4">
+      <c r="CR17" s="4">
         <f>AF17-P17</f>
         <v/>
       </c>
-      <c r="CR17" s="6">
-        <f>IF(COUNT(H17:H36)=20,CORREL(H17:H36,P17:P36),"")</f>
-        <v/>
-      </c>
-      <c r="CS17" s="4">
+      <c r="CS17" s="6">
+        <f>IF(COUNT(H17:H36)=20,IFERROR(CORREL(H17:H36,P17:P36),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT17" s="4">
         <f>AN17-AV17</f>
         <v/>
       </c>
-      <c r="CT17" s="4">
+      <c r="CU17" s="4">
         <f>BD17-BL17</f>
         <v/>
       </c>
-      <c r="CU17" s="6">
-        <f>BY17/CG17</f>
-        <v/>
-      </c>
-      <c r="CV17" s="4">
+      <c r="CV17" s="6">
+        <f>BY17/CF17</f>
+        <v/>
+      </c>
+      <c r="CW17" s="4">
         <f>P17-BT17</f>
         <v/>
       </c>
@@ -1899,75 +1895,76 @@
       <c r="CA18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB18" s="4">
-        <f>IF(COUNT(BY18:BY19)=2,ROUND((BY18/BY19-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC18" s="3" t="n"/>
+      <c r="CB18" s="3" t="n"/>
+      <c r="CC18" s="3" t="n">
+        <v>4.664</v>
+      </c>
       <c r="CD18" s="3" t="n">
-        <v>4.664</v>
+        <v>4.672</v>
       </c>
       <c r="CE18" s="3" t="n">
-        <v>4.672</v>
+        <v>4.603</v>
       </c>
       <c r="CF18" s="3" t="n">
-        <v>4.603</v>
+        <v>4.66</v>
       </c>
       <c r="CG18" s="3" t="n">
         <v>4.66</v>
       </c>
       <c r="CH18" s="3" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="CI18" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI18" s="3" t="n"/>
       <c r="CJ18" s="4">
-        <f>IF(COUNT(CG18:CG19)=2,ROUND((CG18/CG19-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK18" s="3" t="n"/>
+        <f>IF(COUNT(BY18:BY19)=2,ROUND((BY18/BY19-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK18" s="4">
+        <f>IF(COUNT(BY18:BY19)=2,ROUND((BY18/BY19-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL18" s="4">
-        <f>IF(COUNT(BY18:BY19)=2,ROUND((BY18/BY19-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM18" s="5">
-        <f>IF(COUNT(CG18:CG19)=2,(CG18-CG19)*100,"")</f>
+        <f>IF(COUNT(BY18:BY23)=6,ROUND((BY18/BY23-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM18" s="4">
+        <f>IF(COUNT(CK18:CK37)=20,IFERROR(ROUND(STDEV(CK18:CK37),4),""),"")</f>
         <v/>
       </c>
       <c r="CN18" s="4">
-        <f>IF(COUNT(BY18:BY23)=6,ROUND((BY18/BY23-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO18" s="4">
-        <f>IF(COUNT(CL18:CL37)=20,ROUND(STDEV(CL18:CL37),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP18" s="4">
+        <f>IF(COUNT(CF18:CF19)=2,ROUND((CF18/CF19-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO18" s="5">
+        <f>IF(COUNT(CF18:CF19)=2,(CF18-CF19)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP18" s="3" t="n"/>
+      <c r="CQ18" s="4">
         <f>X18-P18</f>
         <v/>
       </c>
-      <c r="CQ18" s="4">
+      <c r="CR18" s="4">
         <f>AF18-P18</f>
         <v/>
       </c>
-      <c r="CR18" s="6">
-        <f>IF(COUNT(H18:H37)=20,CORREL(H18:H37,P18:P37),"")</f>
-        <v/>
-      </c>
-      <c r="CS18" s="4">
+      <c r="CS18" s="6">
+        <f>IF(COUNT(H18:H37)=20,IFERROR(CORREL(H18:H37,P18:P37),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT18" s="4">
         <f>AN18-AV18</f>
         <v/>
       </c>
-      <c r="CT18" s="4">
+      <c r="CU18" s="4">
         <f>BD18-BL18</f>
         <v/>
       </c>
-      <c r="CU18" s="6">
-        <f>BY18/CG18</f>
-        <v/>
-      </c>
-      <c r="CV18" s="4">
+      <c r="CV18" s="6">
+        <f>BY18/CF18</f>
+        <v/>
+      </c>
+      <c r="CW18" s="4">
         <f>P18-BT18</f>
         <v/>
       </c>
@@ -2203,75 +2200,76 @@
       <c r="CA19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB19" s="4">
-        <f>IF(COUNT(BY19:BY20)=2,ROUND((BY19/BY20-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC19" s="3" t="n"/>
+      <c r="CB19" s="3" t="n"/>
+      <c r="CC19" s="3" t="n">
+        <v>4.643</v>
+      </c>
       <c r="CD19" s="3" t="n">
-        <v>4.643</v>
+        <v>4.676</v>
       </c>
       <c r="CE19" s="3" t="n">
-        <v>4.676</v>
+        <v>4.635</v>
       </c>
       <c r="CF19" s="3" t="n">
-        <v>4.635</v>
+        <v>4.67</v>
       </c>
       <c r="CG19" s="3" t="n">
         <v>4.67</v>
       </c>
       <c r="CH19" s="3" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="CI19" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI19" s="3" t="n"/>
       <c r="CJ19" s="4">
-        <f>IF(COUNT(CG19:CG20)=2,ROUND((CG19/CG20-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK19" s="3" t="n"/>
+        <f>IF(COUNT(BY19:BY20)=2,ROUND((BY19/BY20-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK19" s="4">
+        <f>IF(COUNT(BY19:BY20)=2,ROUND((BY19/BY20-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL19" s="4">
-        <f>IF(COUNT(BY19:BY20)=2,ROUND((BY19/BY20-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM19" s="5">
-        <f>IF(COUNT(CG19:CG20)=2,(CG19-CG20)*100,"")</f>
+        <f>IF(COUNT(BY19:BY24)=6,ROUND((BY19/BY24-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM19" s="4">
+        <f>IF(COUNT(CK19:CK38)=20,IFERROR(ROUND(STDEV(CK19:CK38),4),""),"")</f>
         <v/>
       </c>
       <c r="CN19" s="4">
-        <f>IF(COUNT(BY19:BY24)=6,ROUND((BY19/BY24-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO19" s="4">
-        <f>IF(COUNT(CL19:CL38)=20,ROUND(STDEV(CL19:CL38),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP19" s="4">
+        <f>IF(COUNT(CF19:CF20)=2,ROUND((CF19/CF20-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO19" s="5">
+        <f>IF(COUNT(CF19:CF20)=2,(CF19-CF20)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP19" s="3" t="n"/>
+      <c r="CQ19" s="4">
         <f>X19-P19</f>
         <v/>
       </c>
-      <c r="CQ19" s="4">
+      <c r="CR19" s="4">
         <f>AF19-P19</f>
         <v/>
       </c>
-      <c r="CR19" s="6">
-        <f>IF(COUNT(H19:H38)=20,CORREL(H19:H38,P19:P38),"")</f>
-        <v/>
-      </c>
-      <c r="CS19" s="4">
+      <c r="CS19" s="6">
+        <f>IF(COUNT(H19:H38)=20,IFERROR(CORREL(H19:H38,P19:P38),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT19" s="4">
         <f>AN19-AV19</f>
         <v/>
       </c>
-      <c r="CT19" s="4">
+      <c r="CU19" s="4">
         <f>BD19-BL19</f>
         <v/>
       </c>
-      <c r="CU19" s="6">
-        <f>BY19/CG19</f>
-        <v/>
-      </c>
-      <c r="CV19" s="4">
+      <c r="CV19" s="6">
+        <f>BY19/CF19</f>
+        <v/>
+      </c>
+      <c r="CW19" s="4">
         <f>P19-BT19</f>
         <v/>
       </c>
@@ -2507,75 +2505,76 @@
       <c r="CA20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB20" s="4">
-        <f>IF(COUNT(BY20:BY21)=2,ROUND((BY20/BY21-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC20" s="3" t="n"/>
+      <c r="CB20" s="3" t="n"/>
+      <c r="CC20" s="3" t="n">
+        <v>4.609</v>
+      </c>
       <c r="CD20" s="3" t="n">
-        <v>4.609</v>
+        <v>4.639</v>
       </c>
       <c r="CE20" s="3" t="n">
-        <v>4.639</v>
+        <v>4.607</v>
       </c>
       <c r="CF20" s="3" t="n">
-        <v>4.607</v>
+        <v>4.617</v>
       </c>
       <c r="CG20" s="3" t="n">
         <v>4.617</v>
       </c>
       <c r="CH20" s="3" t="n">
-        <v>4.617</v>
-      </c>
-      <c r="CI20" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI20" s="3" t="n"/>
       <c r="CJ20" s="4">
-        <f>IF(COUNT(CG20:CG21)=2,ROUND((CG20/CG21-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK20" s="3" t="n"/>
+        <f>IF(COUNT(BY20:BY21)=2,ROUND((BY20/BY21-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK20" s="4">
+        <f>IF(COUNT(BY20:BY21)=2,ROUND((BY20/BY21-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL20" s="4">
-        <f>IF(COUNT(BY20:BY21)=2,ROUND((BY20/BY21-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM20" s="5">
-        <f>IF(COUNT(CG20:CG21)=2,(CG20-CG21)*100,"")</f>
+        <f>IF(COUNT(BY20:BY25)=6,ROUND((BY20/BY25-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM20" s="4">
+        <f>IF(COUNT(CK20:CK39)=20,IFERROR(ROUND(STDEV(CK20:CK39),4),""),"")</f>
         <v/>
       </c>
       <c r="CN20" s="4">
-        <f>IF(COUNT(BY20:BY25)=6,ROUND((BY20/BY25-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO20" s="4">
-        <f>IF(COUNT(CL20:CL39)=20,ROUND(STDEV(CL20:CL39),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP20" s="4">
+        <f>IF(COUNT(CF20:CF21)=2,ROUND((CF20/CF21-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO20" s="5">
+        <f>IF(COUNT(CF20:CF21)=2,(CF20-CF21)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP20" s="3" t="n"/>
+      <c r="CQ20" s="4">
         <f>X20-P20</f>
         <v/>
       </c>
-      <c r="CQ20" s="4">
+      <c r="CR20" s="4">
         <f>AF20-P20</f>
         <v/>
       </c>
-      <c r="CR20" s="6">
-        <f>IF(COUNT(H20:H39)=20,CORREL(H20:H39,P20:P39),"")</f>
-        <v/>
-      </c>
-      <c r="CS20" s="4">
+      <c r="CS20" s="6">
+        <f>IF(COUNT(H20:H39)=20,IFERROR(CORREL(H20:H39,P20:P39),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT20" s="4">
         <f>AN20-AV20</f>
         <v/>
       </c>
-      <c r="CT20" s="4">
+      <c r="CU20" s="4">
         <f>BD20-BL20</f>
         <v/>
       </c>
-      <c r="CU20" s="6">
-        <f>BY20/CG20</f>
-        <v/>
-      </c>
-      <c r="CV20" s="4">
+      <c r="CV20" s="6">
+        <f>BY20/CF20</f>
+        <v/>
+      </c>
+      <c r="CW20" s="4">
         <f>P20-BT20</f>
         <v/>
       </c>
@@ -2811,75 +2810,76 @@
       <c r="CA21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB21" s="4">
-        <f>IF(COUNT(BY21:BY22)=2,ROUND((BY21/BY22-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC21" s="3" t="n"/>
+      <c r="CB21" s="3" t="n"/>
+      <c r="CC21" s="3" t="n">
+        <v>4.665</v>
+      </c>
       <c r="CD21" s="3" t="n">
-        <v>4.665</v>
+        <v>4.668</v>
       </c>
       <c r="CE21" s="3" t="n">
-        <v>4.668</v>
+        <v>4.619</v>
       </c>
       <c r="CF21" s="3" t="n">
-        <v>4.619</v>
+        <v>4.627</v>
       </c>
       <c r="CG21" s="3" t="n">
         <v>4.627</v>
       </c>
       <c r="CH21" s="3" t="n">
-        <v>4.627</v>
-      </c>
-      <c r="CI21" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI21" s="3" t="n"/>
       <c r="CJ21" s="4">
-        <f>IF(COUNT(CG21:CG22)=2,ROUND((CG21/CG22-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK21" s="3" t="n"/>
+        <f>IF(COUNT(BY21:BY22)=2,ROUND((BY21/BY22-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK21" s="4">
+        <f>IF(COUNT(BY21:BY22)=2,ROUND((BY21/BY22-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL21" s="4">
-        <f>IF(COUNT(BY21:BY22)=2,ROUND((BY21/BY22-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM21" s="5">
-        <f>IF(COUNT(CG21:CG22)=2,(CG21-CG22)*100,"")</f>
+        <f>IF(COUNT(BY21:BY26)=6,ROUND((BY21/BY26-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM21" s="4">
+        <f>IF(COUNT(CK21:CK40)=20,IFERROR(ROUND(STDEV(CK21:CK40),4),""),"")</f>
         <v/>
       </c>
       <c r="CN21" s="4">
-        <f>IF(COUNT(BY21:BY26)=6,ROUND((BY21/BY26-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO21" s="4">
-        <f>IF(COUNT(CL21:CL40)=20,ROUND(STDEV(CL21:CL40),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP21" s="4">
+        <f>IF(COUNT(CF21:CF22)=2,ROUND((CF21/CF22-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO21" s="5">
+        <f>IF(COUNT(CF21:CF22)=2,(CF21-CF22)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP21" s="3" t="n"/>
+      <c r="CQ21" s="4">
         <f>X21-P21</f>
         <v/>
       </c>
-      <c r="CQ21" s="4">
+      <c r="CR21" s="4">
         <f>AF21-P21</f>
         <v/>
       </c>
-      <c r="CR21" s="6">
-        <f>IF(COUNT(H21:H40)=20,CORREL(H21:H40,P21:P40),"")</f>
-        <v/>
-      </c>
-      <c r="CS21" s="4">
+      <c r="CS21" s="6">
+        <f>IF(COUNT(H21:H40)=20,IFERROR(CORREL(H21:H40,P21:P40),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT21" s="4">
         <f>AN21-AV21</f>
         <v/>
       </c>
-      <c r="CT21" s="4">
+      <c r="CU21" s="4">
         <f>BD21-BL21</f>
         <v/>
       </c>
-      <c r="CU21" s="6">
-        <f>BY21/CG21</f>
-        <v/>
-      </c>
-      <c r="CV21" s="4">
+      <c r="CV21" s="6">
+        <f>BY21/CF21</f>
+        <v/>
+      </c>
+      <c r="CW21" s="4">
         <f>P21-BT21</f>
         <v/>
       </c>
@@ -3115,75 +3115,76 @@
       <c r="CA22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB22" s="4">
-        <f>IF(COUNT(BY22:BY23)=2,ROUND((BY22/BY23-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC22" s="3" t="n"/>
+      <c r="CB22" s="3" t="n"/>
+      <c r="CC22" s="3" t="n">
+        <v>4.671</v>
+      </c>
       <c r="CD22" s="3" t="n">
+        <v>4.702</v>
+      </c>
+      <c r="CE22" s="3" t="n">
         <v>4.671</v>
       </c>
-      <c r="CE22" s="3" t="n">
-        <v>4.702</v>
-      </c>
       <c r="CF22" s="3" t="n">
-        <v>4.671</v>
+        <v>4.686</v>
       </c>
       <c r="CG22" s="3" t="n">
         <v>4.686</v>
       </c>
       <c r="CH22" s="3" t="n">
-        <v>4.686</v>
-      </c>
-      <c r="CI22" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI22" s="3" t="n"/>
       <c r="CJ22" s="4">
-        <f>IF(COUNT(CG22:CG23)=2,ROUND((CG22/CG23-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK22" s="3" t="n"/>
+        <f>IF(COUNT(BY22:BY23)=2,ROUND((BY22/BY23-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK22" s="4">
+        <f>IF(COUNT(BY22:BY23)=2,ROUND((BY22/BY23-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL22" s="4">
-        <f>IF(COUNT(BY22:BY23)=2,ROUND((BY22/BY23-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM22" s="5">
-        <f>IF(COUNT(CG22:CG23)=2,(CG22-CG23)*100,"")</f>
+        <f>IF(COUNT(BY22:BY27)=6,ROUND((BY22/BY27-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM22" s="4">
+        <f>IF(COUNT(CK22:CK41)=20,IFERROR(ROUND(STDEV(CK22:CK41),4),""),"")</f>
         <v/>
       </c>
       <c r="CN22" s="4">
-        <f>IF(COUNT(BY22:BY27)=6,ROUND((BY22/BY27-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO22" s="4">
-        <f>IF(COUNT(CL22:CL41)=20,ROUND(STDEV(CL22:CL41),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP22" s="4">
+        <f>IF(COUNT(CF22:CF23)=2,ROUND((CF22/CF23-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO22" s="5">
+        <f>IF(COUNT(CF22:CF23)=2,(CF22-CF23)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP22" s="3" t="n"/>
+      <c r="CQ22" s="4">
         <f>X22-P22</f>
         <v/>
       </c>
-      <c r="CQ22" s="4">
+      <c r="CR22" s="4">
         <f>AF22-P22</f>
         <v/>
       </c>
-      <c r="CR22" s="6">
-        <f>IF(COUNT(H22:H41)=20,CORREL(H22:H41,P22:P41),"")</f>
-        <v/>
-      </c>
-      <c r="CS22" s="4">
+      <c r="CS22" s="6">
+        <f>IF(COUNT(H22:H41)=20,IFERROR(CORREL(H22:H41,P22:P41),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT22" s="4">
         <f>AN22-AV22</f>
         <v/>
       </c>
-      <c r="CT22" s="4">
+      <c r="CU22" s="4">
         <f>BD22-BL22</f>
         <v/>
       </c>
-      <c r="CU22" s="6">
-        <f>BY22/CG22</f>
-        <v/>
-      </c>
-      <c r="CV22" s="4">
+      <c r="CV22" s="6">
+        <f>BY22/CF22</f>
+        <v/>
+      </c>
+      <c r="CW22" s="4">
         <f>P22-BT22</f>
         <v/>
       </c>
@@ -3419,75 +3420,76 @@
       <c r="CA23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB23" s="4">
-        <f>IF(COUNT(BY23:BY24)=2,ROUND((BY23/BY24-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC23" s="3" t="n"/>
+      <c r="CB23" s="3" t="n"/>
+      <c r="CC23" s="3" t="n">
+        <v>4.684</v>
+      </c>
       <c r="CD23" s="3" t="n">
-        <v>4.684</v>
+        <v>4.747</v>
       </c>
       <c r="CE23" s="3" t="n">
-        <v>4.747</v>
+        <v>4.682</v>
       </c>
       <c r="CF23" s="3" t="n">
-        <v>4.682</v>
+        <v>4.745</v>
       </c>
       <c r="CG23" s="3" t="n">
         <v>4.745</v>
       </c>
       <c r="CH23" s="3" t="n">
-        <v>4.745</v>
-      </c>
-      <c r="CI23" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI23" s="3" t="n"/>
       <c r="CJ23" s="4">
-        <f>IF(COUNT(CG23:CG24)=2,ROUND((CG23/CG24-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK23" s="3" t="n"/>
+        <f>IF(COUNT(BY23:BY24)=2,ROUND((BY23/BY24-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK23" s="4">
+        <f>IF(COUNT(BY23:BY24)=2,ROUND((BY23/BY24-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL23" s="4">
-        <f>IF(COUNT(BY23:BY24)=2,ROUND((BY23/BY24-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM23" s="5">
-        <f>IF(COUNT(CG23:CG24)=2,(CG23-CG24)*100,"")</f>
+        <f>IF(COUNT(BY23:BY28)=6,ROUND((BY23/BY28-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM23" s="4">
+        <f>IF(COUNT(CK23:CK42)=20,IFERROR(ROUND(STDEV(CK23:CK42),4),""),"")</f>
         <v/>
       </c>
       <c r="CN23" s="4">
-        <f>IF(COUNT(BY23:BY28)=6,ROUND((BY23/BY28-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO23" s="4">
-        <f>IF(COUNT(CL23:CL42)=20,ROUND(STDEV(CL23:CL42),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP23" s="4">
+        <f>IF(COUNT(CF23:CF24)=2,ROUND((CF23/CF24-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO23" s="5">
+        <f>IF(COUNT(CF23:CF24)=2,(CF23-CF24)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP23" s="3" t="n"/>
+      <c r="CQ23" s="4">
         <f>X23-P23</f>
         <v/>
       </c>
-      <c r="CQ23" s="4">
+      <c r="CR23" s="4">
         <f>AF23-P23</f>
         <v/>
       </c>
-      <c r="CR23" s="6">
-        <f>IF(COUNT(H23:H42)=20,CORREL(H23:H42,P23:P42),"")</f>
-        <v/>
-      </c>
-      <c r="CS23" s="4">
+      <c r="CS23" s="6">
+        <f>IF(COUNT(H23:H42)=20,IFERROR(CORREL(H23:H42,P23:P42),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT23" s="4">
         <f>AN23-AV23</f>
         <v/>
       </c>
-      <c r="CT23" s="4">
+      <c r="CU23" s="4">
         <f>BD23-BL23</f>
         <v/>
       </c>
-      <c r="CU23" s="6">
-        <f>BY23/CG23</f>
-        <v/>
-      </c>
-      <c r="CV23" s="4">
+      <c r="CV23" s="6">
+        <f>BY23/CF23</f>
+        <v/>
+      </c>
+      <c r="CW23" s="4">
         <f>P23-BT23</f>
         <v/>
       </c>
@@ -3723,75 +3725,76 @@
       <c r="CA24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB24" s="4">
-        <f>IF(COUNT(BY24:BY25)=2,ROUND((BY24/BY25-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC24" s="3" t="n"/>
+      <c r="CB24" s="3" t="n"/>
+      <c r="CC24" s="3" t="n">
+        <v>4.669</v>
+      </c>
       <c r="CD24" s="3" t="n">
-        <v>4.669</v>
+        <v>4.686</v>
       </c>
       <c r="CE24" s="3" t="n">
-        <v>4.686</v>
+        <v>4.651</v>
       </c>
       <c r="CF24" s="3" t="n">
-        <v>4.651</v>
+        <v>4.663</v>
       </c>
       <c r="CG24" s="3" t="n">
         <v>4.663</v>
       </c>
       <c r="CH24" s="3" t="n">
-        <v>4.663</v>
-      </c>
-      <c r="CI24" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI24" s="3" t="n"/>
       <c r="CJ24" s="4">
-        <f>IF(COUNT(CG24:CG25)=2,ROUND((CG24/CG25-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK24" s="3" t="n"/>
+        <f>IF(COUNT(BY24:BY25)=2,ROUND((BY24/BY25-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK24" s="4">
+        <f>IF(COUNT(BY24:BY25)=2,ROUND((BY24/BY25-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL24" s="4">
-        <f>IF(COUNT(BY24:BY25)=2,ROUND((BY24/BY25-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM24" s="5">
-        <f>IF(COUNT(CG24:CG25)=2,(CG24-CG25)*100,"")</f>
+        <f>IF(COUNT(BY24:BY29)=6,ROUND((BY24/BY29-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM24" s="4">
+        <f>IF(COUNT(CK24:CK43)=20,IFERROR(ROUND(STDEV(CK24:CK43),4),""),"")</f>
         <v/>
       </c>
       <c r="CN24" s="4">
-        <f>IF(COUNT(BY24:BY29)=6,ROUND((BY24/BY29-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO24" s="4">
-        <f>IF(COUNT(CL24:CL43)=20,ROUND(STDEV(CL24:CL43),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP24" s="4">
+        <f>IF(COUNT(CF24:CF25)=2,ROUND((CF24/CF25-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO24" s="5">
+        <f>IF(COUNT(CF24:CF25)=2,(CF24-CF25)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP24" s="3" t="n"/>
+      <c r="CQ24" s="4">
         <f>X24-P24</f>
         <v/>
       </c>
-      <c r="CQ24" s="4">
+      <c r="CR24" s="4">
         <f>AF24-P24</f>
         <v/>
       </c>
-      <c r="CR24" s="6">
-        <f>IF(COUNT(H24:H43)=20,CORREL(H24:H43,P24:P43),"")</f>
-        <v/>
-      </c>
-      <c r="CS24" s="4">
+      <c r="CS24" s="6">
+        <f>IF(COUNT(H24:H43)=20,IFERROR(CORREL(H24:H43,P24:P43),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT24" s="4">
         <f>AN24-AV24</f>
         <v/>
       </c>
-      <c r="CT24" s="4">
+      <c r="CU24" s="4">
         <f>BD24-BL24</f>
         <v/>
       </c>
-      <c r="CU24" s="6">
-        <f>BY24/CG24</f>
-        <v/>
-      </c>
-      <c r="CV24" s="4">
+      <c r="CV24" s="6">
+        <f>BY24/CF24</f>
+        <v/>
+      </c>
+      <c r="CW24" s="4">
         <f>P24-BT24</f>
         <v/>
       </c>
@@ -4027,75 +4030,76 @@
       <c r="CA25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB25" s="4">
-        <f>IF(COUNT(BY25:BY26)=2,ROUND((BY25/BY26-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC25" s="3" t="n"/>
+      <c r="CB25" s="3" t="n"/>
+      <c r="CC25" s="3" t="n">
+        <v>4.637</v>
+      </c>
       <c r="CD25" s="3" t="n">
-        <v>4.637</v>
+        <v>4.655</v>
       </c>
       <c r="CE25" s="3" t="n">
-        <v>4.655</v>
+        <v>4.61</v>
       </c>
       <c r="CF25" s="3" t="n">
-        <v>4.61</v>
+        <v>4.622</v>
       </c>
       <c r="CG25" s="3" t="n">
         <v>4.622</v>
       </c>
       <c r="CH25" s="3" t="n">
-        <v>4.622</v>
-      </c>
-      <c r="CI25" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI25" s="3" t="n"/>
       <c r="CJ25" s="4">
-        <f>IF(COUNT(CG25:CG26)=2,ROUND((CG25/CG26-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK25" s="3" t="n"/>
+        <f>IF(COUNT(BY25:BY26)=2,ROUND((BY25/BY26-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK25" s="4">
+        <f>IF(COUNT(BY25:BY26)=2,ROUND((BY25/BY26-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL25" s="4">
-        <f>IF(COUNT(BY25:BY26)=2,ROUND((BY25/BY26-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM25" s="5">
-        <f>IF(COUNT(CG25:CG26)=2,(CG25-CG26)*100,"")</f>
+        <f>IF(COUNT(BY25:BY30)=6,ROUND((BY25/BY30-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM25" s="4">
+        <f>IF(COUNT(CK25:CK44)=20,IFERROR(ROUND(STDEV(CK25:CK44),4),""),"")</f>
         <v/>
       </c>
       <c r="CN25" s="4">
-        <f>IF(COUNT(BY25:BY30)=6,ROUND((BY25/BY30-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO25" s="4">
-        <f>IF(COUNT(CL25:CL44)=20,ROUND(STDEV(CL25:CL44),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP25" s="4">
+        <f>IF(COUNT(CF25:CF26)=2,ROUND((CF25/CF26-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO25" s="5">
+        <f>IF(COUNT(CF25:CF26)=2,(CF25-CF26)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP25" s="3" t="n"/>
+      <c r="CQ25" s="4">
         <f>X25-P25</f>
         <v/>
       </c>
-      <c r="CQ25" s="4">
+      <c r="CR25" s="4">
         <f>AF25-P25</f>
         <v/>
       </c>
-      <c r="CR25" s="6">
-        <f>IF(COUNT(H25:H44)=20,CORREL(H25:H44,P25:P44),"")</f>
-        <v/>
-      </c>
-      <c r="CS25" s="4">
+      <c r="CS25" s="6">
+        <f>IF(COUNT(H25:H44)=20,IFERROR(CORREL(H25:H44,P25:P44),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT25" s="4">
         <f>AN25-AV25</f>
         <v/>
       </c>
-      <c r="CT25" s="4">
+      <c r="CU25" s="4">
         <f>BD25-BL25</f>
         <v/>
       </c>
-      <c r="CU25" s="6">
-        <f>BY25/CG25</f>
-        <v/>
-      </c>
-      <c r="CV25" s="4">
+      <c r="CV25" s="6">
+        <f>BY25/CF25</f>
+        <v/>
+      </c>
+      <c r="CW25" s="4">
         <f>P25-BT25</f>
         <v/>
       </c>
@@ -4331,75 +4335,76 @@
       <c r="CA26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB26" s="4">
-        <f>IF(COUNT(BY26:BY27)=2,ROUND((BY26/BY27-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC26" s="3" t="n"/>
+      <c r="CB26" s="3" t="n"/>
+      <c r="CC26" s="3" t="n">
+        <v>4.63</v>
+      </c>
       <c r="CD26" s="3" t="n">
-        <v>4.63</v>
+        <v>4.635</v>
       </c>
       <c r="CE26" s="3" t="n">
-        <v>4.635</v>
+        <v>4.588</v>
       </c>
       <c r="CF26" s="3" t="n">
-        <v>4.588</v>
+        <v>4.604</v>
       </c>
       <c r="CG26" s="3" t="n">
         <v>4.604</v>
       </c>
       <c r="CH26" s="3" t="n">
-        <v>4.604</v>
-      </c>
-      <c r="CI26" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI26" s="3" t="n"/>
       <c r="CJ26" s="4">
-        <f>IF(COUNT(CG26:CG27)=2,ROUND((CG26/CG27-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK26" s="3" t="n"/>
+        <f>IF(COUNT(BY26:BY27)=2,ROUND((BY26/BY27-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK26" s="4">
+        <f>IF(COUNT(BY26:BY27)=2,ROUND((BY26/BY27-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL26" s="4">
-        <f>IF(COUNT(BY26:BY27)=2,ROUND((BY26/BY27-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM26" s="5">
-        <f>IF(COUNT(CG26:CG27)=2,(CG26-CG27)*100,"")</f>
+        <f>IF(COUNT(BY26:BY31)=6,ROUND((BY26/BY31-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM26" s="4">
+        <f>IF(COUNT(CK26:CK45)=20,IFERROR(ROUND(STDEV(CK26:CK45),4),""),"")</f>
         <v/>
       </c>
       <c r="CN26" s="4">
-        <f>IF(COUNT(BY26:BY31)=6,ROUND((BY26/BY31-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO26" s="4">
-        <f>IF(COUNT(CL26:CL45)=20,ROUND(STDEV(CL26:CL45),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP26" s="4">
+        <f>IF(COUNT(CF26:CF27)=2,ROUND((CF26/CF27-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO26" s="5">
+        <f>IF(COUNT(CF26:CF27)=2,(CF26-CF27)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP26" s="3" t="n"/>
+      <c r="CQ26" s="4">
         <f>X26-P26</f>
         <v/>
       </c>
-      <c r="CQ26" s="4">
+      <c r="CR26" s="4">
         <f>AF26-P26</f>
         <v/>
       </c>
-      <c r="CR26" s="6">
-        <f>IF(COUNT(H26:H45)=20,CORREL(H26:H45,P26:P45),"")</f>
-        <v/>
-      </c>
-      <c r="CS26" s="4">
+      <c r="CS26" s="6">
+        <f>IF(COUNT(H26:H45)=20,IFERROR(CORREL(H26:H45,P26:P45),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT26" s="4">
         <f>AN26-AV26</f>
         <v/>
       </c>
-      <c r="CT26" s="4">
+      <c r="CU26" s="4">
         <f>BD26-BL26</f>
         <v/>
       </c>
-      <c r="CU26" s="6">
-        <f>BY26/CG26</f>
-        <v/>
-      </c>
-      <c r="CV26" s="4">
+      <c r="CV26" s="6">
+        <f>BY26/CF26</f>
+        <v/>
+      </c>
+      <c r="CW26" s="4">
         <f>P26-BT26</f>
         <v/>
       </c>
@@ -4635,75 +4640,76 @@
       <c r="CA27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB27" s="4">
-        <f>IF(COUNT(BY27:BY28)=2,ROUND((BY27/BY28-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC27" s="3" t="n"/>
+      <c r="CB27" s="3" t="n"/>
+      <c r="CC27" s="3" t="n">
+        <v>4.647</v>
+      </c>
       <c r="CD27" s="3" t="n">
-        <v>4.647</v>
+        <v>4.665</v>
       </c>
       <c r="CE27" s="3" t="n">
-        <v>4.665</v>
+        <v>4.63</v>
       </c>
       <c r="CF27" s="3" t="n">
-        <v>4.63</v>
+        <v>4.641</v>
       </c>
       <c r="CG27" s="3" t="n">
         <v>4.641</v>
       </c>
       <c r="CH27" s="3" t="n">
-        <v>4.641</v>
-      </c>
-      <c r="CI27" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI27" s="3" t="n"/>
       <c r="CJ27" s="4">
-        <f>IF(COUNT(CG27:CG28)=2,ROUND((CG27/CG28-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK27" s="3" t="n"/>
+        <f>IF(COUNT(BY27:BY28)=2,ROUND((BY27/BY28-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK27" s="4">
+        <f>IF(COUNT(BY27:BY28)=2,ROUND((BY27/BY28-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL27" s="4">
-        <f>IF(COUNT(BY27:BY28)=2,ROUND((BY27/BY28-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM27" s="5">
-        <f>IF(COUNT(CG27:CG28)=2,(CG27-CG28)*100,"")</f>
+        <f>IF(COUNT(BY27:BY32)=6,ROUND((BY27/BY32-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM27" s="4">
+        <f>IF(COUNT(CK27:CK46)=20,IFERROR(ROUND(STDEV(CK27:CK46),4),""),"")</f>
         <v/>
       </c>
       <c r="CN27" s="4">
-        <f>IF(COUNT(BY27:BY32)=6,ROUND((BY27/BY32-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO27" s="4">
-        <f>IF(COUNT(CL27:CL46)=20,ROUND(STDEV(CL27:CL46),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP27" s="4">
+        <f>IF(COUNT(CF27:CF28)=2,ROUND((CF27/CF28-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO27" s="5">
+        <f>IF(COUNT(CF27:CF28)=2,(CF27-CF28)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP27" s="3" t="n"/>
+      <c r="CQ27" s="4">
         <f>X27-P27</f>
         <v/>
       </c>
-      <c r="CQ27" s="4">
+      <c r="CR27" s="4">
         <f>AF27-P27</f>
         <v/>
       </c>
-      <c r="CR27" s="6">
-        <f>IF(COUNT(H27:H46)=20,CORREL(H27:H46,P27:P46),"")</f>
-        <v/>
-      </c>
-      <c r="CS27" s="4">
+      <c r="CS27" s="6">
+        <f>IF(COUNT(H27:H46)=20,IFERROR(CORREL(H27:H46,P27:P46),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT27" s="4">
         <f>AN27-AV27</f>
         <v/>
       </c>
-      <c r="CT27" s="4">
+      <c r="CU27" s="4">
         <f>BD27-BL27</f>
         <v/>
       </c>
-      <c r="CU27" s="6">
-        <f>BY27/CG27</f>
-        <v/>
-      </c>
-      <c r="CV27" s="4">
+      <c r="CV27" s="6">
+        <f>BY27/CF27</f>
+        <v/>
+      </c>
+      <c r="CW27" s="4">
         <f>P27-BT27</f>
         <v/>
       </c>
@@ -4939,75 +4945,76 @@
       <c r="CA28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB28" s="4">
-        <f>IF(COUNT(BY28:BY29)=2,ROUND((BY28/BY29-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC28" s="3" t="n"/>
+      <c r="CB28" s="3" t="n"/>
+      <c r="CC28" s="3" t="n">
+        <v>4.683</v>
+      </c>
       <c r="CD28" s="3" t="n">
-        <v>4.683</v>
+        <v>4.691</v>
       </c>
       <c r="CE28" s="3" t="n">
-        <v>4.691</v>
+        <v>4.651</v>
       </c>
       <c r="CF28" s="3" t="n">
-        <v>4.651</v>
+        <v>4.679</v>
       </c>
       <c r="CG28" s="3" t="n">
         <v>4.679</v>
       </c>
       <c r="CH28" s="3" t="n">
-        <v>4.679</v>
-      </c>
-      <c r="CI28" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI28" s="3" t="n"/>
       <c r="CJ28" s="4">
-        <f>IF(COUNT(CG28:CG29)=2,ROUND((CG28/CG29-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK28" s="3" t="n"/>
+        <f>IF(COUNT(BY28:BY29)=2,ROUND((BY28/BY29-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK28" s="4">
+        <f>IF(COUNT(BY28:BY29)=2,ROUND((BY28/BY29-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL28" s="4">
-        <f>IF(COUNT(BY28:BY29)=2,ROUND((BY28/BY29-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM28" s="5">
-        <f>IF(COUNT(CG28:CG29)=2,(CG28-CG29)*100,"")</f>
+        <f>IF(COUNT(BY28:BY33)=6,ROUND((BY28/BY33-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM28" s="4">
+        <f>IF(COUNT(CK28:CK47)=20,IFERROR(ROUND(STDEV(CK28:CK47),4),""),"")</f>
         <v/>
       </c>
       <c r="CN28" s="4">
-        <f>IF(COUNT(BY28:BY33)=6,ROUND((BY28/BY33-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO28" s="4">
-        <f>IF(COUNT(CL28:CL47)=20,ROUND(STDEV(CL28:CL47),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP28" s="4">
+        <f>IF(COUNT(CF28:CF29)=2,ROUND((CF28/CF29-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO28" s="5">
+        <f>IF(COUNT(CF28:CF29)=2,(CF28-CF29)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP28" s="3" t="n"/>
+      <c r="CQ28" s="4">
         <f>X28-P28</f>
         <v/>
       </c>
-      <c r="CQ28" s="4">
+      <c r="CR28" s="4">
         <f>AF28-P28</f>
         <v/>
       </c>
-      <c r="CR28" s="6">
-        <f>IF(COUNT(H28:H47)=20,CORREL(H28:H47,P28:P47),"")</f>
-        <v/>
-      </c>
-      <c r="CS28" s="4">
+      <c r="CS28" s="6">
+        <f>IF(COUNT(H28:H47)=20,IFERROR(CORREL(H28:H47,P28:P47),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT28" s="4">
         <f>AN28-AV28</f>
         <v/>
       </c>
-      <c r="CT28" s="4">
+      <c r="CU28" s="4">
         <f>BD28-BL28</f>
         <v/>
       </c>
-      <c r="CU28" s="6">
-        <f>BY28/CG28</f>
-        <v/>
-      </c>
-      <c r="CV28" s="4">
+      <c r="CV28" s="6">
+        <f>BY28/CF28</f>
+        <v/>
+      </c>
+      <c r="CW28" s="4">
         <f>P28-BT28</f>
         <v/>
       </c>
@@ -5243,75 +5250,76 @@
       <c r="CA29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB29" s="4">
-        <f>IF(COUNT(BY29:BY30)=2,ROUND((BY29/BY30-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC29" s="3" t="n"/>
+      <c r="CB29" s="3" t="n"/>
+      <c r="CC29" s="3" t="n">
+        <v>4.699</v>
+      </c>
       <c r="CD29" s="3" t="n">
-        <v>4.699</v>
+        <v>4.714</v>
       </c>
       <c r="CE29" s="3" t="n">
-        <v>4.714</v>
+        <v>4.693</v>
       </c>
       <c r="CF29" s="3" t="n">
-        <v>4.693</v>
+        <v>4.703</v>
       </c>
       <c r="CG29" s="3" t="n">
         <v>4.703</v>
       </c>
       <c r="CH29" s="3" t="n">
-        <v>4.703</v>
-      </c>
-      <c r="CI29" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI29" s="3" t="n"/>
       <c r="CJ29" s="4">
-        <f>IF(COUNT(CG29:CG30)=2,ROUND((CG29/CG30-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK29" s="3" t="n"/>
+        <f>IF(COUNT(BY29:BY30)=2,ROUND((BY29/BY30-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK29" s="4">
+        <f>IF(COUNT(BY29:BY30)=2,ROUND((BY29/BY30-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL29" s="4">
-        <f>IF(COUNT(BY29:BY30)=2,ROUND((BY29/BY30-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM29" s="5">
-        <f>IF(COUNT(CG29:CG30)=2,(CG29-CG30)*100,"")</f>
+        <f>IF(COUNT(BY29:BY34)=6,ROUND((BY29/BY34-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM29" s="4">
+        <f>IF(COUNT(CK29:CK48)=20,IFERROR(ROUND(STDEV(CK29:CK48),4),""),"")</f>
         <v/>
       </c>
       <c r="CN29" s="4">
-        <f>IF(COUNT(BY29:BY34)=6,ROUND((BY29/BY34-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO29" s="4">
-        <f>IF(COUNT(CL29:CL48)=20,ROUND(STDEV(CL29:CL48),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP29" s="4">
+        <f>IF(COUNT(CF29:CF30)=2,ROUND((CF29/CF30-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO29" s="5">
+        <f>IF(COUNT(CF29:CF30)=2,(CF29-CF30)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP29" s="3" t="n"/>
+      <c r="CQ29" s="4">
         <f>X29-P29</f>
         <v/>
       </c>
-      <c r="CQ29" s="4">
+      <c r="CR29" s="4">
         <f>AF29-P29</f>
         <v/>
       </c>
-      <c r="CR29" s="6">
-        <f>IF(COUNT(H29:H48)=20,CORREL(H29:H48,P29:P48),"")</f>
-        <v/>
-      </c>
-      <c r="CS29" s="4">
+      <c r="CS29" s="6">
+        <f>IF(COUNT(H29:H48)=20,IFERROR(CORREL(H29:H48,P29:P48),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT29" s="4">
         <f>AN29-AV29</f>
         <v/>
       </c>
-      <c r="CT29" s="4">
+      <c r="CU29" s="4">
         <f>BD29-BL29</f>
         <v/>
       </c>
-      <c r="CU29" s="6">
-        <f>BY29/CG29</f>
-        <v/>
-      </c>
-      <c r="CV29" s="4">
+      <c r="CV29" s="6">
+        <f>BY29/CF29</f>
+        <v/>
+      </c>
+      <c r="CW29" s="4">
         <f>P29-BT29</f>
         <v/>
       </c>
@@ -5547,75 +5555,76 @@
       <c r="CA30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB30" s="4">
-        <f>IF(COUNT(BY30:BY31)=2,ROUND((BY30/BY31-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC30" s="3" t="n"/>
+      <c r="CB30" s="3" t="n"/>
+      <c r="CC30" s="3" t="n">
+        <v>4.64</v>
+      </c>
       <c r="CD30" s="3" t="n">
-        <v>4.64</v>
+        <v>4.661</v>
       </c>
       <c r="CE30" s="3" t="n">
-        <v>4.661</v>
+        <v>4.632</v>
       </c>
       <c r="CF30" s="3" t="n">
-        <v>4.632</v>
+        <v>4.657</v>
       </c>
       <c r="CG30" s="3" t="n">
         <v>4.657</v>
       </c>
       <c r="CH30" s="3" t="n">
-        <v>4.657</v>
-      </c>
-      <c r="CI30" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI30" s="3" t="n"/>
       <c r="CJ30" s="4">
-        <f>IF(COUNT(CG30:CG31)=2,ROUND((CG30/CG31-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK30" s="3" t="n"/>
+        <f>IF(COUNT(BY30:BY31)=2,ROUND((BY30/BY31-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK30" s="4">
+        <f>IF(COUNT(BY30:BY31)=2,ROUND((BY30/BY31-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL30" s="4">
-        <f>IF(COUNT(BY30:BY31)=2,ROUND((BY30/BY31-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM30" s="5">
-        <f>IF(COUNT(CG30:CG31)=2,(CG30-CG31)*100,"")</f>
+        <f>IF(COUNT(BY30:BY35)=6,ROUND((BY30/BY35-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM30" s="4">
+        <f>IF(COUNT(CK30:CK49)=20,IFERROR(ROUND(STDEV(CK30:CK49),4),""),"")</f>
         <v/>
       </c>
       <c r="CN30" s="4">
-        <f>IF(COUNT(BY30:BY35)=6,ROUND((BY30/BY35-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO30" s="4">
-        <f>IF(COUNT(CL30:CL49)=20,ROUND(STDEV(CL30:CL49),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP30" s="4">
+        <f>IF(COUNT(CF30:CF31)=2,ROUND((CF30/CF31-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO30" s="5">
+        <f>IF(COUNT(CF30:CF31)=2,(CF30-CF31)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP30" s="3" t="n"/>
+      <c r="CQ30" s="4">
         <f>X30-P30</f>
         <v/>
       </c>
-      <c r="CQ30" s="4">
+      <c r="CR30" s="4">
         <f>AF30-P30</f>
         <v/>
       </c>
-      <c r="CR30" s="6">
-        <f>IF(COUNT(H30:H49)=20,CORREL(H30:H49,P30:P49),"")</f>
-        <v/>
-      </c>
-      <c r="CS30" s="4">
+      <c r="CS30" s="6">
+        <f>IF(COUNT(H30:H49)=20,IFERROR(CORREL(H30:H49,P30:P49),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT30" s="4">
         <f>AN30-AV30</f>
         <v/>
       </c>
-      <c r="CT30" s="4">
+      <c r="CU30" s="4">
         <f>BD30-BL30</f>
         <v/>
       </c>
-      <c r="CU30" s="6">
-        <f>BY30/CG30</f>
-        <v/>
-      </c>
-      <c r="CV30" s="4">
+      <c r="CV30" s="6">
+        <f>BY30/CF30</f>
+        <v/>
+      </c>
+      <c r="CW30" s="4">
         <f>P30-BT30</f>
         <v/>
       </c>
@@ -5851,75 +5860,76 @@
       <c r="CA31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB31" s="4">
-        <f>IF(COUNT(BY31:BY32)=2,ROUND((BY31/BY32-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC31" s="3" t="n"/>
+      <c r="CB31" s="3" t="n"/>
+      <c r="CC31" s="3" t="n">
+        <v>4.6</v>
+      </c>
       <c r="CD31" s="3" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="CE31" s="3" t="n">
-        <v>4.64</v>
+        <v>4.598</v>
       </c>
       <c r="CF31" s="3" t="n">
-        <v>4.598</v>
+        <v>4.628</v>
       </c>
       <c r="CG31" s="3" t="n">
         <v>4.628</v>
       </c>
       <c r="CH31" s="3" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="CI31" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI31" s="3" t="n"/>
       <c r="CJ31" s="4">
-        <f>IF(COUNT(CG31:CG32)=2,ROUND((CG31/CG32-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK31" s="3" t="n"/>
+        <f>IF(COUNT(BY31:BY32)=2,ROUND((BY31/BY32-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK31" s="4">
+        <f>IF(COUNT(BY31:BY32)=2,ROUND((BY31/BY32-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL31" s="4">
-        <f>IF(COUNT(BY31:BY32)=2,ROUND((BY31/BY32-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM31" s="5">
-        <f>IF(COUNT(CG31:CG32)=2,(CG31-CG32)*100,"")</f>
+        <f>IF(COUNT(BY31:BY36)=6,ROUND((BY31/BY36-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM31" s="4">
+        <f>IF(COUNT(CK31:CK50)=20,IFERROR(ROUND(STDEV(CK31:CK50),4),""),"")</f>
         <v/>
       </c>
       <c r="CN31" s="4">
-        <f>IF(COUNT(BY31:BY36)=6,ROUND((BY31/BY36-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO31" s="4">
-        <f>IF(COUNT(CL31:CL50)=20,ROUND(STDEV(CL31:CL50),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP31" s="4">
+        <f>IF(COUNT(CF31:CF32)=2,ROUND((CF31/CF32-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO31" s="5">
+        <f>IF(COUNT(CF31:CF32)=2,(CF31-CF32)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP31" s="3" t="n"/>
+      <c r="CQ31" s="4">
         <f>X31-P31</f>
         <v/>
       </c>
-      <c r="CQ31" s="4">
+      <c r="CR31" s="4">
         <f>AF31-P31</f>
         <v/>
       </c>
-      <c r="CR31" s="6">
-        <f>IF(COUNT(H31:H50)=20,CORREL(H31:H50,P31:P50),"")</f>
-        <v/>
-      </c>
-      <c r="CS31" s="4">
+      <c r="CS31" s="6">
+        <f>IF(COUNT(H31:H50)=20,IFERROR(CORREL(H31:H50,P31:P50),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT31" s="4">
         <f>AN31-AV31</f>
         <v/>
       </c>
-      <c r="CT31" s="4">
+      <c r="CU31" s="4">
         <f>BD31-BL31</f>
         <v/>
       </c>
-      <c r="CU31" s="6">
-        <f>BY31/CG31</f>
-        <v/>
-      </c>
-      <c r="CV31" s="4">
+      <c r="CV31" s="6">
+        <f>BY31/CF31</f>
+        <v/>
+      </c>
+      <c r="CW31" s="4">
         <f>P31-BT31</f>
         <v/>
       </c>
@@ -6155,75 +6165,76 @@
       <c r="CA32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB32" s="4">
-        <f>IF(COUNT(BY32:BY33)=2,ROUND((BY32/BY33-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC32" s="3" t="n"/>
+      <c r="CB32" s="3" t="n"/>
+      <c r="CC32" s="3" t="n">
+        <v>4.566</v>
+      </c>
       <c r="CD32" s="3" t="n">
-        <v>4.566</v>
+        <v>4.608</v>
       </c>
       <c r="CE32" s="3" t="n">
-        <v>4.608</v>
+        <v>4.56</v>
       </c>
       <c r="CF32" s="3" t="n">
-        <v>4.56</v>
+        <v>4.598</v>
       </c>
       <c r="CG32" s="3" t="n">
         <v>4.598</v>
       </c>
       <c r="CH32" s="3" t="n">
-        <v>4.598</v>
-      </c>
-      <c r="CI32" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI32" s="3" t="n"/>
       <c r="CJ32" s="4">
-        <f>IF(COUNT(CG32:CG33)=2,ROUND((CG32/CG33-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK32" s="3" t="n"/>
+        <f>IF(COUNT(BY32:BY33)=2,ROUND((BY32/BY33-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK32" s="4">
+        <f>IF(COUNT(BY32:BY33)=2,ROUND((BY32/BY33-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL32" s="4">
-        <f>IF(COUNT(BY32:BY33)=2,ROUND((BY32/BY33-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM32" s="5">
-        <f>IF(COUNT(CG32:CG33)=2,(CG32-CG33)*100,"")</f>
+        <f>IF(COUNT(BY32:BY37)=6,ROUND((BY32/BY37-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM32" s="4">
+        <f>IF(COUNT(CK32:CK51)=20,IFERROR(ROUND(STDEV(CK32:CK51),4),""),"")</f>
         <v/>
       </c>
       <c r="CN32" s="4">
-        <f>IF(COUNT(BY32:BY37)=6,ROUND((BY32/BY37-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO32" s="4">
-        <f>IF(COUNT(CL32:CL51)=20,ROUND(STDEV(CL32:CL51),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP32" s="4">
+        <f>IF(COUNT(CF32:CF33)=2,ROUND((CF32/CF33-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO32" s="5">
+        <f>IF(COUNT(CF32:CF33)=2,(CF32-CF33)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP32" s="3" t="n"/>
+      <c r="CQ32" s="4">
         <f>X32-P32</f>
         <v/>
       </c>
-      <c r="CQ32" s="4">
+      <c r="CR32" s="4">
         <f>AF32-P32</f>
         <v/>
       </c>
-      <c r="CR32" s="6">
-        <f>IF(COUNT(H32:H51)=20,CORREL(H32:H51,P32:P51),"")</f>
-        <v/>
-      </c>
-      <c r="CS32" s="4">
+      <c r="CS32" s="6">
+        <f>IF(COUNT(H32:H51)=20,IFERROR(CORREL(H32:H51,P32:P51),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT32" s="4">
         <f>AN32-AV32</f>
         <v/>
       </c>
-      <c r="CT32" s="4">
+      <c r="CU32" s="4">
         <f>BD32-BL32</f>
         <v/>
       </c>
-      <c r="CU32" s="6">
-        <f>BY32/CG32</f>
-        <v/>
-      </c>
-      <c r="CV32" s="4">
+      <c r="CV32" s="6">
+        <f>BY32/CF32</f>
+        <v/>
+      </c>
+      <c r="CW32" s="4">
         <f>P32-BT32</f>
         <v/>
       </c>
@@ -6459,75 +6470,76 @@
       <c r="CA33" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB33" s="4">
-        <f>IF(COUNT(BY33:BY34)=2,ROUND((BY33/BY34-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC33" s="3" t="n"/>
+      <c r="CB33" s="3" t="n"/>
+      <c r="CC33" s="3" t="n">
+        <v>4.521</v>
+      </c>
       <c r="CD33" s="3" t="n">
-        <v>4.521</v>
+        <v>4.55</v>
       </c>
       <c r="CE33" s="3" t="n">
-        <v>4.55</v>
+        <v>4.511</v>
       </c>
       <c r="CF33" s="3" t="n">
-        <v>4.511</v>
+        <v>4.541</v>
       </c>
       <c r="CG33" s="3" t="n">
         <v>4.541</v>
       </c>
       <c r="CH33" s="3" t="n">
-        <v>4.541</v>
-      </c>
-      <c r="CI33" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI33" s="3" t="n"/>
       <c r="CJ33" s="4">
-        <f>IF(COUNT(CG33:CG34)=2,ROUND((CG33/CG34-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK33" s="3" t="n"/>
+        <f>IF(COUNT(BY33:BY34)=2,ROUND((BY33/BY34-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK33" s="4">
+        <f>IF(COUNT(BY33:BY34)=2,ROUND((BY33/BY34-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL33" s="4">
-        <f>IF(COUNT(BY33:BY34)=2,ROUND((BY33/BY34-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM33" s="5">
-        <f>IF(COUNT(CG33:CG34)=2,(CG33-CG34)*100,"")</f>
+        <f>IF(COUNT(BY33:BY38)=6,ROUND((BY33/BY38-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM33" s="4">
+        <f>IF(COUNT(CK33:CK52)=20,IFERROR(ROUND(STDEV(CK33:CK52),4),""),"")</f>
         <v/>
       </c>
       <c r="CN33" s="4">
-        <f>IF(COUNT(BY33:BY38)=6,ROUND((BY33/BY38-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO33" s="4">
-        <f>IF(COUNT(CL33:CL52)=20,ROUND(STDEV(CL33:CL52),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP33" s="4">
+        <f>IF(COUNT(CF33:CF34)=2,ROUND((CF33/CF34-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO33" s="5">
+        <f>IF(COUNT(CF33:CF34)=2,(CF33-CF34)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP33" s="3" t="n"/>
+      <c r="CQ33" s="4">
         <f>X33-P33</f>
         <v/>
       </c>
-      <c r="CQ33" s="4">
+      <c r="CR33" s="4">
         <f>AF33-P33</f>
         <v/>
       </c>
-      <c r="CR33" s="6">
-        <f>IF(COUNT(H33:H52)=20,CORREL(H33:H52,P33:P52),"")</f>
-        <v/>
-      </c>
-      <c r="CS33" s="4">
+      <c r="CS33" s="6">
+        <f>IF(COUNT(H33:H52)=20,IFERROR(CORREL(H33:H52,P33:P52),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT33" s="4">
         <f>AN33-AV33</f>
         <v/>
       </c>
-      <c r="CT33" s="4">
+      <c r="CU33" s="4">
         <f>BD33-BL33</f>
         <v/>
       </c>
-      <c r="CU33" s="6">
-        <f>BY33/CG33</f>
-        <v/>
-      </c>
-      <c r="CV33" s="4">
+      <c r="CV33" s="6">
+        <f>BY33/CF33</f>
+        <v/>
+      </c>
+      <c r="CW33" s="4">
         <f>P33-BT33</f>
         <v/>
       </c>
@@ -6763,75 +6775,76 @@
       <c r="CA34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB34" s="4">
-        <f>IF(COUNT(BY34:BY35)=2,ROUND((BY34/BY35-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC34" s="3" t="n"/>
+      <c r="CB34" s="3" t="n"/>
+      <c r="CC34" s="3" t="n">
+        <v>4.582</v>
+      </c>
       <c r="CD34" s="3" t="n">
-        <v>4.582</v>
+        <v>4.596</v>
       </c>
       <c r="CE34" s="3" t="n">
-        <v>4.596</v>
+        <v>4.561</v>
       </c>
       <c r="CF34" s="3" t="n">
-        <v>4.561</v>
+        <v>4.569</v>
       </c>
       <c r="CG34" s="3" t="n">
         <v>4.569</v>
       </c>
       <c r="CH34" s="3" t="n">
-        <v>4.569</v>
-      </c>
-      <c r="CI34" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI34" s="3" t="n"/>
       <c r="CJ34" s="4">
-        <f>IF(COUNT(CG34:CG35)=2,ROUND((CG34/CG35-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK34" s="3" t="n"/>
+        <f>IF(COUNT(BY34:BY35)=2,ROUND((BY34/BY35-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK34" s="4">
+        <f>IF(COUNT(BY34:BY35)=2,ROUND((BY34/BY35-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL34" s="4">
-        <f>IF(COUNT(BY34:BY35)=2,ROUND((BY34/BY35-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM34" s="5">
-        <f>IF(COUNT(CG34:CG35)=2,(CG34-CG35)*100,"")</f>
+        <f>IF(COUNT(BY34:BY39)=6,ROUND((BY34/BY39-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM34" s="4">
+        <f>IF(COUNT(CK34:CK53)=20,IFERROR(ROUND(STDEV(CK34:CK53),4),""),"")</f>
         <v/>
       </c>
       <c r="CN34" s="4">
-        <f>IF(COUNT(BY34:BY39)=6,ROUND((BY34/BY39-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO34" s="4">
-        <f>IF(COUNT(CL34:CL53)=20,ROUND(STDEV(CL34:CL53),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP34" s="4">
+        <f>IF(COUNT(CF34:CF35)=2,ROUND((CF34/CF35-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO34" s="5">
+        <f>IF(COUNT(CF34:CF35)=2,(CF34-CF35)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP34" s="3" t="n"/>
+      <c r="CQ34" s="4">
         <f>X34-P34</f>
         <v/>
       </c>
-      <c r="CQ34" s="4">
+      <c r="CR34" s="4">
         <f>AF34-P34</f>
         <v/>
       </c>
-      <c r="CR34" s="6">
-        <f>IF(COUNT(H34:H53)=20,CORREL(H34:H53,P34:P53),"")</f>
-        <v/>
-      </c>
-      <c r="CS34" s="4">
+      <c r="CS34" s="6">
+        <f>IF(COUNT(H34:H53)=20,IFERROR(CORREL(H34:H53,P34:P53),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT34" s="4">
         <f>AN34-AV34</f>
         <v/>
       </c>
-      <c r="CT34" s="4">
+      <c r="CU34" s="4">
         <f>BD34-BL34</f>
         <v/>
       </c>
-      <c r="CU34" s="6">
-        <f>BY34/CG34</f>
-        <v/>
-      </c>
-      <c r="CV34" s="4">
+      <c r="CV34" s="6">
+        <f>BY34/CF34</f>
+        <v/>
+      </c>
+      <c r="CW34" s="4">
         <f>P34-BT34</f>
         <v/>
       </c>
@@ -7067,75 +7080,76 @@
       <c r="CA35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB35" s="4">
-        <f>IF(COUNT(BY35:BY36)=2,ROUND((BY35/BY36-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC35" s="3" t="n"/>
+      <c r="CB35" s="3" t="n"/>
+      <c r="CC35" s="3" t="n">
+        <v>4.608</v>
+      </c>
       <c r="CD35" s="3" t="n">
-        <v>4.608</v>
+        <v>4.61</v>
       </c>
       <c r="CE35" s="3" t="n">
-        <v>4.61</v>
+        <v>4.539</v>
       </c>
       <c r="CF35" s="3" t="n">
-        <v>4.539</v>
+        <v>4.545</v>
       </c>
       <c r="CG35" s="3" t="n">
         <v>4.545</v>
       </c>
       <c r="CH35" s="3" t="n">
-        <v>4.545</v>
-      </c>
-      <c r="CI35" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI35" s="3" t="n"/>
       <c r="CJ35" s="4">
-        <f>IF(COUNT(CG35:CG36)=2,ROUND((CG35/CG36-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK35" s="3" t="n"/>
+        <f>IF(COUNT(BY35:BY36)=2,ROUND((BY35/BY36-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK35" s="4">
+        <f>IF(COUNT(BY35:BY36)=2,ROUND((BY35/BY36-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL35" s="4">
-        <f>IF(COUNT(BY35:BY36)=2,ROUND((BY35/BY36-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM35" s="5">
-        <f>IF(COUNT(CG35:CG36)=2,(CG35-CG36)*100,"")</f>
+        <f>IF(COUNT(BY35:BY40)=6,ROUND((BY35/BY40-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM35" s="4">
+        <f>IF(COUNT(CK35:CK54)=20,IFERROR(ROUND(STDEV(CK35:CK54),4),""),"")</f>
         <v/>
       </c>
       <c r="CN35" s="4">
-        <f>IF(COUNT(BY35:BY40)=6,ROUND((BY35/BY40-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO35" s="4">
-        <f>IF(COUNT(CL35:CL54)=20,ROUND(STDEV(CL35:CL54),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP35" s="4">
+        <f>IF(COUNT(CF35:CF36)=2,ROUND((CF35/CF36-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO35" s="5">
+        <f>IF(COUNT(CF35:CF36)=2,(CF35-CF36)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP35" s="3" t="n"/>
+      <c r="CQ35" s="4">
         <f>X35-P35</f>
         <v/>
       </c>
-      <c r="CQ35" s="4">
+      <c r="CR35" s="4">
         <f>AF35-P35</f>
         <v/>
       </c>
-      <c r="CR35" s="6">
-        <f>IF(COUNT(H35:H54)=20,CORREL(H35:H54,P35:P54),"")</f>
-        <v/>
-      </c>
-      <c r="CS35" s="4">
+      <c r="CS35" s="6">
+        <f>IF(COUNT(H35:H54)=20,IFERROR(CORREL(H35:H54,P35:P54),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT35" s="4">
         <f>AN35-AV35</f>
         <v/>
       </c>
-      <c r="CT35" s="4">
+      <c r="CU35" s="4">
         <f>BD35-BL35</f>
         <v/>
       </c>
-      <c r="CU35" s="6">
-        <f>BY35/CG35</f>
-        <v/>
-      </c>
-      <c r="CV35" s="4">
+      <c r="CV35" s="6">
+        <f>BY35/CF35</f>
+        <v/>
+      </c>
+      <c r="CW35" s="4">
         <f>P35-BT35</f>
         <v/>
       </c>
@@ -7371,75 +7385,76 @@
       <c r="CA36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB36" s="4">
-        <f>IF(COUNT(BY36:BY37)=2,ROUND((BY36/BY37-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC36" s="3" t="n"/>
+      <c r="CB36" s="3" t="n"/>
+      <c r="CC36" s="3" t="n">
+        <v>4.614</v>
+      </c>
       <c r="CD36" s="3" t="n">
         <v>4.614</v>
       </c>
       <c r="CE36" s="3" t="n">
-        <v>4.614</v>
+        <v>4.525</v>
       </c>
       <c r="CF36" s="3" t="n">
-        <v>4.525</v>
+        <v>4.585</v>
       </c>
       <c r="CG36" s="3" t="n">
         <v>4.585</v>
       </c>
       <c r="CH36" s="3" t="n">
-        <v>4.585</v>
-      </c>
-      <c r="CI36" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI36" s="3" t="n"/>
       <c r="CJ36" s="4">
-        <f>IF(COUNT(CG36:CG37)=2,ROUND((CG36/CG37-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK36" s="3" t="n"/>
+        <f>IF(COUNT(BY36:BY37)=2,ROUND((BY36/BY37-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK36" s="4">
+        <f>IF(COUNT(BY36:BY37)=2,ROUND((BY36/BY37-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL36" s="4">
-        <f>IF(COUNT(BY36:BY37)=2,ROUND((BY36/BY37-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM36" s="5">
-        <f>IF(COUNT(CG36:CG37)=2,(CG36-CG37)*100,"")</f>
+        <f>IF(COUNT(BY36:BY41)=6,ROUND((BY36/BY41-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM36" s="4">
+        <f>IF(COUNT(CK36:CK55)=20,IFERROR(ROUND(STDEV(CK36:CK55),4),""),"")</f>
         <v/>
       </c>
       <c r="CN36" s="4">
-        <f>IF(COUNT(BY36:BY41)=6,ROUND((BY36/BY41-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO36" s="4">
-        <f>IF(COUNT(CL36:CL55)=20,ROUND(STDEV(CL36:CL55),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP36" s="4">
+        <f>IF(COUNT(CF36:CF37)=2,ROUND((CF36/CF37-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO36" s="5">
+        <f>IF(COUNT(CF36:CF37)=2,(CF36-CF37)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP36" s="3" t="n"/>
+      <c r="CQ36" s="4">
         <f>X36-P36</f>
         <v/>
       </c>
-      <c r="CQ36" s="4">
+      <c r="CR36" s="4">
         <f>AF36-P36</f>
         <v/>
       </c>
-      <c r="CR36" s="6">
-        <f>IF(COUNT(H36:H55)=20,CORREL(H36:H55,P36:P55),"")</f>
-        <v/>
-      </c>
-      <c r="CS36" s="4">
+      <c r="CS36" s="6">
+        <f>IF(COUNT(H36:H55)=20,IFERROR(CORREL(H36:H55,P36:P55),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT36" s="4">
         <f>AN36-AV36</f>
         <v/>
       </c>
-      <c r="CT36" s="4">
+      <c r="CU36" s="4">
         <f>BD36-BL36</f>
         <v/>
       </c>
-      <c r="CU36" s="6">
-        <f>BY36/CG36</f>
-        <v/>
-      </c>
-      <c r="CV36" s="4">
+      <c r="CV36" s="6">
+        <f>BY36/CF36</f>
+        <v/>
+      </c>
+      <c r="CW36" s="4">
         <f>P36-BT36</f>
         <v/>
       </c>
@@ -7675,75 +7690,76 @@
       <c r="CA37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB37" s="4">
-        <f>IF(COUNT(BY37:BY38)=2,ROUND((BY37/BY38-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC37" s="3" t="n"/>
+      <c r="CB37" s="3" t="n"/>
+      <c r="CC37" s="3" t="n">
+        <v>4.585</v>
+      </c>
       <c r="CD37" s="3" t="n">
-        <v>4.585</v>
+        <v>4.618</v>
       </c>
       <c r="CE37" s="3" t="n">
-        <v>4.618</v>
+        <v>4.573</v>
       </c>
       <c r="CF37" s="3" t="n">
-        <v>4.573</v>
+        <v>4.609</v>
       </c>
       <c r="CG37" s="3" t="n">
         <v>4.609</v>
       </c>
       <c r="CH37" s="3" t="n">
-        <v>4.609</v>
-      </c>
-      <c r="CI37" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI37" s="3" t="n"/>
       <c r="CJ37" s="4">
-        <f>IF(COUNT(CG37:CG38)=2,ROUND((CG37/CG38-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK37" s="3" t="n"/>
+        <f>IF(COUNT(BY37:BY38)=2,ROUND((BY37/BY38-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK37" s="4">
+        <f>IF(COUNT(BY37:BY38)=2,ROUND((BY37/BY38-1)*100,4),"")</f>
+        <v/>
+      </c>
       <c r="CL37" s="4">
-        <f>IF(COUNT(BY37:BY38)=2,ROUND((BY37/BY38-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM37" s="5">
-        <f>IF(COUNT(CG37:CG38)=2,(CG37-CG38)*100,"")</f>
+        <f>IF(COUNT(BY37:BY42)=6,ROUND((BY37/BY42-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CM37" s="4">
+        <f>IF(COUNT(CK37:CK56)=20,IFERROR(ROUND(STDEV(CK37:CK56),4),""),"")</f>
         <v/>
       </c>
       <c r="CN37" s="4">
-        <f>IF(COUNT(BY37:BY42)=6,ROUND((BY37/BY42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO37" s="4">
-        <f>IF(COUNT(CL37:CL56)=20,ROUND(STDEV(CL37:CL56),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP37" s="4">
+        <f>IF(COUNT(CF37:CF38)=2,ROUND((CF37/CF38-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO37" s="5">
+        <f>IF(COUNT(CF37:CF38)=2,(CF37-CF38)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP37" s="3" t="n"/>
+      <c r="CQ37" s="4">
         <f>X37-P37</f>
         <v/>
       </c>
-      <c r="CQ37" s="4">
+      <c r="CR37" s="4">
         <f>AF37-P37</f>
         <v/>
       </c>
-      <c r="CR37" s="6">
-        <f>IF(COUNT(H37:H56)=20,CORREL(H37:H56,P37:P56),"")</f>
-        <v/>
-      </c>
-      <c r="CS37" s="4">
+      <c r="CS37" s="6">
+        <f>IF(COUNT(H37:H56)=20,IFERROR(CORREL(H37:H56,P37:P56),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT37" s="4">
         <f>AN37-AV37</f>
         <v/>
       </c>
-      <c r="CT37" s="4">
+      <c r="CU37" s="4">
         <f>BD37-BL37</f>
         <v/>
       </c>
-      <c r="CU37" s="6">
-        <f>BY37/CG37</f>
-        <v/>
-      </c>
-      <c r="CV37" s="4">
+      <c r="CV37" s="6">
+        <f>BY37/CF37</f>
+        <v/>
+      </c>
+      <c r="CW37" s="4">
         <f>P37-BT37</f>
         <v/>
       </c>
@@ -7979,72 +7995,73 @@
       <c r="CA38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB38" s="4">
-        <f>IF(COUNT(BY38:BY39)=2,ROUND((BY38/BY39-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC38" s="3" t="n"/>
+      <c r="CB38" s="3" t="n"/>
+      <c r="CC38" s="3" t="n">
+        <v>4.541</v>
+      </c>
       <c r="CD38" s="3" t="n">
-        <v>4.541</v>
+        <v>4.571</v>
       </c>
       <c r="CE38" s="3" t="n">
-        <v>4.571</v>
+        <v>4.539</v>
       </c>
       <c r="CF38" s="3" t="n">
-        <v>4.539</v>
+        <v>4.569</v>
       </c>
       <c r="CG38" s="3" t="n">
         <v>4.569</v>
       </c>
       <c r="CH38" s="3" t="n">
-        <v>4.569</v>
-      </c>
-      <c r="CI38" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI38" s="3" t="n"/>
       <c r="CJ38" s="4">
-        <f>IF(COUNT(CG38:CG39)=2,ROUND((CG38/CG39-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK38" s="3" t="n"/>
-      <c r="CL38" s="4">
         <f>IF(COUNT(BY38:BY39)=2,ROUND((BY38/BY39-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="CM38" s="5">
-        <f>IF(COUNT(CG38:CG39)=2,(CG38-CG39)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CN38" s="4" t="n"/>
-      <c r="CO38" s="4">
-        <f>IF(COUNT(CL38:CL57)=20,ROUND(STDEV(CL38:CL57),4),"")</f>
-        <v/>
-      </c>
-      <c r="CP38" s="4">
+      <c r="CK38" s="4">
+        <f>IF(COUNT(BY38:BY39)=2,ROUND((BY38/BY39-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CL38" s="4" t="n"/>
+      <c r="CM38" s="4">
+        <f>IF(COUNT(CK38:CK57)=20,IFERROR(ROUND(STDEV(CK38:CK57),4),""),"")</f>
+        <v/>
+      </c>
+      <c r="CN38" s="4">
+        <f>IF(COUNT(CF38:CF39)=2,ROUND((CF38/CF39-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO38" s="5">
+        <f>IF(COUNT(CF38:CF39)=2,(CF38-CF39)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP38" s="3" t="n"/>
+      <c r="CQ38" s="4">
         <f>X38-P38</f>
         <v/>
       </c>
-      <c r="CQ38" s="4">
+      <c r="CR38" s="4">
         <f>AF38-P38</f>
         <v/>
       </c>
-      <c r="CR38" s="6">
-        <f>IF(COUNT(H38:H57)=20,CORREL(H38:H57,P38:P57),"")</f>
-        <v/>
-      </c>
-      <c r="CS38" s="4">
+      <c r="CS38" s="6">
+        <f>IF(COUNT(H38:H57)=20,IFERROR(CORREL(H38:H57,P38:P57),""),"")</f>
+        <v/>
+      </c>
+      <c r="CT38" s="4">
         <f>AN38-AV38</f>
         <v/>
       </c>
-      <c r="CT38" s="4">
+      <c r="CU38" s="4">
         <f>BD38-BL38</f>
         <v/>
       </c>
-      <c r="CU38" s="6">
-        <f>BY38/CG38</f>
-        <v/>
-      </c>
-      <c r="CV38" s="4">
+      <c r="CV38" s="6">
+        <f>BY38/CF38</f>
+        <v/>
+      </c>
+      <c r="CW38" s="4">
         <f>P38-BT38</f>
         <v/>
       </c>
@@ -8280,66 +8297,67 @@
       <c r="CA39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB39" s="4">
-        <f>IF(COUNT(BY39:BY40)=2,ROUND((BY39/BY40-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC39" s="3" t="n"/>
+      <c r="CB39" s="3" t="n"/>
+      <c r="CC39" s="3" t="n">
+        <v>4.577</v>
+      </c>
       <c r="CD39" s="3" t="n">
-        <v>4.577</v>
+        <v>4.581</v>
       </c>
       <c r="CE39" s="3" t="n">
-        <v>4.581</v>
+        <v>4.529</v>
       </c>
       <c r="CF39" s="3" t="n">
-        <v>4.529</v>
+        <v>4.539</v>
       </c>
       <c r="CG39" s="3" t="n">
         <v>4.539</v>
       </c>
       <c r="CH39" s="3" t="n">
-        <v>4.539</v>
-      </c>
-      <c r="CI39" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI39" s="3" t="n"/>
       <c r="CJ39" s="4">
-        <f>IF(COUNT(CG39:CG40)=2,ROUND((CG39/CG40-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK39" s="3" t="n"/>
-      <c r="CL39" s="4">
         <f>IF(COUNT(BY39:BY40)=2,ROUND((BY39/BY40-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="CM39" s="5">
-        <f>IF(COUNT(CG39:CG40)=2,(CG39-CG40)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CN39" s="4" t="n"/>
-      <c r="CO39" s="4" t="n"/>
-      <c r="CP39" s="4">
+      <c r="CK39" s="4">
+        <f>IF(COUNT(BY39:BY40)=2,ROUND((BY39/BY40-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CL39" s="4" t="n"/>
+      <c r="CM39" s="4" t="n"/>
+      <c r="CN39" s="4">
+        <f>IF(COUNT(CF39:CF40)=2,ROUND((CF39/CF40-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO39" s="5">
+        <f>IF(COUNT(CF39:CF40)=2,(CF39-CF40)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP39" s="3" t="n"/>
+      <c r="CQ39" s="4">
         <f>X39-P39</f>
         <v/>
       </c>
-      <c r="CQ39" s="4">
+      <c r="CR39" s="4">
         <f>AF39-P39</f>
         <v/>
       </c>
-      <c r="CR39" s="6" t="n"/>
-      <c r="CS39" s="4">
+      <c r="CS39" s="6" t="n"/>
+      <c r="CT39" s="4">
         <f>AN39-AV39</f>
         <v/>
       </c>
-      <c r="CT39" s="4">
+      <c r="CU39" s="4">
         <f>BD39-BL39</f>
         <v/>
       </c>
-      <c r="CU39" s="6">
-        <f>BY39/CG39</f>
-        <v/>
-      </c>
-      <c r="CV39" s="4">
+      <c r="CV39" s="6">
+        <f>BY39/CF39</f>
+        <v/>
+      </c>
+      <c r="CW39" s="4">
         <f>P39-BT39</f>
         <v/>
       </c>
@@ -8575,66 +8593,67 @@
       <c r="CA40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB40" s="4">
-        <f>IF(COUNT(BY40:BY41)=2,ROUND((BY40/BY41-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC40" s="3" t="n"/>
+      <c r="CB40" s="3" t="n"/>
+      <c r="CC40" s="3" t="n">
+        <v>4.561</v>
+      </c>
       <c r="CD40" s="3" t="n">
-        <v>4.561</v>
+        <v>4.597</v>
       </c>
       <c r="CE40" s="3" t="n">
-        <v>4.597</v>
+        <v>4.557</v>
       </c>
       <c r="CF40" s="3" t="n">
-        <v>4.557</v>
+        <v>4.569</v>
       </c>
       <c r="CG40" s="3" t="n">
         <v>4.569</v>
       </c>
       <c r="CH40" s="3" t="n">
-        <v>4.569</v>
-      </c>
-      <c r="CI40" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI40" s="3" t="n"/>
       <c r="CJ40" s="4">
-        <f>IF(COUNT(CG40:CG41)=2,ROUND((CG40/CG41-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK40" s="3" t="n"/>
-      <c r="CL40" s="4">
         <f>IF(COUNT(BY40:BY41)=2,ROUND((BY40/BY41-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="CM40" s="5">
-        <f>IF(COUNT(CG40:CG41)=2,(CG40-CG41)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CN40" s="4" t="n"/>
-      <c r="CO40" s="4" t="n"/>
-      <c r="CP40" s="4">
+      <c r="CK40" s="4">
+        <f>IF(COUNT(BY40:BY41)=2,ROUND((BY40/BY41-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CL40" s="4" t="n"/>
+      <c r="CM40" s="4" t="n"/>
+      <c r="CN40" s="4">
+        <f>IF(COUNT(CF40:CF41)=2,ROUND((CF40/CF41-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO40" s="5">
+        <f>IF(COUNT(CF40:CF41)=2,(CF40-CF41)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP40" s="3" t="n"/>
+      <c r="CQ40" s="4">
         <f>X40-P40</f>
         <v/>
       </c>
-      <c r="CQ40" s="4">
+      <c r="CR40" s="4">
         <f>AF40-P40</f>
         <v/>
       </c>
-      <c r="CR40" s="6" t="n"/>
-      <c r="CS40" s="4">
+      <c r="CS40" s="6" t="n"/>
+      <c r="CT40" s="4">
         <f>AN40-AV40</f>
         <v/>
       </c>
-      <c r="CT40" s="4">
+      <c r="CU40" s="4">
         <f>BD40-BL40</f>
         <v/>
       </c>
-      <c r="CU40" s="6">
-        <f>BY40/CG40</f>
-        <v/>
-      </c>
-      <c r="CV40" s="4">
+      <c r="CV40" s="6">
+        <f>BY40/CF40</f>
+        <v/>
+      </c>
+      <c r="CW40" s="4">
         <f>P40-BT40</f>
         <v/>
       </c>
@@ -8870,66 +8889,67 @@
       <c r="CA41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB41" s="4">
-        <f>IF(COUNT(BY41:BY42)=2,ROUND((BY41/BY42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CC41" s="3" t="n"/>
+      <c r="CB41" s="3" t="n"/>
+      <c r="CC41" s="3" t="n">
+        <v>4.497</v>
+      </c>
       <c r="CD41" s="3" t="n">
-        <v>4.497</v>
+        <v>4.533</v>
       </c>
       <c r="CE41" s="3" t="n">
-        <v>4.533</v>
+        <v>4.485</v>
       </c>
       <c r="CF41" s="3" t="n">
-        <v>4.485</v>
+        <v>4.529</v>
       </c>
       <c r="CG41" s="3" t="n">
         <v>4.529</v>
       </c>
       <c r="CH41" s="3" t="n">
-        <v>4.529</v>
-      </c>
-      <c r="CI41" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="CI41" s="3" t="n"/>
       <c r="CJ41" s="4">
-        <f>IF(COUNT(CG41:CG42)=2,ROUND((CG41/CG42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK41" s="3" t="n"/>
-      <c r="CL41" s="4">
         <f>IF(COUNT(BY41:BY42)=2,ROUND((BY41/BY42-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="CM41" s="5">
-        <f>IF(COUNT(CG41:CG42)=2,(CG41-CG42)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CN41" s="4" t="n"/>
-      <c r="CO41" s="4" t="n"/>
-      <c r="CP41" s="4">
+      <c r="CK41" s="4">
+        <f>IF(COUNT(BY41:BY42)=2,ROUND((BY41/BY42-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CL41" s="4" t="n"/>
+      <c r="CM41" s="4" t="n"/>
+      <c r="CN41" s="4">
+        <f>IF(COUNT(CF41:CF42)=2,ROUND((CF41/CF42-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO41" s="5">
+        <f>IF(COUNT(CF41:CF42)=2,(CF41-CF42)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP41" s="3" t="n"/>
+      <c r="CQ41" s="4">
         <f>X41-P41</f>
         <v/>
       </c>
-      <c r="CQ41" s="4">
+      <c r="CR41" s="4">
         <f>AF41-P41</f>
         <v/>
       </c>
-      <c r="CR41" s="6" t="n"/>
-      <c r="CS41" s="4">
+      <c r="CS41" s="6" t="n"/>
+      <c r="CT41" s="4">
         <f>AN41-AV41</f>
         <v/>
       </c>
-      <c r="CT41" s="4">
+      <c r="CU41" s="4">
         <f>BD41-BL41</f>
         <v/>
       </c>
-      <c r="CU41" s="6">
-        <f>BY41/CG41</f>
-        <v/>
-      </c>
-      <c r="CV41" s="4">
+      <c r="CV41" s="6">
+        <f>BY41/CF41</f>
+        <v/>
+      </c>
+      <c r="CW41" s="4">
         <f>P41-BT41</f>
         <v/>
       </c>
@@ -9138,60 +9158,67 @@
       <c r="CA42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CB42" s="4" t="n"/>
-      <c r="CC42" s="3" t="n"/>
+      <c r="CB42" s="3" t="n"/>
+      <c r="CC42" s="3" t="n">
+        <v>4.457</v>
+      </c>
       <c r="CD42" s="3" t="n">
+        <v>4.491</v>
+      </c>
+      <c r="CE42" s="3" t="n">
         <v>4.457</v>
       </c>
-      <c r="CE42" s="3" t="n">
-        <v>4.491</v>
-      </c>
       <c r="CF42" s="3" t="n">
-        <v>4.457</v>
+        <v>4.479</v>
       </c>
       <c r="CG42" s="3" t="n">
         <v>4.479</v>
       </c>
       <c r="CH42" s="3" t="n">
-        <v>4.479</v>
-      </c>
-      <c r="CI42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="CJ42" s="4" t="n"/>
-      <c r="CK42" s="3" t="n"/>
-      <c r="CL42" s="4">
+      <c r="CI42" s="3" t="n"/>
+      <c r="CJ42" s="4">
         <f>IF(COUNT(BY42:BY43)=2,ROUND((BY42/BY43-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="CM42" s="5">
-        <f>IF(COUNT(CG42:CG43)=2,(CG42-CG43)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CN42" s="4" t="n"/>
-      <c r="CO42" s="4" t="n"/>
-      <c r="CP42" s="4">
+      <c r="CK42" s="4">
+        <f>IF(COUNT(BY42:BY43)=2,ROUND((BY42/BY43-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CL42" s="4" t="n"/>
+      <c r="CM42" s="4" t="n"/>
+      <c r="CN42" s="4">
+        <f>IF(COUNT(CF42:CF43)=2,ROUND((CF42/CF43-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CO42" s="5">
+        <f>IF(COUNT(CF42:CF43)=2,(CF42-CF43)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CP42" s="3" t="n"/>
+      <c r="CQ42" s="4">
         <f>X42-P42</f>
         <v/>
       </c>
-      <c r="CQ42" s="4">
+      <c r="CR42" s="4">
         <f>AF42-P42</f>
         <v/>
       </c>
-      <c r="CR42" s="6" t="n"/>
-      <c r="CS42" s="4">
+      <c r="CS42" s="6" t="n"/>
+      <c r="CT42" s="4">
         <f>AN42-AV42</f>
         <v/>
       </c>
-      <c r="CT42" s="4">
+      <c r="CU42" s="4">
         <f>BD42-BL42</f>
         <v/>
       </c>
-      <c r="CU42" s="6">
-        <f>BY42/CG42</f>
-        <v/>
-      </c>
-      <c r="CV42" s="4">
+      <c r="CV42" s="6">
+        <f>BY42/CF42</f>
+        <v/>
+      </c>
+      <c r="CW42" s="4">
         <f>P42-BT42</f>
         <v/>
       </c>

--- a/04_结果/示例审批/外部数据新版式示例.xlsx
+++ b/04_结果/示例审批/外部数据新版式示例.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A14:CW42"/>
+  <dimension ref="A14:CW40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -769,11 +769,27 @@
       <c r="CH14" s="2" t="n"/>
       <c r="CI14" s="2" t="n"/>
       <c r="CJ14" s="2" t="n"/>
-      <c r="CK14" s="2" t="n"/>
-      <c r="CL14" s="2" t="n"/>
-      <c r="CM14" s="2" t="n"/>
+      <c r="CK14" s="2" t="inlineStr">
+        <is>
+          <t>VIX_Chg%</t>
+        </is>
+      </c>
+      <c r="CL14" s="2" t="inlineStr">
+        <is>
+          <t>VIX_5dChg</t>
+        </is>
+      </c>
+      <c r="CM14" s="2" t="inlineStr">
+        <is>
+          <t>VIX_20dVol</t>
+        </is>
+      </c>
       <c r="CN14" s="2" t="n"/>
-      <c r="CO14" s="2" t="n"/>
+      <c r="CO14" s="2" t="inlineStr">
+        <is>
+          <t>TNX_ChgBp</t>
+        </is>
+      </c>
       <c r="CP14" s="2" t="n"/>
       <c r="CQ14" s="2" t="inlineStr">
         <is>
@@ -1210,17 +1226,17 @@
       </c>
       <c r="CK15" s="2" t="inlineStr">
         <is>
-          <t>VIX_Chg%</t>
+          <t>VIX_close/昨VIX_close-1</t>
         </is>
       </c>
       <c r="CL15" s="2" t="inlineStr">
         <is>
-          <t>VIX_5dChg</t>
+          <t>VIX_close/5日前VIX_close-1</t>
         </is>
       </c>
       <c r="CM15" s="2" t="inlineStr">
         <is>
-          <t>VIX_20dVol</t>
+          <t>STDEV(VIX日变化,近20日)</t>
         </is>
       </c>
       <c r="CN15" s="2" t="inlineStr">
@@ -1230,7 +1246,7 @@
       </c>
       <c r="CO15" s="2" t="inlineStr">
         <is>
-          <t>TNX_ChgBp</t>
+          <t>(TNX_close-昨TNX_close)*100</t>
         </is>
       </c>
       <c r="CP15" s="2" t="n"/>
@@ -1273,141 +1289,249 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026/08/11</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>771.02</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>773.92</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>769.61</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>773.26</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>773.26</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>43557000</v>
+      </c>
       <c r="H16" s="4">
         <f>IF(COUNT(F16:F17)=2,ROUND((F16/F17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
+      <c r="J16" s="3" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>82.84999999999999</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>96118900</v>
+      </c>
       <c r="P16" s="4">
         <f>IF(COUNT(N16:N17)=2,ROUND((N16/N17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="Q16" s="3" t="n"/>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
-      <c r="T16" s="3" t="n"/>
-      <c r="U16" s="3" t="n"/>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
+      <c r="R16" s="3" t="n">
+        <v>79.67</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>79.69</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>79.56999999999999</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>79.61</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>79.61</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>23458100</v>
+      </c>
       <c r="X16" s="4">
         <f>IF(COUNT(V16:V17)=2,ROUND((V16/V17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="Y16" s="3" t="n"/>
-      <c r="Z16" s="3" t="n"/>
-      <c r="AA16" s="3" t="n"/>
-      <c r="AB16" s="3" t="n"/>
-      <c r="AC16" s="3" t="n"/>
-      <c r="AD16" s="3" t="n"/>
-      <c r="AE16" s="3" t="n"/>
+      <c r="Z16" s="3" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="AA16" s="3" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="AB16" s="3" t="n">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="AC16" s="3" t="n">
+        <v>95.81</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>95.81</v>
+      </c>
+      <c r="AE16" s="3" t="n">
+        <v>9024100</v>
+      </c>
       <c r="AF16" s="4">
         <f>IF(COUNT(AD16:AD17)=2,ROUND((AD16/AD17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AG16" s="3" t="n"/>
-      <c r="AH16" s="3" t="n"/>
-      <c r="AI16" s="3" t="n"/>
-      <c r="AJ16" s="3" t="n"/>
-      <c r="AK16" s="3" t="n"/>
-      <c r="AL16" s="3" t="n"/>
-      <c r="AM16" s="3" t="n"/>
+      <c r="AH16" s="3" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="AI16" s="3" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="AJ16" s="3" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="AL16" s="3" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="AM16" s="3" t="n">
+        <v>1718300</v>
+      </c>
       <c r="AN16" s="4">
         <f>IF(COUNT(AL16:AL17)=2,ROUND((AL16/AL17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AO16" s="3" t="n"/>
-      <c r="AP16" s="3" t="n"/>
-      <c r="AQ16" s="3" t="n"/>
-      <c r="AR16" s="3" t="n"/>
-      <c r="AS16" s="3" t="n"/>
-      <c r="AT16" s="3" t="n"/>
-      <c r="AU16" s="3" t="n"/>
+      <c r="AP16" s="3" t="n">
+        <v>399.6</v>
+      </c>
+      <c r="AQ16" s="3" t="n">
+        <v>400.66</v>
+      </c>
+      <c r="AR16" s="3" t="n">
+        <v>396.95</v>
+      </c>
+      <c r="AS16" s="3" t="n">
+        <v>398.47</v>
+      </c>
+      <c r="AT16" s="3" t="n">
+        <v>398.47</v>
+      </c>
+      <c r="AU16" s="3" t="n">
+        <v>13301600</v>
+      </c>
       <c r="AV16" s="4">
         <f>IF(COUNT(AT16:AT17)=2,ROUND((AT16/AT17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW16" s="3" t="n"/>
-      <c r="AX16" s="3" t="n"/>
-      <c r="AY16" s="3" t="n"/>
-      <c r="AZ16" s="3" t="n"/>
-      <c r="BA16" s="3" t="n"/>
-      <c r="BB16" s="3" t="n"/>
-      <c r="BC16" s="3" t="n"/>
+      <c r="AX16" s="3" t="n">
+        <v>187.99</v>
+      </c>
+      <c r="AY16" s="3" t="n">
+        <v>188.73</v>
+      </c>
+      <c r="AZ16" s="3" t="n">
+        <v>185.74</v>
+      </c>
+      <c r="BA16" s="3" t="n">
+        <v>187.97</v>
+      </c>
+      <c r="BB16" s="3" t="n">
+        <v>187.97</v>
+      </c>
+      <c r="BC16" s="3" t="n">
+        <v>6357700</v>
+      </c>
       <c r="BD16" s="4">
         <f>IF(COUNT(BB16:BB17)=2,ROUND((BB16/BB17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BE16" s="3" t="n"/>
-      <c r="BF16" s="3" t="n"/>
-      <c r="BG16" s="3" t="n"/>
-      <c r="BH16" s="3" t="n"/>
-      <c r="BI16" s="3" t="n"/>
-      <c r="BJ16" s="3" t="n"/>
-      <c r="BK16" s="3" t="n"/>
+      <c r="BF16" s="3" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="BG16" s="3" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="BH16" s="3" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="BI16" s="3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="BJ16" s="3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="BK16" s="3" t="n">
+        <v>20778200</v>
+      </c>
       <c r="BL16" s="4">
         <f>IF(COUNT(BJ16:BJ17)=2,ROUND((BJ16/BJ17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BM16" s="3" t="n"/>
-      <c r="BN16" s="3" t="n"/>
-      <c r="BO16" s="3" t="n"/>
-      <c r="BP16" s="3" t="n"/>
-      <c r="BQ16" s="3" t="n"/>
-      <c r="BR16" s="3" t="n"/>
-      <c r="BS16" s="3" t="n"/>
+      <c r="BN16" s="3" t="n">
+        <v>107.11</v>
+      </c>
+      <c r="BO16" s="3" t="n">
+        <v>107.14</v>
+      </c>
+      <c r="BP16" s="3" t="n">
+        <v>106.99</v>
+      </c>
+      <c r="BQ16" s="3" t="n">
+        <v>107.08</v>
+      </c>
+      <c r="BR16" s="3" t="n">
+        <v>107.08</v>
+      </c>
+      <c r="BS16" s="3" t="n">
+        <v>1146300</v>
+      </c>
       <c r="BT16" s="4">
         <f>IF(COUNT(BR16:BR17)=2,ROUND((BR16/BR17-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BU16" s="3" t="n"/>
       <c r="BV16" s="3" t="n">
-        <v>15.42</v>
+        <v>15.3</v>
       </c>
       <c r="BW16" s="3" t="n">
-        <v>15.61</v>
+        <v>15.36</v>
       </c>
       <c r="BX16" s="3" t="n">
-        <v>15.23</v>
+        <v>14.77</v>
       </c>
       <c r="BY16" s="3" t="n">
-        <v>15.28</v>
+        <v>14.9</v>
       </c>
       <c r="BZ16" s="3" t="n">
-        <v>15.28</v>
+        <v>14.9</v>
       </c>
       <c r="CA16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB16" s="3" t="n"/>
       <c r="CC16" s="3" t="n">
-        <v>4.692</v>
+        <v>4.664</v>
       </c>
       <c r="CD16" s="3" t="n">
-        <v>4.703</v>
+        <v>4.672</v>
       </c>
       <c r="CE16" s="3" t="n">
-        <v>4.668</v>
+        <v>4.603</v>
       </c>
       <c r="CF16" s="3" t="n">
-        <v>4.684</v>
+        <v>4.66</v>
       </c>
       <c r="CG16" s="3" t="n">
-        <v>4.684</v>
+        <v>4.66</v>
       </c>
       <c r="CH16" s="3" t="n">
         <v>0</v>
@@ -1439,11 +1563,11 @@
       </c>
       <c r="CP16" s="3" t="n"/>
       <c r="CQ16" s="4">
-        <f>X16-P16</f>
+        <f>IFERROR(X16-P16,"")</f>
         <v/>
       </c>
       <c r="CR16" s="4">
-        <f>AF16-P16</f>
+        <f>IFERROR(AF16-P16,"")</f>
         <v/>
       </c>
       <c r="CS16" s="6">
@@ -1451,11 +1575,11 @@
         <v/>
       </c>
       <c r="CT16" s="4">
-        <f>AN16-AV16</f>
+        <f>IFERROR(AN16-AV16,"")</f>
         <v/>
       </c>
       <c r="CU16" s="4">
-        <f>BD16-BL16</f>
+        <f>IFERROR(BD16-BL16,"")</f>
         <v/>
       </c>
       <c r="CV16" s="6">
@@ -1463,148 +1587,256 @@
         <v/>
       </c>
       <c r="CW16" s="4">
-        <f>P16-BT16</f>
+        <f>IFERROR(P16-BT16,"")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026/08/10</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
-      <c r="G17" s="3" t="n"/>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>770.21</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>771.8200000000001</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>767.46</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>768.5599999999999</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>768.5599999999999</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>38416900</v>
+      </c>
       <c r="H17" s="4">
         <f>IF(COUNT(F17:F18)=2,ROUND((F17/F18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
+      <c r="J17" s="3" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>82.92</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>82.52</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>82.52</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>27566600</v>
+      </c>
       <c r="P17" s="4">
         <f>IF(COUNT(N17:N18)=2,ROUND((N17/N18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="Q17" s="3" t="n"/>
-      <c r="R17" s="3" t="n"/>
-      <c r="S17" s="3" t="n"/>
-      <c r="T17" s="3" t="n"/>
-      <c r="U17" s="3" t="n"/>
-      <c r="V17" s="3" t="n"/>
-      <c r="W17" s="3" t="n"/>
+      <c r="R17" s="3" t="n">
+        <v>79.51000000000001</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>79.51000000000001</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>79.41</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>79.45999999999999</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>79.45999999999999</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>25818200</v>
+      </c>
       <c r="X17" s="4">
         <f>IF(COUNT(V17:V18)=2,ROUND((V17/V18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="Y17" s="3" t="n"/>
-      <c r="Z17" s="3" t="n"/>
-      <c r="AA17" s="3" t="n"/>
-      <c r="AB17" s="3" t="n"/>
-      <c r="AC17" s="3" t="n"/>
-      <c r="AD17" s="3" t="n"/>
-      <c r="AE17" s="3" t="n"/>
+      <c r="Z17" s="3" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="AA17" s="3" t="n">
+        <v>95.73999999999999</v>
+      </c>
+      <c r="AB17" s="3" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="AC17" s="3" t="n">
+        <v>95.61</v>
+      </c>
+      <c r="AD17" s="3" t="n">
+        <v>95.61</v>
+      </c>
+      <c r="AE17" s="3" t="n">
+        <v>2389400</v>
+      </c>
       <c r="AF17" s="4">
         <f>IF(COUNT(AD17:AD18)=2,ROUND((AD17/AD18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AG17" s="3" t="n"/>
-      <c r="AH17" s="3" t="n"/>
-      <c r="AI17" s="3" t="n"/>
-      <c r="AJ17" s="3" t="n"/>
-      <c r="AK17" s="3" t="n"/>
-      <c r="AL17" s="3" t="n"/>
-      <c r="AM17" s="3" t="n"/>
+      <c r="AH17" s="3" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AJ17" s="3" t="n">
+        <v>28.11</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="AL17" s="3" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="AM17" s="3" t="n">
+        <v>1666000</v>
+      </c>
       <c r="AN17" s="4">
         <f>IF(COUNT(AL17:AL18)=2,ROUND((AL17/AL18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AO17" s="3" t="n"/>
-      <c r="AP17" s="3" t="n"/>
-      <c r="AQ17" s="3" t="n"/>
-      <c r="AR17" s="3" t="n"/>
-      <c r="AS17" s="3" t="n"/>
-      <c r="AT17" s="3" t="n"/>
-      <c r="AU17" s="3" t="n"/>
+      <c r="AP17" s="3" t="n">
+        <v>389.5</v>
+      </c>
+      <c r="AQ17" s="3" t="n">
+        <v>392.12</v>
+      </c>
+      <c r="AR17" s="3" t="n">
+        <v>387.27</v>
+      </c>
+      <c r="AS17" s="3" t="n">
+        <v>389.67</v>
+      </c>
+      <c r="AT17" s="3" t="n">
+        <v>389.67</v>
+      </c>
+      <c r="AU17" s="3" t="n">
+        <v>10954300</v>
+      </c>
       <c r="AV17" s="4">
         <f>IF(COUNT(AT17:AT18)=2,ROUND((AT17/AT18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="AW17" s="3" t="n"/>
-      <c r="AX17" s="3" t="n"/>
-      <c r="AY17" s="3" t="n"/>
-      <c r="AZ17" s="3" t="n"/>
-      <c r="BA17" s="3" t="n"/>
-      <c r="BB17" s="3" t="n"/>
-      <c r="BC17" s="3" t="n"/>
+      <c r="AX17" s="3" t="n">
+        <v>183.19</v>
+      </c>
+      <c r="AY17" s="3" t="n">
+        <v>186.91</v>
+      </c>
+      <c r="AZ17" s="3" t="n">
+        <v>182.06</v>
+      </c>
+      <c r="BA17" s="3" t="n">
+        <v>185.33</v>
+      </c>
+      <c r="BB17" s="3" t="n">
+        <v>185.33</v>
+      </c>
+      <c r="BC17" s="3" t="n">
+        <v>6706000</v>
+      </c>
       <c r="BD17" s="4">
         <f>IF(COUNT(BB17:BB18)=2,ROUND((BB17/BB18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BE17" s="3" t="n"/>
-      <c r="BF17" s="3" t="n"/>
-      <c r="BG17" s="3" t="n"/>
-      <c r="BH17" s="3" t="n"/>
-      <c r="BI17" s="3" t="n"/>
-      <c r="BJ17" s="3" t="n"/>
-      <c r="BK17" s="3" t="n"/>
+      <c r="BF17" s="3" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="BG17" s="3" t="n">
+        <v>58.38</v>
+      </c>
+      <c r="BH17" s="3" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="BI17" s="3" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="BJ17" s="3" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="BK17" s="3" t="n">
+        <v>27704200</v>
+      </c>
       <c r="BL17" s="4">
         <f>IF(COUNT(BJ17:BJ18)=2,ROUND((BJ17/BJ18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BM17" s="3" t="n"/>
-      <c r="BN17" s="3" t="n"/>
-      <c r="BO17" s="3" t="n"/>
-      <c r="BP17" s="3" t="n"/>
-      <c r="BQ17" s="3" t="n"/>
-      <c r="BR17" s="3" t="n"/>
-      <c r="BS17" s="3" t="n"/>
+      <c r="BN17" s="3" t="n">
+        <v>106.94</v>
+      </c>
+      <c r="BO17" s="3" t="n">
+        <v>106.97</v>
+      </c>
+      <c r="BP17" s="3" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="BQ17" s="3" t="n">
+        <v>106.87</v>
+      </c>
+      <c r="BR17" s="3" t="n">
+        <v>106.87</v>
+      </c>
+      <c r="BS17" s="3" t="n">
+        <v>1962900</v>
+      </c>
       <c r="BT17" s="4">
         <f>IF(COUNT(BR17:BR18)=2,ROUND((BR17/BR18-1)*100,4),"")</f>
         <v/>
       </c>
       <c r="BU17" s="3" t="n"/>
       <c r="BV17" s="3" t="n">
-        <v>15.4</v>
+        <v>15.83</v>
       </c>
       <c r="BW17" s="3" t="n">
-        <v>15.72</v>
+        <v>16.03</v>
       </c>
       <c r="BX17" s="3" t="n">
-        <v>15.1</v>
+        <v>15.11</v>
       </c>
       <c r="BY17" s="3" t="n">
-        <v>15.46</v>
+        <v>15.15</v>
       </c>
       <c r="BZ17" s="3" t="n">
-        <v>15.46</v>
+        <v>15.15</v>
       </c>
       <c r="CA17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB17" s="3" t="n"/>
       <c r="CC17" s="3" t="n">
-        <v>4.662</v>
+        <v>4.643</v>
       </c>
       <c r="CD17" s="3" t="n">
-        <v>4.703</v>
+        <v>4.676</v>
       </c>
       <c r="CE17" s="3" t="n">
-        <v>4.662</v>
+        <v>4.635</v>
       </c>
       <c r="CF17" s="3" t="n">
-        <v>4.699</v>
+        <v>4.67</v>
       </c>
       <c r="CG17" s="3" t="n">
-        <v>4.699</v>
+        <v>4.67</v>
       </c>
       <c r="CH17" s="3" t="n">
         <v>0</v>
@@ -1636,11 +1868,11 @@
       </c>
       <c r="CP17" s="3" t="n"/>
       <c r="CQ17" s="4">
-        <f>X17-P17</f>
+        <f>IFERROR(X17-P17,"")</f>
         <v/>
       </c>
       <c r="CR17" s="4">
-        <f>AF17-P17</f>
+        <f>IFERROR(AF17-P17,"")</f>
         <v/>
       </c>
       <c r="CS17" s="6">
@@ -1648,11 +1880,11 @@
         <v/>
       </c>
       <c r="CT17" s="4">
-        <f>AN17-AV17</f>
+        <f>IFERROR(AN17-AV17,"")</f>
         <v/>
       </c>
       <c r="CU17" s="4">
-        <f>BD17-BL17</f>
+        <f>IFERROR(BD17-BL17,"")</f>
         <v/>
       </c>
       <c r="CV17" s="6">
@@ -1660,33 +1892,33 @@
         <v/>
       </c>
       <c r="CW17" s="4">
-        <f>P17-BT17</f>
+        <f>IFERROR(P17-BT17,"")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>771.02</v>
+        <v>775.85</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>773.92</v>
+        <v>776.85</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>769.61</v>
+        <v>769.51</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>773.26</v>
+        <v>769.79</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>773.26</v>
+        <v>769.79</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>43557000</v>
+        <v>44689100</v>
       </c>
       <c r="H18" s="4">
         <f>IF(COUNT(F18:F19)=2,ROUND((F18/F19-1)*100,4),"")</f>
@@ -1694,22 +1926,22 @@
       </c>
       <c r="I18" s="3" t="n"/>
       <c r="J18" s="3" t="n">
+        <v>82.95</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>83.15000000000001</v>
+      </c>
+      <c r="L18" s="3" t="n">
         <v>82.8</v>
       </c>
-      <c r="K18" s="3" t="n">
-        <v>82.84999999999999</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>82.48</v>
-      </c>
       <c r="M18" s="3" t="n">
-        <v>82.76000000000001</v>
+        <v>83</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>82.76000000000001</v>
+        <v>83</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>96118900</v>
+        <v>29465800</v>
       </c>
       <c r="P18" s="4">
         <f>IF(COUNT(N18:N19)=2,ROUND((N18/N19-1)*100,4),"")</f>
@@ -1717,22 +1949,22 @@
       </c>
       <c r="Q18" s="3" t="n"/>
       <c r="R18" s="3" t="n">
-        <v>79.67</v>
+        <v>79.55</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>79.69</v>
+        <v>79.56</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>79.56999999999999</v>
+        <v>79.44</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>79.61</v>
+        <v>79.52</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>79.61</v>
+        <v>79.52</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>23458100</v>
+        <v>25771800</v>
       </c>
       <c r="X18" s="4">
         <f>IF(COUNT(V18:V19)=2,ROUND((V18/V19-1)*100,4),"")</f>
@@ -1740,22 +1972,22 @@
       </c>
       <c r="Y18" s="3" t="n"/>
       <c r="Z18" s="3" t="n">
-        <v>95.84999999999999</v>
+        <v>95.77</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="AB18" s="3" t="n">
-        <v>95.76000000000001</v>
+        <v>95.64</v>
       </c>
       <c r="AC18" s="3" t="n">
-        <v>95.81</v>
+        <v>95.67</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>95.81</v>
+        <v>95.67</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>9024100</v>
+        <v>3009000</v>
       </c>
       <c r="AF18" s="4">
         <f>IF(COUNT(AD18:AD19)=2,ROUND((AD18/AD19-1)*100,4),"")</f>
@@ -1763,22 +1995,22 @@
       </c>
       <c r="AG18" s="3" t="n"/>
       <c r="AH18" s="3" t="n">
-        <v>28.06</v>
+        <v>28.1</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>28.11</v>
+        <v>28.12</v>
       </c>
       <c r="AJ18" s="3" t="n">
-        <v>28.05</v>
+        <v>28.08</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>28.07</v>
+        <v>28.09</v>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>28.07</v>
+        <v>28.09</v>
       </c>
       <c r="AM18" s="3" t="n">
-        <v>1718300</v>
+        <v>2092700</v>
       </c>
       <c r="AN18" s="4">
         <f>IF(COUNT(AL18:AL19)=2,ROUND((AL18/AL19-1)*100,4),"")</f>
@@ -1786,22 +2018,22 @@
       </c>
       <c r="AO18" s="3" t="n"/>
       <c r="AP18" s="3" t="n">
-        <v>399.6</v>
+        <v>384.96</v>
       </c>
       <c r="AQ18" s="3" t="n">
-        <v>400.66</v>
+        <v>391.51</v>
       </c>
       <c r="AR18" s="3" t="n">
-        <v>396.95</v>
+        <v>384.32</v>
       </c>
       <c r="AS18" s="3" t="n">
-        <v>398.47</v>
+        <v>389.64</v>
       </c>
       <c r="AT18" s="3" t="n">
-        <v>398.47</v>
+        <v>389.64</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>13301600</v>
+        <v>14758700</v>
       </c>
       <c r="AV18" s="4">
         <f>IF(COUNT(AT18:AT19)=2,ROUND((AT18/AT19-1)*100,4),"")</f>
@@ -1809,22 +2041,22 @@
       </c>
       <c r="AW18" s="3" t="n"/>
       <c r="AX18" s="3" t="n">
-        <v>187.99</v>
+        <v>187.34</v>
       </c>
       <c r="AY18" s="3" t="n">
-        <v>188.73</v>
+        <v>188.62</v>
       </c>
       <c r="AZ18" s="3" t="n">
-        <v>185.74</v>
+        <v>185.71</v>
       </c>
       <c r="BA18" s="3" t="n">
-        <v>187.97</v>
+        <v>185.91</v>
       </c>
       <c r="BB18" s="3" t="n">
-        <v>187.97</v>
+        <v>185.91</v>
       </c>
       <c r="BC18" s="3" t="n">
-        <v>6357700</v>
+        <v>7571400</v>
       </c>
       <c r="BD18" s="4">
         <f>IF(COUNT(BB18:BB19)=2,ROUND((BB18/BB19-1)*100,4),"")</f>
@@ -1832,22 +2064,22 @@
       </c>
       <c r="BE18" s="3" t="n"/>
       <c r="BF18" s="3" t="n">
-        <v>57.61</v>
+        <v>58.18</v>
       </c>
       <c r="BG18" s="3" t="n">
-        <v>57.79</v>
+        <v>58.41</v>
       </c>
       <c r="BH18" s="3" t="n">
-        <v>57.34</v>
+        <v>57.8</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>57.6</v>
+        <v>58</v>
       </c>
       <c r="BJ18" s="3" t="n">
-        <v>57.6</v>
+        <v>58</v>
       </c>
       <c r="BK18" s="3" t="n">
-        <v>20778200</v>
+        <v>34275600</v>
       </c>
       <c r="BL18" s="4">
         <f>IF(COUNT(BJ18:BJ19)=2,ROUND((BJ18/BJ19-1)*100,4),"")</f>
@@ -1855,22 +2087,22 @@
       </c>
       <c r="BM18" s="3" t="n"/>
       <c r="BN18" s="3" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="BO18" s="3" t="n">
         <v>107.11</v>
       </c>
-      <c r="BO18" s="3" t="n">
-        <v>107.14</v>
-      </c>
       <c r="BP18" s="3" t="n">
-        <v>106.99</v>
+        <v>106.92</v>
       </c>
       <c r="BQ18" s="3" t="n">
-        <v>107.08</v>
+        <v>107</v>
       </c>
       <c r="BR18" s="3" t="n">
-        <v>107.08</v>
+        <v>107</v>
       </c>
       <c r="BS18" s="3" t="n">
-        <v>1146300</v>
+        <v>1768800</v>
       </c>
       <c r="BT18" s="4">
         <f>IF(COUNT(BR18:BR19)=2,ROUND((BR18/BR19-1)*100,4),"")</f>
@@ -1878,38 +2110,38 @@
       </c>
       <c r="BU18" s="3" t="n"/>
       <c r="BV18" s="3" t="n">
-        <v>15.3</v>
+        <v>16.15</v>
       </c>
       <c r="BW18" s="3" t="n">
-        <v>15.36</v>
+        <v>18.43</v>
       </c>
       <c r="BX18" s="3" t="n">
-        <v>14.77</v>
+        <v>15.48</v>
       </c>
       <c r="BY18" s="3" t="n">
-        <v>14.9</v>
+        <v>15.81</v>
       </c>
       <c r="BZ18" s="3" t="n">
-        <v>14.9</v>
+        <v>15.81</v>
       </c>
       <c r="CA18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB18" s="3" t="n"/>
       <c r="CC18" s="3" t="n">
-        <v>4.664</v>
+        <v>4.609</v>
       </c>
       <c r="CD18" s="3" t="n">
-        <v>4.672</v>
+        <v>4.639</v>
       </c>
       <c r="CE18" s="3" t="n">
-        <v>4.603</v>
+        <v>4.607</v>
       </c>
       <c r="CF18" s="3" t="n">
-        <v>4.66</v>
+        <v>4.617</v>
       </c>
       <c r="CG18" s="3" t="n">
-        <v>4.66</v>
+        <v>4.617</v>
       </c>
       <c r="CH18" s="3" t="n">
         <v>0</v>
@@ -1941,11 +2173,11 @@
       </c>
       <c r="CP18" s="3" t="n"/>
       <c r="CQ18" s="4">
-        <f>X18-P18</f>
+        <f>IFERROR(X18-P18,"")</f>
         <v/>
       </c>
       <c r="CR18" s="4">
-        <f>AF18-P18</f>
+        <f>IFERROR(AF18-P18,"")</f>
         <v/>
       </c>
       <c r="CS18" s="6">
@@ -1953,11 +2185,11 @@
         <v/>
       </c>
       <c r="CT18" s="4">
-        <f>AN18-AV18</f>
+        <f>IFERROR(AN18-AV18,"")</f>
         <v/>
       </c>
       <c r="CU18" s="4">
-        <f>BD18-BL18</f>
+        <f>IFERROR(BD18-BL18,"")</f>
         <v/>
       </c>
       <c r="CV18" s="6">
@@ -1965,33 +2197,33 @@
         <v/>
       </c>
       <c r="CW18" s="4">
-        <f>P18-BT18</f>
+        <f>IFERROR(P18-BT18,"")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>770.21</v>
+        <v>760.63</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>771.8200000000001</v>
+        <v>773.41</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>767.46</v>
+        <v>760.52</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>768.5599999999999</v>
+        <v>771.33</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>768.5599999999999</v>
+        <v>771.33</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>38416900</v>
+        <v>69154800</v>
       </c>
       <c r="H19" s="4">
         <f>IF(COUNT(F19:F20)=2,ROUND((F19/F20-1)*100,4),"")</f>
@@ -1999,22 +2231,22 @@
       </c>
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n">
-        <v>82.77</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>82.92</v>
+        <v>82.84</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>82.52</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>82.52</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>27566600</v>
+        <v>38408600</v>
       </c>
       <c r="P19" s="4">
         <f>IF(COUNT(N19:N20)=2,ROUND((N19/N20-1)*100,4),"")</f>
@@ -2022,22 +2254,22 @@
       </c>
       <c r="Q19" s="3" t="n"/>
       <c r="R19" s="3" t="n">
-        <v>79.51000000000001</v>
+        <v>79.37</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>79.51000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>79.41</v>
+        <v>79.37</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>79.45999999999999</v>
+        <v>79.55</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>79.45999999999999</v>
+        <v>79.55</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>25818200</v>
+        <v>46524700</v>
       </c>
       <c r="X19" s="4">
         <f>IF(COUNT(V19:V20)=2,ROUND((V19/V20-1)*100,4),"")</f>
@@ -2045,22 +2277,22 @@
       </c>
       <c r="Y19" s="3" t="n"/>
       <c r="Z19" s="3" t="n">
-        <v>95.7</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="AA19" s="3" t="n">
-        <v>95.73999999999999</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="AB19" s="3" t="n">
-        <v>95.56999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="AC19" s="3" t="n">
-        <v>95.61</v>
+        <v>95.75</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>95.61</v>
+        <v>95.75</v>
       </c>
       <c r="AE19" s="3" t="n">
-        <v>2389400</v>
+        <v>3982700</v>
       </c>
       <c r="AF19" s="4">
         <f>IF(COUNT(AD19:AD20)=2,ROUND((AD19/AD20-1)*100,4),"")</f>
@@ -2068,22 +2300,22 @@
       </c>
       <c r="AG19" s="3" t="n"/>
       <c r="AH19" s="3" t="n">
-        <v>28.12</v>
+        <v>28.16</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>28.2</v>
+        <v>28.17</v>
       </c>
       <c r="AJ19" s="3" t="n">
-        <v>28.11</v>
+        <v>28.13</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>28.19</v>
+        <v>28.16</v>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>28.19</v>
+        <v>28.16</v>
       </c>
       <c r="AM19" s="3" t="n">
-        <v>1666000</v>
+        <v>2144400</v>
       </c>
       <c r="AN19" s="4">
         <f>IF(COUNT(AL19:AL20)=2,ROUND((AL19/AL20-1)*100,4),"")</f>
@@ -2091,22 +2323,22 @@
       </c>
       <c r="AO19" s="3" t="n"/>
       <c r="AP19" s="3" t="n">
-        <v>389.5</v>
+        <v>374.14</v>
       </c>
       <c r="AQ19" s="3" t="n">
-        <v>392.12</v>
+        <v>376.69</v>
       </c>
       <c r="AR19" s="3" t="n">
-        <v>387.27</v>
+        <v>373.71</v>
       </c>
       <c r="AS19" s="3" t="n">
-        <v>389.67</v>
+        <v>374.16</v>
       </c>
       <c r="AT19" s="3" t="n">
-        <v>389.67</v>
+        <v>374.16</v>
       </c>
       <c r="AU19" s="3" t="n">
-        <v>10954300</v>
+        <v>5723100</v>
       </c>
       <c r="AV19" s="4">
         <f>IF(COUNT(AT19:AT20)=2,ROUND((AT19/AT20-1)*100,4),"")</f>
@@ -2114,22 +2346,22 @@
       </c>
       <c r="AW19" s="3" t="n"/>
       <c r="AX19" s="3" t="n">
-        <v>183.19</v>
+        <v>182.52</v>
       </c>
       <c r="AY19" s="3" t="n">
-        <v>186.91</v>
+        <v>187.71</v>
       </c>
       <c r="AZ19" s="3" t="n">
-        <v>182.06</v>
+        <v>181.87</v>
       </c>
       <c r="BA19" s="3" t="n">
-        <v>185.33</v>
+        <v>186.9</v>
       </c>
       <c r="BB19" s="3" t="n">
-        <v>185.33</v>
+        <v>186.9</v>
       </c>
       <c r="BC19" s="3" t="n">
-        <v>6706000</v>
+        <v>13495800</v>
       </c>
       <c r="BD19" s="4">
         <f>IF(COUNT(BB19:BB20)=2,ROUND((BB19/BB20-1)*100,4),"")</f>
@@ -2137,22 +2369,22 @@
       </c>
       <c r="BE19" s="3" t="n"/>
       <c r="BF19" s="3" t="n">
-        <v>58.38</v>
+        <v>57.22</v>
       </c>
       <c r="BG19" s="3" t="n">
-        <v>58.38</v>
+        <v>58.02</v>
       </c>
       <c r="BH19" s="3" t="n">
-        <v>57.59</v>
+        <v>57.19</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>57.81</v>
+        <v>57.88</v>
       </c>
       <c r="BJ19" s="3" t="n">
-        <v>57.81</v>
+        <v>57.88</v>
       </c>
       <c r="BK19" s="3" t="n">
-        <v>27704200</v>
+        <v>31466100</v>
       </c>
       <c r="BL19" s="4">
         <f>IF(COUNT(BJ19:BJ20)=2,ROUND((BJ19/BJ20-1)*100,4),"")</f>
@@ -2160,22 +2392,22 @@
       </c>
       <c r="BM19" s="3" t="n"/>
       <c r="BN19" s="3" t="n">
-        <v>106.94</v>
+        <v>107.1</v>
       </c>
       <c r="BO19" s="3" t="n">
-        <v>106.97</v>
+        <v>107.13</v>
       </c>
       <c r="BP19" s="3" t="n">
-        <v>106.8</v>
+        <v>106.99</v>
       </c>
       <c r="BQ19" s="3" t="n">
-        <v>106.87</v>
+        <v>107.05</v>
       </c>
       <c r="BR19" s="3" t="n">
-        <v>106.87</v>
+        <v>107.05</v>
       </c>
       <c r="BS19" s="3" t="n">
-        <v>1962900</v>
+        <v>2324900</v>
       </c>
       <c r="BT19" s="4">
         <f>IF(COUNT(BR19:BR20)=2,ROUND((BR19/BR20-1)*100,4),"")</f>
@@ -2183,38 +2415,38 @@
       </c>
       <c r="BU19" s="3" t="n"/>
       <c r="BV19" s="3" t="n">
-        <v>15.83</v>
+        <v>15.76</v>
       </c>
       <c r="BW19" s="3" t="n">
-        <v>16.03</v>
+        <v>16.65</v>
       </c>
       <c r="BX19" s="3" t="n">
-        <v>15.11</v>
+        <v>15.51</v>
       </c>
       <c r="BY19" s="3" t="n">
-        <v>15.15</v>
+        <v>16.5</v>
       </c>
       <c r="BZ19" s="3" t="n">
-        <v>15.15</v>
+        <v>16.5</v>
       </c>
       <c r="CA19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB19" s="3" t="n"/>
       <c r="CC19" s="3" t="n">
-        <v>4.643</v>
+        <v>4.665</v>
       </c>
       <c r="CD19" s="3" t="n">
-        <v>4.676</v>
+        <v>4.668</v>
       </c>
       <c r="CE19" s="3" t="n">
-        <v>4.635</v>
+        <v>4.619</v>
       </c>
       <c r="CF19" s="3" t="n">
-        <v>4.67</v>
+        <v>4.627</v>
       </c>
       <c r="CG19" s="3" t="n">
-        <v>4.67</v>
+        <v>4.627</v>
       </c>
       <c r="CH19" s="3" t="n">
         <v>0</v>
@@ -2246,11 +2478,11 @@
       </c>
       <c r="CP19" s="3" t="n"/>
       <c r="CQ19" s="4">
-        <f>X19-P19</f>
+        <f>IFERROR(X19-P19,"")</f>
         <v/>
       </c>
       <c r="CR19" s="4">
-        <f>AF19-P19</f>
+        <f>IFERROR(AF19-P19,"")</f>
         <v/>
       </c>
       <c r="CS19" s="6">
@@ -2258,11 +2490,11 @@
         <v/>
       </c>
       <c r="CT19" s="4">
-        <f>AN19-AV19</f>
+        <f>IFERROR(AN19-AV19,"")</f>
         <v/>
       </c>
       <c r="CU19" s="4">
-        <f>BD19-BL19</f>
+        <f>IFERROR(BD19-BL19,"")</f>
         <v/>
       </c>
       <c r="CV19" s="6">
@@ -2270,33 +2502,33 @@
         <v/>
       </c>
       <c r="CW19" s="4">
-        <f>P19-BT19</f>
+        <f>IFERROR(P19-BT19,"")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>775.85</v>
+        <v>749.4400000000001</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>776.85</v>
+        <v>758.58</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>769.51</v>
+        <v>748.8</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>769.79</v>
+        <v>757.67</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>769.79</v>
+        <v>757.67</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>44689100</v>
+        <v>59927500</v>
       </c>
       <c r="H20" s="4">
         <f>IF(COUNT(F20:F21)=2,ROUND((F20/F21-1)*100,4),"")</f>
@@ -2304,22 +2536,22 @@
       </c>
       <c r="I20" s="3" t="n"/>
       <c r="J20" s="3" t="n">
-        <v>82.95</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>83.15000000000001</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>82.8</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>83</v>
+        <v>82.19</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>83</v>
+        <v>82.19</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>29465800</v>
+        <v>32050800</v>
       </c>
       <c r="P20" s="4">
         <f>IF(COUNT(N20:N21)=2,ROUND((N20/N21-1)*100,4),"")</f>
@@ -2327,22 +2559,22 @@
       </c>
       <c r="Q20" s="3" t="n"/>
       <c r="R20" s="3" t="n">
-        <v>79.55</v>
+        <v>79.25</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>79.56</v>
+        <v>79.33</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>79.44</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>79.52</v>
+        <v>79.31</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>79.52</v>
+        <v>79.31</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>25771800</v>
+        <v>30860100</v>
       </c>
       <c r="X20" s="4">
         <f>IF(COUNT(V20:V21)=2,ROUND((V20/V21-1)*100,4),"")</f>
@@ -2350,22 +2582,22 @@
       </c>
       <c r="Y20" s="3" t="n"/>
       <c r="Z20" s="3" t="n">
-        <v>95.77</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="AA20" s="3" t="n">
-        <v>95.79000000000001</v>
+        <v>95.47</v>
       </c>
       <c r="AB20" s="3" t="n">
-        <v>95.64</v>
+        <v>95.23</v>
       </c>
       <c r="AC20" s="3" t="n">
-        <v>95.67</v>
+        <v>95.45</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>95.67</v>
+        <v>95.45</v>
       </c>
       <c r="AE20" s="3" t="n">
-        <v>3009000</v>
+        <v>3460600</v>
       </c>
       <c r="AF20" s="4">
         <f>IF(COUNT(AD20:AD21)=2,ROUND((AD20/AD21-1)*100,4),"")</f>
@@ -2373,22 +2605,22 @@
       </c>
       <c r="AG20" s="3" t="n"/>
       <c r="AH20" s="3" t="n">
-        <v>28.1</v>
+        <v>28.11</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>28.12</v>
+        <v>28.19</v>
       </c>
       <c r="AJ20" s="3" t="n">
-        <v>28.08</v>
+        <v>28.11</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>28.09</v>
+        <v>28.17</v>
       </c>
       <c r="AL20" s="3" t="n">
-        <v>28.09</v>
+        <v>28.17</v>
       </c>
       <c r="AM20" s="3" t="n">
-        <v>2092700</v>
+        <v>2506000</v>
       </c>
       <c r="AN20" s="4">
         <f>IF(COUNT(AL20:AL21)=2,ROUND((AL20/AL21-1)*100,4),"")</f>
@@ -2396,22 +2628,22 @@
       </c>
       <c r="AO20" s="3" t="n"/>
       <c r="AP20" s="3" t="n">
-        <v>384.96</v>
+        <v>370.1</v>
       </c>
       <c r="AQ20" s="3" t="n">
-        <v>391.51</v>
+        <v>372.04</v>
       </c>
       <c r="AR20" s="3" t="n">
-        <v>384.32</v>
+        <v>368.64</v>
       </c>
       <c r="AS20" s="3" t="n">
-        <v>389.64</v>
+        <v>371.71</v>
       </c>
       <c r="AT20" s="3" t="n">
-        <v>389.64</v>
+        <v>371.71</v>
       </c>
       <c r="AU20" s="3" t="n">
-        <v>14758700</v>
+        <v>4968900</v>
       </c>
       <c r="AV20" s="4">
         <f>IF(COUNT(AT20:AT21)=2,ROUND((AT20/AT21-1)*100,4),"")</f>
@@ -2419,22 +2651,22 @@
       </c>
       <c r="AW20" s="3" t="n"/>
       <c r="AX20" s="3" t="n">
-        <v>187.34</v>
+        <v>174.01</v>
       </c>
       <c r="AY20" s="3" t="n">
-        <v>188.62</v>
+        <v>178.92</v>
       </c>
       <c r="AZ20" s="3" t="n">
-        <v>185.71</v>
+        <v>173.04</v>
       </c>
       <c r="BA20" s="3" t="n">
-        <v>185.91</v>
+        <v>178.04</v>
       </c>
       <c r="BB20" s="3" t="n">
-        <v>185.91</v>
+        <v>178.04</v>
       </c>
       <c r="BC20" s="3" t="n">
-        <v>7571400</v>
+        <v>9343400</v>
       </c>
       <c r="BD20" s="4">
         <f>IF(COUNT(BB20:BB21)=2,ROUND((BB20/BB21-1)*100,4),"")</f>
@@ -2442,22 +2674,22 @@
       </c>
       <c r="BE20" s="3" t="n"/>
       <c r="BF20" s="3" t="n">
-        <v>58.18</v>
+        <v>57.29</v>
       </c>
       <c r="BG20" s="3" t="n">
-        <v>58.41</v>
+        <v>57.55</v>
       </c>
       <c r="BH20" s="3" t="n">
-        <v>57.8</v>
+        <v>57</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>58</v>
+        <v>57.38</v>
       </c>
       <c r="BJ20" s="3" t="n">
-        <v>58</v>
+        <v>57.38</v>
       </c>
       <c r="BK20" s="3" t="n">
-        <v>34275600</v>
+        <v>31019400</v>
       </c>
       <c r="BL20" s="4">
         <f>IF(COUNT(BJ20:BJ21)=2,ROUND((BJ20/BJ21-1)*100,4),"")</f>
@@ -2465,22 +2697,22 @@
       </c>
       <c r="BM20" s="3" t="n"/>
       <c r="BN20" s="3" t="n">
-        <v>107.05</v>
+        <v>106.89</v>
       </c>
       <c r="BO20" s="3" t="n">
-        <v>107.11</v>
+        <v>106.97</v>
       </c>
       <c r="BP20" s="3" t="n">
-        <v>106.92</v>
+        <v>106.76</v>
       </c>
       <c r="BQ20" s="3" t="n">
-        <v>107</v>
+        <v>106.86</v>
       </c>
       <c r="BR20" s="3" t="n">
-        <v>107</v>
+        <v>106.86</v>
       </c>
       <c r="BS20" s="3" t="n">
-        <v>1768800</v>
+        <v>2609900</v>
       </c>
       <c r="BT20" s="4">
         <f>IF(COUNT(BR20:BR21)=2,ROUND((BR20/BR21-1)*100,4),"")</f>
@@ -2488,38 +2720,38 @@
       </c>
       <c r="BU20" s="3" t="n"/>
       <c r="BV20" s="3" t="n">
-        <v>16.15</v>
+        <v>16.03</v>
       </c>
       <c r="BW20" s="3" t="n">
-        <v>18.43</v>
+        <v>16.3</v>
       </c>
       <c r="BX20" s="3" t="n">
-        <v>15.48</v>
+        <v>15.54</v>
       </c>
       <c r="BY20" s="3" t="n">
-        <v>15.81</v>
+        <v>15.86</v>
       </c>
       <c r="BZ20" s="3" t="n">
-        <v>15.81</v>
+        <v>15.86</v>
       </c>
       <c r="CA20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB20" s="3" t="n"/>
       <c r="CC20" s="3" t="n">
-        <v>4.609</v>
+        <v>4.671</v>
       </c>
       <c r="CD20" s="3" t="n">
-        <v>4.639</v>
+        <v>4.702</v>
       </c>
       <c r="CE20" s="3" t="n">
-        <v>4.607</v>
+        <v>4.671</v>
       </c>
       <c r="CF20" s="3" t="n">
-        <v>4.617</v>
+        <v>4.686</v>
       </c>
       <c r="CG20" s="3" t="n">
-        <v>4.617</v>
+        <v>4.686</v>
       </c>
       <c r="CH20" s="3" t="n">
         <v>0</v>
@@ -2551,11 +2783,11 @@
       </c>
       <c r="CP20" s="3" t="n"/>
       <c r="CQ20" s="4">
-        <f>X20-P20</f>
+        <f>IFERROR(X20-P20,"")</f>
         <v/>
       </c>
       <c r="CR20" s="4">
-        <f>AF20-P20</f>
+        <f>IFERROR(AF20-P20,"")</f>
         <v/>
       </c>
       <c r="CS20" s="6">
@@ -2563,11 +2795,11 @@
         <v/>
       </c>
       <c r="CT20" s="4">
-        <f>AN20-AV20</f>
+        <f>IFERROR(AN20-AV20,"")</f>
         <v/>
       </c>
       <c r="CU20" s="4">
-        <f>BD20-BL20</f>
+        <f>IFERROR(BD20-BL20,"")</f>
         <v/>
       </c>
       <c r="CV20" s="6">
@@ -2575,33 +2807,33 @@
         <v/>
       </c>
       <c r="CW20" s="4">
-        <f>P20-BT20</f>
+        <f>IFERROR(P20-BT20,"")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>760.63</v>
+        <v>744.6799999999999</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>773.41</v>
+        <v>748.9</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>760.52</v>
+        <v>737.6799999999999</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>771.33</v>
+        <v>747.03</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>771.33</v>
+        <v>747.03</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>69154800</v>
+        <v>62445900</v>
       </c>
       <c r="H21" s="4">
         <f>IF(COUNT(F21:F22)=2,ROUND((F21/F22-1)*100,4),"")</f>
@@ -2609,22 +2841,22 @@
       </c>
       <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n">
-        <v>82.65000000000001</v>
+        <v>82.45</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>82.84</v>
+        <v>82.45</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>82.56999999999999</v>
+        <v>81.89</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>82.81999999999999</v>
+        <v>82.25</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>82.81999999999999</v>
+        <v>81.92</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>38408600</v>
+        <v>50359800</v>
       </c>
       <c r="P21" s="4">
         <f>IF(COUNT(N21:N22)=2,ROUND((N21/N22-1)*100,4),"")</f>
@@ -2632,22 +2864,22 @@
       </c>
       <c r="Q21" s="3" t="n"/>
       <c r="R21" s="3" t="n">
-        <v>79.37</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>79.37</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>79.55</v>
+        <v>79.48</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>79.55</v>
+        <v>79.096</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>46524700</v>
+        <v>38659800</v>
       </c>
       <c r="X21" s="4">
         <f>IF(COUNT(V21:V22)=2,ROUND((V21/V22-1)*100,4),"")</f>
@@ -2655,22 +2887,22 @@
       </c>
       <c r="Y21" s="3" t="n"/>
       <c r="Z21" s="3" t="n">
-        <v>95.48999999999999</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>95.81999999999999</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="AB21" s="3" t="n">
-        <v>95.45</v>
+        <v>95.37</v>
       </c>
       <c r="AC21" s="3" t="n">
-        <v>95.75</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>95.75</v>
+        <v>95.15300000000001</v>
       </c>
       <c r="AE21" s="3" t="n">
-        <v>3982700</v>
+        <v>4787100</v>
       </c>
       <c r="AF21" s="4">
         <f>IF(COUNT(AD21:AD22)=2,ROUND((AD21/AD22-1)*100,4),"")</f>
@@ -2678,22 +2910,22 @@
       </c>
       <c r="AG21" s="3" t="n"/>
       <c r="AH21" s="3" t="n">
-        <v>28.16</v>
+        <v>28.24</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>28.17</v>
+        <v>28.31</v>
       </c>
       <c r="AJ21" s="3" t="n">
         <v>28.13</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>28.16</v>
+        <v>28.17</v>
       </c>
       <c r="AL21" s="3" t="n">
-        <v>28.16</v>
+        <v>28.17</v>
       </c>
       <c r="AM21" s="3" t="n">
-        <v>2144400</v>
+        <v>2731200</v>
       </c>
       <c r="AN21" s="4">
         <f>IF(COUNT(AL21:AL22)=2,ROUND((AL21/AL22-1)*100,4),"")</f>
@@ -2701,22 +2933,22 @@
       </c>
       <c r="AO21" s="3" t="n"/>
       <c r="AP21" s="3" t="n">
-        <v>374.14</v>
+        <v>370.84</v>
       </c>
       <c r="AQ21" s="3" t="n">
-        <v>376.69</v>
+        <v>372.01</v>
       </c>
       <c r="AR21" s="3" t="n">
-        <v>373.71</v>
+        <v>368.82</v>
       </c>
       <c r="AS21" s="3" t="n">
-        <v>374.16</v>
+        <v>371.54</v>
       </c>
       <c r="AT21" s="3" t="n">
-        <v>374.16</v>
+        <v>371.54</v>
       </c>
       <c r="AU21" s="3" t="n">
-        <v>5723100</v>
+        <v>6825900</v>
       </c>
       <c r="AV21" s="4">
         <f>IF(COUNT(AT21:AT22)=2,ROUND((AT21/AT22-1)*100,4),"")</f>
@@ -2724,22 +2956,22 @@
       </c>
       <c r="AW21" s="3" t="n"/>
       <c r="AX21" s="3" t="n">
-        <v>182.52</v>
+        <v>177.46</v>
       </c>
       <c r="AY21" s="3" t="n">
-        <v>187.71</v>
+        <v>178.62</v>
       </c>
       <c r="AZ21" s="3" t="n">
-        <v>181.87</v>
+        <v>172.7</v>
       </c>
       <c r="BA21" s="3" t="n">
-        <v>186.9</v>
+        <v>175.35</v>
       </c>
       <c r="BB21" s="3" t="n">
-        <v>186.9</v>
+        <v>175.35</v>
       </c>
       <c r="BC21" s="3" t="n">
-        <v>13495800</v>
+        <v>9146200</v>
       </c>
       <c r="BD21" s="4">
         <f>IF(COUNT(BB21:BB22)=2,ROUND((BB21/BB22-1)*100,4),"")</f>
@@ -2747,22 +2979,22 @@
       </c>
       <c r="BE21" s="3" t="n"/>
       <c r="BF21" s="3" t="n">
-        <v>57.22</v>
+        <v>56.81</v>
       </c>
       <c r="BG21" s="3" t="n">
-        <v>58.02</v>
+        <v>57.12</v>
       </c>
       <c r="BH21" s="3" t="n">
-        <v>57.19</v>
+        <v>56.69</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>57.88</v>
+        <v>56.94</v>
       </c>
       <c r="BJ21" s="3" t="n">
-        <v>57.88</v>
+        <v>56.94</v>
       </c>
       <c r="BK21" s="3" t="n">
-        <v>31466100</v>
+        <v>32543500</v>
       </c>
       <c r="BL21" s="4">
         <f>IF(COUNT(BJ21:BJ22)=2,ROUND((BJ21/BJ22-1)*100,4),"")</f>
@@ -2770,22 +3002,22 @@
       </c>
       <c r="BM21" s="3" t="n"/>
       <c r="BN21" s="3" t="n">
-        <v>107.1</v>
+        <v>107.55</v>
       </c>
       <c r="BO21" s="3" t="n">
-        <v>107.13</v>
+        <v>107.63</v>
       </c>
       <c r="BP21" s="3" t="n">
-        <v>106.99</v>
+        <v>107.34</v>
       </c>
       <c r="BQ21" s="3" t="n">
-        <v>107.05</v>
+        <v>107.63</v>
       </c>
       <c r="BR21" s="3" t="n">
-        <v>107.05</v>
+        <v>106.846</v>
       </c>
       <c r="BS21" s="3" t="n">
-        <v>2324900</v>
+        <v>3868300</v>
       </c>
       <c r="BT21" s="4">
         <f>IF(COUNT(BR21:BR22)=2,ROUND((BR21/BR22-1)*100,4),"")</f>
@@ -2793,38 +3025,38 @@
       </c>
       <c r="BU21" s="3" t="n"/>
       <c r="BV21" s="3" t="n">
-        <v>15.76</v>
+        <v>16.82</v>
       </c>
       <c r="BW21" s="3" t="n">
-        <v>16.65</v>
+        <v>18.7</v>
       </c>
       <c r="BX21" s="3" t="n">
-        <v>15.51</v>
+        <v>15.82</v>
       </c>
       <c r="BY21" s="3" t="n">
-        <v>16.5</v>
+        <v>15.99</v>
       </c>
       <c r="BZ21" s="3" t="n">
-        <v>16.5</v>
+        <v>15.99</v>
       </c>
       <c r="CA21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB21" s="3" t="n"/>
       <c r="CC21" s="3" t="n">
-        <v>4.665</v>
+        <v>4.684</v>
       </c>
       <c r="CD21" s="3" t="n">
-        <v>4.668</v>
+        <v>4.747</v>
       </c>
       <c r="CE21" s="3" t="n">
-        <v>4.619</v>
+        <v>4.682</v>
       </c>
       <c r="CF21" s="3" t="n">
-        <v>4.627</v>
+        <v>4.745</v>
       </c>
       <c r="CG21" s="3" t="n">
-        <v>4.627</v>
+        <v>4.745</v>
       </c>
       <c r="CH21" s="3" t="n">
         <v>0</v>
@@ -2856,11 +3088,11 @@
       </c>
       <c r="CP21" s="3" t="n"/>
       <c r="CQ21" s="4">
-        <f>X21-P21</f>
+        <f>IFERROR(X21-P21,"")</f>
         <v/>
       </c>
       <c r="CR21" s="4">
-        <f>AF21-P21</f>
+        <f>IFERROR(AF21-P21,"")</f>
         <v/>
       </c>
       <c r="CS21" s="6">
@@ -2868,11 +3100,11 @@
         <v/>
       </c>
       <c r="CT21" s="4">
-        <f>AN21-AV21</f>
+        <f>IFERROR(AN21-AV21,"")</f>
         <v/>
       </c>
       <c r="CU21" s="4">
-        <f>BD21-BL21</f>
+        <f>IFERROR(BD21-BL21,"")</f>
         <v/>
       </c>
       <c r="CV21" s="6">
@@ -2880,33 +3112,33 @@
         <v/>
       </c>
       <c r="CW21" s="4">
-        <f>P21-BT21</f>
+        <f>IFERROR(P21-BT21,"")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>749.4400000000001</v>
+        <v>736.05</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>758.58</v>
+        <v>742.45</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>748.8</v>
+        <v>734.59</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>757.67</v>
+        <v>741.6900000000001</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>757.67</v>
+        <v>741.6900000000001</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>59927500</v>
+        <v>66811300</v>
       </c>
       <c r="H22" s="4">
         <f>IF(COUNT(F22:F23)=2,ROUND((F22/F23-1)*100,4),"")</f>
@@ -2914,22 +3146,22 @@
       </c>
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n">
-        <v>82.23999999999999</v>
+        <v>82.81</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>82.34999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>82.01000000000001</v>
+        <v>82.52</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>82.19</v>
+        <v>82.8</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>82.19</v>
+        <v>82.4678</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>32050800</v>
+        <v>40407300</v>
       </c>
       <c r="P22" s="4">
         <f>IF(COUNT(N22:N23)=2,ROUND((N22/N23-1)*100,4),"")</f>
@@ -2937,22 +3169,22 @@
       </c>
       <c r="Q22" s="3" t="n"/>
       <c r="R22" s="3" t="n">
-        <v>79.25</v>
+        <v>79.38</v>
       </c>
       <c r="S22" s="3" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="T22" s="3" t="n">
         <v>79.33</v>
       </c>
-      <c r="T22" s="3" t="n">
-        <v>79.15000000000001</v>
-      </c>
       <c r="U22" s="3" t="n">
-        <v>79.31</v>
+        <v>79.47</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>79.31</v>
+        <v>79.086</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>30860100</v>
+        <v>30570700</v>
       </c>
       <c r="X22" s="4">
         <f>IF(COUNT(V22:V23)=2,ROUND((V22/V23-1)*100,4),"")</f>
@@ -2960,22 +3192,22 @@
       </c>
       <c r="Y22" s="3" t="n"/>
       <c r="Z22" s="3" t="n">
-        <v>95.29000000000001</v>
+        <v>95.52</v>
       </c>
       <c r="AA22" s="3" t="n">
-        <v>95.47</v>
+        <v>95.7</v>
       </c>
       <c r="AB22" s="3" t="n">
-        <v>95.23</v>
+        <v>95.52</v>
       </c>
       <c r="AC22" s="3" t="n">
-        <v>95.45</v>
+        <v>95.66</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>95.45</v>
+        <v>95.1331</v>
       </c>
       <c r="AE22" s="3" t="n">
-        <v>3460600</v>
+        <v>3477300</v>
       </c>
       <c r="AF22" s="4">
         <f>IF(COUNT(AD22:AD23)=2,ROUND((AD22/AD23-1)*100,4),"")</f>
@@ -2983,22 +3215,22 @@
       </c>
       <c r="AG22" s="3" t="n"/>
       <c r="AH22" s="3" t="n">
-        <v>28.11</v>
+        <v>28.36</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>28.19</v>
+        <v>28.36</v>
       </c>
       <c r="AJ22" s="3" t="n">
-        <v>28.11</v>
+        <v>28.12</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>28.17</v>
+        <v>28.14</v>
       </c>
       <c r="AL22" s="3" t="n">
-        <v>28.17</v>
+        <v>28.14</v>
       </c>
       <c r="AM22" s="3" t="n">
-        <v>2506000</v>
+        <v>4809000</v>
       </c>
       <c r="AN22" s="4">
         <f>IF(COUNT(AL22:AL23)=2,ROUND((AL22/AL23-1)*100,4),"")</f>
@@ -3006,22 +3238,22 @@
       </c>
       <c r="AO22" s="3" t="n"/>
       <c r="AP22" s="3" t="n">
-        <v>370.1</v>
+        <v>374.16</v>
       </c>
       <c r="AQ22" s="3" t="n">
-        <v>372.04</v>
+        <v>377.86</v>
       </c>
       <c r="AR22" s="3" t="n">
-        <v>368.64</v>
+        <v>373.76</v>
       </c>
       <c r="AS22" s="3" t="n">
-        <v>371.71</v>
+        <v>377.16</v>
       </c>
       <c r="AT22" s="3" t="n">
-        <v>371.71</v>
+        <v>377.16</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>4968900</v>
+        <v>5968400</v>
       </c>
       <c r="AV22" s="4">
         <f>IF(COUNT(AT22:AT23)=2,ROUND((AT22/AT23-1)*100,4),"")</f>
@@ -3029,22 +3261,22 @@
       </c>
       <c r="AW22" s="3" t="n"/>
       <c r="AX22" s="3" t="n">
-        <v>174.01</v>
+        <v>172.81</v>
       </c>
       <c r="AY22" s="3" t="n">
-        <v>178.92</v>
+        <v>176.09</v>
       </c>
       <c r="AZ22" s="3" t="n">
-        <v>173.04</v>
+        <v>172.16</v>
       </c>
       <c r="BA22" s="3" t="n">
-        <v>178.04</v>
+        <v>175.73</v>
       </c>
       <c r="BB22" s="3" t="n">
-        <v>178.04</v>
+        <v>175.73</v>
       </c>
       <c r="BC22" s="3" t="n">
-        <v>9343400</v>
+        <v>15098400</v>
       </c>
       <c r="BD22" s="4">
         <f>IF(COUNT(BB22:BB23)=2,ROUND((BB22/BB23-1)*100,4),"")</f>
@@ -3052,22 +3284,22 @@
       </c>
       <c r="BE22" s="3" t="n"/>
       <c r="BF22" s="3" t="n">
-        <v>57.29</v>
+        <v>56.82</v>
       </c>
       <c r="BG22" s="3" t="n">
-        <v>57.55</v>
+        <v>57.05</v>
       </c>
       <c r="BH22" s="3" t="n">
+        <v>56.18</v>
+      </c>
+      <c r="BI22" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="BI22" s="3" t="n">
-        <v>57.38</v>
-      </c>
       <c r="BJ22" s="3" t="n">
-        <v>57.38</v>
+        <v>57</v>
       </c>
       <c r="BK22" s="3" t="n">
-        <v>31019400</v>
+        <v>33184200</v>
       </c>
       <c r="BL22" s="4">
         <f>IF(COUNT(BJ22:BJ23)=2,ROUND((BJ22/BJ23-1)*100,4),"")</f>
@@ -3075,22 +3307,22 @@
       </c>
       <c r="BM22" s="3" t="n"/>
       <c r="BN22" s="3" t="n">
-        <v>106.89</v>
+        <v>107.83</v>
       </c>
       <c r="BO22" s="3" t="n">
-        <v>106.97</v>
+        <v>107.89</v>
       </c>
       <c r="BP22" s="3" t="n">
-        <v>106.76</v>
+        <v>107.67</v>
       </c>
       <c r="BQ22" s="3" t="n">
-        <v>106.86</v>
+        <v>107.74</v>
       </c>
       <c r="BR22" s="3" t="n">
-        <v>106.86</v>
+        <v>106.9552</v>
       </c>
       <c r="BS22" s="3" t="n">
-        <v>2609900</v>
+        <v>2203000</v>
       </c>
       <c r="BT22" s="4">
         <f>IF(COUNT(BR22:BR23)=2,ROUND((BR22/BR23-1)*100,4),"")</f>
@@ -3098,38 +3330,38 @@
       </c>
       <c r="BU22" s="3" t="n"/>
       <c r="BV22" s="3" t="n">
-        <v>16.03</v>
+        <v>19.56</v>
       </c>
       <c r="BW22" s="3" t="n">
-        <v>16.3</v>
+        <v>20.08</v>
       </c>
       <c r="BX22" s="3" t="n">
-        <v>15.54</v>
+        <v>17</v>
       </c>
       <c r="BY22" s="3" t="n">
-        <v>15.86</v>
+        <v>17.09</v>
       </c>
       <c r="BZ22" s="3" t="n">
-        <v>15.86</v>
+        <v>17.09</v>
       </c>
       <c r="CA22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB22" s="3" t="n"/>
       <c r="CC22" s="3" t="n">
-        <v>4.671</v>
+        <v>4.669</v>
       </c>
       <c r="CD22" s="3" t="n">
-        <v>4.702</v>
+        <v>4.686</v>
       </c>
       <c r="CE22" s="3" t="n">
-        <v>4.671</v>
+        <v>4.651</v>
       </c>
       <c r="CF22" s="3" t="n">
-        <v>4.686</v>
+        <v>4.663</v>
       </c>
       <c r="CG22" s="3" t="n">
-        <v>4.686</v>
+        <v>4.663</v>
       </c>
       <c r="CH22" s="3" t="n">
         <v>0</v>
@@ -3161,11 +3393,11 @@
       </c>
       <c r="CP22" s="3" t="n"/>
       <c r="CQ22" s="4">
-        <f>X22-P22</f>
+        <f>IFERROR(X22-P22,"")</f>
         <v/>
       </c>
       <c r="CR22" s="4">
-        <f>AF22-P22</f>
+        <f>IFERROR(AF22-P22,"")</f>
         <v/>
       </c>
       <c r="CS22" s="6">
@@ -3173,11 +3405,11 @@
         <v/>
       </c>
       <c r="CT22" s="4">
-        <f>AN22-AV22</f>
+        <f>IFERROR(AN22-AV22,"")</f>
         <v/>
       </c>
       <c r="CU22" s="4">
-        <f>BD22-BL22</f>
+        <f>IFERROR(BD22-BL22,"")</f>
         <v/>
       </c>
       <c r="CV22" s="6">
@@ -3185,33 +3417,33 @@
         <v/>
       </c>
       <c r="CW22" s="4">
-        <f>P22-BT22</f>
+        <f>IFERROR(P22-BT22,"")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026/07/31</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>744.6799999999999</v>
+        <v>739.97</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>748.9</v>
+        <v>742.6799999999999</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>737.6799999999999</v>
+        <v>729.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>747.03</v>
+        <v>729.46</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>747.03</v>
+        <v>729.46</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>62445900</v>
+        <v>70697200</v>
       </c>
       <c r="H23" s="4">
         <f>IF(COUNT(F23:F24)=2,ROUND((F23/F24-1)*100,4),"")</f>
@@ -3219,22 +3451,22 @@
       </c>
       <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n">
-        <v>82.45</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>82.45</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>81.89</v>
+        <v>82.7</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>82.25</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>81.92</v>
+        <v>82.5176</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>50359800</v>
+        <v>41445200</v>
       </c>
       <c r="P23" s="4">
         <f>IF(COUNT(N23:N24)=2,ROUND((N23/N24-1)*100,4),"")</f>
@@ -3242,22 +3474,22 @@
       </c>
       <c r="Q23" s="3" t="n"/>
       <c r="R23" s="3" t="n">
-        <v>79.45999999999999</v>
+        <v>79.37</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>79.54000000000001</v>
+        <v>79.48</v>
       </c>
       <c r="T23" s="3" t="n">
+        <v>79.14</v>
+      </c>
+      <c r="U23" s="3" t="n">
         <v>79.23999999999999</v>
       </c>
-      <c r="U23" s="3" t="n">
-        <v>79.48</v>
-      </c>
       <c r="V23" s="3" t="n">
-        <v>79.096</v>
+        <v>78.85720000000001</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>38659800</v>
+        <v>53074500</v>
       </c>
       <c r="X23" s="4">
         <f>IF(COUNT(V23:V24)=2,ROUND((V23/V24-1)*100,4),"")</f>
@@ -3265,22 +3497,22 @@
       </c>
       <c r="Y23" s="3" t="n"/>
       <c r="Z23" s="3" t="n">
-        <v>95.65000000000001</v>
+        <v>95.58</v>
       </c>
       <c r="AA23" s="3" t="n">
-        <v>95.76000000000001</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="AB23" s="3" t="n">
-        <v>95.37</v>
+        <v>95.28</v>
       </c>
       <c r="AC23" s="3" t="n">
-        <v>95.68000000000001</v>
+        <v>95.39</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>95.15300000000001</v>
+        <v>94.8646</v>
       </c>
       <c r="AE23" s="3" t="n">
-        <v>4787100</v>
+        <v>2210500</v>
       </c>
       <c r="AF23" s="4">
         <f>IF(COUNT(AD23:AD24)=2,ROUND((AD23/AD24-1)*100,4),"")</f>
@@ -3288,22 +3520,22 @@
       </c>
       <c r="AG23" s="3" t="n"/>
       <c r="AH23" s="3" t="n">
-        <v>28.24</v>
+        <v>28.57</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>28.31</v>
+        <v>28.59</v>
       </c>
       <c r="AJ23" s="3" t="n">
-        <v>28.13</v>
+        <v>28.3</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>28.17</v>
+        <v>28.42</v>
       </c>
       <c r="AL23" s="3" t="n">
-        <v>28.17</v>
+        <v>28.42</v>
       </c>
       <c r="AM23" s="3" t="n">
-        <v>2731200</v>
+        <v>2286600</v>
       </c>
       <c r="AN23" s="4">
         <f>IF(COUNT(AL23:AL24)=2,ROUND((AL23/AL24-1)*100,4),"")</f>
@@ -3311,22 +3543,22 @@
       </c>
       <c r="AO23" s="3" t="n"/>
       <c r="AP23" s="3" t="n">
-        <v>370.84</v>
+        <v>368.29</v>
       </c>
       <c r="AQ23" s="3" t="n">
-        <v>372.01</v>
+        <v>377.62</v>
       </c>
       <c r="AR23" s="3" t="n">
-        <v>368.82</v>
+        <v>366.53</v>
       </c>
       <c r="AS23" s="3" t="n">
-        <v>371.54</v>
+        <v>371.08</v>
       </c>
       <c r="AT23" s="3" t="n">
-        <v>371.54</v>
+        <v>371.08</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>6825900</v>
+        <v>11839900</v>
       </c>
       <c r="AV23" s="4">
         <f>IF(COUNT(AT23:AT24)=2,ROUND((AT23/AT24-1)*100,4),"")</f>
@@ -3334,22 +3566,22 @@
       </c>
       <c r="AW23" s="3" t="n"/>
       <c r="AX23" s="3" t="n">
-        <v>177.46</v>
+        <v>171.12</v>
       </c>
       <c r="AY23" s="3" t="n">
-        <v>178.62</v>
+        <v>172.51</v>
       </c>
       <c r="AZ23" s="3" t="n">
-        <v>172.7</v>
+        <v>166.46</v>
       </c>
       <c r="BA23" s="3" t="n">
-        <v>175.35</v>
+        <v>166.57</v>
       </c>
       <c r="BB23" s="3" t="n">
-        <v>175.35</v>
+        <v>166.57</v>
       </c>
       <c r="BC23" s="3" t="n">
-        <v>9146200</v>
+        <v>14372900</v>
       </c>
       <c r="BD23" s="4">
         <f>IF(COUNT(BB23:BB24)=2,ROUND((BB23/BB24-1)*100,4),"")</f>
@@ -3357,22 +3589,22 @@
       </c>
       <c r="BE23" s="3" t="n"/>
       <c r="BF23" s="3" t="n">
-        <v>56.81</v>
+        <v>57.29</v>
       </c>
       <c r="BG23" s="3" t="n">
-        <v>57.12</v>
+        <v>57.47</v>
       </c>
       <c r="BH23" s="3" t="n">
-        <v>56.69</v>
+        <v>56.59</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>56.94</v>
+        <v>56.68</v>
       </c>
       <c r="BJ23" s="3" t="n">
-        <v>56.94</v>
+        <v>56.68</v>
       </c>
       <c r="BK23" s="3" t="n">
-        <v>32543500</v>
+        <v>49038800</v>
       </c>
       <c r="BL23" s="4">
         <f>IF(COUNT(BJ23:BJ24)=2,ROUND((BJ23/BJ24-1)*100,4),"")</f>
@@ -3380,22 +3612,22 @@
       </c>
       <c r="BM23" s="3" t="n"/>
       <c r="BN23" s="3" t="n">
-        <v>107.55</v>
+        <v>107.64</v>
       </c>
       <c r="BO23" s="3" t="n">
-        <v>107.63</v>
+        <v>108.01</v>
       </c>
       <c r="BP23" s="3" t="n">
-        <v>107.34</v>
+        <v>107.48</v>
       </c>
       <c r="BQ23" s="3" t="n">
-        <v>107.63</v>
+        <v>107.77</v>
       </c>
       <c r="BR23" s="3" t="n">
-        <v>106.846</v>
+        <v>106.985</v>
       </c>
       <c r="BS23" s="3" t="n">
-        <v>3868300</v>
+        <v>1759400</v>
       </c>
       <c r="BT23" s="4">
         <f>IF(COUNT(BR23:BR24)=2,ROUND((BR23/BR24-1)*100,4),"")</f>
@@ -3403,38 +3635,38 @@
       </c>
       <c r="BU23" s="3" t="n"/>
       <c r="BV23" s="3" t="n">
-        <v>16.82</v>
+        <v>18.27</v>
       </c>
       <c r="BW23" s="3" t="n">
-        <v>18.7</v>
+        <v>20.88</v>
       </c>
       <c r="BX23" s="3" t="n">
-        <v>15.82</v>
+        <v>17.45</v>
       </c>
       <c r="BY23" s="3" t="n">
-        <v>15.99</v>
+        <v>20.66</v>
       </c>
       <c r="BZ23" s="3" t="n">
-        <v>15.99</v>
+        <v>20.66</v>
       </c>
       <c r="CA23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB23" s="3" t="n"/>
       <c r="CC23" s="3" t="n">
-        <v>4.684</v>
+        <v>4.637</v>
       </c>
       <c r="CD23" s="3" t="n">
-        <v>4.747</v>
+        <v>4.655</v>
       </c>
       <c r="CE23" s="3" t="n">
-        <v>4.682</v>
+        <v>4.61</v>
       </c>
       <c r="CF23" s="3" t="n">
-        <v>4.745</v>
+        <v>4.622</v>
       </c>
       <c r="CG23" s="3" t="n">
-        <v>4.745</v>
+        <v>4.622</v>
       </c>
       <c r="CH23" s="3" t="n">
         <v>0</v>
@@ -3466,11 +3698,11 @@
       </c>
       <c r="CP23" s="3" t="n"/>
       <c r="CQ23" s="4">
-        <f>X23-P23</f>
+        <f>IFERROR(X23-P23,"")</f>
         <v/>
       </c>
       <c r="CR23" s="4">
-        <f>AF23-P23</f>
+        <f>IFERROR(AF23-P23,"")</f>
         <v/>
       </c>
       <c r="CS23" s="6">
@@ -3478,11 +3710,11 @@
         <v/>
       </c>
       <c r="CT23" s="4">
-        <f>AN23-AV23</f>
+        <f>IFERROR(AN23-AV23,"")</f>
         <v/>
       </c>
       <c r="CU23" s="4">
-        <f>BD23-BL23</f>
+        <f>IFERROR(BD23-BL23,"")</f>
         <v/>
       </c>
       <c r="CV23" s="6">
@@ -3490,33 +3722,33 @@
         <v/>
       </c>
       <c r="CW23" s="4">
-        <f>P23-BT23</f>
+        <f>IFERROR(P23-BT23,"")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/07/28</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>736.05</v>
+        <v>739.1900000000001</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>742.45</v>
+        <v>742.79</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>734.59</v>
+        <v>735.98</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>741.6900000000001</v>
+        <v>740.86</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>741.6900000000001</v>
+        <v>740.86</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>66811300</v>
+        <v>47322200</v>
       </c>
       <c r="H24" s="4">
         <f>IF(COUNT(F24:F25)=2,ROUND((F24/F25-1)*100,4),"")</f>
@@ -3524,22 +3756,22 @@
       </c>
       <c r="I24" s="3" t="n"/>
       <c r="J24" s="3" t="n">
-        <v>82.81</v>
+        <v>83.86</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>84.34</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>82.52</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>82.8</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>82.4678</v>
+        <v>83.902</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>40407300</v>
+        <v>25366900</v>
       </c>
       <c r="P24" s="4">
         <f>IF(COUNT(N24:N25)=2,ROUND((N24/N25-1)*100,4),"")</f>
@@ -3547,22 +3779,22 @@
       </c>
       <c r="Q24" s="3" t="n"/>
       <c r="R24" s="3" t="n">
-        <v>79.38</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>79.5</v>
+        <v>79.42</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>79.33</v>
+        <v>79.25</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>79.47</v>
+        <v>79.42</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>79.086</v>
+        <v>79.0363</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>30570700</v>
+        <v>33698300</v>
       </c>
       <c r="X24" s="4">
         <f>IF(COUNT(V24:V25)=2,ROUND((V24/V25-1)*100,4),"")</f>
@@ -3570,22 +3802,22 @@
       </c>
       <c r="Y24" s="3" t="n"/>
       <c r="Z24" s="3" t="n">
-        <v>95.52</v>
+        <v>95.53</v>
       </c>
       <c r="AA24" s="3" t="n">
-        <v>95.7</v>
+        <v>95.62</v>
       </c>
       <c r="AB24" s="3" t="n">
-        <v>95.52</v>
+        <v>95.45</v>
       </c>
       <c r="AC24" s="3" t="n">
-        <v>95.66</v>
+        <v>95.61</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>95.1331</v>
+        <v>95.0834</v>
       </c>
       <c r="AE24" s="3" t="n">
-        <v>3477300</v>
+        <v>1216600</v>
       </c>
       <c r="AF24" s="4">
         <f>IF(COUNT(AD24:AD25)=2,ROUND((AD24/AD25-1)*100,4),"")</f>
@@ -3593,22 +3825,22 @@
       </c>
       <c r="AG24" s="3" t="n"/>
       <c r="AH24" s="3" t="n">
-        <v>28.36</v>
+        <v>28.59</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>28.36</v>
+        <v>28.6</v>
       </c>
       <c r="AJ24" s="3" t="n">
-        <v>28.12</v>
+        <v>28.52</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>28.14</v>
+        <v>28.58</v>
       </c>
       <c r="AL24" s="3" t="n">
-        <v>28.14</v>
+        <v>28.58</v>
       </c>
       <c r="AM24" s="3" t="n">
-        <v>4809000</v>
+        <v>1037400</v>
       </c>
       <c r="AN24" s="4">
         <f>IF(COUNT(AL24:AL25)=2,ROUND((AL24/AL25-1)*100,4),"")</f>
@@ -3616,22 +3848,22 @@
       </c>
       <c r="AO24" s="3" t="n"/>
       <c r="AP24" s="3" t="n">
-        <v>374.16</v>
+        <v>369.61</v>
       </c>
       <c r="AQ24" s="3" t="n">
-        <v>377.86</v>
+        <v>371.23</v>
       </c>
       <c r="AR24" s="3" t="n">
-        <v>373.76</v>
+        <v>367.98</v>
       </c>
       <c r="AS24" s="3" t="n">
-        <v>377.16</v>
+        <v>369.37</v>
       </c>
       <c r="AT24" s="3" t="n">
-        <v>377.16</v>
+        <v>369.37</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>5968400</v>
+        <v>4819300</v>
       </c>
       <c r="AV24" s="4">
         <f>IF(COUNT(AT24:AT25)=2,ROUND((AT24/AT25-1)*100,4),"")</f>
@@ -3639,22 +3871,22 @@
       </c>
       <c r="AW24" s="3" t="n"/>
       <c r="AX24" s="3" t="n">
-        <v>172.81</v>
+        <v>171.21</v>
       </c>
       <c r="AY24" s="3" t="n">
-        <v>176.09</v>
+        <v>172.17</v>
       </c>
       <c r="AZ24" s="3" t="n">
-        <v>172.16</v>
+        <v>167.54</v>
       </c>
       <c r="BA24" s="3" t="n">
-        <v>175.73</v>
+        <v>171.09</v>
       </c>
       <c r="BB24" s="3" t="n">
-        <v>175.73</v>
+        <v>171.09</v>
       </c>
       <c r="BC24" s="3" t="n">
-        <v>15098400</v>
+        <v>10049300</v>
       </c>
       <c r="BD24" s="4">
         <f>IF(COUNT(BB24:BB25)=2,ROUND((BB24/BB25-1)*100,4),"")</f>
@@ -3662,22 +3894,22 @@
       </c>
       <c r="BE24" s="3" t="n"/>
       <c r="BF24" s="3" t="n">
-        <v>56.82</v>
+        <v>57.13</v>
       </c>
       <c r="BG24" s="3" t="n">
-        <v>57.05</v>
+        <v>57.6</v>
       </c>
       <c r="BH24" s="3" t="n">
-        <v>56.18</v>
+        <v>56.95</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>57</v>
+        <v>57.6</v>
       </c>
       <c r="BJ24" s="3" t="n">
-        <v>57</v>
+        <v>57.6</v>
       </c>
       <c r="BK24" s="3" t="n">
-        <v>33184200</v>
+        <v>34204400</v>
       </c>
       <c r="BL24" s="4">
         <f>IF(COUNT(BJ24:BJ25)=2,ROUND((BJ24/BJ25-1)*100,4),"")</f>
@@ -3685,22 +3917,22 @@
       </c>
       <c r="BM24" s="3" t="n"/>
       <c r="BN24" s="3" t="n">
-        <v>107.83</v>
+        <v>107.5</v>
       </c>
       <c r="BO24" s="3" t="n">
-        <v>107.89</v>
+        <v>107.8</v>
       </c>
       <c r="BP24" s="3" t="n">
-        <v>107.67</v>
+        <v>107.48</v>
       </c>
       <c r="BQ24" s="3" t="n">
-        <v>107.74</v>
+        <v>107.66</v>
       </c>
       <c r="BR24" s="3" t="n">
-        <v>106.9552</v>
+        <v>106.8758</v>
       </c>
       <c r="BS24" s="3" t="n">
-        <v>2203000</v>
+        <v>2765800</v>
       </c>
       <c r="BT24" s="4">
         <f>IF(COUNT(BR24:BR25)=2,ROUND((BR24/BR25-1)*100,4),"")</f>
@@ -3708,38 +3940,38 @@
       </c>
       <c r="BU24" s="3" t="n"/>
       <c r="BV24" s="3" t="n">
-        <v>19.56</v>
+        <v>19.05</v>
       </c>
       <c r="BW24" s="3" t="n">
-        <v>20.08</v>
+        <v>19.52</v>
       </c>
       <c r="BX24" s="3" t="n">
-        <v>17</v>
+        <v>17.88</v>
       </c>
       <c r="BY24" s="3" t="n">
-        <v>17.09</v>
+        <v>18.21</v>
       </c>
       <c r="BZ24" s="3" t="n">
-        <v>17.09</v>
+        <v>18.21</v>
       </c>
       <c r="CA24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB24" s="3" t="n"/>
       <c r="CC24" s="3" t="n">
-        <v>4.669</v>
+        <v>4.63</v>
       </c>
       <c r="CD24" s="3" t="n">
-        <v>4.686</v>
+        <v>4.635</v>
       </c>
       <c r="CE24" s="3" t="n">
-        <v>4.651</v>
+        <v>4.588</v>
       </c>
       <c r="CF24" s="3" t="n">
-        <v>4.663</v>
+        <v>4.604</v>
       </c>
       <c r="CG24" s="3" t="n">
-        <v>4.663</v>
+        <v>4.604</v>
       </c>
       <c r="CH24" s="3" t="n">
         <v>0</v>
@@ -3771,11 +4003,11 @@
       </c>
       <c r="CP24" s="3" t="n"/>
       <c r="CQ24" s="4">
-        <f>X24-P24</f>
+        <f>IFERROR(X24-P24,"")</f>
         <v/>
       </c>
       <c r="CR24" s="4">
-        <f>AF24-P24</f>
+        <f>IFERROR(AF24-P24,"")</f>
         <v/>
       </c>
       <c r="CS24" s="6">
@@ -3783,11 +4015,11 @@
         <v/>
       </c>
       <c r="CT24" s="4">
-        <f>AN24-AV24</f>
+        <f>IFERROR(AN24-AV24,"")</f>
         <v/>
       </c>
       <c r="CU24" s="4">
-        <f>BD24-BL24</f>
+        <f>IFERROR(BD24-BL24,"")</f>
         <v/>
       </c>
       <c r="CV24" s="6">
@@ -3795,33 +4027,33 @@
         <v/>
       </c>
       <c r="CW24" s="4">
-        <f>P24-BT24</f>
+        <f>IFERROR(P24-BT24,"")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>739.97</v>
+        <v>744.91</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>742.6799999999999</v>
+        <v>745.53</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>729.1</v>
+        <v>735.87</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>729.46</v>
+        <v>739.09</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>729.46</v>
+        <v>739.09</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>70697200</v>
+        <v>41461200</v>
       </c>
       <c r="H25" s="4">
         <f>IF(COUNT(F25:F26)=2,ROUND((F25/F26-1)*100,4),"")</f>
@@ -3829,22 +4061,22 @@
       </c>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>83.73</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>84.15000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>82.7</v>
+        <v>83.52</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>82.84999999999999</v>
+        <v>83.75</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>82.5176</v>
+        <v>83.414</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>41445200</v>
+        <v>23816200</v>
       </c>
       <c r="P25" s="4">
         <f>IF(COUNT(N25:N26)=2,ROUND((N25/N26-1)*100,4),"")</f>
@@ -3852,22 +4084,22 @@
       </c>
       <c r="Q25" s="3" t="n"/>
       <c r="R25" s="3" t="n">
-        <v>79.37</v>
+        <v>79.34</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>79.48</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>79.14</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>79.23999999999999</v>
+        <v>79.27</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>78.85720000000001</v>
+        <v>78.887</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>53074500</v>
+        <v>28939800</v>
       </c>
       <c r="X25" s="4">
         <f>IF(COUNT(V25:V26)=2,ROUND((V25/V26-1)*100,4),"")</f>
@@ -3875,22 +4107,22 @@
       </c>
       <c r="Y25" s="3" t="n"/>
       <c r="Z25" s="3" t="n">
-        <v>95.58</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="AA25" s="3" t="n">
-        <v>95.68000000000001</v>
+        <v>95.62</v>
       </c>
       <c r="AB25" s="3" t="n">
-        <v>95.28</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="AC25" s="3" t="n">
-        <v>95.39</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>94.8646</v>
+        <v>94.9342</v>
       </c>
       <c r="AE25" s="3" t="n">
-        <v>2210500</v>
+        <v>1704500</v>
       </c>
       <c r="AF25" s="4">
         <f>IF(COUNT(AD25:AD26)=2,ROUND((AD25/AD26-1)*100,4),"")</f>
@@ -3898,22 +4130,22 @@
       </c>
       <c r="AG25" s="3" t="n"/>
       <c r="AH25" s="3" t="n">
-        <v>28.57</v>
+        <v>28.56</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>28.59</v>
+        <v>28.6</v>
       </c>
       <c r="AJ25" s="3" t="n">
-        <v>28.3</v>
+        <v>28.55</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>28.42</v>
+        <v>28.6</v>
       </c>
       <c r="AL25" s="3" t="n">
-        <v>28.42</v>
+        <v>28.6</v>
       </c>
       <c r="AM25" s="3" t="n">
-        <v>2286600</v>
+        <v>1602600</v>
       </c>
       <c r="AN25" s="4">
         <f>IF(COUNT(AL25:AL26)=2,ROUND((AL25/AL26-1)*100,4),"")</f>
@@ -3921,22 +4153,22 @@
       </c>
       <c r="AO25" s="3" t="n"/>
       <c r="AP25" s="3" t="n">
-        <v>368.29</v>
+        <v>373.89</v>
       </c>
       <c r="AQ25" s="3" t="n">
-        <v>377.62</v>
+        <v>375.53</v>
       </c>
       <c r="AR25" s="3" t="n">
-        <v>366.53</v>
+        <v>372.91</v>
       </c>
       <c r="AS25" s="3" t="n">
-        <v>371.08</v>
+        <v>374.63</v>
       </c>
       <c r="AT25" s="3" t="n">
-        <v>371.08</v>
+        <v>374.63</v>
       </c>
       <c r="AU25" s="3" t="n">
-        <v>11839900</v>
+        <v>3700000</v>
       </c>
       <c r="AV25" s="4">
         <f>IF(COUNT(AT25:AT26)=2,ROUND((AT25/AT26-1)*100,4),"")</f>
@@ -3944,22 +4176,22 @@
       </c>
       <c r="AW25" s="3" t="n"/>
       <c r="AX25" s="3" t="n">
-        <v>171.12</v>
+        <v>177.83</v>
       </c>
       <c r="AY25" s="3" t="n">
-        <v>172.51</v>
+        <v>178.3</v>
       </c>
       <c r="AZ25" s="3" t="n">
-        <v>166.46</v>
+        <v>171.73</v>
       </c>
       <c r="BA25" s="3" t="n">
-        <v>166.57</v>
+        <v>174.3</v>
       </c>
       <c r="BB25" s="3" t="n">
-        <v>166.57</v>
+        <v>174.3</v>
       </c>
       <c r="BC25" s="3" t="n">
-        <v>14372900</v>
+        <v>8376600</v>
       </c>
       <c r="BD25" s="4">
         <f>IF(COUNT(BB25:BB26)=2,ROUND((BB25/BB26-1)*100,4),"")</f>
@@ -3967,22 +4199,22 @@
       </c>
       <c r="BE25" s="3" t="n"/>
       <c r="BF25" s="3" t="n">
-        <v>57.29</v>
+        <v>56.76</v>
       </c>
       <c r="BG25" s="3" t="n">
-        <v>57.47</v>
+        <v>57.13</v>
       </c>
       <c r="BH25" s="3" t="n">
         <v>56.59</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>56.68</v>
+        <v>56.88</v>
       </c>
       <c r="BJ25" s="3" t="n">
-        <v>56.68</v>
+        <v>56.88</v>
       </c>
       <c r="BK25" s="3" t="n">
-        <v>49038800</v>
+        <v>29805900</v>
       </c>
       <c r="BL25" s="4">
         <f>IF(COUNT(BJ25:BJ26)=2,ROUND((BJ25/BJ26-1)*100,4),"")</f>
@@ -3990,22 +4222,22 @@
       </c>
       <c r="BM25" s="3" t="n"/>
       <c r="BN25" s="3" t="n">
-        <v>107.64</v>
+        <v>107.57</v>
       </c>
       <c r="BO25" s="3" t="n">
-        <v>108.01</v>
+        <v>107.63</v>
       </c>
       <c r="BP25" s="3" t="n">
-        <v>107.48</v>
+        <v>107.39</v>
       </c>
       <c r="BQ25" s="3" t="n">
-        <v>107.77</v>
+        <v>107.39</v>
       </c>
       <c r="BR25" s="3" t="n">
-        <v>106.985</v>
+        <v>106.6077</v>
       </c>
       <c r="BS25" s="3" t="n">
-        <v>1759400</v>
+        <v>1262000</v>
       </c>
       <c r="BT25" s="4">
         <f>IF(COUNT(BR25:BR26)=2,ROUND((BR25/BR26-1)*100,4),"")</f>
@@ -4013,38 +4245,38 @@
       </c>
       <c r="BU25" s="3" t="n"/>
       <c r="BV25" s="3" t="n">
-        <v>18.27</v>
+        <v>17.62</v>
       </c>
       <c r="BW25" s="3" t="n">
-        <v>20.88</v>
+        <v>19.93</v>
       </c>
       <c r="BX25" s="3" t="n">
-        <v>17.45</v>
+        <v>17.53</v>
       </c>
       <c r="BY25" s="3" t="n">
-        <v>20.66</v>
+        <v>18.67</v>
       </c>
       <c r="BZ25" s="3" t="n">
-        <v>20.66</v>
+        <v>18.67</v>
       </c>
       <c r="CA25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB25" s="3" t="n"/>
       <c r="CC25" s="3" t="n">
-        <v>4.637</v>
+        <v>4.647</v>
       </c>
       <c r="CD25" s="3" t="n">
-        <v>4.655</v>
+        <v>4.665</v>
       </c>
       <c r="CE25" s="3" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="CF25" s="3" t="n">
-        <v>4.622</v>
+        <v>4.641</v>
       </c>
       <c r="CG25" s="3" t="n">
-        <v>4.622</v>
+        <v>4.641</v>
       </c>
       <c r="CH25" s="3" t="n">
         <v>0</v>
@@ -4076,11 +4308,11 @@
       </c>
       <c r="CP25" s="3" t="n"/>
       <c r="CQ25" s="4">
-        <f>X25-P25</f>
+        <f>IFERROR(X25-P25,"")</f>
         <v/>
       </c>
       <c r="CR25" s="4">
-        <f>AF25-P25</f>
+        <f>IFERROR(AF25-P25,"")</f>
         <v/>
       </c>
       <c r="CS25" s="6">
@@ -4088,11 +4320,11 @@
         <v/>
       </c>
       <c r="CT25" s="4">
-        <f>AN25-AV25</f>
+        <f>IFERROR(AN25-AV25,"")</f>
         <v/>
       </c>
       <c r="CU25" s="4">
-        <f>BD25-BL25</f>
+        <f>IFERROR(BD25-BL25,"")</f>
         <v/>
       </c>
       <c r="CV25" s="6">
@@ -4100,33 +4332,33 @@
         <v/>
       </c>
       <c r="CW25" s="4">
-        <f>P25-BT25</f>
+        <f>IFERROR(P25-BT25,"")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026/07/28</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>739.1900000000001</v>
+        <v>738.51</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>742.79</v>
+        <v>743.72</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>735.98</v>
+        <v>737.29</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>740.86</v>
+        <v>738.9299999999999</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>740.86</v>
+        <v>738.9299999999999</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>47322200</v>
+        <v>44782000</v>
       </c>
       <c r="H26" s="4">
         <f>IF(COUNT(F26:F27)=2,ROUND((F26/F27-1)*100,4),"")</f>
@@ -4134,22 +4366,22 @@
       </c>
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n">
-        <v>83.86</v>
+        <v>83.31</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>84.34</v>
+        <v>83.66</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>83.84999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>84.23999999999999</v>
+        <v>83.25</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>83.902</v>
+        <v>82.916</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>25366900</v>
+        <v>15106000</v>
       </c>
       <c r="P26" s="4">
         <f>IF(COUNT(N26:N27)=2,ROUND((N26/N27-1)*100,4),"")</f>
@@ -4157,22 +4389,22 @@
       </c>
       <c r="Q26" s="3" t="n"/>
       <c r="R26" s="3" t="n">
-        <v>79.31999999999999</v>
+        <v>79.25</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>79.42</v>
+        <v>79.31</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>79.25</v>
+        <v>79.16</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>79.42</v>
+        <v>79.23</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>79.0363</v>
+        <v>78.8472</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>33698300</v>
+        <v>41964600</v>
       </c>
       <c r="X26" s="4">
         <f>IF(COUNT(V26:V27)=2,ROUND((V26/V27-1)*100,4),"")</f>
@@ -4180,22 +4412,22 @@
       </c>
       <c r="Y26" s="3" t="n"/>
       <c r="Z26" s="3" t="n">
-        <v>95.53</v>
+        <v>95.41</v>
       </c>
       <c r="AA26" s="3" t="n">
-        <v>95.62</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="AB26" s="3" t="n">
-        <v>95.45</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="AC26" s="3" t="n">
-        <v>95.61</v>
+        <v>95.39</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>95.0834</v>
+        <v>94.8646</v>
       </c>
       <c r="AE26" s="3" t="n">
-        <v>1216600</v>
+        <v>2602400</v>
       </c>
       <c r="AF26" s="4">
         <f>IF(COUNT(AD26:AD27)=2,ROUND((AD26/AD27-1)*100,4),"")</f>
@@ -4203,10 +4435,10 @@
       </c>
       <c r="AG26" s="3" t="n"/>
       <c r="AH26" s="3" t="n">
-        <v>28.59</v>
+        <v>28.58</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>28.6</v>
+        <v>28.58</v>
       </c>
       <c r="AJ26" s="3" t="n">
         <v>28.52</v>
@@ -4218,7 +4450,7 @@
         <v>28.58</v>
       </c>
       <c r="AM26" s="3" t="n">
-        <v>1037400</v>
+        <v>1113500</v>
       </c>
       <c r="AN26" s="4">
         <f>IF(COUNT(AL26:AL27)=2,ROUND((AL26/AL27-1)*100,4),"")</f>
@@ -4226,22 +4458,22 @@
       </c>
       <c r="AO26" s="3" t="n"/>
       <c r="AP26" s="3" t="n">
-        <v>369.61</v>
+        <v>371.26</v>
       </c>
       <c r="AQ26" s="3" t="n">
-        <v>371.23</v>
+        <v>374.49</v>
       </c>
       <c r="AR26" s="3" t="n">
-        <v>367.98</v>
+        <v>371.03</v>
       </c>
       <c r="AS26" s="3" t="n">
-        <v>369.37</v>
+        <v>371.9</v>
       </c>
       <c r="AT26" s="3" t="n">
-        <v>369.37</v>
+        <v>371.9</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>4819300</v>
+        <v>3852400</v>
       </c>
       <c r="AV26" s="4">
         <f>IF(COUNT(AT26:AT27)=2,ROUND((AT26/AT27-1)*100,4),"")</f>
@@ -4249,22 +4481,22 @@
       </c>
       <c r="AW26" s="3" t="n"/>
       <c r="AX26" s="3" t="n">
-        <v>171.21</v>
+        <v>177.82</v>
       </c>
       <c r="AY26" s="3" t="n">
-        <v>172.17</v>
+        <v>179.01</v>
       </c>
       <c r="AZ26" s="3" t="n">
-        <v>167.54</v>
+        <v>175.05</v>
       </c>
       <c r="BA26" s="3" t="n">
-        <v>171.09</v>
+        <v>175.88</v>
       </c>
       <c r="BB26" s="3" t="n">
-        <v>171.09</v>
+        <v>175.88</v>
       </c>
       <c r="BC26" s="3" t="n">
-        <v>10049300</v>
+        <v>7739600</v>
       </c>
       <c r="BD26" s="4">
         <f>IF(COUNT(BB26:BB27)=2,ROUND((BB26/BB27-1)*100,4),"")</f>
@@ -4272,22 +4504,22 @@
       </c>
       <c r="BE26" s="3" t="n"/>
       <c r="BF26" s="3" t="n">
-        <v>57.13</v>
+        <v>55.83</v>
       </c>
       <c r="BG26" s="3" t="n">
-        <v>57.6</v>
+        <v>56.38</v>
       </c>
       <c r="BH26" s="3" t="n">
-        <v>56.95</v>
+        <v>55.69</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>57.6</v>
+        <v>56.31</v>
       </c>
       <c r="BJ26" s="3" t="n">
-        <v>57.6</v>
+        <v>56.31</v>
       </c>
       <c r="BK26" s="3" t="n">
-        <v>34204400</v>
+        <v>32212900</v>
       </c>
       <c r="BL26" s="4">
         <f>IF(COUNT(BJ26:BJ27)=2,ROUND((BJ26/BJ27-1)*100,4),"")</f>
@@ -4295,22 +4527,22 @@
       </c>
       <c r="BM26" s="3" t="n"/>
       <c r="BN26" s="3" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="BO26" s="3" t="n">
+        <v>107.74</v>
+      </c>
+      <c r="BP26" s="3" t="n">
         <v>107.5</v>
       </c>
-      <c r="BO26" s="3" t="n">
-        <v>107.8</v>
-      </c>
-      <c r="BP26" s="3" t="n">
-        <v>107.48</v>
-      </c>
       <c r="BQ26" s="3" t="n">
-        <v>107.66</v>
+        <v>107.5</v>
       </c>
       <c r="BR26" s="3" t="n">
-        <v>106.8758</v>
+        <v>106.7169</v>
       </c>
       <c r="BS26" s="3" t="n">
-        <v>2765800</v>
+        <v>1220700</v>
       </c>
       <c r="BT26" s="4">
         <f>IF(COUNT(BR26:BR27)=2,ROUND((BR26/BR27-1)*100,4),"")</f>
@@ -4318,38 +4550,38 @@
       </c>
       <c r="BU26" s="3" t="n"/>
       <c r="BV26" s="3" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="BW26" s="3" t="n">
         <v>19.05</v>
       </c>
-      <c r="BW26" s="3" t="n">
-        <v>19.52</v>
-      </c>
       <c r="BX26" s="3" t="n">
-        <v>17.88</v>
+        <v>17.41</v>
       </c>
       <c r="BY26" s="3" t="n">
-        <v>18.21</v>
+        <v>18.58</v>
       </c>
       <c r="BZ26" s="3" t="n">
-        <v>18.21</v>
+        <v>18.58</v>
       </c>
       <c r="CA26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB26" s="3" t="n"/>
       <c r="CC26" s="3" t="n">
-        <v>4.63</v>
+        <v>4.683</v>
       </c>
       <c r="CD26" s="3" t="n">
-        <v>4.635</v>
+        <v>4.691</v>
       </c>
       <c r="CE26" s="3" t="n">
-        <v>4.588</v>
+        <v>4.651</v>
       </c>
       <c r="CF26" s="3" t="n">
-        <v>4.604</v>
+        <v>4.679</v>
       </c>
       <c r="CG26" s="3" t="n">
-        <v>4.604</v>
+        <v>4.679</v>
       </c>
       <c r="CH26" s="3" t="n">
         <v>0</v>
@@ -4381,11 +4613,11 @@
       </c>
       <c r="CP26" s="3" t="n"/>
       <c r="CQ26" s="4">
-        <f>X26-P26</f>
+        <f>IFERROR(X26-P26,"")</f>
         <v/>
       </c>
       <c r="CR26" s="4">
-        <f>AF26-P26</f>
+        <f>IFERROR(AF26-P26,"")</f>
         <v/>
       </c>
       <c r="CS26" s="6">
@@ -4393,11 +4625,11 @@
         <v/>
       </c>
       <c r="CT26" s="4">
-        <f>AN26-AV26</f>
+        <f>IFERROR(AN26-AV26,"")</f>
         <v/>
       </c>
       <c r="CU26" s="4">
-        <f>BD26-BL26</f>
+        <f>IFERROR(BD26-BL26,"")</f>
         <v/>
       </c>
       <c r="CV26" s="6">
@@ -4405,33 +4637,33 @@
         <v/>
       </c>
       <c r="CW26" s="4">
-        <f>P26-BT26</f>
+        <f>IFERROR(P26-BT26,"")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>744.91</v>
+        <v>739.37</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>745.53</v>
+        <v>742.5599999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>735.87</v>
+        <v>735.21</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>739.09</v>
+        <v>738.1799999999999</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>739.09</v>
+        <v>738.1799999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>41461200</v>
+        <v>55437300</v>
       </c>
       <c r="H27" s="4">
         <f>IF(COUNT(F27:F28)=2,ROUND((F27/F28-1)*100,4),"")</f>
@@ -4439,22 +4671,22 @@
       </c>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n">
-        <v>83.73</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>83.87</v>
+        <v>83.25</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>83.52</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>83.75</v>
+        <v>83.17</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>83.414</v>
+        <v>82.83629999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>23816200</v>
+        <v>29152800</v>
       </c>
       <c r="P27" s="4">
         <f>IF(COUNT(N27:N28)=2,ROUND((N27/N28-1)*100,4),"")</f>
@@ -4462,22 +4694,22 @@
       </c>
       <c r="Q27" s="3" t="n"/>
       <c r="R27" s="3" t="n">
-        <v>79.34</v>
+        <v>79.28</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>79.37</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>79.23999999999999</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>79.27</v>
+        <v>79.23</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>78.887</v>
+        <v>78.8472</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>28939800</v>
+        <v>52554200</v>
       </c>
       <c r="X27" s="4">
         <f>IF(COUNT(V27:V28)=2,ROUND((V27/V28-1)*100,4),"")</f>
@@ -4485,22 +4717,22 @@
       </c>
       <c r="Y27" s="3" t="n"/>
       <c r="Z27" s="3" t="n">
-        <v>95.54000000000001</v>
+        <v>95.42</v>
       </c>
       <c r="AA27" s="3" t="n">
-        <v>95.62</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="AB27" s="3" t="n">
-        <v>95.43000000000001</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="AC27" s="3" t="n">
-        <v>95.45999999999999</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>94.9342</v>
+        <v>94.8745</v>
       </c>
       <c r="AE27" s="3" t="n">
-        <v>1704500</v>
+        <v>3439400</v>
       </c>
       <c r="AF27" s="4">
         <f>IF(COUNT(AD27:AD28)=2,ROUND((AD27/AD28-1)*100,4),"")</f>
@@ -4508,22 +4740,22 @@
       </c>
       <c r="AG27" s="3" t="n"/>
       <c r="AH27" s="3" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="AI27" s="3" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="AJ27" s="3" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="AK27" s="3" t="n">
         <v>28.56</v>
       </c>
-      <c r="AI27" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="AJ27" s="3" t="n">
-        <v>28.55</v>
-      </c>
-      <c r="AK27" s="3" t="n">
-        <v>28.6</v>
-      </c>
       <c r="AL27" s="3" t="n">
-        <v>28.6</v>
+        <v>28.56</v>
       </c>
       <c r="AM27" s="3" t="n">
-        <v>1602600</v>
+        <v>1529300</v>
       </c>
       <c r="AN27" s="4">
         <f>IF(COUNT(AL27:AL28)=2,ROUND((AL27/AL28-1)*100,4),"")</f>
@@ -4531,22 +4763,22 @@
       </c>
       <c r="AO27" s="3" t="n"/>
       <c r="AP27" s="3" t="n">
-        <v>373.89</v>
+        <v>372.36</v>
       </c>
       <c r="AQ27" s="3" t="n">
-        <v>375.53</v>
+        <v>373.09</v>
       </c>
       <c r="AR27" s="3" t="n">
-        <v>372.91</v>
+        <v>370.53</v>
       </c>
       <c r="AS27" s="3" t="n">
-        <v>374.63</v>
+        <v>371.52</v>
       </c>
       <c r="AT27" s="3" t="n">
-        <v>374.63</v>
+        <v>371.52</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>3700000</v>
+        <v>9820600</v>
       </c>
       <c r="AV27" s="4">
         <f>IF(COUNT(AT27:AT28)=2,ROUND((AT27/AT28-1)*100,4),"")</f>
@@ -4554,22 +4786,22 @@
       </c>
       <c r="AW27" s="3" t="n"/>
       <c r="AX27" s="3" t="n">
-        <v>177.83</v>
+        <v>178.8</v>
       </c>
       <c r="AY27" s="3" t="n">
-        <v>178.3</v>
+        <v>180.39</v>
       </c>
       <c r="AZ27" s="3" t="n">
-        <v>171.73</v>
+        <v>177.2</v>
       </c>
       <c r="BA27" s="3" t="n">
-        <v>174.3</v>
+        <v>178.45</v>
       </c>
       <c r="BB27" s="3" t="n">
-        <v>174.3</v>
+        <v>178.45</v>
       </c>
       <c r="BC27" s="3" t="n">
-        <v>8376600</v>
+        <v>7177000</v>
       </c>
       <c r="BD27" s="4">
         <f>IF(COUNT(BB27:BB28)=2,ROUND((BB27/BB28-1)*100,4),"")</f>
@@ -4577,22 +4809,22 @@
       </c>
       <c r="BE27" s="3" t="n"/>
       <c r="BF27" s="3" t="n">
-        <v>56.76</v>
+        <v>55.68</v>
       </c>
       <c r="BG27" s="3" t="n">
-        <v>57.13</v>
+        <v>55.86</v>
       </c>
       <c r="BH27" s="3" t="n">
-        <v>56.59</v>
+        <v>55.45</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>56.88</v>
+        <v>55.83</v>
       </c>
       <c r="BJ27" s="3" t="n">
-        <v>56.88</v>
+        <v>55.83</v>
       </c>
       <c r="BK27" s="3" t="n">
-        <v>29805900</v>
+        <v>24311000</v>
       </c>
       <c r="BL27" s="4">
         <f>IF(COUNT(BJ27:BJ28)=2,ROUND((BJ27/BJ28-1)*100,4),"")</f>
@@ -4600,22 +4832,22 @@
       </c>
       <c r="BM27" s="3" t="n"/>
       <c r="BN27" s="3" t="n">
-        <v>107.57</v>
+        <v>107.54</v>
       </c>
       <c r="BO27" s="3" t="n">
-        <v>107.63</v>
+        <v>107.65</v>
       </c>
       <c r="BP27" s="3" t="n">
-        <v>107.39</v>
+        <v>107.48</v>
       </c>
       <c r="BQ27" s="3" t="n">
-        <v>107.39</v>
+        <v>107.49</v>
       </c>
       <c r="BR27" s="3" t="n">
-        <v>106.6077</v>
+        <v>106.707</v>
       </c>
       <c r="BS27" s="3" t="n">
-        <v>1262000</v>
+        <v>2261200</v>
       </c>
       <c r="BT27" s="4">
         <f>IF(COUNT(BR27:BR28)=2,ROUND((BR27/BR28-1)*100,4),"")</f>
@@ -4623,38 +4855,38 @@
       </c>
       <c r="BU27" s="3" t="n"/>
       <c r="BV27" s="3" t="n">
-        <v>17.62</v>
+        <v>17.67</v>
       </c>
       <c r="BW27" s="3" t="n">
-        <v>19.93</v>
+        <v>20.31</v>
       </c>
       <c r="BX27" s="3" t="n">
-        <v>17.53</v>
+        <v>17.32</v>
       </c>
       <c r="BY27" s="3" t="n">
-        <v>18.67</v>
+        <v>18.7</v>
       </c>
       <c r="BZ27" s="3" t="n">
-        <v>18.67</v>
+        <v>18.7</v>
       </c>
       <c r="CA27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB27" s="3" t="n"/>
       <c r="CC27" s="3" t="n">
-        <v>4.647</v>
+        <v>4.699</v>
       </c>
       <c r="CD27" s="3" t="n">
-        <v>4.665</v>
+        <v>4.714</v>
       </c>
       <c r="CE27" s="3" t="n">
-        <v>4.63</v>
+        <v>4.693</v>
       </c>
       <c r="CF27" s="3" t="n">
-        <v>4.641</v>
+        <v>4.703</v>
       </c>
       <c r="CG27" s="3" t="n">
-        <v>4.641</v>
+        <v>4.703</v>
       </c>
       <c r="CH27" s="3" t="n">
         <v>0</v>
@@ -4686,11 +4918,11 @@
       </c>
       <c r="CP27" s="3" t="n"/>
       <c r="CQ27" s="4">
-        <f>X27-P27</f>
+        <f>IFERROR(X27-P27,"")</f>
         <v/>
       </c>
       <c r="CR27" s="4">
-        <f>AF27-P27</f>
+        <f>IFERROR(AF27-P27,"")</f>
         <v/>
       </c>
       <c r="CS27" s="6">
@@ -4698,11 +4930,11 @@
         <v/>
       </c>
       <c r="CT27" s="4">
-        <f>AN27-AV27</f>
+        <f>IFERROR(AN27-AV27,"")</f>
         <v/>
       </c>
       <c r="CU27" s="4">
-        <f>BD27-BL27</f>
+        <f>IFERROR(BD27-BL27,"")</f>
         <v/>
       </c>
       <c r="CV27" s="6">
@@ -4710,33 +4942,33 @@
         <v/>
       </c>
       <c r="CW27" s="4">
-        <f>P27-BT27</f>
+        <f>IFERROR(P27-BT27,"")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/22</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>738.51</v>
+        <v>746.62</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>743.72</v>
+        <v>750.02</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>737.29</v>
+        <v>746.37</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>738.9299999999999</v>
+        <v>747.41</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>738.9299999999999</v>
+        <v>747.41</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>44782000</v>
+        <v>32836200</v>
       </c>
       <c r="H28" s="4">
         <f>IF(COUNT(F28:F29)=2,ROUND((F28/F29-1)*100,4),"")</f>
@@ -4744,22 +4976,22 @@
       </c>
       <c r="I28" s="3" t="n"/>
       <c r="J28" s="3" t="n">
-        <v>83.31</v>
+        <v>83.61</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>83.66</v>
+        <v>83.7</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>83.23</v>
+        <v>83.38</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>83.25</v>
+        <v>83.44</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>82.916</v>
+        <v>83.1052</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>15106000</v>
+        <v>15988400</v>
       </c>
       <c r="P28" s="4">
         <f>IF(COUNT(N28:N29)=2,ROUND((N28/N29-1)*100,4),"")</f>
@@ -4767,22 +4999,22 @@
       </c>
       <c r="Q28" s="3" t="n"/>
       <c r="R28" s="3" t="n">
-        <v>79.25</v>
+        <v>79.61</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>79.31</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>79.16</v>
+        <v>79.48</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>79.23</v>
+        <v>79.52</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>78.8472</v>
+        <v>79.1358</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>41964600</v>
+        <v>24851700</v>
       </c>
       <c r="X28" s="4">
         <f>IF(COUNT(V28:V29)=2,ROUND((V28/V29-1)*100,4),"")</f>
@@ -4790,22 +5022,22 @@
       </c>
       <c r="Y28" s="3" t="n"/>
       <c r="Z28" s="3" t="n">
-        <v>95.41</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="AA28" s="3" t="n">
-        <v>95.56999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AB28" s="3" t="n">
-        <v>95.31999999999999</v>
+        <v>95.69</v>
       </c>
       <c r="AC28" s="3" t="n">
-        <v>95.39</v>
+        <v>95.75</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>94.8646</v>
+        <v>95.2226</v>
       </c>
       <c r="AE28" s="3" t="n">
-        <v>2602400</v>
+        <v>2546100</v>
       </c>
       <c r="AF28" s="4">
         <f>IF(COUNT(AD28:AD29)=2,ROUND((AD28/AD29-1)*100,4),"")</f>
@@ -4813,22 +5045,22 @@
       </c>
       <c r="AG28" s="3" t="n"/>
       <c r="AH28" s="3" t="n">
-        <v>28.58</v>
+        <v>28.43</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>28.58</v>
+        <v>28.47</v>
       </c>
       <c r="AJ28" s="3" t="n">
-        <v>28.52</v>
+        <v>28.43</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>28.58</v>
+        <v>28.45</v>
       </c>
       <c r="AL28" s="3" t="n">
-        <v>28.58</v>
+        <v>28.45</v>
       </c>
       <c r="AM28" s="3" t="n">
-        <v>1113500</v>
+        <v>1230800</v>
       </c>
       <c r="AN28" s="4">
         <f>IF(COUNT(AL28:AL29)=2,ROUND((AL28/AL29-1)*100,4),"")</f>
@@ -4836,22 +5068,22 @@
       </c>
       <c r="AO28" s="3" t="n"/>
       <c r="AP28" s="3" t="n">
-        <v>371.26</v>
+        <v>379.07</v>
       </c>
       <c r="AQ28" s="3" t="n">
-        <v>374.49</v>
+        <v>382.22</v>
       </c>
       <c r="AR28" s="3" t="n">
-        <v>371.03</v>
+        <v>378.83</v>
       </c>
       <c r="AS28" s="3" t="n">
-        <v>371.9</v>
+        <v>379.12</v>
       </c>
       <c r="AT28" s="3" t="n">
-        <v>371.9</v>
+        <v>379.12</v>
       </c>
       <c r="AU28" s="3" t="n">
-        <v>3852400</v>
+        <v>7115100</v>
       </c>
       <c r="AV28" s="4">
         <f>IF(COUNT(AT28:AT29)=2,ROUND((AT28/AT29-1)*100,4),"")</f>
@@ -4859,22 +5091,22 @@
       </c>
       <c r="AW28" s="3" t="n"/>
       <c r="AX28" s="3" t="n">
-        <v>177.82</v>
+        <v>178.16</v>
       </c>
       <c r="AY28" s="3" t="n">
-        <v>179.01</v>
+        <v>181.43</v>
       </c>
       <c r="AZ28" s="3" t="n">
-        <v>175.05</v>
+        <v>178.15</v>
       </c>
       <c r="BA28" s="3" t="n">
-        <v>175.88</v>
+        <v>180.27</v>
       </c>
       <c r="BB28" s="3" t="n">
-        <v>175.88</v>
+        <v>180.27</v>
       </c>
       <c r="BC28" s="3" t="n">
-        <v>7739600</v>
+        <v>5357600</v>
       </c>
       <c r="BD28" s="4">
         <f>IF(COUNT(BB28:BB29)=2,ROUND((BB28/BB29-1)*100,4),"")</f>
@@ -4882,22 +5114,22 @@
       </c>
       <c r="BE28" s="3" t="n"/>
       <c r="BF28" s="3" t="n">
-        <v>55.83</v>
+        <v>56.14</v>
       </c>
       <c r="BG28" s="3" t="n">
-        <v>56.38</v>
+        <v>56.28</v>
       </c>
       <c r="BH28" s="3" t="n">
-        <v>55.69</v>
+        <v>55.91</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>56.31</v>
+        <v>56.05</v>
       </c>
       <c r="BJ28" s="3" t="n">
-        <v>56.31</v>
+        <v>56.05</v>
       </c>
       <c r="BK28" s="3" t="n">
-        <v>32212900</v>
+        <v>25430900</v>
       </c>
       <c r="BL28" s="4">
         <f>IF(COUNT(BJ28:BJ29)=2,ROUND((BJ28/BJ29-1)*100,4),"")</f>
@@ -4905,22 +5137,22 @@
       </c>
       <c r="BM28" s="3" t="n"/>
       <c r="BN28" s="3" t="n">
-        <v>107.55</v>
+        <v>107.95</v>
       </c>
       <c r="BO28" s="3" t="n">
-        <v>107.74</v>
+        <v>107.96</v>
       </c>
       <c r="BP28" s="3" t="n">
-        <v>107.5</v>
+        <v>107.76</v>
       </c>
       <c r="BQ28" s="3" t="n">
-        <v>107.5</v>
+        <v>107.77</v>
       </c>
       <c r="BR28" s="3" t="n">
-        <v>106.7169</v>
+        <v>106.985</v>
       </c>
       <c r="BS28" s="3" t="n">
-        <v>1220700</v>
+        <v>1743300</v>
       </c>
       <c r="BT28" s="4">
         <f>IF(COUNT(BR28:BR29)=2,ROUND((BR28/BR29-1)*100,4),"")</f>
@@ -4928,38 +5160,38 @@
       </c>
       <c r="BU28" s="3" t="n"/>
       <c r="BV28" s="3" t="n">
-        <v>18.96</v>
+        <v>17.42</v>
       </c>
       <c r="BW28" s="3" t="n">
-        <v>19.05</v>
+        <v>19.49</v>
       </c>
       <c r="BX28" s="3" t="n">
-        <v>17.41</v>
+        <v>16.64</v>
       </c>
       <c r="BY28" s="3" t="n">
-        <v>18.58</v>
+        <v>16.64</v>
       </c>
       <c r="BZ28" s="3" t="n">
-        <v>18.58</v>
+        <v>16.64</v>
       </c>
       <c r="CA28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB28" s="3" t="n"/>
       <c r="CC28" s="3" t="n">
-        <v>4.683</v>
+        <v>4.64</v>
       </c>
       <c r="CD28" s="3" t="n">
-        <v>4.691</v>
+        <v>4.661</v>
       </c>
       <c r="CE28" s="3" t="n">
-        <v>4.651</v>
+        <v>4.632</v>
       </c>
       <c r="CF28" s="3" t="n">
-        <v>4.679</v>
+        <v>4.657</v>
       </c>
       <c r="CG28" s="3" t="n">
-        <v>4.679</v>
+        <v>4.657</v>
       </c>
       <c r="CH28" s="3" t="n">
         <v>0</v>
@@ -4991,11 +5223,11 @@
       </c>
       <c r="CP28" s="3" t="n"/>
       <c r="CQ28" s="4">
-        <f>X28-P28</f>
+        <f>IFERROR(X28-P28,"")</f>
         <v/>
       </c>
       <c r="CR28" s="4">
-        <f>AF28-P28</f>
+        <f>IFERROR(AF28-P28,"")</f>
         <v/>
       </c>
       <c r="CS28" s="6">
@@ -5003,11 +5235,11 @@
         <v/>
       </c>
       <c r="CT28" s="4">
-        <f>AN28-AV28</f>
+        <f>IFERROR(AN28-AV28,"")</f>
         <v/>
       </c>
       <c r="CU28" s="4">
-        <f>BD28-BL28</f>
+        <f>IFERROR(BD28-BL28,"")</f>
         <v/>
       </c>
       <c r="CV28" s="6">
@@ -5015,33 +5247,33 @@
         <v/>
       </c>
       <c r="CW28" s="4">
-        <f>P28-BT28</f>
+        <f>IFERROR(P28-BT28,"")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/21</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>739.37</v>
+        <v>746.29</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>742.5599999999999</v>
+        <v>749.04</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>735.21</v>
+        <v>744.1799999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>738.1799999999999</v>
+        <v>748.28</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>738.1799999999999</v>
+        <v>748.28</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>55437300</v>
+        <v>34324300</v>
       </c>
       <c r="H29" s="4">
         <f>IF(COUNT(F29:F30)=2,ROUND((F29/F30-1)*100,4),"")</f>
@@ -5049,22 +5281,22 @@
       </c>
       <c r="I29" s="3" t="n"/>
       <c r="J29" s="3" t="n">
-        <v>82.98999999999999</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>83.25</v>
+        <v>83.77</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>82.95999999999999</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>83.17</v>
+        <v>83.66</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>82.83629999999999</v>
+        <v>83.32429999999999</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>29152800</v>
+        <v>14287500</v>
       </c>
       <c r="P29" s="4">
         <f>IF(COUNT(N29:N30)=2,ROUND((N29/N30-1)*100,4),"")</f>
@@ -5072,22 +5304,22 @@
       </c>
       <c r="Q29" s="3" t="n"/>
       <c r="R29" s="3" t="n">
-        <v>79.28</v>
+        <v>79.72</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>79.37</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>79.15000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>79.23</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>78.8472</v>
+        <v>79.26519999999999</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>52554200</v>
+        <v>27198800</v>
       </c>
       <c r="X29" s="4">
         <f>IF(COUNT(V29:V30)=2,ROUND((V29/V30-1)*100,4),"")</f>
@@ -5095,22 +5327,22 @@
       </c>
       <c r="Y29" s="3" t="n"/>
       <c r="Z29" s="3" t="n">
-        <v>95.42</v>
+        <v>96</v>
       </c>
       <c r="AA29" s="3" t="n">
-        <v>95.56999999999999</v>
+        <v>96</v>
       </c>
       <c r="AB29" s="3" t="n">
-        <v>95.29000000000001</v>
+        <v>95.84</v>
       </c>
       <c r="AC29" s="3" t="n">
-        <v>95.40000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AD29" s="3" t="n">
-        <v>94.8745</v>
+        <v>95.37179999999999</v>
       </c>
       <c r="AE29" s="3" t="n">
-        <v>3439400</v>
+        <v>2091100</v>
       </c>
       <c r="AF29" s="4">
         <f>IF(COUNT(AD29:AD30)=2,ROUND((AD29/AD30-1)*100,4),"")</f>
@@ -5118,22 +5350,22 @@
       </c>
       <c r="AG29" s="3" t="n"/>
       <c r="AH29" s="3" t="n">
-        <v>28.54</v>
+        <v>28.43</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>28.59</v>
+        <v>28.48</v>
       </c>
       <c r="AJ29" s="3" t="n">
-        <v>28.53</v>
+        <v>28.42</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>28.56</v>
+        <v>28.48</v>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>28.56</v>
+        <v>28.48</v>
       </c>
       <c r="AM29" s="3" t="n">
-        <v>1529300</v>
+        <v>1231400</v>
       </c>
       <c r="AN29" s="4">
         <f>IF(COUNT(AL29:AL30)=2,ROUND((AL29/AL30-1)*100,4),"")</f>
@@ -5141,22 +5373,22 @@
       </c>
       <c r="AO29" s="3" t="n"/>
       <c r="AP29" s="3" t="n">
-        <v>372.36</v>
+        <v>371.7</v>
       </c>
       <c r="AQ29" s="3" t="n">
-        <v>373.09</v>
+        <v>375.01</v>
       </c>
       <c r="AR29" s="3" t="n">
-        <v>370.53</v>
+        <v>371.07</v>
       </c>
       <c r="AS29" s="3" t="n">
-        <v>371.52</v>
+        <v>374.81</v>
       </c>
       <c r="AT29" s="3" t="n">
-        <v>371.52</v>
+        <v>374.81</v>
       </c>
       <c r="AU29" s="3" t="n">
-        <v>9820600</v>
+        <v>6070600</v>
       </c>
       <c r="AV29" s="4">
         <f>IF(COUNT(AT29:AT30)=2,ROUND((AT29/AT30-1)*100,4),"")</f>
@@ -5164,22 +5396,22 @@
       </c>
       <c r="AW29" s="3" t="n"/>
       <c r="AX29" s="3" t="n">
-        <v>178.8</v>
+        <v>179.56</v>
       </c>
       <c r="AY29" s="3" t="n">
-        <v>180.39</v>
+        <v>181.02</v>
       </c>
       <c r="AZ29" s="3" t="n">
-        <v>177.2</v>
+        <v>178.17</v>
       </c>
       <c r="BA29" s="3" t="n">
-        <v>178.45</v>
+        <v>180.78</v>
       </c>
       <c r="BB29" s="3" t="n">
-        <v>178.45</v>
+        <v>180.78</v>
       </c>
       <c r="BC29" s="3" t="n">
-        <v>7177000</v>
+        <v>7506800</v>
       </c>
       <c r="BD29" s="4">
         <f>IF(COUNT(BB29:BB30)=2,ROUND((BB29/BB30-1)*100,4),"")</f>
@@ -5187,22 +5419,22 @@
       </c>
       <c r="BE29" s="3" t="n"/>
       <c r="BF29" s="3" t="n">
-        <v>55.68</v>
+        <v>55.99</v>
       </c>
       <c r="BG29" s="3" t="n">
-        <v>55.86</v>
+        <v>56.34</v>
       </c>
       <c r="BH29" s="3" t="n">
-        <v>55.45</v>
+        <v>55.72</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>55.83</v>
+        <v>56.11</v>
       </c>
       <c r="BJ29" s="3" t="n">
-        <v>55.83</v>
+        <v>56.11</v>
       </c>
       <c r="BK29" s="3" t="n">
-        <v>24311000</v>
+        <v>26399000</v>
       </c>
       <c r="BL29" s="4">
         <f>IF(COUNT(BJ29:BJ30)=2,ROUND((BJ29/BJ30-1)*100,4),"")</f>
@@ -5210,22 +5442,22 @@
       </c>
       <c r="BM29" s="3" t="n"/>
       <c r="BN29" s="3" t="n">
-        <v>107.54</v>
+        <v>108</v>
       </c>
       <c r="BO29" s="3" t="n">
-        <v>107.65</v>
+        <v>108.01</v>
       </c>
       <c r="BP29" s="3" t="n">
-        <v>107.48</v>
+        <v>107.84</v>
       </c>
       <c r="BQ29" s="3" t="n">
-        <v>107.49</v>
+        <v>107.88</v>
       </c>
       <c r="BR29" s="3" t="n">
-        <v>106.707</v>
+        <v>107.0942</v>
       </c>
       <c r="BS29" s="3" t="n">
-        <v>2261200</v>
+        <v>1487900</v>
       </c>
       <c r="BT29" s="4">
         <f>IF(COUNT(BR29:BR30)=2,ROUND((BR29/BR30-1)*100,4),"")</f>
@@ -5233,38 +5465,38 @@
       </c>
       <c r="BU29" s="3" t="n"/>
       <c r="BV29" s="3" t="n">
-        <v>17.67</v>
+        <v>17.48</v>
       </c>
       <c r="BW29" s="3" t="n">
-        <v>20.31</v>
+        <v>17.99</v>
       </c>
       <c r="BX29" s="3" t="n">
-        <v>17.32</v>
+        <v>16.86</v>
       </c>
       <c r="BY29" s="3" t="n">
-        <v>18.7</v>
+        <v>17.05</v>
       </c>
       <c r="BZ29" s="3" t="n">
-        <v>18.7</v>
+        <v>17.05</v>
       </c>
       <c r="CA29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB29" s="3" t="n"/>
       <c r="CC29" s="3" t="n">
-        <v>4.699</v>
+        <v>4.6</v>
       </c>
       <c r="CD29" s="3" t="n">
-        <v>4.714</v>
+        <v>4.64</v>
       </c>
       <c r="CE29" s="3" t="n">
-        <v>4.693</v>
+        <v>4.598</v>
       </c>
       <c r="CF29" s="3" t="n">
-        <v>4.703</v>
+        <v>4.628</v>
       </c>
       <c r="CG29" s="3" t="n">
-        <v>4.703</v>
+        <v>4.628</v>
       </c>
       <c r="CH29" s="3" t="n">
         <v>0</v>
@@ -5296,11 +5528,11 @@
       </c>
       <c r="CP29" s="3" t="n"/>
       <c r="CQ29" s="4">
-        <f>X29-P29</f>
+        <f>IFERROR(X29-P29,"")</f>
         <v/>
       </c>
       <c r="CR29" s="4">
-        <f>AF29-P29</f>
+        <f>IFERROR(AF29-P29,"")</f>
         <v/>
       </c>
       <c r="CS29" s="6">
@@ -5308,11 +5540,11 @@
         <v/>
       </c>
       <c r="CT29" s="4">
-        <f>AN29-AV29</f>
+        <f>IFERROR(AN29-AV29,"")</f>
         <v/>
       </c>
       <c r="CU29" s="4">
-        <f>BD29-BL29</f>
+        <f>IFERROR(BD29-BL29,"")</f>
         <v/>
       </c>
       <c r="CV29" s="6">
@@ -5320,33 +5552,33 @@
         <v/>
       </c>
       <c r="CW29" s="4">
-        <f>P29-BT29</f>
+        <f>IFERROR(P29-BT29,"")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026/07/22</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>746.62</v>
+        <v>747.0599999999999</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>750.02</v>
+        <v>748.73</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>746.37</v>
+        <v>741.51</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>747.41</v>
+        <v>742.09</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>747.41</v>
+        <v>742.09</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>32836200</v>
+        <v>50422300</v>
       </c>
       <c r="H30" s="4">
         <f>IF(COUNT(F30:F31)=2,ROUND((F30/F31-1)*100,4),"")</f>
@@ -5354,22 +5586,22 @@
       </c>
       <c r="I30" s="3" t="n"/>
       <c r="J30" s="3" t="n">
-        <v>83.61</v>
+        <v>84.31</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>83.7</v>
+        <v>84.34</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>83.38</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>83.44</v>
+        <v>83.89</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>83.1052</v>
+        <v>83.5534</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>15988400</v>
+        <v>24289000</v>
       </c>
       <c r="P30" s="4">
         <f>IF(COUNT(N30:N31)=2,ROUND((N30/N31-1)*100,4),"")</f>
@@ -5377,22 +5609,22 @@
       </c>
       <c r="Q30" s="3" t="n"/>
       <c r="R30" s="3" t="n">
-        <v>79.61</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>79.65000000000001</v>
+        <v>79.77</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>79.48</v>
+        <v>79.67</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>79.52</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>79.1358</v>
+        <v>79.295</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>24851700</v>
+        <v>19767900</v>
       </c>
       <c r="X30" s="4">
         <f>IF(COUNT(V30:V31)=2,ROUND((V30/V31-1)*100,4),"")</f>
@@ -5400,22 +5632,22 @@
       </c>
       <c r="Y30" s="3" t="n"/>
       <c r="Z30" s="3" t="n">
-        <v>95.84999999999999</v>
+        <v>96.02</v>
       </c>
       <c r="AA30" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>96.08</v>
       </c>
       <c r="AB30" s="3" t="n">
-        <v>95.69</v>
+        <v>95.92</v>
       </c>
       <c r="AC30" s="3" t="n">
-        <v>95.75</v>
+        <v>95.95</v>
       </c>
       <c r="AD30" s="3" t="n">
-        <v>95.2226</v>
+        <v>95.42149999999999</v>
       </c>
       <c r="AE30" s="3" t="n">
-        <v>2546100</v>
+        <v>1897200</v>
       </c>
       <c r="AF30" s="4">
         <f>IF(COUNT(AD30:AD31)=2,ROUND((AD30/AD31-1)*100,4),"")</f>
@@ -5423,22 +5655,22 @@
       </c>
       <c r="AG30" s="3" t="n"/>
       <c r="AH30" s="3" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="AI30" s="3" t="n">
         <v>28.43</v>
       </c>
-      <c r="AI30" s="3" t="n">
-        <v>28.47</v>
-      </c>
       <c r="AJ30" s="3" t="n">
-        <v>28.43</v>
+        <v>28.38</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>28.45</v>
+        <v>28.39</v>
       </c>
       <c r="AL30" s="3" t="n">
-        <v>28.45</v>
+        <v>28.39</v>
       </c>
       <c r="AM30" s="3" t="n">
-        <v>1230800</v>
+        <v>1898100</v>
       </c>
       <c r="AN30" s="4">
         <f>IF(COUNT(AL30:AL31)=2,ROUND((AL30/AL31-1)*100,4),"")</f>
@@ -5446,22 +5678,22 @@
       </c>
       <c r="AO30" s="3" t="n"/>
       <c r="AP30" s="3" t="n">
-        <v>379.07</v>
+        <v>367.79</v>
       </c>
       <c r="AQ30" s="3" t="n">
-        <v>382.22</v>
+        <v>368.79</v>
       </c>
       <c r="AR30" s="3" t="n">
-        <v>378.83</v>
+        <v>366.8</v>
       </c>
       <c r="AS30" s="3" t="n">
-        <v>379.12</v>
+        <v>367.6</v>
       </c>
       <c r="AT30" s="3" t="n">
-        <v>379.12</v>
+        <v>367.6</v>
       </c>
       <c r="AU30" s="3" t="n">
-        <v>7115100</v>
+        <v>3922500</v>
       </c>
       <c r="AV30" s="4">
         <f>IF(COUNT(AT30:AT31)=2,ROUND((AT30/AT31-1)*100,4),"")</f>
@@ -5469,22 +5701,22 @@
       </c>
       <c r="AW30" s="3" t="n"/>
       <c r="AX30" s="3" t="n">
-        <v>178.16</v>
+        <v>177.19</v>
       </c>
       <c r="AY30" s="3" t="n">
-        <v>181.43</v>
+        <v>178.7</v>
       </c>
       <c r="AZ30" s="3" t="n">
-        <v>178.15</v>
+        <v>175.52</v>
       </c>
       <c r="BA30" s="3" t="n">
-        <v>180.27</v>
+        <v>175.71</v>
       </c>
       <c r="BB30" s="3" t="n">
-        <v>180.27</v>
+        <v>175.71</v>
       </c>
       <c r="BC30" s="3" t="n">
-        <v>5357600</v>
+        <v>7638600</v>
       </c>
       <c r="BD30" s="4">
         <f>IF(COUNT(BB30:BB31)=2,ROUND((BB30/BB31-1)*100,4),"")</f>
@@ -5492,22 +5724,22 @@
       </c>
       <c r="BE30" s="3" t="n"/>
       <c r="BF30" s="3" t="n">
-        <v>56.14</v>
+        <v>56.3</v>
       </c>
       <c r="BG30" s="3" t="n">
-        <v>56.28</v>
+        <v>56.38</v>
       </c>
       <c r="BH30" s="3" t="n">
-        <v>55.91</v>
+        <v>55.89</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>56.05</v>
+        <v>56.04</v>
       </c>
       <c r="BJ30" s="3" t="n">
-        <v>56.05</v>
+        <v>56.04</v>
       </c>
       <c r="BK30" s="3" t="n">
-        <v>25430900</v>
+        <v>38162600</v>
       </c>
       <c r="BL30" s="4">
         <f>IF(COUNT(BJ30:BJ31)=2,ROUND((BJ30/BJ31-1)*100,4),"")</f>
@@ -5515,22 +5747,22 @@
       </c>
       <c r="BM30" s="3" t="n"/>
       <c r="BN30" s="3" t="n">
-        <v>107.95</v>
+        <v>108.19</v>
       </c>
       <c r="BO30" s="3" t="n">
-        <v>107.96</v>
+        <v>108.22</v>
       </c>
       <c r="BP30" s="3" t="n">
-        <v>107.76</v>
+        <v>108.01</v>
       </c>
       <c r="BQ30" s="3" t="n">
-        <v>107.77</v>
+        <v>108.05</v>
       </c>
       <c r="BR30" s="3" t="n">
-        <v>106.985</v>
+        <v>107.2629</v>
       </c>
       <c r="BS30" s="3" t="n">
-        <v>1743300</v>
+        <v>1010500</v>
       </c>
       <c r="BT30" s="4">
         <f>IF(COUNT(BR30:BR31)=2,ROUND((BR30/BR31-1)*100,4),"")</f>
@@ -5538,38 +5770,38 @@
       </c>
       <c r="BU30" s="3" t="n"/>
       <c r="BV30" s="3" t="n">
-        <v>17.42</v>
+        <v>18.9</v>
       </c>
       <c r="BW30" s="3" t="n">
-        <v>19.49</v>
+        <v>18.94</v>
       </c>
       <c r="BX30" s="3" t="n">
-        <v>16.64</v>
+        <v>17.41</v>
       </c>
       <c r="BY30" s="3" t="n">
-        <v>16.64</v>
+        <v>18.65</v>
       </c>
       <c r="BZ30" s="3" t="n">
-        <v>16.64</v>
+        <v>18.65</v>
       </c>
       <c r="CA30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB30" s="3" t="n"/>
       <c r="CC30" s="3" t="n">
-        <v>4.64</v>
+        <v>4.566</v>
       </c>
       <c r="CD30" s="3" t="n">
-        <v>4.661</v>
+        <v>4.608</v>
       </c>
       <c r="CE30" s="3" t="n">
-        <v>4.632</v>
+        <v>4.56</v>
       </c>
       <c r="CF30" s="3" t="n">
-        <v>4.657</v>
+        <v>4.598</v>
       </c>
       <c r="CG30" s="3" t="n">
-        <v>4.657</v>
+        <v>4.598</v>
       </c>
       <c r="CH30" s="3" t="n">
         <v>0</v>
@@ -5601,11 +5833,11 @@
       </c>
       <c r="CP30" s="3" t="n"/>
       <c r="CQ30" s="4">
-        <f>X30-P30</f>
+        <f>IFERROR(X30-P30,"")</f>
         <v/>
       </c>
       <c r="CR30" s="4">
-        <f>AF30-P30</f>
+        <f>IFERROR(AF30-P30,"")</f>
         <v/>
       </c>
       <c r="CS30" s="6">
@@ -5613,11 +5845,11 @@
         <v/>
       </c>
       <c r="CT30" s="4">
-        <f>AN30-AV30</f>
+        <f>IFERROR(AN30-AV30,"")</f>
         <v/>
       </c>
       <c r="CU30" s="4">
-        <f>BD30-BL30</f>
+        <f>IFERROR(BD30-BL30,"")</f>
         <v/>
       </c>
       <c r="CV30" s="6">
@@ -5625,33 +5857,33 @@
         <v/>
       </c>
       <c r="CW30" s="4">
-        <f>P30-BT30</f>
+        <f>IFERROR(P30-BT30,"")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026/07/21</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>746.29</v>
+        <v>742.08</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>749.04</v>
+        <v>747.29</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>744.1799999999999</v>
+        <v>740.8</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>748.28</v>
+        <v>743.29</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>748.28</v>
+        <v>743.29</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>34324300</v>
+        <v>62651000</v>
       </c>
       <c r="H31" s="4">
         <f>IF(COUNT(F31:F32)=2,ROUND((F31/F32-1)*100,4),"")</f>
@@ -5659,22 +5891,22 @@
       </c>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n">
-        <v>83.73999999999999</v>
+        <v>84.62</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>83.77</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>83.43000000000001</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>83.66</v>
+        <v>84.52</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>83.32429999999999</v>
+        <v>84.18089999999999</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>14287500</v>
+        <v>22065600</v>
       </c>
       <c r="P31" s="4">
         <f>IF(COUNT(N31:N32)=2,ROUND((N31/N32-1)*100,4),"")</f>
@@ -5682,13 +5914,13 @@
       </c>
       <c r="Q31" s="3" t="n"/>
       <c r="R31" s="3" t="n">
-        <v>79.72</v>
+        <v>79.75</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>79.73999999999999</v>
+        <v>79.84</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>79.63</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>79.65000000000001</v>
@@ -5697,7 +5929,7 @@
         <v>79.26519999999999</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>27198800</v>
+        <v>42020100</v>
       </c>
       <c r="X31" s="4">
         <f>IF(COUNT(V31:V32)=2,ROUND((V31/V32-1)*100,4),"")</f>
@@ -5705,22 +5937,22 @@
       </c>
       <c r="Y31" s="3" t="n"/>
       <c r="Z31" s="3" t="n">
-        <v>96</v>
+        <v>96.09</v>
       </c>
       <c r="AA31" s="3" t="n">
-        <v>96</v>
+        <v>96.14</v>
       </c>
       <c r="AB31" s="3" t="n">
-        <v>95.84</v>
+        <v>95.95</v>
       </c>
       <c r="AC31" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>95.98</v>
       </c>
       <c r="AD31" s="3" t="n">
-        <v>95.37179999999999</v>
+        <v>95.4513</v>
       </c>
       <c r="AE31" s="3" t="n">
-        <v>2091100</v>
+        <v>1387300</v>
       </c>
       <c r="AF31" s="4">
         <f>IF(COUNT(AD31:AD32)=2,ROUND((AD31/AD32-1)*100,4),"")</f>
@@ -5728,22 +5960,22 @@
       </c>
       <c r="AG31" s="3" t="n"/>
       <c r="AH31" s="3" t="n">
-        <v>28.43</v>
+        <v>28.38</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>28.48</v>
+        <v>28.38</v>
       </c>
       <c r="AJ31" s="3" t="n">
-        <v>28.42</v>
+        <v>28.33</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>28.48</v>
+        <v>28.33</v>
       </c>
       <c r="AL31" s="3" t="n">
-        <v>28.48</v>
+        <v>28.33</v>
       </c>
       <c r="AM31" s="3" t="n">
-        <v>1231400</v>
+        <v>1134200</v>
       </c>
       <c r="AN31" s="4">
         <f>IF(COUNT(AL31:AL32)=2,ROUND((AL31/AL32-1)*100,4),"")</f>
@@ -5751,22 +5983,22 @@
       </c>
       <c r="AO31" s="3" t="n"/>
       <c r="AP31" s="3" t="n">
-        <v>371.7</v>
+        <v>364.11</v>
       </c>
       <c r="AQ31" s="3" t="n">
-        <v>375.01</v>
+        <v>369.21</v>
       </c>
       <c r="AR31" s="3" t="n">
-        <v>371.07</v>
+        <v>363.6</v>
       </c>
       <c r="AS31" s="3" t="n">
-        <v>374.81</v>
+        <v>368.41</v>
       </c>
       <c r="AT31" s="3" t="n">
-        <v>374.81</v>
+        <v>368.41</v>
       </c>
       <c r="AU31" s="3" t="n">
-        <v>6070600</v>
+        <v>6456600</v>
       </c>
       <c r="AV31" s="4">
         <f>IF(COUNT(AT31:AT32)=2,ROUND((AT31/AT32-1)*100,4),"")</f>
@@ -5774,22 +6006,22 @@
       </c>
       <c r="AW31" s="3" t="n"/>
       <c r="AX31" s="3" t="n">
-        <v>179.56</v>
+        <v>172.85</v>
       </c>
       <c r="AY31" s="3" t="n">
-        <v>181.02</v>
+        <v>177.92</v>
       </c>
       <c r="AZ31" s="3" t="n">
-        <v>178.17</v>
+        <v>171.34</v>
       </c>
       <c r="BA31" s="3" t="n">
-        <v>180.78</v>
+        <v>175.59</v>
       </c>
       <c r="BB31" s="3" t="n">
-        <v>180.78</v>
+        <v>175.59</v>
       </c>
       <c r="BC31" s="3" t="n">
-        <v>7506800</v>
+        <v>12036700</v>
       </c>
       <c r="BD31" s="4">
         <f>IF(COUNT(BB31:BB32)=2,ROUND((BB31/BB32-1)*100,4),"")</f>
@@ -5797,22 +6029,22 @@
       </c>
       <c r="BE31" s="3" t="n"/>
       <c r="BF31" s="3" t="n">
-        <v>55.99</v>
+        <v>56.43</v>
       </c>
       <c r="BG31" s="3" t="n">
-        <v>56.34</v>
+        <v>56.94</v>
       </c>
       <c r="BH31" s="3" t="n">
-        <v>55.72</v>
+        <v>56.12</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>56.11</v>
+        <v>56.26</v>
       </c>
       <c r="BJ31" s="3" t="n">
-        <v>56.11</v>
+        <v>56.26</v>
       </c>
       <c r="BK31" s="3" t="n">
-        <v>26399000</v>
+        <v>42881800</v>
       </c>
       <c r="BL31" s="4">
         <f>IF(COUNT(BJ31:BJ32)=2,ROUND((BJ31/BJ32-1)*100,4),"")</f>
@@ -5820,22 +6052,22 @@
       </c>
       <c r="BM31" s="3" t="n"/>
       <c r="BN31" s="3" t="n">
-        <v>108</v>
+        <v>108.27</v>
       </c>
       <c r="BO31" s="3" t="n">
-        <v>108.01</v>
+        <v>108.37</v>
       </c>
       <c r="BP31" s="3" t="n">
-        <v>107.84</v>
+        <v>108.17</v>
       </c>
       <c r="BQ31" s="3" t="n">
-        <v>107.88</v>
+        <v>108.27</v>
       </c>
       <c r="BR31" s="3" t="n">
-        <v>107.0942</v>
+        <v>107.4813</v>
       </c>
       <c r="BS31" s="3" t="n">
-        <v>1487900</v>
+        <v>1788800</v>
       </c>
       <c r="BT31" s="4">
         <f>IF(COUNT(BR31:BR32)=2,ROUND((BR31/BR32-1)*100,4),"")</f>
@@ -5843,38 +6075,38 @@
       </c>
       <c r="BU31" s="3" t="n"/>
       <c r="BV31" s="3" t="n">
-        <v>17.48</v>
+        <v>18.01</v>
       </c>
       <c r="BW31" s="3" t="n">
-        <v>17.99</v>
+        <v>19.5</v>
       </c>
       <c r="BX31" s="3" t="n">
-        <v>16.86</v>
+        <v>17.68</v>
       </c>
       <c r="BY31" s="3" t="n">
-        <v>17.05</v>
+        <v>18.77</v>
       </c>
       <c r="BZ31" s="3" t="n">
-        <v>17.05</v>
+        <v>18.77</v>
       </c>
       <c r="CA31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB31" s="3" t="n"/>
       <c r="CC31" s="3" t="n">
-        <v>4.6</v>
+        <v>4.521</v>
       </c>
       <c r="CD31" s="3" t="n">
-        <v>4.64</v>
+        <v>4.55</v>
       </c>
       <c r="CE31" s="3" t="n">
-        <v>4.598</v>
+        <v>4.511</v>
       </c>
       <c r="CF31" s="3" t="n">
-        <v>4.628</v>
+        <v>4.541</v>
       </c>
       <c r="CG31" s="3" t="n">
-        <v>4.628</v>
+        <v>4.541</v>
       </c>
       <c r="CH31" s="3" t="n">
         <v>0</v>
@@ -5906,11 +6138,11 @@
       </c>
       <c r="CP31" s="3" t="n"/>
       <c r="CQ31" s="4">
-        <f>X31-P31</f>
+        <f>IFERROR(X31-P31,"")</f>
         <v/>
       </c>
       <c r="CR31" s="4">
-        <f>AF31-P31</f>
+        <f>IFERROR(AF31-P31,"")</f>
         <v/>
       </c>
       <c r="CS31" s="6">
@@ -5918,11 +6150,11 @@
         <v/>
       </c>
       <c r="CT31" s="4">
-        <f>AN31-AV31</f>
+        <f>IFERROR(AN31-AV31,"")</f>
         <v/>
       </c>
       <c r="CU31" s="4">
-        <f>BD31-BL31</f>
+        <f>IFERROR(BD31-BL31,"")</f>
         <v/>
       </c>
       <c r="CV31" s="6">
@@ -5930,33 +6162,33 @@
         <v/>
       </c>
       <c r="CW31" s="4">
-        <f>P31-BT31</f>
+        <f>IFERROR(P31-BT31,"")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>747.0599999999999</v>
+        <v>752.76</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>748.73</v>
+        <v>754.5700000000001</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>741.51</v>
+        <v>747.88</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>742.09</v>
+        <v>750.72</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>742.09</v>
+        <v>750.72</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>50422300</v>
+        <v>46409800</v>
       </c>
       <c r="H32" s="4">
         <f>IF(COUNT(F32:F33)=2,ROUND((F32/F33-1)*100,4),"")</f>
@@ -5964,22 +6196,22 @@
       </c>
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n">
-        <v>84.31</v>
+        <v>83.84</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>84.34</v>
+        <v>84.22</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>83.81999999999999</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>83.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>83.5534</v>
+        <v>83.8721</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>24289000</v>
+        <v>20817800</v>
       </c>
       <c r="P32" s="4">
         <f>IF(COUNT(N32:N33)=2,ROUND((N32/N33-1)*100,4),"")</f>
@@ -5987,22 +6219,22 @@
       </c>
       <c r="Q32" s="3" t="n"/>
       <c r="R32" s="3" t="n">
-        <v>79.73999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>79.77</v>
+        <v>79.84</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>79.67</v>
+        <v>79.73</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>79.68000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>79.295</v>
+        <v>79.4145</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>19767900</v>
+        <v>22780300</v>
       </c>
       <c r="X32" s="4">
         <f>IF(COUNT(V32:V33)=2,ROUND((V32/V33-1)*100,4),"")</f>
@@ -6010,22 +6242,22 @@
       </c>
       <c r="Y32" s="3" t="n"/>
       <c r="Z32" s="3" t="n">
-        <v>96.02</v>
+        <v>96</v>
       </c>
       <c r="AA32" s="3" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="AB32" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="AC32" s="3" t="n">
         <v>96.08</v>
       </c>
-      <c r="AB32" s="3" t="n">
-        <v>95.92</v>
-      </c>
-      <c r="AC32" s="3" t="n">
-        <v>95.95</v>
-      </c>
       <c r="AD32" s="3" t="n">
-        <v>95.42149999999999</v>
+        <v>95.5508</v>
       </c>
       <c r="AE32" s="3" t="n">
-        <v>1897200</v>
+        <v>1653500</v>
       </c>
       <c r="AF32" s="4">
         <f>IF(COUNT(AD32:AD33)=2,ROUND((AD32/AD33-1)*100,4),"")</f>
@@ -6033,22 +6265,22 @@
       </c>
       <c r="AG32" s="3" t="n"/>
       <c r="AH32" s="3" t="n">
-        <v>28.38</v>
+        <v>28.28</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>28.43</v>
+        <v>28.35</v>
       </c>
       <c r="AJ32" s="3" t="n">
-        <v>28.38</v>
+        <v>28.28</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>28.39</v>
+        <v>28.34</v>
       </c>
       <c r="AL32" s="3" t="n">
-        <v>28.39</v>
+        <v>28.34</v>
       </c>
       <c r="AM32" s="3" t="n">
-        <v>1898100</v>
+        <v>2893800</v>
       </c>
       <c r="AN32" s="4">
         <f>IF(COUNT(AL32:AL33)=2,ROUND((AL32/AL33-1)*100,4),"")</f>
@@ -6056,22 +6288,22 @@
       </c>
       <c r="AO32" s="3" t="n"/>
       <c r="AP32" s="3" t="n">
-        <v>367.79</v>
+        <v>367.45</v>
       </c>
       <c r="AQ32" s="3" t="n">
-        <v>368.79</v>
+        <v>368.43</v>
       </c>
       <c r="AR32" s="3" t="n">
-        <v>366.8</v>
+        <v>364.05</v>
       </c>
       <c r="AS32" s="3" t="n">
-        <v>367.6</v>
+        <v>364.96</v>
       </c>
       <c r="AT32" s="3" t="n">
-        <v>367.6</v>
+        <v>364.96</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>3922500</v>
+        <v>9048000</v>
       </c>
       <c r="AV32" s="4">
         <f>IF(COUNT(AT32:AT33)=2,ROUND((AT32/AT33-1)*100,4),"")</f>
@@ -6079,22 +6311,22 @@
       </c>
       <c r="AW32" s="3" t="n"/>
       <c r="AX32" s="3" t="n">
-        <v>177.19</v>
+        <v>179</v>
       </c>
       <c r="AY32" s="3" t="n">
-        <v>178.7</v>
+        <v>179.48</v>
       </c>
       <c r="AZ32" s="3" t="n">
-        <v>175.52</v>
+        <v>176.41</v>
       </c>
       <c r="BA32" s="3" t="n">
-        <v>175.71</v>
+        <v>177.52</v>
       </c>
       <c r="BB32" s="3" t="n">
-        <v>175.71</v>
+        <v>177.52</v>
       </c>
       <c r="BC32" s="3" t="n">
-        <v>7638600</v>
+        <v>8666500</v>
       </c>
       <c r="BD32" s="4">
         <f>IF(COUNT(BB32:BB33)=2,ROUND((BB32/BB33-1)*100,4),"")</f>
@@ -6102,22 +6334,22 @@
       </c>
       <c r="BE32" s="3" t="n"/>
       <c r="BF32" s="3" t="n">
-        <v>56.3</v>
+        <v>56.76</v>
       </c>
       <c r="BG32" s="3" t="n">
-        <v>56.38</v>
+        <v>56.84</v>
       </c>
       <c r="BH32" s="3" t="n">
-        <v>55.89</v>
+        <v>56.39</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>56.04</v>
+        <v>56.75</v>
       </c>
       <c r="BJ32" s="3" t="n">
-        <v>56.04</v>
+        <v>56.75</v>
       </c>
       <c r="BK32" s="3" t="n">
-        <v>38162600</v>
+        <v>27591200</v>
       </c>
       <c r="BL32" s="4">
         <f>IF(COUNT(BJ32:BJ33)=2,ROUND((BJ32/BJ33-1)*100,4),"")</f>
@@ -6125,22 +6357,22 @@
       </c>
       <c r="BM32" s="3" t="n"/>
       <c r="BN32" s="3" t="n">
-        <v>108.19</v>
+        <v>107.98</v>
       </c>
       <c r="BO32" s="3" t="n">
-        <v>108.22</v>
+        <v>108.05</v>
       </c>
       <c r="BP32" s="3" t="n">
-        <v>108.01</v>
+        <v>107.92</v>
       </c>
       <c r="BQ32" s="3" t="n">
-        <v>108.05</v>
+        <v>107.97</v>
       </c>
       <c r="BR32" s="3" t="n">
-        <v>107.2629</v>
+        <v>107.1835</v>
       </c>
       <c r="BS32" s="3" t="n">
-        <v>1010500</v>
+        <v>863900</v>
       </c>
       <c r="BT32" s="4">
         <f>IF(COUNT(BR32:BR33)=2,ROUND((BR32/BR33-1)*100,4),"")</f>
@@ -6148,38 +6380,38 @@
       </c>
       <c r="BU32" s="3" t="n"/>
       <c r="BV32" s="3" t="n">
-        <v>18.9</v>
+        <v>15.82</v>
       </c>
       <c r="BW32" s="3" t="n">
-        <v>18.94</v>
+        <v>17.23</v>
       </c>
       <c r="BX32" s="3" t="n">
-        <v>17.41</v>
+        <v>15.77</v>
       </c>
       <c r="BY32" s="3" t="n">
-        <v>18.65</v>
+        <v>16.73</v>
       </c>
       <c r="BZ32" s="3" t="n">
-        <v>18.65</v>
+        <v>16.73</v>
       </c>
       <c r="CA32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB32" s="3" t="n"/>
       <c r="CC32" s="3" t="n">
-        <v>4.566</v>
+        <v>4.582</v>
       </c>
       <c r="CD32" s="3" t="n">
-        <v>4.608</v>
+        <v>4.596</v>
       </c>
       <c r="CE32" s="3" t="n">
-        <v>4.56</v>
+        <v>4.561</v>
       </c>
       <c r="CF32" s="3" t="n">
-        <v>4.598</v>
+        <v>4.569</v>
       </c>
       <c r="CG32" s="3" t="n">
-        <v>4.598</v>
+        <v>4.569</v>
       </c>
       <c r="CH32" s="3" t="n">
         <v>0</v>
@@ -6211,11 +6443,11 @@
       </c>
       <c r="CP32" s="3" t="n"/>
       <c r="CQ32" s="4">
-        <f>X32-P32</f>
+        <f>IFERROR(X32-P32,"")</f>
         <v/>
       </c>
       <c r="CR32" s="4">
-        <f>AF32-P32</f>
+        <f>IFERROR(AF32-P32,"")</f>
         <v/>
       </c>
       <c r="CS32" s="6">
@@ -6223,11 +6455,11 @@
         <v/>
       </c>
       <c r="CT32" s="4">
-        <f>AN32-AV32</f>
+        <f>IFERROR(AN32-AV32,"")</f>
         <v/>
       </c>
       <c r="CU32" s="4">
-        <f>BD32-BL32</f>
+        <f>IFERROR(BD32-BL32,"")</f>
         <v/>
       </c>
       <c r="CV32" s="6">
@@ -6235,33 +6467,33 @@
         <v/>
       </c>
       <c r="CW32" s="4">
-        <f>P32-BT32</f>
+        <f>IFERROR(P32-BT32,"")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/07/15</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>742.08</v>
+        <v>754.24</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>747.29</v>
+        <v>755.58</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>740.8</v>
+        <v>750.2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>743.29</v>
+        <v>754.8099999999999</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>743.29</v>
+        <v>754.8099999999999</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>62651000</v>
+        <v>43844800</v>
       </c>
       <c r="H33" s="4">
         <f>IF(COUNT(F33:F34)=2,ROUND((F33/F34-1)*100,4),"")</f>
@@ -6269,22 +6501,22 @@
       </c>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n">
-        <v>84.62</v>
+        <v>84.08</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>84.81999999999999</v>
+        <v>84.41</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>84.48999999999999</v>
+        <v>84.08</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>84.52</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>84.18089999999999</v>
+        <v>83.902</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>22065600</v>
+        <v>17837800</v>
       </c>
       <c r="P33" s="4">
         <f>IF(COUNT(N33:N34)=2,ROUND((N33/N34-1)*100,4),"")</f>
@@ -6292,22 +6524,22 @@
       </c>
       <c r="Q33" s="3" t="n"/>
       <c r="R33" s="3" t="n">
-        <v>79.75</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>79.84</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>79.63</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>79.65000000000001</v>
+        <v>79.81</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>79.26519999999999</v>
+        <v>79.42440000000001</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>42020100</v>
+        <v>26948800</v>
       </c>
       <c r="X33" s="4">
         <f>IF(COUNT(V33:V34)=2,ROUND((V33/V34-1)*100,4),"")</f>
@@ -6315,22 +6547,22 @@
       </c>
       <c r="Y33" s="3" t="n"/>
       <c r="Z33" s="3" t="n">
-        <v>96.09</v>
+        <v>96</v>
       </c>
       <c r="AA33" s="3" t="n">
-        <v>96.14</v>
+        <v>96.13</v>
       </c>
       <c r="AB33" s="3" t="n">
-        <v>95.95</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC33" s="3" t="n">
-        <v>95.98</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="AD33" s="3" t="n">
-        <v>95.4513</v>
+        <v>95.5408</v>
       </c>
       <c r="AE33" s="3" t="n">
-        <v>1387300</v>
+        <v>1807300</v>
       </c>
       <c r="AF33" s="4">
         <f>IF(COUNT(AD33:AD34)=2,ROUND((AD33/AD34-1)*100,4),"")</f>
@@ -6338,22 +6570,22 @@
       </c>
       <c r="AG33" s="3" t="n"/>
       <c r="AH33" s="3" t="n">
-        <v>28.38</v>
+        <v>28.37</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>28.38</v>
+        <v>28.37</v>
       </c>
       <c r="AJ33" s="3" t="n">
-        <v>28.33</v>
+        <v>28.22</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>28.33</v>
+        <v>28.25</v>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>28.33</v>
+        <v>28.25</v>
       </c>
       <c r="AM33" s="3" t="n">
-        <v>1134200</v>
+        <v>2209200</v>
       </c>
       <c r="AN33" s="4">
         <f>IF(COUNT(AL33:AL34)=2,ROUND((AL33/AL34-1)*100,4),"")</f>
@@ -6361,22 +6593,22 @@
       </c>
       <c r="AO33" s="3" t="n"/>
       <c r="AP33" s="3" t="n">
-        <v>364.11</v>
+        <v>372.11</v>
       </c>
       <c r="AQ33" s="3" t="n">
-        <v>369.21</v>
+        <v>374.49</v>
       </c>
       <c r="AR33" s="3" t="n">
-        <v>363.6</v>
+        <v>369.5</v>
       </c>
       <c r="AS33" s="3" t="n">
-        <v>368.41</v>
+        <v>372.35</v>
       </c>
       <c r="AT33" s="3" t="n">
-        <v>368.41</v>
+        <v>372.35</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>6456600</v>
+        <v>7683700</v>
       </c>
       <c r="AV33" s="4">
         <f>IF(COUNT(AT33:AT34)=2,ROUND((AT33/AT34-1)*100,4),"")</f>
@@ -6384,22 +6616,22 @@
       </c>
       <c r="AW33" s="3" t="n"/>
       <c r="AX33" s="3" t="n">
-        <v>172.85</v>
+        <v>185.11</v>
       </c>
       <c r="AY33" s="3" t="n">
-        <v>177.92</v>
+        <v>185.29</v>
       </c>
       <c r="AZ33" s="3" t="n">
-        <v>171.34</v>
+        <v>178.22</v>
       </c>
       <c r="BA33" s="3" t="n">
-        <v>175.59</v>
+        <v>181.58</v>
       </c>
       <c r="BB33" s="3" t="n">
-        <v>175.59</v>
+        <v>181.58</v>
       </c>
       <c r="BC33" s="3" t="n">
-        <v>12036700</v>
+        <v>9256800</v>
       </c>
       <c r="BD33" s="4">
         <f>IF(COUNT(BB33:BB34)=2,ROUND((BB33/BB34-1)*100,4),"")</f>
@@ -6407,22 +6639,22 @@
       </c>
       <c r="BE33" s="3" t="n"/>
       <c r="BF33" s="3" t="n">
-        <v>56.43</v>
+        <v>56.3</v>
       </c>
       <c r="BG33" s="3" t="n">
-        <v>56.94</v>
+        <v>56.82</v>
       </c>
       <c r="BH33" s="3" t="n">
-        <v>56.12</v>
+        <v>56.18</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>56.26</v>
+        <v>56.56</v>
       </c>
       <c r="BJ33" s="3" t="n">
-        <v>56.26</v>
+        <v>56.56</v>
       </c>
       <c r="BK33" s="3" t="n">
-        <v>42881800</v>
+        <v>49425400</v>
       </c>
       <c r="BL33" s="4">
         <f>IF(COUNT(BJ33:BJ34)=2,ROUND((BJ33/BJ34-1)*100,4),"")</f>
@@ -6430,22 +6662,22 @@
       </c>
       <c r="BM33" s="3" t="n"/>
       <c r="BN33" s="3" t="n">
-        <v>108.27</v>
+        <v>107.99</v>
       </c>
       <c r="BO33" s="3" t="n">
-        <v>108.37</v>
+        <v>108.16</v>
       </c>
       <c r="BP33" s="3" t="n">
-        <v>108.17</v>
+        <v>107.99</v>
       </c>
       <c r="BQ33" s="3" t="n">
-        <v>108.27</v>
+        <v>108.07</v>
       </c>
       <c r="BR33" s="3" t="n">
-        <v>107.4813</v>
+        <v>107.2828</v>
       </c>
       <c r="BS33" s="3" t="n">
-        <v>1788800</v>
+        <v>1900400</v>
       </c>
       <c r="BT33" s="4">
         <f>IF(COUNT(BR33:BR34)=2,ROUND((BR33/BR34-1)*100,4),"")</f>
@@ -6453,38 +6685,38 @@
       </c>
       <c r="BU33" s="3" t="n"/>
       <c r="BV33" s="3" t="n">
-        <v>18.01</v>
+        <v>16.2</v>
       </c>
       <c r="BW33" s="3" t="n">
-        <v>19.5</v>
+        <v>16.57</v>
       </c>
       <c r="BX33" s="3" t="n">
-        <v>17.68</v>
+        <v>15.64</v>
       </c>
       <c r="BY33" s="3" t="n">
-        <v>18.77</v>
+        <v>15.67</v>
       </c>
       <c r="BZ33" s="3" t="n">
-        <v>18.77</v>
+        <v>15.67</v>
       </c>
       <c r="CA33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB33" s="3" t="n"/>
       <c r="CC33" s="3" t="n">
-        <v>4.521</v>
+        <v>4.608</v>
       </c>
       <c r="CD33" s="3" t="n">
-        <v>4.55</v>
+        <v>4.61</v>
       </c>
       <c r="CE33" s="3" t="n">
-        <v>4.511</v>
+        <v>4.539</v>
       </c>
       <c r="CF33" s="3" t="n">
-        <v>4.541</v>
+        <v>4.545</v>
       </c>
       <c r="CG33" s="3" t="n">
-        <v>4.541</v>
+        <v>4.545</v>
       </c>
       <c r="CH33" s="3" t="n">
         <v>0</v>
@@ -6516,11 +6748,11 @@
       </c>
       <c r="CP33" s="3" t="n"/>
       <c r="CQ33" s="4">
-        <f>X33-P33</f>
+        <f>IFERROR(X33-P33,"")</f>
         <v/>
       </c>
       <c r="CR33" s="4">
-        <f>AF33-P33</f>
+        <f>IFERROR(AF33-P33,"")</f>
         <v/>
       </c>
       <c r="CS33" s="6">
@@ -6528,11 +6760,11 @@
         <v/>
       </c>
       <c r="CT33" s="4">
-        <f>AN33-AV33</f>
+        <f>IFERROR(AN33-AV33,"")</f>
         <v/>
       </c>
       <c r="CU33" s="4">
-        <f>BD33-BL33</f>
+        <f>IFERROR(BD33-BL33,"")</f>
         <v/>
       </c>
       <c r="CV33" s="6">
@@ -6540,33 +6772,33 @@
         <v/>
       </c>
       <c r="CW33" s="4">
-        <f>P33-BT33</f>
+        <f>IFERROR(P33-BT33,"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>752.76</v>
+        <v>750.91</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>754.5700000000001</v>
+        <v>753.34</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>747.88</v>
+        <v>748.66</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>750.72</v>
+        <v>751.83</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>750.72</v>
+        <v>751.83</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>46409800</v>
+        <v>35143100</v>
       </c>
       <c r="H34" s="4">
         <f>IF(COUNT(F34:F35)=2,ROUND((F34/F35-1)*100,4),"")</f>
@@ -6574,22 +6806,22 @@
       </c>
       <c r="I34" s="3" t="n"/>
       <c r="J34" s="3" t="n">
-        <v>83.84</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>84.22</v>
+        <v>84.5</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>83.79000000000001</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>84.20999999999999</v>
+        <v>84.08</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>83.8721</v>
+        <v>83.7427</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>20817800</v>
+        <v>23793500</v>
       </c>
       <c r="P34" s="4">
         <f>IF(COUNT(N34:N35)=2,ROUND((N34/N35-1)*100,4),"")</f>
@@ -6597,22 +6829,22 @@
       </c>
       <c r="Q34" s="3" t="n"/>
       <c r="R34" s="3" t="n">
-        <v>79.76000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>79.84</v>
+        <v>79.69</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>79.73</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>79.8</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>79.4145</v>
+        <v>79.295</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>22780300</v>
+        <v>28248700</v>
       </c>
       <c r="X34" s="4">
         <f>IF(COUNT(V34:V35)=2,ROUND((V34/V35-1)*100,4),"")</f>
@@ -6620,22 +6852,22 @@
       </c>
       <c r="Y34" s="3" t="n"/>
       <c r="Z34" s="3" t="n">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AA34" s="3" t="n">
-        <v>96.12</v>
+        <v>96.03</v>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>96</v>
+        <v>95.81</v>
       </c>
       <c r="AC34" s="3" t="n">
-        <v>96.08</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AD34" s="3" t="n">
-        <v>95.5508</v>
+        <v>95.37179999999999</v>
       </c>
       <c r="AE34" s="3" t="n">
-        <v>1653500</v>
+        <v>2297200</v>
       </c>
       <c r="AF34" s="4">
         <f>IF(COUNT(AD34:AD35)=2,ROUND((AD34/AD35-1)*100,4),"")</f>
@@ -6643,22 +6875,22 @@
       </c>
       <c r="AG34" s="3" t="n"/>
       <c r="AH34" s="3" t="n">
-        <v>28.28</v>
+        <v>28.32</v>
       </c>
       <c r="AI34" s="3" t="n">
-        <v>28.35</v>
+        <v>28.4</v>
       </c>
       <c r="AJ34" s="3" t="n">
-        <v>28.28</v>
+        <v>28.29</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>28.34</v>
+        <v>28.39</v>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>28.34</v>
+        <v>28.39</v>
       </c>
       <c r="AM34" s="3" t="n">
-        <v>2893800</v>
+        <v>2503500</v>
       </c>
       <c r="AN34" s="4">
         <f>IF(COUNT(AL34:AL35)=2,ROUND((AL34/AL35-1)*100,4),"")</f>
@@ -6666,22 +6898,22 @@
       </c>
       <c r="AO34" s="3" t="n"/>
       <c r="AP34" s="3" t="n">
-        <v>367.45</v>
+        <v>374.53</v>
       </c>
       <c r="AQ34" s="3" t="n">
-        <v>368.43</v>
+        <v>376.28</v>
       </c>
       <c r="AR34" s="3" t="n">
-        <v>364.05</v>
+        <v>370.92</v>
       </c>
       <c r="AS34" s="3" t="n">
-        <v>364.96</v>
+        <v>372.15</v>
       </c>
       <c r="AT34" s="3" t="n">
-        <v>364.96</v>
+        <v>372.15</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>9048000</v>
+        <v>6303400</v>
       </c>
       <c r="AV34" s="4">
         <f>IF(COUNT(AT34:AT35)=2,ROUND((AT34/AT35-1)*100,4),"")</f>
@@ -6689,22 +6921,22 @@
       </c>
       <c r="AW34" s="3" t="n"/>
       <c r="AX34" s="3" t="n">
-        <v>179</v>
+        <v>183.71</v>
       </c>
       <c r="AY34" s="3" t="n">
-        <v>179.48</v>
+        <v>184.43</v>
       </c>
       <c r="AZ34" s="3" t="n">
-        <v>176.41</v>
+        <v>181.33</v>
       </c>
       <c r="BA34" s="3" t="n">
-        <v>177.52</v>
+        <v>183.62</v>
       </c>
       <c r="BB34" s="3" t="n">
-        <v>177.52</v>
+        <v>183.62</v>
       </c>
       <c r="BC34" s="3" t="n">
-        <v>8666500</v>
+        <v>6399600</v>
       </c>
       <c r="BD34" s="4">
         <f>IF(COUNT(BB34:BB35)=2,ROUND((BB34/BB35-1)*100,4),"")</f>
@@ -6712,22 +6944,22 @@
       </c>
       <c r="BE34" s="3" t="n"/>
       <c r="BF34" s="3" t="n">
-        <v>56.76</v>
+        <v>55.6</v>
       </c>
       <c r="BG34" s="3" t="n">
-        <v>56.84</v>
+        <v>56.8</v>
       </c>
       <c r="BH34" s="3" t="n">
-        <v>56.39</v>
+        <v>55.59</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>56.75</v>
+        <v>56.18</v>
       </c>
       <c r="BJ34" s="3" t="n">
-        <v>56.75</v>
+        <v>56.18</v>
       </c>
       <c r="BK34" s="3" t="n">
-        <v>27591200</v>
+        <v>43208800</v>
       </c>
       <c r="BL34" s="4">
         <f>IF(COUNT(BJ34:BJ35)=2,ROUND((BJ34/BJ35-1)*100,4),"")</f>
@@ -6735,22 +6967,22 @@
       </c>
       <c r="BM34" s="3" t="n"/>
       <c r="BN34" s="3" t="n">
-        <v>107.98</v>
+        <v>107.95</v>
       </c>
       <c r="BO34" s="3" t="n">
-        <v>108.05</v>
+        <v>108.13</v>
       </c>
       <c r="BP34" s="3" t="n">
-        <v>107.92</v>
+        <v>107.91</v>
       </c>
       <c r="BQ34" s="3" t="n">
-        <v>107.97</v>
+        <v>108.01</v>
       </c>
       <c r="BR34" s="3" t="n">
-        <v>107.1835</v>
+        <v>107.2232</v>
       </c>
       <c r="BS34" s="3" t="n">
-        <v>863900</v>
+        <v>1451500</v>
       </c>
       <c r="BT34" s="4">
         <f>IF(COUNT(BR34:BR35)=2,ROUND((BR34/BR35-1)*100,4),"")</f>
@@ -6758,38 +6990,38 @@
       </c>
       <c r="BU34" s="3" t="n"/>
       <c r="BV34" s="3" t="n">
-        <v>15.82</v>
+        <v>17.21</v>
       </c>
       <c r="BW34" s="3" t="n">
-        <v>17.23</v>
+        <v>17.56</v>
       </c>
       <c r="BX34" s="3" t="n">
-        <v>15.77</v>
+        <v>16.15</v>
       </c>
       <c r="BY34" s="3" t="n">
-        <v>16.73</v>
+        <v>16.5</v>
       </c>
       <c r="BZ34" s="3" t="n">
-        <v>16.73</v>
+        <v>16.5</v>
       </c>
       <c r="CA34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB34" s="3" t="n"/>
       <c r="CC34" s="3" t="n">
-        <v>4.582</v>
+        <v>4.614</v>
       </c>
       <c r="CD34" s="3" t="n">
-        <v>4.596</v>
+        <v>4.614</v>
       </c>
       <c r="CE34" s="3" t="n">
-        <v>4.561</v>
+        <v>4.525</v>
       </c>
       <c r="CF34" s="3" t="n">
-        <v>4.569</v>
+        <v>4.585</v>
       </c>
       <c r="CG34" s="3" t="n">
-        <v>4.569</v>
+        <v>4.585</v>
       </c>
       <c r="CH34" s="3" t="n">
         <v>0</v>
@@ -6821,11 +7053,11 @@
       </c>
       <c r="CP34" s="3" t="n"/>
       <c r="CQ34" s="4">
-        <f>X34-P34</f>
+        <f>IFERROR(X34-P34,"")</f>
         <v/>
       </c>
       <c r="CR34" s="4">
-        <f>AF34-P34</f>
+        <f>IFERROR(AF34-P34,"")</f>
         <v/>
       </c>
       <c r="CS34" s="6">
@@ -6833,11 +7065,11 @@
         <v/>
       </c>
       <c r="CT34" s="4">
-        <f>AN34-AV34</f>
+        <f>IFERROR(AN34-AV34,"")</f>
         <v/>
       </c>
       <c r="CU34" s="4">
-        <f>BD34-BL34</f>
+        <f>IFERROR(BD34-BL34,"")</f>
         <v/>
       </c>
       <c r="CV34" s="6">
@@ -6845,33 +7077,33 @@
         <v/>
       </c>
       <c r="CW34" s="4">
-        <f>P34-BT34</f>
+        <f>IFERROR(P34-BT34,"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>754.24</v>
+        <v>752.47</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>755.58</v>
+        <v>753.91</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>750.2</v>
+        <v>748</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>754.8099999999999</v>
+        <v>749.17</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>754.8099999999999</v>
+        <v>749.17</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>43844800</v>
+        <v>44013600</v>
       </c>
       <c r="H35" s="4">
         <f>IF(COUNT(F35:F36)=2,ROUND((F35/F36-1)*100,4),"")</f>
@@ -6879,22 +7111,22 @@
       </c>
       <c r="I35" s="3" t="n"/>
       <c r="J35" s="3" t="n">
-        <v>84.08</v>
+        <v>84.19</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>84.41</v>
+        <v>84.28</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>84.08</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>84.23999999999999</v>
+        <v>83.97</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>83.902</v>
+        <v>83.6331</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>17837800</v>
+        <v>18742500</v>
       </c>
       <c r="P35" s="4">
         <f>IF(COUNT(N35:N36)=2,ROUND((N35/N36-1)*100,4),"")</f>
@@ -6902,22 +7134,22 @@
       </c>
       <c r="Q35" s="3" t="n"/>
       <c r="R35" s="3" t="n">
-        <v>79.70999999999999</v>
+        <v>79.67</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>79.84</v>
+        <v>79.69</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>79.70999999999999</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>79.81</v>
+        <v>79.52</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>79.42440000000001</v>
+        <v>79.1358</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>26948800</v>
+        <v>32133300</v>
       </c>
       <c r="X35" s="4">
         <f>IF(COUNT(V35:V36)=2,ROUND((V35/V36-1)*100,4),"")</f>
@@ -6925,22 +7157,22 @@
       </c>
       <c r="Y35" s="3" t="n"/>
       <c r="Z35" s="3" t="n">
-        <v>96</v>
+        <v>95.87</v>
       </c>
       <c r="AA35" s="3" t="n">
-        <v>96.13</v>
+        <v>95.92</v>
       </c>
       <c r="AB35" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="AC35" s="3" t="n">
-        <v>96.06999999999999</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="AD35" s="3" t="n">
-        <v>95.5408</v>
+        <v>95.23260000000001</v>
       </c>
       <c r="AE35" s="3" t="n">
-        <v>1807300</v>
+        <v>3234500</v>
       </c>
       <c r="AF35" s="4">
         <f>IF(COUNT(AD35:AD36)=2,ROUND((AD35/AD36-1)*100,4),"")</f>
@@ -6948,22 +7180,22 @@
       </c>
       <c r="AG35" s="3" t="n"/>
       <c r="AH35" s="3" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="AI35" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AJ35" s="3" t="n">
         <v>28.37</v>
       </c>
-      <c r="AI35" s="3" t="n">
-        <v>28.37</v>
-      </c>
-      <c r="AJ35" s="3" t="n">
-        <v>28.22</v>
-      </c>
       <c r="AK35" s="3" t="n">
-        <v>28.25</v>
+        <v>28.5</v>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>28.25</v>
+        <v>28.5</v>
       </c>
       <c r="AM35" s="3" t="n">
-        <v>2209200</v>
+        <v>3187900</v>
       </c>
       <c r="AN35" s="4">
         <f>IF(COUNT(AL35:AL36)=2,ROUND((AL35/AL36-1)*100,4),"")</f>
@@ -6971,22 +7203,22 @@
       </c>
       <c r="AO35" s="3" t="n"/>
       <c r="AP35" s="3" t="n">
-        <v>372.11</v>
+        <v>372.77</v>
       </c>
       <c r="AQ35" s="3" t="n">
-        <v>374.49</v>
+        <v>372.89</v>
       </c>
       <c r="AR35" s="3" t="n">
-        <v>369.5</v>
+        <v>365.77</v>
       </c>
       <c r="AS35" s="3" t="n">
-        <v>372.35</v>
+        <v>367.13</v>
       </c>
       <c r="AT35" s="3" t="n">
-        <v>372.35</v>
+        <v>367.13</v>
       </c>
       <c r="AU35" s="3" t="n">
-        <v>7683700</v>
+        <v>7161700</v>
       </c>
       <c r="AV35" s="4">
         <f>IF(COUNT(AT35:AT36)=2,ROUND((AT35/AT36-1)*100,4),"")</f>
@@ -6994,22 +7226,22 @@
       </c>
       <c r="AW35" s="3" t="n"/>
       <c r="AX35" s="3" t="n">
-        <v>185.11</v>
+        <v>183.1</v>
       </c>
       <c r="AY35" s="3" t="n">
-        <v>185.29</v>
+        <v>183.9</v>
       </c>
       <c r="AZ35" s="3" t="n">
-        <v>178.22</v>
+        <v>180.54</v>
       </c>
       <c r="BA35" s="3" t="n">
-        <v>181.58</v>
+        <v>181.28</v>
       </c>
       <c r="BB35" s="3" t="n">
-        <v>181.58</v>
+        <v>181.28</v>
       </c>
       <c r="BC35" s="3" t="n">
-        <v>9256800</v>
+        <v>8595100</v>
       </c>
       <c r="BD35" s="4">
         <f>IF(COUNT(BB35:BB36)=2,ROUND((BB35/BB36-1)*100,4),"")</f>
@@ -7017,22 +7249,22 @@
       </c>
       <c r="BE35" s="3" t="n"/>
       <c r="BF35" s="3" t="n">
-        <v>56.3</v>
+        <v>55.98</v>
       </c>
       <c r="BG35" s="3" t="n">
-        <v>56.82</v>
+        <v>56.16</v>
       </c>
       <c r="BH35" s="3" t="n">
-        <v>56.18</v>
+        <v>55.61</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>56.56</v>
+        <v>56.07</v>
       </c>
       <c r="BJ35" s="3" t="n">
-        <v>56.56</v>
+        <v>56.07</v>
       </c>
       <c r="BK35" s="3" t="n">
-        <v>49425400</v>
+        <v>33391000</v>
       </c>
       <c r="BL35" s="4">
         <f>IF(COUNT(BJ35:BJ36)=2,ROUND((BJ35/BJ36-1)*100,4),"")</f>
@@ -7040,22 +7272,22 @@
       </c>
       <c r="BM35" s="3" t="n"/>
       <c r="BN35" s="3" t="n">
-        <v>107.99</v>
+        <v>108.05</v>
       </c>
       <c r="BO35" s="3" t="n">
-        <v>108.16</v>
+        <v>108.05</v>
       </c>
       <c r="BP35" s="3" t="n">
-        <v>107.99</v>
+        <v>107.82</v>
       </c>
       <c r="BQ35" s="3" t="n">
-        <v>108.07</v>
+        <v>107.91</v>
       </c>
       <c r="BR35" s="3" t="n">
-        <v>107.2828</v>
+        <v>107.124</v>
       </c>
       <c r="BS35" s="3" t="n">
-        <v>1900400</v>
+        <v>1153800</v>
       </c>
       <c r="BT35" s="4">
         <f>IF(COUNT(BR35:BR36)=2,ROUND((BR35/BR36-1)*100,4),"")</f>
@@ -7063,38 +7295,38 @@
       </c>
       <c r="BU35" s="3" t="n"/>
       <c r="BV35" s="3" t="n">
-        <v>16.2</v>
+        <v>16.32</v>
       </c>
       <c r="BW35" s="3" t="n">
-        <v>16.57</v>
+        <v>17.41</v>
       </c>
       <c r="BX35" s="3" t="n">
-        <v>15.64</v>
+        <v>16.03</v>
       </c>
       <c r="BY35" s="3" t="n">
-        <v>15.67</v>
+        <v>17.16</v>
       </c>
       <c r="BZ35" s="3" t="n">
-        <v>15.67</v>
+        <v>17.16</v>
       </c>
       <c r="CA35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB35" s="3" t="n"/>
       <c r="CC35" s="3" t="n">
-        <v>4.608</v>
+        <v>4.585</v>
       </c>
       <c r="CD35" s="3" t="n">
-        <v>4.61</v>
+        <v>4.618</v>
       </c>
       <c r="CE35" s="3" t="n">
-        <v>4.539</v>
+        <v>4.573</v>
       </c>
       <c r="CF35" s="3" t="n">
-        <v>4.545</v>
+        <v>4.609</v>
       </c>
       <c r="CG35" s="3" t="n">
-        <v>4.545</v>
+        <v>4.609</v>
       </c>
       <c r="CH35" s="3" t="n">
         <v>0</v>
@@ -7126,11 +7358,11 @@
       </c>
       <c r="CP35" s="3" t="n"/>
       <c r="CQ35" s="4">
-        <f>X35-P35</f>
+        <f>IFERROR(X35-P35,"")</f>
         <v/>
       </c>
       <c r="CR35" s="4">
-        <f>AF35-P35</f>
+        <f>IFERROR(AF35-P35,"")</f>
         <v/>
       </c>
       <c r="CS35" s="6">
@@ -7138,11 +7370,11 @@
         <v/>
       </c>
       <c r="CT35" s="4">
-        <f>AN35-AV35</f>
+        <f>IFERROR(AN35-AV35,"")</f>
         <v/>
       </c>
       <c r="CU35" s="4">
-        <f>BD35-BL35</f>
+        <f>IFERROR(BD35-BL35,"")</f>
         <v/>
       </c>
       <c r="CV35" s="6">
@@ -7150,33 +7382,33 @@
         <v/>
       </c>
       <c r="CW35" s="4">
-        <f>P35-BT35</f>
+        <f>IFERROR(P35-BT35,"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>750.91</v>
+        <v>752.05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>753.34</v>
+        <v>755.42</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>748.66</v>
+        <v>748.1</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>751.83</v>
+        <v>754.95</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>751.83</v>
+        <v>754.95</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>35143100</v>
+        <v>42191300</v>
       </c>
       <c r="H36" s="4">
         <f>IF(COUNT(F36:F37)=2,ROUND((F36/F37-1)*100,4),"")</f>
@@ -7184,22 +7416,22 @@
       </c>
       <c r="I36" s="3" t="n"/>
       <c r="J36" s="3" t="n">
-        <v>84.18000000000001</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>84.5</v>
+        <v>84.63</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>84.04000000000001</v>
+        <v>84.28</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>84.08</v>
+        <v>84.47</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>83.7427</v>
+        <v>84.1311</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>23793500</v>
+        <v>14454100</v>
       </c>
       <c r="P36" s="4">
         <f>IF(COUNT(N36:N37)=2,ROUND((N36/N37-1)*100,4),"")</f>
@@ -7207,22 +7439,22 @@
       </c>
       <c r="Q36" s="3" t="n"/>
       <c r="R36" s="3" t="n">
-        <v>79.68000000000001</v>
+        <v>79.78</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>79.69</v>
+        <v>79.83</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>79.56999999999999</v>
+        <v>79.62</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>79.68000000000001</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>79.295</v>
+        <v>79.3249</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>28248700</v>
+        <v>24550300</v>
       </c>
       <c r="X36" s="4">
         <f>IF(COUNT(V36:V37)=2,ROUND((V36/V37-1)*100,4),"")</f>
@@ -7230,22 +7462,22 @@
       </c>
       <c r="Y36" s="3" t="n"/>
       <c r="Z36" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>96.06</v>
       </c>
       <c r="AA36" s="3" t="n">
-        <v>96.03</v>
+        <v>96.08</v>
       </c>
       <c r="AB36" s="3" t="n">
-        <v>95.81</v>
+        <v>95.86</v>
       </c>
       <c r="AC36" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>95.93000000000001</v>
       </c>
       <c r="AD36" s="3" t="n">
-        <v>95.37179999999999</v>
+        <v>95.4016</v>
       </c>
       <c r="AE36" s="3" t="n">
-        <v>2297200</v>
+        <v>2389400</v>
       </c>
       <c r="AF36" s="4">
         <f>IF(COUNT(AD36:AD37)=2,ROUND((AD36/AD37-1)*100,4),"")</f>
@@ -7253,13 +7485,13 @@
       </c>
       <c r="AG36" s="3" t="n"/>
       <c r="AH36" s="3" t="n">
-        <v>28.32</v>
+        <v>28.36</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>28.4</v>
+        <v>28.39</v>
       </c>
       <c r="AJ36" s="3" t="n">
-        <v>28.29</v>
+        <v>28.31</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>28.39</v>
@@ -7268,7 +7500,7 @@
         <v>28.39</v>
       </c>
       <c r="AM36" s="3" t="n">
-        <v>2503500</v>
+        <v>1810500</v>
       </c>
       <c r="AN36" s="4">
         <f>IF(COUNT(AL36:AL37)=2,ROUND((AL36/AL37-1)*100,4),"")</f>
@@ -7276,22 +7508,22 @@
       </c>
       <c r="AO36" s="3" t="n"/>
       <c r="AP36" s="3" t="n">
-        <v>374.53</v>
+        <v>375</v>
       </c>
       <c r="AQ36" s="3" t="n">
-        <v>376.28</v>
+        <v>377.55</v>
       </c>
       <c r="AR36" s="3" t="n">
-        <v>370.92</v>
+        <v>373.7</v>
       </c>
       <c r="AS36" s="3" t="n">
-        <v>372.15</v>
+        <v>377.01</v>
       </c>
       <c r="AT36" s="3" t="n">
-        <v>372.15</v>
+        <v>377.01</v>
       </c>
       <c r="AU36" s="3" t="n">
-        <v>6303400</v>
+        <v>5455400</v>
       </c>
       <c r="AV36" s="4">
         <f>IF(COUNT(AT36:AT37)=2,ROUND((AT36/AT37-1)*100,4),"")</f>
@@ -7299,22 +7531,22 @@
       </c>
       <c r="AW36" s="3" t="n"/>
       <c r="AX36" s="3" t="n">
-        <v>183.71</v>
+        <v>184.01</v>
       </c>
       <c r="AY36" s="3" t="n">
-        <v>184.43</v>
+        <v>186.23</v>
       </c>
       <c r="AZ36" s="3" t="n">
-        <v>181.33</v>
+        <v>183.09</v>
       </c>
       <c r="BA36" s="3" t="n">
-        <v>183.62</v>
+        <v>185.78</v>
       </c>
       <c r="BB36" s="3" t="n">
-        <v>183.62</v>
+        <v>185.78</v>
       </c>
       <c r="BC36" s="3" t="n">
-        <v>6399600</v>
+        <v>6162000</v>
       </c>
       <c r="BD36" s="4">
         <f>IF(COUNT(BB36:BB37)=2,ROUND((BB36/BB37-1)*100,4),"")</f>
@@ -7322,22 +7554,22 @@
       </c>
       <c r="BE36" s="3" t="n"/>
       <c r="BF36" s="3" t="n">
-        <v>55.6</v>
+        <v>55.99</v>
       </c>
       <c r="BG36" s="3" t="n">
-        <v>56.8</v>
+        <v>56.03</v>
       </c>
       <c r="BH36" s="3" t="n">
-        <v>55.59</v>
+        <v>55.36</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>56.18</v>
+        <v>55.71</v>
       </c>
       <c r="BJ36" s="3" t="n">
-        <v>56.18</v>
+        <v>55.71</v>
       </c>
       <c r="BK36" s="3" t="n">
-        <v>43208800</v>
+        <v>24046300</v>
       </c>
       <c r="BL36" s="4">
         <f>IF(COUNT(BJ36:BJ37)=2,ROUND((BJ36/BJ37-1)*100,4),"")</f>
@@ -7345,22 +7577,22 @@
       </c>
       <c r="BM36" s="3" t="n"/>
       <c r="BN36" s="3" t="n">
-        <v>107.95</v>
+        <v>108.08</v>
       </c>
       <c r="BO36" s="3" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="BP36" s="3" t="n">
+        <v>107.98</v>
+      </c>
+      <c r="BQ36" s="3" t="n">
         <v>108.13</v>
       </c>
-      <c r="BP36" s="3" t="n">
-        <v>107.91</v>
-      </c>
-      <c r="BQ36" s="3" t="n">
-        <v>108.01</v>
-      </c>
       <c r="BR36" s="3" t="n">
-        <v>107.2232</v>
+        <v>107.3424</v>
       </c>
       <c r="BS36" s="3" t="n">
-        <v>1451500</v>
+        <v>1162700</v>
       </c>
       <c r="BT36" s="4">
         <f>IF(COUNT(BR36:BR37)=2,ROUND((BR36/BR37-1)*100,4),"")</f>
@@ -7368,38 +7600,38 @@
       </c>
       <c r="BU36" s="3" t="n"/>
       <c r="BV36" s="3" t="n">
-        <v>17.21</v>
+        <v>16.06</v>
       </c>
       <c r="BW36" s="3" t="n">
-        <v>17.56</v>
+        <v>16.16</v>
       </c>
       <c r="BX36" s="3" t="n">
-        <v>16.15</v>
+        <v>14.96</v>
       </c>
       <c r="BY36" s="3" t="n">
-        <v>16.5</v>
+        <v>15.03</v>
       </c>
       <c r="BZ36" s="3" t="n">
-        <v>16.5</v>
+        <v>15.03</v>
       </c>
       <c r="CA36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB36" s="3" t="n"/>
       <c r="CC36" s="3" t="n">
-        <v>4.614</v>
+        <v>4.541</v>
       </c>
       <c r="CD36" s="3" t="n">
-        <v>4.614</v>
+        <v>4.571</v>
       </c>
       <c r="CE36" s="3" t="n">
-        <v>4.525</v>
+        <v>4.539</v>
       </c>
       <c r="CF36" s="3" t="n">
-        <v>4.585</v>
+        <v>4.569</v>
       </c>
       <c r="CG36" s="3" t="n">
-        <v>4.585</v>
+        <v>4.569</v>
       </c>
       <c r="CH36" s="3" t="n">
         <v>0</v>
@@ -7413,10 +7645,7 @@
         <f>IF(COUNT(BY36:BY37)=2,ROUND((BY36/BY37-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="CL36" s="4">
-        <f>IF(COUNT(BY36:BY41)=6,ROUND((BY36/BY41-1)*100,4),"")</f>
-        <v/>
-      </c>
+      <c r="CL36" s="4" t="n"/>
       <c r="CM36" s="4">
         <f>IF(COUNT(CK36:CK55)=20,IFERROR(ROUND(STDEV(CK36:CK55),4),""),"")</f>
         <v/>
@@ -7431,11 +7660,11 @@
       </c>
       <c r="CP36" s="3" t="n"/>
       <c r="CQ36" s="4">
-        <f>X36-P36</f>
+        <f>IFERROR(X36-P36,"")</f>
         <v/>
       </c>
       <c r="CR36" s="4">
-        <f>AF36-P36</f>
+        <f>IFERROR(AF36-P36,"")</f>
         <v/>
       </c>
       <c r="CS36" s="6">
@@ -7443,11 +7672,11 @@
         <v/>
       </c>
       <c r="CT36" s="4">
-        <f>AN36-AV36</f>
+        <f>IFERROR(AN36-AV36,"")</f>
         <v/>
       </c>
       <c r="CU36" s="4">
-        <f>BD36-BL36</f>
+        <f>IFERROR(BD36-BL36,"")</f>
         <v/>
       </c>
       <c r="CV36" s="6">
@@ -7455,33 +7684,33 @@
         <v/>
       </c>
       <c r="CW36" s="4">
-        <f>P36-BT36</f>
+        <f>IFERROR(P36-BT36,"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/09</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>752.47</v>
+        <v>747.35</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>753.91</v>
+        <v>751.97</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>748</v>
+        <v>745.59</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>749.17</v>
+        <v>751.71</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>749.17</v>
+        <v>751.71</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>44013600</v>
+        <v>41441700</v>
       </c>
       <c r="H37" s="4">
         <f>IF(COUNT(F37:F38)=2,ROUND((F37/F38-1)*100,4),"")</f>
@@ -7489,22 +7718,22 @@
       </c>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n">
-        <v>84.19</v>
+        <v>84.28</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>84.28</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>83.93000000000001</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>83.97</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>83.6331</v>
+        <v>84.151</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>18742500</v>
+        <v>18625300</v>
       </c>
       <c r="P37" s="4">
         <f>IF(COUNT(N37:N38)=2,ROUND((N37/N38-1)*100,4),"")</f>
@@ -7512,22 +7741,22 @@
       </c>
       <c r="Q37" s="3" t="n"/>
       <c r="R37" s="3" t="n">
+        <v>79.73</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>79.86</v>
+      </c>
+      <c r="T37" s="3" t="n">
         <v>79.67</v>
       </c>
-      <c r="S37" s="3" t="n">
-        <v>79.69</v>
-      </c>
-      <c r="T37" s="3" t="n">
-        <v>79.45999999999999</v>
-      </c>
       <c r="U37" s="3" t="n">
-        <v>79.52</v>
+        <v>79.75</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>79.1358</v>
+        <v>79.3647</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>32133300</v>
+        <v>21882200</v>
       </c>
       <c r="X37" s="4">
         <f>IF(COUNT(V37:V38)=2,ROUND((V37/V38-1)*100,4),"")</f>
@@ -7535,22 +7764,22 @@
       </c>
       <c r="Y37" s="3" t="n"/>
       <c r="Z37" s="3" t="n">
-        <v>95.87</v>
+        <v>95.97</v>
       </c>
       <c r="AA37" s="3" t="n">
-        <v>95.92</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="AB37" s="3" t="n">
-        <v>95.68000000000001</v>
+        <v>95.91</v>
       </c>
       <c r="AC37" s="3" t="n">
-        <v>95.76000000000001</v>
+        <v>96</v>
       </c>
       <c r="AD37" s="3" t="n">
-        <v>95.23260000000001</v>
+        <v>95.4712</v>
       </c>
       <c r="AE37" s="3" t="n">
-        <v>3234500</v>
+        <v>2655000</v>
       </c>
       <c r="AF37" s="4">
         <f>IF(COUNT(AD37:AD38)=2,ROUND((AD37/AD38-1)*100,4),"")</f>
@@ -7558,22 +7787,22 @@
       </c>
       <c r="AG37" s="3" t="n"/>
       <c r="AH37" s="3" t="n">
-        <v>28.38</v>
+        <v>28.35</v>
       </c>
       <c r="AI37" s="3" t="n">
-        <v>28.5</v>
+        <v>28.37</v>
       </c>
       <c r="AJ37" s="3" t="n">
-        <v>28.37</v>
+        <v>28.33</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>28.5</v>
+        <v>28.36</v>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>28.5</v>
+        <v>28.36</v>
       </c>
       <c r="AM37" s="3" t="n">
-        <v>3187900</v>
+        <v>1543400</v>
       </c>
       <c r="AN37" s="4">
         <f>IF(COUNT(AL37:AL38)=2,ROUND((AL37/AL38-1)*100,4),"")</f>
@@ -7581,22 +7810,22 @@
       </c>
       <c r="AO37" s="3" t="n"/>
       <c r="AP37" s="3" t="n">
-        <v>372.77</v>
+        <v>378.51</v>
       </c>
       <c r="AQ37" s="3" t="n">
-        <v>372.89</v>
+        <v>379.65</v>
       </c>
       <c r="AR37" s="3" t="n">
-        <v>365.77</v>
+        <v>377.41</v>
       </c>
       <c r="AS37" s="3" t="n">
-        <v>367.13</v>
+        <v>378.18</v>
       </c>
       <c r="AT37" s="3" t="n">
-        <v>367.13</v>
+        <v>378.18</v>
       </c>
       <c r="AU37" s="3" t="n">
-        <v>7161700</v>
+        <v>4754600</v>
       </c>
       <c r="AV37" s="4">
         <f>IF(COUNT(AT37:AT38)=2,ROUND((AT37/AT38-1)*100,4),"")</f>
@@ -7604,22 +7833,22 @@
       </c>
       <c r="AW37" s="3" t="n"/>
       <c r="AX37" s="3" t="n">
-        <v>183.1</v>
+        <v>184.76</v>
       </c>
       <c r="AY37" s="3" t="n">
-        <v>183.9</v>
+        <v>186.4</v>
       </c>
       <c r="AZ37" s="3" t="n">
-        <v>180.54</v>
+        <v>183.56</v>
       </c>
       <c r="BA37" s="3" t="n">
-        <v>181.28</v>
+        <v>185.35</v>
       </c>
       <c r="BB37" s="3" t="n">
-        <v>181.28</v>
+        <v>185.35</v>
       </c>
       <c r="BC37" s="3" t="n">
-        <v>8595100</v>
+        <v>7756600</v>
       </c>
       <c r="BD37" s="4">
         <f>IF(COUNT(BB37:BB38)=2,ROUND((BB37/BB38-1)*100,4),"")</f>
@@ -7627,22 +7856,22 @@
       </c>
       <c r="BE37" s="3" t="n"/>
       <c r="BF37" s="3" t="n">
-        <v>55.98</v>
+        <v>55.07</v>
       </c>
       <c r="BG37" s="3" t="n">
-        <v>56.16</v>
+        <v>55.69</v>
       </c>
       <c r="BH37" s="3" t="n">
-        <v>55.61</v>
+        <v>54.97</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>56.07</v>
+        <v>55.54</v>
       </c>
       <c r="BJ37" s="3" t="n">
-        <v>56.07</v>
+        <v>55.54</v>
       </c>
       <c r="BK37" s="3" t="n">
-        <v>33391000</v>
+        <v>26542000</v>
       </c>
       <c r="BL37" s="4">
         <f>IF(COUNT(BJ37:BJ38)=2,ROUND((BJ37/BJ38-1)*100,4),"")</f>
@@ -7650,22 +7879,22 @@
       </c>
       <c r="BM37" s="3" t="n"/>
       <c r="BN37" s="3" t="n">
-        <v>108.05</v>
+        <v>108.14</v>
       </c>
       <c r="BO37" s="3" t="n">
-        <v>108.05</v>
+        <v>108.22</v>
       </c>
       <c r="BP37" s="3" t="n">
-        <v>107.82</v>
+        <v>108.09</v>
       </c>
       <c r="BQ37" s="3" t="n">
-        <v>107.91</v>
+        <v>108.12</v>
       </c>
       <c r="BR37" s="3" t="n">
-        <v>107.124</v>
+        <v>107.3324</v>
       </c>
       <c r="BS37" s="3" t="n">
-        <v>1153800</v>
+        <v>1170800</v>
       </c>
       <c r="BT37" s="4">
         <f>IF(COUNT(BR37:BR38)=2,ROUND((BR37/BR38-1)*100,4),"")</f>
@@ -7673,38 +7902,38 @@
       </c>
       <c r="BU37" s="3" t="n"/>
       <c r="BV37" s="3" t="n">
-        <v>16.32</v>
+        <v>16.58</v>
       </c>
       <c r="BW37" s="3" t="n">
-        <v>17.41</v>
+        <v>17.27</v>
       </c>
       <c r="BX37" s="3" t="n">
-        <v>16.03</v>
+        <v>15.76</v>
       </c>
       <c r="BY37" s="3" t="n">
-        <v>17.16</v>
+        <v>15.84</v>
       </c>
       <c r="BZ37" s="3" t="n">
-        <v>17.16</v>
+        <v>15.84</v>
       </c>
       <c r="CA37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB37" s="3" t="n"/>
       <c r="CC37" s="3" t="n">
-        <v>4.585</v>
+        <v>4.577</v>
       </c>
       <c r="CD37" s="3" t="n">
-        <v>4.618</v>
+        <v>4.581</v>
       </c>
       <c r="CE37" s="3" t="n">
-        <v>4.573</v>
+        <v>4.529</v>
       </c>
       <c r="CF37" s="3" t="n">
-        <v>4.609</v>
+        <v>4.539</v>
       </c>
       <c r="CG37" s="3" t="n">
-        <v>4.609</v>
+        <v>4.539</v>
       </c>
       <c r="CH37" s="3" t="n">
         <v>0</v>
@@ -7718,14 +7947,8 @@
         <f>IF(COUNT(BY37:BY38)=2,ROUND((BY37/BY38-1)*100,4),"")</f>
         <v/>
       </c>
-      <c r="CL37" s="4">
-        <f>IF(COUNT(BY37:BY42)=6,ROUND((BY37/BY42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CM37" s="4">
-        <f>IF(COUNT(CK37:CK56)=20,IFERROR(ROUND(STDEV(CK37:CK56),4),""),"")</f>
-        <v/>
-      </c>
+      <c r="CL37" s="4" t="n"/>
+      <c r="CM37" s="4" t="n"/>
       <c r="CN37" s="4">
         <f>IF(COUNT(CF37:CF38)=2,ROUND((CF37/CF38-1)*100,4),"")</f>
         <v/>
@@ -7736,23 +7959,20 @@
       </c>
       <c r="CP37" s="3" t="n"/>
       <c r="CQ37" s="4">
-        <f>X37-P37</f>
+        <f>IFERROR(X37-P37,"")</f>
         <v/>
       </c>
       <c r="CR37" s="4">
-        <f>AF37-P37</f>
-        <v/>
-      </c>
-      <c r="CS37" s="6">
-        <f>IF(COUNT(H37:H56)=20,IFERROR(CORREL(H37:H56,P37:P56),""),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(AF37-P37,"")</f>
+        <v/>
+      </c>
+      <c r="CS37" s="6" t="n"/>
       <c r="CT37" s="4">
-        <f>AN37-AV37</f>
+        <f>IFERROR(AN37-AV37,"")</f>
         <v/>
       </c>
       <c r="CU37" s="4">
-        <f>BD37-BL37</f>
+        <f>IFERROR(BD37-BL37,"")</f>
         <v/>
       </c>
       <c r="CV37" s="6">
@@ -7760,33 +7980,33 @@
         <v/>
       </c>
       <c r="CW37" s="4">
-        <f>P37-BT37</f>
+        <f>IFERROR(P37-BT37,"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>752.05</v>
+        <v>743.16</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>755.42</v>
+        <v>746.15</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>748.1</v>
+        <v>739.51</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>754.95</v>
+        <v>745.4</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>754.95</v>
+        <v>745.4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>42191300</v>
+        <v>43767400</v>
       </c>
       <c r="H38" s="4">
         <f>IF(COUNT(F38:F39)=2,ROUND((F38/F39-1)*100,4),"")</f>
@@ -7794,22 +8014,22 @@
       </c>
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n">
-        <v>84.51000000000001</v>
+        <v>84.31</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>84.63</v>
+        <v>84.45</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>84.28</v>
+        <v>84.06</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>84.47</v>
+        <v>84.36</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>84.1311</v>
+        <v>84.0215</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>14454100</v>
+        <v>25806600</v>
       </c>
       <c r="P38" s="4">
         <f>IF(COUNT(N38:N39)=2,ROUND((N38/N39-1)*100,4),"")</f>
@@ -7817,22 +8037,22 @@
       </c>
       <c r="Q38" s="3" t="n"/>
       <c r="R38" s="3" t="n">
-        <v>79.78</v>
+        <v>79.61</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>79.83</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>79.62</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>79.70999999999999</v>
+        <v>79.66</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>79.3249</v>
+        <v>79.27509999999999</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>24550300</v>
+        <v>30771300</v>
       </c>
       <c r="X38" s="4">
         <f>IF(COUNT(V38:V39)=2,ROUND((V38/V39-1)*100,4),"")</f>
@@ -7840,22 +8060,22 @@
       </c>
       <c r="Y38" s="3" t="n"/>
       <c r="Z38" s="3" t="n">
-        <v>96.06</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="AA38" s="3" t="n">
-        <v>96.08</v>
+        <v>95.91</v>
       </c>
       <c r="AB38" s="3" t="n">
-        <v>95.86</v>
+        <v>95.75</v>
       </c>
       <c r="AC38" s="3" t="n">
-        <v>95.93000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AD38" s="3" t="n">
-        <v>95.4016</v>
+        <v>95.37179999999999</v>
       </c>
       <c r="AE38" s="3" t="n">
-        <v>2389400</v>
+        <v>2989300</v>
       </c>
       <c r="AF38" s="4">
         <f>IF(COUNT(AD38:AD39)=2,ROUND((AD38/AD39-1)*100,4),"")</f>
@@ -7863,22 +8083,22 @@
       </c>
       <c r="AG38" s="3" t="n"/>
       <c r="AH38" s="3" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="AI38" s="3" t="n">
+        <v>28.46</v>
+      </c>
+      <c r="AJ38" s="3" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="AK38" s="3" t="n">
         <v>28.36</v>
       </c>
-      <c r="AI38" s="3" t="n">
-        <v>28.39</v>
-      </c>
-      <c r="AJ38" s="3" t="n">
-        <v>28.31</v>
-      </c>
-      <c r="AK38" s="3" t="n">
-        <v>28.39</v>
-      </c>
       <c r="AL38" s="3" t="n">
-        <v>28.39</v>
+        <v>28.36</v>
       </c>
       <c r="AM38" s="3" t="n">
-        <v>1810500</v>
+        <v>1338200</v>
       </c>
       <c r="AN38" s="4">
         <f>IF(COUNT(AL38:AL39)=2,ROUND((AL38/AL39-1)*100,4),"")</f>
@@ -7886,22 +8106,22 @@
       </c>
       <c r="AO38" s="3" t="n"/>
       <c r="AP38" s="3" t="n">
-        <v>375</v>
+        <v>373.17</v>
       </c>
       <c r="AQ38" s="3" t="n">
-        <v>377.55</v>
+        <v>375.47</v>
       </c>
       <c r="AR38" s="3" t="n">
-        <v>373.7</v>
+        <v>368.95</v>
       </c>
       <c r="AS38" s="3" t="n">
-        <v>377.01</v>
+        <v>374.45</v>
       </c>
       <c r="AT38" s="3" t="n">
-        <v>377.01</v>
+        <v>374.45</v>
       </c>
       <c r="AU38" s="3" t="n">
-        <v>5455400</v>
+        <v>7728500</v>
       </c>
       <c r="AV38" s="4">
         <f>IF(COUNT(AT38:AT39)=2,ROUND((AT38/AT39-1)*100,4),"")</f>
@@ -7909,22 +8129,22 @@
       </c>
       <c r="AW38" s="3" t="n"/>
       <c r="AX38" s="3" t="n">
-        <v>184.01</v>
+        <v>177.48</v>
       </c>
       <c r="AY38" s="3" t="n">
-        <v>186.23</v>
+        <v>181.63</v>
       </c>
       <c r="AZ38" s="3" t="n">
-        <v>183.09</v>
+        <v>177.15</v>
       </c>
       <c r="BA38" s="3" t="n">
-        <v>185.78</v>
+        <v>181.4</v>
       </c>
       <c r="BB38" s="3" t="n">
-        <v>185.78</v>
+        <v>181.4</v>
       </c>
       <c r="BC38" s="3" t="n">
-        <v>6162000</v>
+        <v>10528300</v>
       </c>
       <c r="BD38" s="4">
         <f>IF(COUNT(BB38:BB39)=2,ROUND((BB38/BB39-1)*100,4),"")</f>
@@ -7932,22 +8152,22 @@
       </c>
       <c r="BE38" s="3" t="n"/>
       <c r="BF38" s="3" t="n">
-        <v>55.99</v>
+        <v>55.79</v>
       </c>
       <c r="BG38" s="3" t="n">
-        <v>56.03</v>
+        <v>55.8</v>
       </c>
       <c r="BH38" s="3" t="n">
-        <v>55.36</v>
+        <v>54.95</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>55.71</v>
+        <v>54.97</v>
       </c>
       <c r="BJ38" s="3" t="n">
-        <v>55.71</v>
+        <v>54.97</v>
       </c>
       <c r="BK38" s="3" t="n">
-        <v>24046300</v>
+        <v>41648100</v>
       </c>
       <c r="BL38" s="4">
         <f>IF(COUNT(BJ38:BJ39)=2,ROUND((BJ38/BJ39-1)*100,4),"")</f>
@@ -7955,22 +8175,22 @@
       </c>
       <c r="BM38" s="3" t="n"/>
       <c r="BN38" s="3" t="n">
-        <v>108.08</v>
+        <v>108.09</v>
       </c>
       <c r="BO38" s="3" t="n">
-        <v>108.15</v>
+        <v>108.12</v>
       </c>
       <c r="BP38" s="3" t="n">
         <v>107.98</v>
       </c>
       <c r="BQ38" s="3" t="n">
-        <v>108.13</v>
+        <v>108.05</v>
       </c>
       <c r="BR38" s="3" t="n">
-        <v>107.3424</v>
+        <v>107.2629</v>
       </c>
       <c r="BS38" s="3" t="n">
-        <v>1162700</v>
+        <v>941700</v>
       </c>
       <c r="BT38" s="4">
         <f>IF(COUNT(BR38:BR39)=2,ROUND((BR38/BR39-1)*100,4),"")</f>
@@ -7978,32 +8198,32 @@
       </c>
       <c r="BU38" s="3" t="n"/>
       <c r="BV38" s="3" t="n">
-        <v>16.06</v>
+        <v>16.55</v>
       </c>
       <c r="BW38" s="3" t="n">
-        <v>16.16</v>
+        <v>18.91</v>
       </c>
       <c r="BX38" s="3" t="n">
-        <v>14.96</v>
+        <v>16.35</v>
       </c>
       <c r="BY38" s="3" t="n">
-        <v>15.03</v>
+        <v>16.9</v>
       </c>
       <c r="BZ38" s="3" t="n">
-        <v>15.03</v>
+        <v>16.9</v>
       </c>
       <c r="CA38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB38" s="3" t="n"/>
       <c r="CC38" s="3" t="n">
-        <v>4.541</v>
+        <v>4.561</v>
       </c>
       <c r="CD38" s="3" t="n">
-        <v>4.571</v>
+        <v>4.597</v>
       </c>
       <c r="CE38" s="3" t="n">
-        <v>4.539</v>
+        <v>4.557</v>
       </c>
       <c r="CF38" s="3" t="n">
         <v>4.569</v>
@@ -8024,10 +8244,7 @@
         <v/>
       </c>
       <c r="CL38" s="4" t="n"/>
-      <c r="CM38" s="4">
-        <f>IF(COUNT(CK38:CK57)=20,IFERROR(ROUND(STDEV(CK38:CK57),4),""),"")</f>
-        <v/>
-      </c>
+      <c r="CM38" s="4" t="n"/>
       <c r="CN38" s="4">
         <f>IF(COUNT(CF38:CF39)=2,ROUND((CF38/CF39-1)*100,4),"")</f>
         <v/>
@@ -8038,23 +8255,20 @@
       </c>
       <c r="CP38" s="3" t="n"/>
       <c r="CQ38" s="4">
-        <f>X38-P38</f>
+        <f>IFERROR(X38-P38,"")</f>
         <v/>
       </c>
       <c r="CR38" s="4">
-        <f>AF38-P38</f>
-        <v/>
-      </c>
-      <c r="CS38" s="6">
-        <f>IF(COUNT(H38:H57)=20,IFERROR(CORREL(H38:H57,P38:P57),""),"")</f>
-        <v/>
-      </c>
+        <f>IFERROR(AF38-P38,"")</f>
+        <v/>
+      </c>
+      <c r="CS38" s="6" t="n"/>
       <c r="CT38" s="4">
-        <f>AN38-AV38</f>
+        <f>IFERROR(AN38-AV38,"")</f>
         <v/>
       </c>
       <c r="CU38" s="4">
-        <f>BD38-BL38</f>
+        <f>IFERROR(BD38-BL38,"")</f>
         <v/>
       </c>
       <c r="CV38" s="6">
@@ -8062,33 +8276,33 @@
         <v/>
       </c>
       <c r="CW38" s="4">
-        <f>P38-BT38</f>
+        <f>IFERROR(P38-BT38,"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026/07/09</t>
+          <t>2026/07/07</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>747.35</v>
+        <v>750.22</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>751.97</v>
+        <v>750.96</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>745.59</v>
+        <v>745.21</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>751.71</v>
+        <v>747.71</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>751.71</v>
+        <v>747.71</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>41441700</v>
+        <v>43721500</v>
       </c>
       <c r="H39" s="4">
         <f>IF(COUNT(F39:F40)=2,ROUND((F39/F40-1)*100,4),"")</f>
@@ -8096,22 +8310,22 @@
       </c>
       <c r="I39" s="3" t="n"/>
       <c r="J39" s="3" t="n">
-        <v>84.28</v>
+        <v>85.12</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>84.68000000000001</v>
+        <v>85.17</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>84.26000000000001</v>
+        <v>84.54000000000001</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>84.48999999999999</v>
+        <v>84.55</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>84.151</v>
+        <v>84.21080000000001</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>18625300</v>
+        <v>24816400</v>
       </c>
       <c r="P39" s="4">
         <f>IF(COUNT(N39:N40)=2,ROUND((N39/N40-1)*100,4),"")</f>
@@ -8119,22 +8333,22 @@
       </c>
       <c r="Q39" s="3" t="n"/>
       <c r="R39" s="3" t="n">
-        <v>79.73</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>79.86</v>
+        <v>79.88</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>79.67</v>
+        <v>79.72</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>79.75</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>79.3647</v>
+        <v>79.3746</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>21882200</v>
+        <v>28558300</v>
       </c>
       <c r="X39" s="4">
         <f>IF(COUNT(V39:V40)=2,ROUND((V39/V40-1)*100,4),"")</f>
@@ -8142,22 +8356,22 @@
       </c>
       <c r="Y39" s="3" t="n"/>
       <c r="Z39" s="3" t="n">
-        <v>95.97</v>
+        <v>96.16</v>
       </c>
       <c r="AA39" s="3" t="n">
-        <v>96.15000000000001</v>
+        <v>96.16</v>
       </c>
       <c r="AB39" s="3" t="n">
-        <v>95.91</v>
+        <v>95.98</v>
       </c>
       <c r="AC39" s="3" t="n">
-        <v>96</v>
+        <v>96.05</v>
       </c>
       <c r="AD39" s="3" t="n">
-        <v>95.4712</v>
+        <v>95.521</v>
       </c>
       <c r="AE39" s="3" t="n">
-        <v>2655000</v>
+        <v>2279500</v>
       </c>
       <c r="AF39" s="4">
         <f>IF(COUNT(AD39:AD40)=2,ROUND((AD39/AD40-1)*100,4),"")</f>
@@ -8165,22 +8379,22 @@
       </c>
       <c r="AG39" s="3" t="n"/>
       <c r="AH39" s="3" t="n">
-        <v>28.35</v>
+        <v>28.34</v>
       </c>
       <c r="AI39" s="3" t="n">
-        <v>28.37</v>
+        <v>28.41</v>
       </c>
       <c r="AJ39" s="3" t="n">
         <v>28.33</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>28.36</v>
+        <v>28.4</v>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>28.36</v>
+        <v>28.4</v>
       </c>
       <c r="AM39" s="3" t="n">
-        <v>1543400</v>
+        <v>1902000</v>
       </c>
       <c r="AN39" s="4">
         <f>IF(COUNT(AL39:AL40)=2,ROUND((AL39/AL40-1)*100,4),"")</f>
@@ -8188,22 +8402,22 @@
       </c>
       <c r="AO39" s="3" t="n"/>
       <c r="AP39" s="3" t="n">
-        <v>378.51</v>
+        <v>382.39</v>
       </c>
       <c r="AQ39" s="3" t="n">
-        <v>379.65</v>
+        <v>383.6</v>
       </c>
       <c r="AR39" s="3" t="n">
-        <v>377.41</v>
+        <v>375.52</v>
       </c>
       <c r="AS39" s="3" t="n">
-        <v>378.18</v>
+        <v>377.49</v>
       </c>
       <c r="AT39" s="3" t="n">
-        <v>378.18</v>
+        <v>377.49</v>
       </c>
       <c r="AU39" s="3" t="n">
-        <v>4754600</v>
+        <v>4815400</v>
       </c>
       <c r="AV39" s="4">
         <f>IF(COUNT(AT39:AT40)=2,ROUND((AT39/AT40-1)*100,4),"")</f>
@@ -8211,22 +8425,22 @@
       </c>
       <c r="AW39" s="3" t="n"/>
       <c r="AX39" s="3" t="n">
-        <v>184.76</v>
+        <v>179.84</v>
       </c>
       <c r="AY39" s="3" t="n">
-        <v>186.4</v>
+        <v>180.72</v>
       </c>
       <c r="AZ39" s="3" t="n">
-        <v>183.56</v>
+        <v>176.36</v>
       </c>
       <c r="BA39" s="3" t="n">
-        <v>185.35</v>
+        <v>179.18</v>
       </c>
       <c r="BB39" s="3" t="n">
-        <v>185.35</v>
+        <v>179.18</v>
       </c>
       <c r="BC39" s="3" t="n">
-        <v>7756600</v>
+        <v>12254800</v>
       </c>
       <c r="BD39" s="4">
         <f>IF(COUNT(BB39:BB40)=2,ROUND((BB39/BB40-1)*100,4),"")</f>
@@ -8234,22 +8448,22 @@
       </c>
       <c r="BE39" s="3" t="n"/>
       <c r="BF39" s="3" t="n">
-        <v>55.07</v>
+        <v>56.31</v>
       </c>
       <c r="BG39" s="3" t="n">
-        <v>55.69</v>
+        <v>56.59</v>
       </c>
       <c r="BH39" s="3" t="n">
-        <v>54.97</v>
+        <v>56.01</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>55.54</v>
+        <v>56.05</v>
       </c>
       <c r="BJ39" s="3" t="n">
-        <v>55.54</v>
+        <v>56.05</v>
       </c>
       <c r="BK39" s="3" t="n">
-        <v>26542000</v>
+        <v>27116500</v>
       </c>
       <c r="BL39" s="4">
         <f>IF(COUNT(BJ39:BJ40)=2,ROUND((BJ39/BJ40-1)*100,4),"")</f>
@@ -8257,22 +8471,22 @@
       </c>
       <c r="BM39" s="3" t="n"/>
       <c r="BN39" s="3" t="n">
-        <v>108.14</v>
+        <v>108.36</v>
       </c>
       <c r="BO39" s="3" t="n">
-        <v>108.22</v>
+        <v>108.36</v>
       </c>
       <c r="BP39" s="3" t="n">
-        <v>108.09</v>
+        <v>108.11</v>
       </c>
       <c r="BQ39" s="3" t="n">
-        <v>108.12</v>
+        <v>108.17</v>
       </c>
       <c r="BR39" s="3" t="n">
-        <v>107.3324</v>
+        <v>107.3821</v>
       </c>
       <c r="BS39" s="3" t="n">
-        <v>1170800</v>
+        <v>1755100</v>
       </c>
       <c r="BT39" s="4">
         <f>IF(COUNT(BR39:BR40)=2,ROUND((BR39/BR40-1)*100,4),"")</f>
@@ -8280,38 +8494,38 @@
       </c>
       <c r="BU39" s="3" t="n"/>
       <c r="BV39" s="3" t="n">
-        <v>16.58</v>
+        <v>15.87</v>
       </c>
       <c r="BW39" s="3" t="n">
-        <v>17.27</v>
+        <v>16.64</v>
       </c>
       <c r="BX39" s="3" t="n">
-        <v>15.76</v>
+        <v>15.53</v>
       </c>
       <c r="BY39" s="3" t="n">
-        <v>15.84</v>
+        <v>16.13</v>
       </c>
       <c r="BZ39" s="3" t="n">
-        <v>15.84</v>
+        <v>16.13</v>
       </c>
       <c r="CA39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB39" s="3" t="n"/>
       <c r="CC39" s="3" t="n">
-        <v>4.577</v>
+        <v>4.497</v>
       </c>
       <c r="CD39" s="3" t="n">
-        <v>4.581</v>
+        <v>4.533</v>
       </c>
       <c r="CE39" s="3" t="n">
+        <v>4.485</v>
+      </c>
+      <c r="CF39" s="3" t="n">
         <v>4.529</v>
       </c>
-      <c r="CF39" s="3" t="n">
-        <v>4.539</v>
-      </c>
       <c r="CG39" s="3" t="n">
-        <v>4.539</v>
+        <v>4.529</v>
       </c>
       <c r="CH39" s="3" t="n">
         <v>0</v>
@@ -8337,20 +8551,20 @@
       </c>
       <c r="CP39" s="3" t="n"/>
       <c r="CQ39" s="4">
-        <f>X39-P39</f>
+        <f>IFERROR(X39-P39,"")</f>
         <v/>
       </c>
       <c r="CR39" s="4">
-        <f>AF39-P39</f>
+        <f>IFERROR(AF39-P39,"")</f>
         <v/>
       </c>
       <c r="CS39" s="6" t="n"/>
       <c r="CT39" s="4">
-        <f>AN39-AV39</f>
+        <f>IFERROR(AN39-AV39,"")</f>
         <v/>
       </c>
       <c r="CU39" s="4">
-        <f>BD39-BL39</f>
+        <f>IFERROR(BD39-BL39,"")</f>
         <v/>
       </c>
       <c r="CV39" s="6">
@@ -8358,256 +8572,229 @@
         <v/>
       </c>
       <c r="CW39" s="4">
-        <f>P39-BT39</f>
+        <f>IFERROR(P39-BT39,"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>743.16</v>
+        <v>748.74</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>746.15</v>
+        <v>752.41</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>739.51</v>
+        <v>747.41</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>745.4</v>
+        <v>751.28</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>745.4</v>
+        <v>751.28</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>43767400</v>
-      </c>
-      <c r="H40" s="4">
-        <f>IF(COUNT(F40:F41)=2,ROUND((F40/F41-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <v>50673300</v>
+      </c>
+      <c r="H40" s="4" t="n"/>
       <c r="I40" s="3" t="n"/>
       <c r="J40" s="3" t="n">
-        <v>84.31</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>84.45</v>
+        <v>85.48</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>84.06</v>
+        <v>85.18000000000001</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>84.36</v>
+        <v>85.45</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>84.0215</v>
+        <v>85.10720000000001</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>25806600</v>
-      </c>
-      <c r="P40" s="4">
-        <f>IF(COUNT(N40:N41)=2,ROUND((N40/N41-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <v>17940900</v>
+      </c>
+      <c r="P40" s="4" t="n"/>
       <c r="Q40" s="3" t="n"/>
       <c r="R40" s="3" t="n">
-        <v>79.61</v>
+        <v>79.73</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>79.68000000000001</v>
+        <v>79.91</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>79.54000000000001</v>
+        <v>79.73</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>79.66</v>
+        <v>79.87</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>79.27509999999999</v>
+        <v>79.4841</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>30771300</v>
-      </c>
-      <c r="X40" s="4">
-        <f>IF(COUNT(V40:V41)=2,ROUND((V40/V41-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <v>25159400</v>
+      </c>
+      <c r="X40" s="4" t="n"/>
       <c r="Y40" s="3" t="n"/>
       <c r="Z40" s="3" t="n">
-        <v>95.84999999999999</v>
+        <v>95.98</v>
       </c>
       <c r="AA40" s="3" t="n">
-        <v>95.91</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="AB40" s="3" t="n">
-        <v>95.75</v>
+        <v>95.98</v>
       </c>
       <c r="AC40" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="AD40" s="3" t="n">
-        <v>95.37179999999999</v>
+        <v>95.6204</v>
       </c>
       <c r="AE40" s="3" t="n">
-        <v>2989300</v>
-      </c>
-      <c r="AF40" s="4">
-        <f>IF(COUNT(AD40:AD41)=2,ROUND((AD40/AD41-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <v>1716000</v>
+      </c>
+      <c r="AF40" s="4" t="n"/>
       <c r="AG40" s="3" t="n"/>
       <c r="AH40" s="3" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="AI40" s="3" t="n">
         <v>28.41</v>
       </c>
-      <c r="AI40" s="3" t="n">
-        <v>28.46</v>
-      </c>
       <c r="AJ40" s="3" t="n">
-        <v>28.35</v>
+        <v>28.31</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>28.36</v>
+        <v>28.32</v>
       </c>
       <c r="AL40" s="3" t="n">
-        <v>28.36</v>
+        <v>28.32</v>
       </c>
       <c r="AM40" s="3" t="n">
-        <v>1338200</v>
-      </c>
-      <c r="AN40" s="4">
-        <f>IF(COUNT(AL40:AL41)=2,ROUND((AL40/AL41-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <v>2837900</v>
+      </c>
+      <c r="AN40" s="4" t="n"/>
       <c r="AO40" s="3" t="n"/>
       <c r="AP40" s="3" t="n">
-        <v>373.17</v>
+        <v>380.21</v>
       </c>
       <c r="AQ40" s="3" t="n">
-        <v>375.47</v>
+        <v>382.43</v>
       </c>
       <c r="AR40" s="3" t="n">
-        <v>368.95</v>
+        <v>378.83</v>
       </c>
       <c r="AS40" s="3" t="n">
-        <v>374.45</v>
+        <v>382.13</v>
       </c>
       <c r="AT40" s="3" t="n">
-        <v>374.45</v>
+        <v>382.13</v>
       </c>
       <c r="AU40" s="3" t="n">
-        <v>7728500</v>
-      </c>
-      <c r="AV40" s="4">
-        <f>IF(COUNT(AT40:AT41)=2,ROUND((AT40/AT41-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <v>3906500</v>
+      </c>
+      <c r="AV40" s="4" t="n"/>
       <c r="AW40" s="3" t="n"/>
       <c r="AX40" s="3" t="n">
-        <v>177.48</v>
+        <v>182.66</v>
       </c>
       <c r="AY40" s="3" t="n">
-        <v>181.63</v>
+        <v>185.71</v>
       </c>
       <c r="AZ40" s="3" t="n">
-        <v>177.15</v>
+        <v>182.04</v>
       </c>
       <c r="BA40" s="3" t="n">
-        <v>181.4</v>
+        <v>183.57</v>
       </c>
       <c r="BB40" s="3" t="n">
-        <v>181.4</v>
+        <v>183.57</v>
       </c>
       <c r="BC40" s="3" t="n">
-        <v>10528300</v>
-      </c>
-      <c r="BD40" s="4">
-        <f>IF(COUNT(BB40:BB41)=2,ROUND((BB40/BB41-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <v>8923100</v>
+      </c>
+      <c r="BD40" s="4" t="n"/>
       <c r="BE40" s="3" t="n"/>
       <c r="BF40" s="3" t="n">
-        <v>55.79</v>
+        <v>55.85</v>
       </c>
       <c r="BG40" s="3" t="n">
-        <v>55.8</v>
+        <v>56.16</v>
       </c>
       <c r="BH40" s="3" t="n">
-        <v>54.95</v>
+        <v>55.58</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>54.97</v>
+        <v>56.14</v>
       </c>
       <c r="BJ40" s="3" t="n">
-        <v>54.97</v>
+        <v>56.14</v>
       </c>
       <c r="BK40" s="3" t="n">
-        <v>41648100</v>
-      </c>
-      <c r="BL40" s="4">
-        <f>IF(COUNT(BJ40:BJ41)=2,ROUND((BJ40/BJ41-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <v>32043700</v>
+      </c>
+      <c r="BL40" s="4" t="n"/>
       <c r="BM40" s="3" t="n"/>
       <c r="BN40" s="3" t="n">
-        <v>108.09</v>
+        <v>108.43</v>
       </c>
       <c r="BO40" s="3" t="n">
-        <v>108.12</v>
+        <v>108.49</v>
       </c>
       <c r="BP40" s="3" t="n">
-        <v>107.98</v>
+        <v>108.3</v>
       </c>
       <c r="BQ40" s="3" t="n">
-        <v>108.05</v>
+        <v>108.49</v>
       </c>
       <c r="BR40" s="3" t="n">
-        <v>107.2629</v>
+        <v>107.6997</v>
       </c>
       <c r="BS40" s="3" t="n">
-        <v>941700</v>
-      </c>
-      <c r="BT40" s="4">
-        <f>IF(COUNT(BR40:BR41)=2,ROUND((BR40/BR41-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <v>1346000</v>
+      </c>
+      <c r="BT40" s="4" t="n"/>
       <c r="BU40" s="3" t="n"/>
       <c r="BV40" s="3" t="n">
-        <v>16.55</v>
+        <v>16.4</v>
       </c>
       <c r="BW40" s="3" t="n">
-        <v>18.91</v>
+        <v>16.5</v>
       </c>
       <c r="BX40" s="3" t="n">
-        <v>16.35</v>
+        <v>15.56</v>
       </c>
       <c r="BY40" s="3" t="n">
-        <v>16.9</v>
+        <v>15.57</v>
       </c>
       <c r="BZ40" s="3" t="n">
-        <v>16.9</v>
+        <v>15.57</v>
       </c>
       <c r="CA40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="CB40" s="3" t="n"/>
       <c r="CC40" s="3" t="n">
-        <v>4.561</v>
+        <v>4.457</v>
       </c>
       <c r="CD40" s="3" t="n">
-        <v>4.597</v>
+        <v>4.491</v>
       </c>
       <c r="CE40" s="3" t="n">
-        <v>4.557</v>
+        <v>4.457</v>
       </c>
       <c r="CF40" s="3" t="n">
-        <v>4.569</v>
+        <v>4.479</v>
       </c>
       <c r="CG40" s="3" t="n">
-        <v>4.569</v>
+        <v>4.479</v>
       </c>
       <c r="CH40" s="3" t="n">
         <v>0</v>
@@ -8633,20 +8820,20 @@
       </c>
       <c r="CP40" s="3" t="n"/>
       <c r="CQ40" s="4">
-        <f>X40-P40</f>
+        <f>IFERROR(X40-P40,"")</f>
         <v/>
       </c>
       <c r="CR40" s="4">
-        <f>AF40-P40</f>
+        <f>IFERROR(AF40-P40,"")</f>
         <v/>
       </c>
       <c r="CS40" s="6" t="n"/>
       <c r="CT40" s="4">
-        <f>AN40-AV40</f>
+        <f>IFERROR(AN40-AV40,"")</f>
         <v/>
       </c>
       <c r="CU40" s="4">
-        <f>BD40-BL40</f>
+        <f>IFERROR(BD40-BL40,"")</f>
         <v/>
       </c>
       <c r="CV40" s="6">
@@ -8654,572 +8841,7 @@
         <v/>
       </c>
       <c r="CW40" s="4">
-        <f>P40-BT40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>2026/07/07</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>750.22</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>750.96</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>745.21</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>747.71</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>747.71</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>43721500</v>
-      </c>
-      <c r="H41" s="4">
-        <f>IF(COUNT(F41:F42)=2,ROUND((F41/F42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n">
-        <v>85.12</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>85.17</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>84.54000000000001</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>84.55</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>84.21080000000001</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>24816400</v>
-      </c>
-      <c r="P41" s="4">
-        <f>IF(COUNT(N41:N42)=2,ROUND((N41/N42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="Q41" s="3" t="n"/>
-      <c r="R41" s="3" t="n">
-        <v>79.84999999999999</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>79.88</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>79.72</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>79.76000000000001</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>79.3746</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>28558300</v>
-      </c>
-      <c r="X41" s="4">
-        <f>IF(COUNT(V41:V42)=2,ROUND((V41/V42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="Y41" s="3" t="n"/>
-      <c r="Z41" s="3" t="n">
-        <v>96.16</v>
-      </c>
-      <c r="AA41" s="3" t="n">
-        <v>96.16</v>
-      </c>
-      <c r="AB41" s="3" t="n">
-        <v>95.98</v>
-      </c>
-      <c r="AC41" s="3" t="n">
-        <v>96.05</v>
-      </c>
-      <c r="AD41" s="3" t="n">
-        <v>95.521</v>
-      </c>
-      <c r="AE41" s="3" t="n">
-        <v>2279500</v>
-      </c>
-      <c r="AF41" s="4">
-        <f>IF(COUNT(AD41:AD42)=2,ROUND((AD41/AD42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="AG41" s="3" t="n"/>
-      <c r="AH41" s="3" t="n">
-        <v>28.34</v>
-      </c>
-      <c r="AI41" s="3" t="n">
-        <v>28.41</v>
-      </c>
-      <c r="AJ41" s="3" t="n">
-        <v>28.33</v>
-      </c>
-      <c r="AK41" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="AL41" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="AM41" s="3" t="n">
-        <v>1902000</v>
-      </c>
-      <c r="AN41" s="4">
-        <f>IF(COUNT(AL41:AL42)=2,ROUND((AL41/AL42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="AO41" s="3" t="n"/>
-      <c r="AP41" s="3" t="n">
-        <v>382.39</v>
-      </c>
-      <c r="AQ41" s="3" t="n">
-        <v>383.6</v>
-      </c>
-      <c r="AR41" s="3" t="n">
-        <v>375.52</v>
-      </c>
-      <c r="AS41" s="3" t="n">
-        <v>377.49</v>
-      </c>
-      <c r="AT41" s="3" t="n">
-        <v>377.49</v>
-      </c>
-      <c r="AU41" s="3" t="n">
-        <v>4815400</v>
-      </c>
-      <c r="AV41" s="4">
-        <f>IF(COUNT(AT41:AT42)=2,ROUND((AT41/AT42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="AW41" s="3" t="n"/>
-      <c r="AX41" s="3" t="n">
-        <v>179.84</v>
-      </c>
-      <c r="AY41" s="3" t="n">
-        <v>180.72</v>
-      </c>
-      <c r="AZ41" s="3" t="n">
-        <v>176.36</v>
-      </c>
-      <c r="BA41" s="3" t="n">
-        <v>179.18</v>
-      </c>
-      <c r="BB41" s="3" t="n">
-        <v>179.18</v>
-      </c>
-      <c r="BC41" s="3" t="n">
-        <v>12254800</v>
-      </c>
-      <c r="BD41" s="4">
-        <f>IF(COUNT(BB41:BB42)=2,ROUND((BB41/BB42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BE41" s="3" t="n"/>
-      <c r="BF41" s="3" t="n">
-        <v>56.31</v>
-      </c>
-      <c r="BG41" s="3" t="n">
-        <v>56.59</v>
-      </c>
-      <c r="BH41" s="3" t="n">
-        <v>56.01</v>
-      </c>
-      <c r="BI41" s="3" t="n">
-        <v>56.05</v>
-      </c>
-      <c r="BJ41" s="3" t="n">
-        <v>56.05</v>
-      </c>
-      <c r="BK41" s="3" t="n">
-        <v>27116500</v>
-      </c>
-      <c r="BL41" s="4">
-        <f>IF(COUNT(BJ41:BJ42)=2,ROUND((BJ41/BJ42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BM41" s="3" t="n"/>
-      <c r="BN41" s="3" t="n">
-        <v>108.36</v>
-      </c>
-      <c r="BO41" s="3" t="n">
-        <v>108.36</v>
-      </c>
-      <c r="BP41" s="3" t="n">
-        <v>108.11</v>
-      </c>
-      <c r="BQ41" s="3" t="n">
-        <v>108.17</v>
-      </c>
-      <c r="BR41" s="3" t="n">
-        <v>107.3821</v>
-      </c>
-      <c r="BS41" s="3" t="n">
-        <v>1755100</v>
-      </c>
-      <c r="BT41" s="4">
-        <f>IF(COUNT(BR41:BR42)=2,ROUND((BR41/BR42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="BU41" s="3" t="n"/>
-      <c r="BV41" s="3" t="n">
-        <v>15.87</v>
-      </c>
-      <c r="BW41" s="3" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="BX41" s="3" t="n">
-        <v>15.53</v>
-      </c>
-      <c r="BY41" s="3" t="n">
-        <v>16.13</v>
-      </c>
-      <c r="BZ41" s="3" t="n">
-        <v>16.13</v>
-      </c>
-      <c r="CA41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB41" s="3" t="n"/>
-      <c r="CC41" s="3" t="n">
-        <v>4.497</v>
-      </c>
-      <c r="CD41" s="3" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="CE41" s="3" t="n">
-        <v>4.485</v>
-      </c>
-      <c r="CF41" s="3" t="n">
-        <v>4.529</v>
-      </c>
-      <c r="CG41" s="3" t="n">
-        <v>4.529</v>
-      </c>
-      <c r="CH41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI41" s="3" t="n"/>
-      <c r="CJ41" s="4">
-        <f>IF(COUNT(BY41:BY42)=2,ROUND((BY41/BY42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK41" s="4">
-        <f>IF(COUNT(BY41:BY42)=2,ROUND((BY41/BY42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL41" s="4" t="n"/>
-      <c r="CM41" s="4" t="n"/>
-      <c r="CN41" s="4">
-        <f>IF(COUNT(CF41:CF42)=2,ROUND((CF41/CF42-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO41" s="5">
-        <f>IF(COUNT(CF41:CF42)=2,(CF41-CF42)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP41" s="3" t="n"/>
-      <c r="CQ41" s="4">
-        <f>X41-P41</f>
-        <v/>
-      </c>
-      <c r="CR41" s="4">
-        <f>AF41-P41</f>
-        <v/>
-      </c>
-      <c r="CS41" s="6" t="n"/>
-      <c r="CT41" s="4">
-        <f>AN41-AV41</f>
-        <v/>
-      </c>
-      <c r="CU41" s="4">
-        <f>BD41-BL41</f>
-        <v/>
-      </c>
-      <c r="CV41" s="6">
-        <f>BY41/CF41</f>
-        <v/>
-      </c>
-      <c r="CW41" s="4">
-        <f>P41-BT41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>748.74</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>752.41</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>747.41</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>751.28</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>751.28</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>50673300</v>
-      </c>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n">
-        <v>85.43000000000001</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>85.48</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>85.18000000000001</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>85.45</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>85.10720000000001</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>17940900</v>
-      </c>
-      <c r="P42" s="4" t="n"/>
-      <c r="Q42" s="3" t="n"/>
-      <c r="R42" s="3" t="n">
-        <v>79.73</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>79.91</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>79.73</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>79.87</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>79.4841</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>25159400</v>
-      </c>
-      <c r="X42" s="4" t="n"/>
-      <c r="Y42" s="3" t="n"/>
-      <c r="Z42" s="3" t="n">
-        <v>95.98</v>
-      </c>
-      <c r="AA42" s="3" t="n">
-        <v>96.20999999999999</v>
-      </c>
-      <c r="AB42" s="3" t="n">
-        <v>95.98</v>
-      </c>
-      <c r="AC42" s="3" t="n">
-        <v>96.15000000000001</v>
-      </c>
-      <c r="AD42" s="3" t="n">
-        <v>95.6204</v>
-      </c>
-      <c r="AE42" s="3" t="n">
-        <v>1716000</v>
-      </c>
-      <c r="AF42" s="4" t="n"/>
-      <c r="AG42" s="3" t="n"/>
-      <c r="AH42" s="3" t="n">
-        <v>28.39</v>
-      </c>
-      <c r="AI42" s="3" t="n">
-        <v>28.41</v>
-      </c>
-      <c r="AJ42" s="3" t="n">
-        <v>28.31</v>
-      </c>
-      <c r="AK42" s="3" t="n">
-        <v>28.32</v>
-      </c>
-      <c r="AL42" s="3" t="n">
-        <v>28.32</v>
-      </c>
-      <c r="AM42" s="3" t="n">
-        <v>2837900</v>
-      </c>
-      <c r="AN42" s="4" t="n"/>
-      <c r="AO42" s="3" t="n"/>
-      <c r="AP42" s="3" t="n">
-        <v>380.21</v>
-      </c>
-      <c r="AQ42" s="3" t="n">
-        <v>382.43</v>
-      </c>
-      <c r="AR42" s="3" t="n">
-        <v>378.83</v>
-      </c>
-      <c r="AS42" s="3" t="n">
-        <v>382.13</v>
-      </c>
-      <c r="AT42" s="3" t="n">
-        <v>382.13</v>
-      </c>
-      <c r="AU42" s="3" t="n">
-        <v>3906500</v>
-      </c>
-      <c r="AV42" s="4" t="n"/>
-      <c r="AW42" s="3" t="n"/>
-      <c r="AX42" s="3" t="n">
-        <v>182.66</v>
-      </c>
-      <c r="AY42" s="3" t="n">
-        <v>185.71</v>
-      </c>
-      <c r="AZ42" s="3" t="n">
-        <v>182.04</v>
-      </c>
-      <c r="BA42" s="3" t="n">
-        <v>183.57</v>
-      </c>
-      <c r="BB42" s="3" t="n">
-        <v>183.57</v>
-      </c>
-      <c r="BC42" s="3" t="n">
-        <v>8923100</v>
-      </c>
-      <c r="BD42" s="4" t="n"/>
-      <c r="BE42" s="3" t="n"/>
-      <c r="BF42" s="3" t="n">
-        <v>55.85</v>
-      </c>
-      <c r="BG42" s="3" t="n">
-        <v>56.16</v>
-      </c>
-      <c r="BH42" s="3" t="n">
-        <v>55.58</v>
-      </c>
-      <c r="BI42" s="3" t="n">
-        <v>56.14</v>
-      </c>
-      <c r="BJ42" s="3" t="n">
-        <v>56.14</v>
-      </c>
-      <c r="BK42" s="3" t="n">
-        <v>32043700</v>
-      </c>
-      <c r="BL42" s="4" t="n"/>
-      <c r="BM42" s="3" t="n"/>
-      <c r="BN42" s="3" t="n">
-        <v>108.43</v>
-      </c>
-      <c r="BO42" s="3" t="n">
-        <v>108.49</v>
-      </c>
-      <c r="BP42" s="3" t="n">
-        <v>108.3</v>
-      </c>
-      <c r="BQ42" s="3" t="n">
-        <v>108.49</v>
-      </c>
-      <c r="BR42" s="3" t="n">
-        <v>107.6997</v>
-      </c>
-      <c r="BS42" s="3" t="n">
-        <v>1346000</v>
-      </c>
-      <c r="BT42" s="4" t="n"/>
-      <c r="BU42" s="3" t="n"/>
-      <c r="BV42" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="BW42" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BX42" s="3" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="BY42" s="3" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="BZ42" s="3" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="CA42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB42" s="3" t="n"/>
-      <c r="CC42" s="3" t="n">
-        <v>4.457</v>
-      </c>
-      <c r="CD42" s="3" t="n">
-        <v>4.491</v>
-      </c>
-      <c r="CE42" s="3" t="n">
-        <v>4.457</v>
-      </c>
-      <c r="CF42" s="3" t="n">
-        <v>4.479</v>
-      </c>
-      <c r="CG42" s="3" t="n">
-        <v>4.479</v>
-      </c>
-      <c r="CH42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI42" s="3" t="n"/>
-      <c r="CJ42" s="4">
-        <f>IF(COUNT(BY42:BY43)=2,ROUND((BY42/BY43-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK42" s="4">
-        <f>IF(COUNT(BY42:BY43)=2,ROUND((BY42/BY43-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL42" s="4" t="n"/>
-      <c r="CM42" s="4" t="n"/>
-      <c r="CN42" s="4">
-        <f>IF(COUNT(CF42:CF43)=2,ROUND((CF42/CF43-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO42" s="5">
-        <f>IF(COUNT(CF42:CF43)=2,(CF42-CF43)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP42" s="3" t="n"/>
-      <c r="CQ42" s="4">
-        <f>X42-P42</f>
-        <v/>
-      </c>
-      <c r="CR42" s="4">
-        <f>AF42-P42</f>
-        <v/>
-      </c>
-      <c r="CS42" s="6" t="n"/>
-      <c r="CT42" s="4">
-        <f>AN42-AV42</f>
-        <v/>
-      </c>
-      <c r="CU42" s="4">
-        <f>BD42-BL42</f>
-        <v/>
-      </c>
-      <c r="CV42" s="6">
-        <f>BY42/CF42</f>
-        <v/>
-      </c>
-      <c r="CW42" s="4">
-        <f>P42-BT42</f>
+        <f>IFERROR(P40-BT40,"")</f>
         <v/>
       </c>
     </row>

--- a/04_结果/示例审批/外部数据新版式示例.xlsx
+++ b/04_结果/示例审批/外部数据新版式示例.xlsx
@@ -490,7 +490,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1. VIX/TNX 原始数据按 ETF 格式展示：第14行=名称，第15行=Open/High/Low/Close/Adj Close/Volume。</t>
+          <t>1. VIX/TNX 原始数据按 ETF 格式展示：第14行=名称，第15行=Open/High/Low/Close（只保留 OHLC，不展示 Adj Close/Volume）。</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A14:CW40"/>
+  <dimension ref="A14:CS40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -626,10 +626,6 @@
     <col width="14" customWidth="1" min="95" max="95"/>
     <col width="14" customWidth="1" min="96" max="96"/>
     <col width="14" customWidth="1" min="97" max="97"/>
-    <col width="14" customWidth="1" min="98" max="98"/>
-    <col width="14" customWidth="1" min="99" max="99"/>
-    <col width="14" customWidth="1" min="100" max="100"/>
-    <col width="14" customWidth="1" min="101" max="101"/>
   </cols>
   <sheetData>
     <row r="14" ht="30" customHeight="1">
@@ -757,71 +753,67 @@
       <c r="BZ14" s="2" t="n"/>
       <c r="CA14" s="2" t="n"/>
       <c r="CB14" s="2" t="n"/>
-      <c r="CC14" s="2" t="n"/>
+      <c r="CC14" s="2" t="inlineStr">
+        <is>
+          <t>TNX</t>
+        </is>
+      </c>
       <c r="CD14" s="2" t="n"/>
-      <c r="CE14" s="2" t="inlineStr">
-        <is>
-          <t>TNX</t>
-        </is>
-      </c>
+      <c r="CE14" s="2" t="n"/>
       <c r="CF14" s="2" t="n"/>
-      <c r="CG14" s="2" t="n"/>
-      <c r="CH14" s="2" t="n"/>
-      <c r="CI14" s="2" t="n"/>
+      <c r="CG14" s="2" t="inlineStr">
+        <is>
+          <t>VIX_Chg%</t>
+        </is>
+      </c>
+      <c r="CH14" s="2" t="inlineStr">
+        <is>
+          <t>VIX_5dChg</t>
+        </is>
+      </c>
+      <c r="CI14" s="2" t="inlineStr">
+        <is>
+          <t>VIX_20dVol</t>
+        </is>
+      </c>
       <c r="CJ14" s="2" t="n"/>
       <c r="CK14" s="2" t="inlineStr">
         <is>
-          <t>VIX_Chg%</t>
-        </is>
-      </c>
-      <c r="CL14" s="2" t="inlineStr">
-        <is>
-          <t>VIX_5dChg</t>
-        </is>
-      </c>
+          <t>TNX_ChgBp</t>
+        </is>
+      </c>
+      <c r="CL14" s="2" t="n"/>
       <c r="CM14" s="2" t="inlineStr">
         <is>
-          <t>VIX_20dVol</t>
-        </is>
-      </c>
-      <c r="CN14" s="2" t="n"/>
+          <t>CreditSpread</t>
+        </is>
+      </c>
+      <c r="CN14" s="2" t="inlineStr">
+        <is>
+          <t>JNKSpread</t>
+        </is>
+      </c>
       <c r="CO14" s="2" t="inlineStr">
         <is>
-          <t>TNX_ChgBp</t>
-        </is>
-      </c>
-      <c r="CP14" s="2" t="n"/>
+          <t>StkBonCorr</t>
+        </is>
+      </c>
+      <c r="CP14" s="2" t="inlineStr">
+        <is>
+          <t>USDGoldRatio</t>
+        </is>
+      </c>
       <c r="CQ14" s="2" t="inlineStr">
         <is>
-          <t>CreditSpread</t>
+          <t>SectRotation</t>
         </is>
       </c>
       <c r="CR14" s="2" t="inlineStr">
         <is>
-          <t>JNKSpread</t>
+          <t>VIX_TNX_Ratio</t>
         </is>
       </c>
       <c r="CS14" s="2" t="inlineStr">
-        <is>
-          <t>StkBonCorr</t>
-        </is>
-      </c>
-      <c r="CT14" s="2" t="inlineStr">
-        <is>
-          <t>USDGoldRatio</t>
-        </is>
-      </c>
-      <c r="CU14" s="2" t="inlineStr">
-        <is>
-          <t>SectRotation</t>
-        </is>
-      </c>
-      <c r="CV14" s="2" t="inlineStr">
-        <is>
-          <t>VIX_TNX_Ratio</t>
-        </is>
-      </c>
-      <c r="CW14" s="2" t="inlineStr">
         <is>
           <t>YldCurveProxy</t>
         </is>
@@ -1177,110 +1169,90 @@
           <t>Close</t>
         </is>
       </c>
-      <c r="BZ15" s="2" t="inlineStr">
-        <is>
-          <t>Adj Close</t>
-        </is>
-      </c>
+      <c r="BZ15" s="2" t="n"/>
       <c r="CA15" s="2" t="inlineStr">
         <is>
-          <t>Volume</t>
-        </is>
-      </c>
-      <c r="CB15" s="2" t="n"/>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="CB15" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="CC15" s="2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="CD15" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="CE15" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="CE15" s="2" t="n"/>
       <c r="CF15" s="2" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>VIX回报</t>
         </is>
       </c>
       <c r="CG15" s="2" t="inlineStr">
         <is>
-          <t>Adj Close</t>
+          <t>VIX_close/昨VIX_close-1</t>
         </is>
       </c>
       <c r="CH15" s="2" t="inlineStr">
         <is>
-          <t>Volume</t>
-        </is>
-      </c>
-      <c r="CI15" s="2" t="n"/>
+          <t>VIX_close/5日前VIX_close-1</t>
+        </is>
+      </c>
+      <c r="CI15" s="2" t="inlineStr">
+        <is>
+          <t>STDEV(VIX日变化,近20日)</t>
+        </is>
+      </c>
       <c r="CJ15" s="2" t="inlineStr">
         <is>
-          <t>VIX回报</t>
+          <t>TNX回报</t>
         </is>
       </c>
       <c r="CK15" s="2" t="inlineStr">
         <is>
-          <t>VIX_close/昨VIX_close-1</t>
-        </is>
-      </c>
-      <c r="CL15" s="2" t="inlineStr">
-        <is>
-          <t>VIX_close/5日前VIX_close-1</t>
-        </is>
-      </c>
+          <t>(TNX_close-昨TNX_close)*100</t>
+        </is>
+      </c>
+      <c r="CL15" s="2" t="n"/>
       <c r="CM15" s="2" t="inlineStr">
         <is>
-          <t>STDEV(VIX日变化,近20日)</t>
+          <t>HYG-TLT</t>
         </is>
       </c>
       <c r="CN15" s="2" t="inlineStr">
         <is>
-          <t>TNX回报</t>
+          <t>JNK-TLT</t>
         </is>
       </c>
       <c r="CO15" s="2" t="inlineStr">
         <is>
-          <t>(TNX_close-昨TNX_close)*100</t>
-        </is>
-      </c>
-      <c r="CP15" s="2" t="n"/>
+          <t>CORREL(SPY,TLT,近20日)</t>
+        </is>
+      </c>
+      <c r="CP15" s="2" t="inlineStr">
+        <is>
+          <t>UUP-GLD</t>
+        </is>
+      </c>
       <c r="CQ15" s="2" t="inlineStr">
         <is>
-          <t>HYG-TLT</t>
+          <t>XLK-XLF</t>
         </is>
       </c>
       <c r="CR15" s="2" t="inlineStr">
         <is>
-          <t>JNK-TLT</t>
+          <t>VIX_close/TNX_close</t>
         </is>
       </c>
       <c r="CS15" s="2" t="inlineStr">
-        <is>
-          <t>CORREL(SPY,TLT,近20日)</t>
-        </is>
-      </c>
-      <c r="CT15" s="2" t="inlineStr">
-        <is>
-          <t>UUP-GLD</t>
-        </is>
-      </c>
-      <c r="CU15" s="2" t="inlineStr">
-        <is>
-          <t>XLK-XLF</t>
-        </is>
-      </c>
-      <c r="CV15" s="2" t="inlineStr">
-        <is>
-          <t>VIX_close/TNX_close</t>
-        </is>
-      </c>
-      <c r="CW15" s="2" t="inlineStr">
         <is>
           <t>TLT-TIP</t>
         </is>
@@ -1511,82 +1483,70 @@
       <c r="BY16" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="BZ16" s="3" t="n">
-        <v>14.9</v>
-      </c>
+      <c r="BZ16" s="3" t="n"/>
       <c r="CA16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB16" s="3" t="n"/>
+        <v>4.664</v>
+      </c>
+      <c r="CB16" s="3" t="n">
+        <v>4.672</v>
+      </c>
       <c r="CC16" s="3" t="n">
-        <v>4.664</v>
+        <v>4.603</v>
       </c>
       <c r="CD16" s="3" t="n">
-        <v>4.672</v>
-      </c>
-      <c r="CE16" s="3" t="n">
-        <v>4.603</v>
-      </c>
-      <c r="CF16" s="3" t="n">
         <v>4.66</v>
       </c>
-      <c r="CG16" s="3" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="CH16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI16" s="3" t="n"/>
+      <c r="CE16" s="3" t="n"/>
+      <c r="CF16" s="4">
+        <f>IF(COUNT(BY16:BY17)=2,ROUND((BY16/BY17-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG16" s="4">
+        <f>IF(COUNT(BY16:BY17)=2,ROUND((BY16/BY17-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH16" s="4">
+        <f>IF(COUNT(BY16:BY21)=6,ROUND((BY16/BY21-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI16" s="4">
+        <f>IF(COUNT(CG16:CG35)=20,IFERROR(ROUND(STDEV(CG16:CG35),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ16" s="4">
-        <f>IF(COUNT(BY16:BY17)=2,ROUND((BY16/BY17-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK16" s="4">
-        <f>IF(COUNT(BY16:BY17)=2,ROUND((BY16/BY17-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL16" s="4">
-        <f>IF(COUNT(BY16:BY21)=6,ROUND((BY16/BY21-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD16:CD17)=2,ROUND((CD16/CD17-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK16" s="5">
+        <f>IF(COUNT(CD16:CD17)=2,(CD16-CD17)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL16" s="3" t="n"/>
       <c r="CM16" s="4">
-        <f>IF(COUNT(CK16:CK35)=20,IFERROR(ROUND(STDEV(CK16:CK35),4),""),"")</f>
+        <f>IFERROR(X16-P16,"")</f>
         <v/>
       </c>
       <c r="CN16" s="4">
-        <f>IF(COUNT(CF16:CF17)=2,ROUND((CF16/CF17-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO16" s="5">
-        <f>IF(COUNT(CF16:CF17)=2,(CF16-CF17)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP16" s="3" t="n"/>
+        <f>IFERROR(AF16-P16,"")</f>
+        <v/>
+      </c>
+      <c r="CO16" s="6">
+        <f>IF(COUNT(H16:H35)=20,IFERROR(CORREL(H16:H35,P16:P35),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP16" s="4">
+        <f>IFERROR(AN16-AV16,"")</f>
+        <v/>
+      </c>
       <c r="CQ16" s="4">
-        <f>IFERROR(X16-P16,"")</f>
-        <v/>
-      </c>
-      <c r="CR16" s="4">
-        <f>IFERROR(AF16-P16,"")</f>
-        <v/>
-      </c>
-      <c r="CS16" s="6">
-        <f>IF(COUNT(H16:H35)=20,IFERROR(CORREL(H16:H35,P16:P35),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT16" s="4">
-        <f>IFERROR(AN16-AV16,"")</f>
-        <v/>
-      </c>
-      <c r="CU16" s="4">
         <f>IFERROR(BD16-BL16,"")</f>
         <v/>
       </c>
-      <c r="CV16" s="6">
-        <f>BY16/CF16</f>
-        <v/>
-      </c>
-      <c r="CW16" s="4">
+      <c r="CR16" s="6">
+        <f>BY16/CD16</f>
+        <v/>
+      </c>
+      <c r="CS16" s="4">
         <f>IFERROR(P16-BT16,"")</f>
         <v/>
       </c>
@@ -1816,82 +1776,70 @@
       <c r="BY17" s="3" t="n">
         <v>15.15</v>
       </c>
-      <c r="BZ17" s="3" t="n">
-        <v>15.15</v>
-      </c>
+      <c r="BZ17" s="3" t="n"/>
       <c r="CA17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB17" s="3" t="n"/>
+        <v>4.643</v>
+      </c>
+      <c r="CB17" s="3" t="n">
+        <v>4.676</v>
+      </c>
       <c r="CC17" s="3" t="n">
-        <v>4.643</v>
+        <v>4.635</v>
       </c>
       <c r="CD17" s="3" t="n">
-        <v>4.676</v>
-      </c>
-      <c r="CE17" s="3" t="n">
-        <v>4.635</v>
-      </c>
-      <c r="CF17" s="3" t="n">
         <v>4.67</v>
       </c>
-      <c r="CG17" s="3" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="CH17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI17" s="3" t="n"/>
+      <c r="CE17" s="3" t="n"/>
+      <c r="CF17" s="4">
+        <f>IF(COUNT(BY17:BY18)=2,ROUND((BY17/BY18-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG17" s="4">
+        <f>IF(COUNT(BY17:BY18)=2,ROUND((BY17/BY18-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH17" s="4">
+        <f>IF(COUNT(BY17:BY22)=6,ROUND((BY17/BY22-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI17" s="4">
+        <f>IF(COUNT(CG17:CG36)=20,IFERROR(ROUND(STDEV(CG17:CG36),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ17" s="4">
-        <f>IF(COUNT(BY17:BY18)=2,ROUND((BY17/BY18-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK17" s="4">
-        <f>IF(COUNT(BY17:BY18)=2,ROUND((BY17/BY18-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL17" s="4">
-        <f>IF(COUNT(BY17:BY22)=6,ROUND((BY17/BY22-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD17:CD18)=2,ROUND((CD17/CD18-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK17" s="5">
+        <f>IF(COUNT(CD17:CD18)=2,(CD17-CD18)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL17" s="3" t="n"/>
       <c r="CM17" s="4">
-        <f>IF(COUNT(CK17:CK36)=20,IFERROR(ROUND(STDEV(CK17:CK36),4),""),"")</f>
+        <f>IFERROR(X17-P17,"")</f>
         <v/>
       </c>
       <c r="CN17" s="4">
-        <f>IF(COUNT(CF17:CF18)=2,ROUND((CF17/CF18-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO17" s="5">
-        <f>IF(COUNT(CF17:CF18)=2,(CF17-CF18)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP17" s="3" t="n"/>
+        <f>IFERROR(AF17-P17,"")</f>
+        <v/>
+      </c>
+      <c r="CO17" s="6">
+        <f>IF(COUNT(H17:H36)=20,IFERROR(CORREL(H17:H36,P17:P36),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP17" s="4">
+        <f>IFERROR(AN17-AV17,"")</f>
+        <v/>
+      </c>
       <c r="CQ17" s="4">
-        <f>IFERROR(X17-P17,"")</f>
-        <v/>
-      </c>
-      <c r="CR17" s="4">
-        <f>IFERROR(AF17-P17,"")</f>
-        <v/>
-      </c>
-      <c r="CS17" s="6">
-        <f>IF(COUNT(H17:H36)=20,IFERROR(CORREL(H17:H36,P17:P36),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT17" s="4">
-        <f>IFERROR(AN17-AV17,"")</f>
-        <v/>
-      </c>
-      <c r="CU17" s="4">
         <f>IFERROR(BD17-BL17,"")</f>
         <v/>
       </c>
-      <c r="CV17" s="6">
-        <f>BY17/CF17</f>
-        <v/>
-      </c>
-      <c r="CW17" s="4">
+      <c r="CR17" s="6">
+        <f>BY17/CD17</f>
+        <v/>
+      </c>
+      <c r="CS17" s="4">
         <f>IFERROR(P17-BT17,"")</f>
         <v/>
       </c>
@@ -2121,82 +2069,70 @@
       <c r="BY18" s="3" t="n">
         <v>15.81</v>
       </c>
-      <c r="BZ18" s="3" t="n">
-        <v>15.81</v>
-      </c>
+      <c r="BZ18" s="3" t="n"/>
       <c r="CA18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB18" s="3" t="n"/>
+        <v>4.609</v>
+      </c>
+      <c r="CB18" s="3" t="n">
+        <v>4.639</v>
+      </c>
       <c r="CC18" s="3" t="n">
-        <v>4.609</v>
+        <v>4.607</v>
       </c>
       <c r="CD18" s="3" t="n">
-        <v>4.639</v>
-      </c>
-      <c r="CE18" s="3" t="n">
-        <v>4.607</v>
-      </c>
-      <c r="CF18" s="3" t="n">
         <v>4.617</v>
       </c>
-      <c r="CG18" s="3" t="n">
-        <v>4.617</v>
-      </c>
-      <c r="CH18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI18" s="3" t="n"/>
+      <c r="CE18" s="3" t="n"/>
+      <c r="CF18" s="4">
+        <f>IF(COUNT(BY18:BY19)=2,ROUND((BY18/BY19-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG18" s="4">
+        <f>IF(COUNT(BY18:BY19)=2,ROUND((BY18/BY19-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH18" s="4">
+        <f>IF(COUNT(BY18:BY23)=6,ROUND((BY18/BY23-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI18" s="4">
+        <f>IF(COUNT(CG18:CG37)=20,IFERROR(ROUND(STDEV(CG18:CG37),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ18" s="4">
-        <f>IF(COUNT(BY18:BY19)=2,ROUND((BY18/BY19-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK18" s="4">
-        <f>IF(COUNT(BY18:BY19)=2,ROUND((BY18/BY19-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL18" s="4">
-        <f>IF(COUNT(BY18:BY23)=6,ROUND((BY18/BY23-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD18:CD19)=2,ROUND((CD18/CD19-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK18" s="5">
+        <f>IF(COUNT(CD18:CD19)=2,(CD18-CD19)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL18" s="3" t="n"/>
       <c r="CM18" s="4">
-        <f>IF(COUNT(CK18:CK37)=20,IFERROR(ROUND(STDEV(CK18:CK37),4),""),"")</f>
+        <f>IFERROR(X18-P18,"")</f>
         <v/>
       </c>
       <c r="CN18" s="4">
-        <f>IF(COUNT(CF18:CF19)=2,ROUND((CF18/CF19-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO18" s="5">
-        <f>IF(COUNT(CF18:CF19)=2,(CF18-CF19)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP18" s="3" t="n"/>
+        <f>IFERROR(AF18-P18,"")</f>
+        <v/>
+      </c>
+      <c r="CO18" s="6">
+        <f>IF(COUNT(H18:H37)=20,IFERROR(CORREL(H18:H37,P18:P37),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP18" s="4">
+        <f>IFERROR(AN18-AV18,"")</f>
+        <v/>
+      </c>
       <c r="CQ18" s="4">
-        <f>IFERROR(X18-P18,"")</f>
-        <v/>
-      </c>
-      <c r="CR18" s="4">
-        <f>IFERROR(AF18-P18,"")</f>
-        <v/>
-      </c>
-      <c r="CS18" s="6">
-        <f>IF(COUNT(H18:H37)=20,IFERROR(CORREL(H18:H37,P18:P37),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT18" s="4">
-        <f>IFERROR(AN18-AV18,"")</f>
-        <v/>
-      </c>
-      <c r="CU18" s="4">
         <f>IFERROR(BD18-BL18,"")</f>
         <v/>
       </c>
-      <c r="CV18" s="6">
-        <f>BY18/CF18</f>
-        <v/>
-      </c>
-      <c r="CW18" s="4">
+      <c r="CR18" s="6">
+        <f>BY18/CD18</f>
+        <v/>
+      </c>
+      <c r="CS18" s="4">
         <f>IFERROR(P18-BT18,"")</f>
         <v/>
       </c>
@@ -2426,82 +2362,70 @@
       <c r="BY19" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="BZ19" s="3" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="BZ19" s="3" t="n"/>
       <c r="CA19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB19" s="3" t="n"/>
+        <v>4.665</v>
+      </c>
+      <c r="CB19" s="3" t="n">
+        <v>4.668</v>
+      </c>
       <c r="CC19" s="3" t="n">
-        <v>4.665</v>
+        <v>4.619</v>
       </c>
       <c r="CD19" s="3" t="n">
-        <v>4.668</v>
-      </c>
-      <c r="CE19" s="3" t="n">
-        <v>4.619</v>
-      </c>
-      <c r="CF19" s="3" t="n">
         <v>4.627</v>
       </c>
-      <c r="CG19" s="3" t="n">
-        <v>4.627</v>
-      </c>
-      <c r="CH19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI19" s="3" t="n"/>
+      <c r="CE19" s="3" t="n"/>
+      <c r="CF19" s="4">
+        <f>IF(COUNT(BY19:BY20)=2,ROUND((BY19/BY20-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG19" s="4">
+        <f>IF(COUNT(BY19:BY20)=2,ROUND((BY19/BY20-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH19" s="4">
+        <f>IF(COUNT(BY19:BY24)=6,ROUND((BY19/BY24-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI19" s="4">
+        <f>IF(COUNT(CG19:CG38)=20,IFERROR(ROUND(STDEV(CG19:CG38),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ19" s="4">
-        <f>IF(COUNT(BY19:BY20)=2,ROUND((BY19/BY20-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK19" s="4">
-        <f>IF(COUNT(BY19:BY20)=2,ROUND((BY19/BY20-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL19" s="4">
-        <f>IF(COUNT(BY19:BY24)=6,ROUND((BY19/BY24-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD19:CD20)=2,ROUND((CD19/CD20-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK19" s="5">
+        <f>IF(COUNT(CD19:CD20)=2,(CD19-CD20)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL19" s="3" t="n"/>
       <c r="CM19" s="4">
-        <f>IF(COUNT(CK19:CK38)=20,IFERROR(ROUND(STDEV(CK19:CK38),4),""),"")</f>
+        <f>IFERROR(X19-P19,"")</f>
         <v/>
       </c>
       <c r="CN19" s="4">
-        <f>IF(COUNT(CF19:CF20)=2,ROUND((CF19/CF20-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO19" s="5">
-        <f>IF(COUNT(CF19:CF20)=2,(CF19-CF20)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP19" s="3" t="n"/>
+        <f>IFERROR(AF19-P19,"")</f>
+        <v/>
+      </c>
+      <c r="CO19" s="6">
+        <f>IF(COUNT(H19:H38)=20,IFERROR(CORREL(H19:H38,P19:P38),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP19" s="4">
+        <f>IFERROR(AN19-AV19,"")</f>
+        <v/>
+      </c>
       <c r="CQ19" s="4">
-        <f>IFERROR(X19-P19,"")</f>
-        <v/>
-      </c>
-      <c r="CR19" s="4">
-        <f>IFERROR(AF19-P19,"")</f>
-        <v/>
-      </c>
-      <c r="CS19" s="6">
-        <f>IF(COUNT(H19:H38)=20,IFERROR(CORREL(H19:H38,P19:P38),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT19" s="4">
-        <f>IFERROR(AN19-AV19,"")</f>
-        <v/>
-      </c>
-      <c r="CU19" s="4">
         <f>IFERROR(BD19-BL19,"")</f>
         <v/>
       </c>
-      <c r="CV19" s="6">
-        <f>BY19/CF19</f>
-        <v/>
-      </c>
-      <c r="CW19" s="4">
+      <c r="CR19" s="6">
+        <f>BY19/CD19</f>
+        <v/>
+      </c>
+      <c r="CS19" s="4">
         <f>IFERROR(P19-BT19,"")</f>
         <v/>
       </c>
@@ -2731,82 +2655,70 @@
       <c r="BY20" s="3" t="n">
         <v>15.86</v>
       </c>
-      <c r="BZ20" s="3" t="n">
-        <v>15.86</v>
-      </c>
+      <c r="BZ20" s="3" t="n"/>
       <c r="CA20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB20" s="3" t="n"/>
+        <v>4.671</v>
+      </c>
+      <c r="CB20" s="3" t="n">
+        <v>4.702</v>
+      </c>
       <c r="CC20" s="3" t="n">
         <v>4.671</v>
       </c>
       <c r="CD20" s="3" t="n">
-        <v>4.702</v>
-      </c>
-      <c r="CE20" s="3" t="n">
-        <v>4.671</v>
-      </c>
-      <c r="CF20" s="3" t="n">
         <v>4.686</v>
       </c>
-      <c r="CG20" s="3" t="n">
-        <v>4.686</v>
-      </c>
-      <c r="CH20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI20" s="3" t="n"/>
+      <c r="CE20" s="3" t="n"/>
+      <c r="CF20" s="4">
+        <f>IF(COUNT(BY20:BY21)=2,ROUND((BY20/BY21-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG20" s="4">
+        <f>IF(COUNT(BY20:BY21)=2,ROUND((BY20/BY21-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH20" s="4">
+        <f>IF(COUNT(BY20:BY25)=6,ROUND((BY20/BY25-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI20" s="4">
+        <f>IF(COUNT(CG20:CG39)=20,IFERROR(ROUND(STDEV(CG20:CG39),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ20" s="4">
-        <f>IF(COUNT(BY20:BY21)=2,ROUND((BY20/BY21-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK20" s="4">
-        <f>IF(COUNT(BY20:BY21)=2,ROUND((BY20/BY21-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL20" s="4">
-        <f>IF(COUNT(BY20:BY25)=6,ROUND((BY20/BY25-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD20:CD21)=2,ROUND((CD20/CD21-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK20" s="5">
+        <f>IF(COUNT(CD20:CD21)=2,(CD20-CD21)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL20" s="3" t="n"/>
       <c r="CM20" s="4">
-        <f>IF(COUNT(CK20:CK39)=20,IFERROR(ROUND(STDEV(CK20:CK39),4),""),"")</f>
+        <f>IFERROR(X20-P20,"")</f>
         <v/>
       </c>
       <c r="CN20" s="4">
-        <f>IF(COUNT(CF20:CF21)=2,ROUND((CF20/CF21-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO20" s="5">
-        <f>IF(COUNT(CF20:CF21)=2,(CF20-CF21)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP20" s="3" t="n"/>
+        <f>IFERROR(AF20-P20,"")</f>
+        <v/>
+      </c>
+      <c r="CO20" s="6">
+        <f>IF(COUNT(H20:H39)=20,IFERROR(CORREL(H20:H39,P20:P39),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP20" s="4">
+        <f>IFERROR(AN20-AV20,"")</f>
+        <v/>
+      </c>
       <c r="CQ20" s="4">
-        <f>IFERROR(X20-P20,"")</f>
-        <v/>
-      </c>
-      <c r="CR20" s="4">
-        <f>IFERROR(AF20-P20,"")</f>
-        <v/>
-      </c>
-      <c r="CS20" s="6">
-        <f>IF(COUNT(H20:H39)=20,IFERROR(CORREL(H20:H39,P20:P39),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT20" s="4">
-        <f>IFERROR(AN20-AV20,"")</f>
-        <v/>
-      </c>
-      <c r="CU20" s="4">
         <f>IFERROR(BD20-BL20,"")</f>
         <v/>
       </c>
-      <c r="CV20" s="6">
-        <f>BY20/CF20</f>
-        <v/>
-      </c>
-      <c r="CW20" s="4">
+      <c r="CR20" s="6">
+        <f>BY20/CD20</f>
+        <v/>
+      </c>
+      <c r="CS20" s="4">
         <f>IFERROR(P20-BT20,"")</f>
         <v/>
       </c>
@@ -3036,82 +2948,70 @@
       <c r="BY21" s="3" t="n">
         <v>15.99</v>
       </c>
-      <c r="BZ21" s="3" t="n">
-        <v>15.99</v>
-      </c>
+      <c r="BZ21" s="3" t="n"/>
       <c r="CA21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB21" s="3" t="n"/>
+        <v>4.684</v>
+      </c>
+      <c r="CB21" s="3" t="n">
+        <v>4.747</v>
+      </c>
       <c r="CC21" s="3" t="n">
-        <v>4.684</v>
+        <v>4.682</v>
       </c>
       <c r="CD21" s="3" t="n">
-        <v>4.747</v>
-      </c>
-      <c r="CE21" s="3" t="n">
-        <v>4.682</v>
-      </c>
-      <c r="CF21" s="3" t="n">
         <v>4.745</v>
       </c>
-      <c r="CG21" s="3" t="n">
-        <v>4.745</v>
-      </c>
-      <c r="CH21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI21" s="3" t="n"/>
+      <c r="CE21" s="3" t="n"/>
+      <c r="CF21" s="4">
+        <f>IF(COUNT(BY21:BY22)=2,ROUND((BY21/BY22-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG21" s="4">
+        <f>IF(COUNT(BY21:BY22)=2,ROUND((BY21/BY22-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH21" s="4">
+        <f>IF(COUNT(BY21:BY26)=6,ROUND((BY21/BY26-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI21" s="4">
+        <f>IF(COUNT(CG21:CG40)=20,IFERROR(ROUND(STDEV(CG21:CG40),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ21" s="4">
-        <f>IF(COUNT(BY21:BY22)=2,ROUND((BY21/BY22-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK21" s="4">
-        <f>IF(COUNT(BY21:BY22)=2,ROUND((BY21/BY22-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL21" s="4">
-        <f>IF(COUNT(BY21:BY26)=6,ROUND((BY21/BY26-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD21:CD22)=2,ROUND((CD21/CD22-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK21" s="5">
+        <f>IF(COUNT(CD21:CD22)=2,(CD21-CD22)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL21" s="3" t="n"/>
       <c r="CM21" s="4">
-        <f>IF(COUNT(CK21:CK40)=20,IFERROR(ROUND(STDEV(CK21:CK40),4),""),"")</f>
+        <f>IFERROR(X21-P21,"")</f>
         <v/>
       </c>
       <c r="CN21" s="4">
-        <f>IF(COUNT(CF21:CF22)=2,ROUND((CF21/CF22-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO21" s="5">
-        <f>IF(COUNT(CF21:CF22)=2,(CF21-CF22)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP21" s="3" t="n"/>
+        <f>IFERROR(AF21-P21,"")</f>
+        <v/>
+      </c>
+      <c r="CO21" s="6">
+        <f>IF(COUNT(H21:H40)=20,IFERROR(CORREL(H21:H40,P21:P40),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP21" s="4">
+        <f>IFERROR(AN21-AV21,"")</f>
+        <v/>
+      </c>
       <c r="CQ21" s="4">
-        <f>IFERROR(X21-P21,"")</f>
-        <v/>
-      </c>
-      <c r="CR21" s="4">
-        <f>IFERROR(AF21-P21,"")</f>
-        <v/>
-      </c>
-      <c r="CS21" s="6">
-        <f>IF(COUNT(H21:H40)=20,IFERROR(CORREL(H21:H40,P21:P40),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT21" s="4">
-        <f>IFERROR(AN21-AV21,"")</f>
-        <v/>
-      </c>
-      <c r="CU21" s="4">
         <f>IFERROR(BD21-BL21,"")</f>
         <v/>
       </c>
-      <c r="CV21" s="6">
-        <f>BY21/CF21</f>
-        <v/>
-      </c>
-      <c r="CW21" s="4">
+      <c r="CR21" s="6">
+        <f>BY21/CD21</f>
+        <v/>
+      </c>
+      <c r="CS21" s="4">
         <f>IFERROR(P21-BT21,"")</f>
         <v/>
       </c>
@@ -3341,82 +3241,70 @@
       <c r="BY22" s="3" t="n">
         <v>17.09</v>
       </c>
-      <c r="BZ22" s="3" t="n">
-        <v>17.09</v>
-      </c>
+      <c r="BZ22" s="3" t="n"/>
       <c r="CA22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB22" s="3" t="n"/>
+        <v>4.669</v>
+      </c>
+      <c r="CB22" s="3" t="n">
+        <v>4.686</v>
+      </c>
       <c r="CC22" s="3" t="n">
-        <v>4.669</v>
+        <v>4.651</v>
       </c>
       <c r="CD22" s="3" t="n">
-        <v>4.686</v>
-      </c>
-      <c r="CE22" s="3" t="n">
-        <v>4.651</v>
-      </c>
-      <c r="CF22" s="3" t="n">
         <v>4.663</v>
       </c>
-      <c r="CG22" s="3" t="n">
-        <v>4.663</v>
-      </c>
-      <c r="CH22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI22" s="3" t="n"/>
+      <c r="CE22" s="3" t="n"/>
+      <c r="CF22" s="4">
+        <f>IF(COUNT(BY22:BY23)=2,ROUND((BY22/BY23-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG22" s="4">
+        <f>IF(COUNT(BY22:BY23)=2,ROUND((BY22/BY23-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH22" s="4">
+        <f>IF(COUNT(BY22:BY27)=6,ROUND((BY22/BY27-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI22" s="4">
+        <f>IF(COUNT(CG22:CG41)=20,IFERROR(ROUND(STDEV(CG22:CG41),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ22" s="4">
-        <f>IF(COUNT(BY22:BY23)=2,ROUND((BY22/BY23-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK22" s="4">
-        <f>IF(COUNT(BY22:BY23)=2,ROUND((BY22/BY23-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL22" s="4">
-        <f>IF(COUNT(BY22:BY27)=6,ROUND((BY22/BY27-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD22:CD23)=2,ROUND((CD22/CD23-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK22" s="5">
+        <f>IF(COUNT(CD22:CD23)=2,(CD22-CD23)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL22" s="3" t="n"/>
       <c r="CM22" s="4">
-        <f>IF(COUNT(CK22:CK41)=20,IFERROR(ROUND(STDEV(CK22:CK41),4),""),"")</f>
+        <f>IFERROR(X22-P22,"")</f>
         <v/>
       </c>
       <c r="CN22" s="4">
-        <f>IF(COUNT(CF22:CF23)=2,ROUND((CF22/CF23-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO22" s="5">
-        <f>IF(COUNT(CF22:CF23)=2,(CF22-CF23)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP22" s="3" t="n"/>
+        <f>IFERROR(AF22-P22,"")</f>
+        <v/>
+      </c>
+      <c r="CO22" s="6">
+        <f>IF(COUNT(H22:H41)=20,IFERROR(CORREL(H22:H41,P22:P41),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP22" s="4">
+        <f>IFERROR(AN22-AV22,"")</f>
+        <v/>
+      </c>
       <c r="CQ22" s="4">
-        <f>IFERROR(X22-P22,"")</f>
-        <v/>
-      </c>
-      <c r="CR22" s="4">
-        <f>IFERROR(AF22-P22,"")</f>
-        <v/>
-      </c>
-      <c r="CS22" s="6">
-        <f>IF(COUNT(H22:H41)=20,IFERROR(CORREL(H22:H41,P22:P41),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT22" s="4">
-        <f>IFERROR(AN22-AV22,"")</f>
-        <v/>
-      </c>
-      <c r="CU22" s="4">
         <f>IFERROR(BD22-BL22,"")</f>
         <v/>
       </c>
-      <c r="CV22" s="6">
-        <f>BY22/CF22</f>
-        <v/>
-      </c>
-      <c r="CW22" s="4">
+      <c r="CR22" s="6">
+        <f>BY22/CD22</f>
+        <v/>
+      </c>
+      <c r="CS22" s="4">
         <f>IFERROR(P22-BT22,"")</f>
         <v/>
       </c>
@@ -3646,82 +3534,70 @@
       <c r="BY23" s="3" t="n">
         <v>20.66</v>
       </c>
-      <c r="BZ23" s="3" t="n">
-        <v>20.66</v>
-      </c>
+      <c r="BZ23" s="3" t="n"/>
       <c r="CA23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB23" s="3" t="n"/>
+        <v>4.637</v>
+      </c>
+      <c r="CB23" s="3" t="n">
+        <v>4.655</v>
+      </c>
       <c r="CC23" s="3" t="n">
-        <v>4.637</v>
+        <v>4.61</v>
       </c>
       <c r="CD23" s="3" t="n">
-        <v>4.655</v>
-      </c>
-      <c r="CE23" s="3" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="CF23" s="3" t="n">
         <v>4.622</v>
       </c>
-      <c r="CG23" s="3" t="n">
-        <v>4.622</v>
-      </c>
-      <c r="CH23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI23" s="3" t="n"/>
+      <c r="CE23" s="3" t="n"/>
+      <c r="CF23" s="4">
+        <f>IF(COUNT(BY23:BY24)=2,ROUND((BY23/BY24-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG23" s="4">
+        <f>IF(COUNT(BY23:BY24)=2,ROUND((BY23/BY24-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH23" s="4">
+        <f>IF(COUNT(BY23:BY28)=6,ROUND((BY23/BY28-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI23" s="4">
+        <f>IF(COUNT(CG23:CG42)=20,IFERROR(ROUND(STDEV(CG23:CG42),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ23" s="4">
-        <f>IF(COUNT(BY23:BY24)=2,ROUND((BY23/BY24-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK23" s="4">
-        <f>IF(COUNT(BY23:BY24)=2,ROUND((BY23/BY24-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL23" s="4">
-        <f>IF(COUNT(BY23:BY28)=6,ROUND((BY23/BY28-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD23:CD24)=2,ROUND((CD23/CD24-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK23" s="5">
+        <f>IF(COUNT(CD23:CD24)=2,(CD23-CD24)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL23" s="3" t="n"/>
       <c r="CM23" s="4">
-        <f>IF(COUNT(CK23:CK42)=20,IFERROR(ROUND(STDEV(CK23:CK42),4),""),"")</f>
+        <f>IFERROR(X23-P23,"")</f>
         <v/>
       </c>
       <c r="CN23" s="4">
-        <f>IF(COUNT(CF23:CF24)=2,ROUND((CF23/CF24-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO23" s="5">
-        <f>IF(COUNT(CF23:CF24)=2,(CF23-CF24)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP23" s="3" t="n"/>
+        <f>IFERROR(AF23-P23,"")</f>
+        <v/>
+      </c>
+      <c r="CO23" s="6">
+        <f>IF(COUNT(H23:H42)=20,IFERROR(CORREL(H23:H42,P23:P42),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP23" s="4">
+        <f>IFERROR(AN23-AV23,"")</f>
+        <v/>
+      </c>
       <c r="CQ23" s="4">
-        <f>IFERROR(X23-P23,"")</f>
-        <v/>
-      </c>
-      <c r="CR23" s="4">
-        <f>IFERROR(AF23-P23,"")</f>
-        <v/>
-      </c>
-      <c r="CS23" s="6">
-        <f>IF(COUNT(H23:H42)=20,IFERROR(CORREL(H23:H42,P23:P42),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT23" s="4">
-        <f>IFERROR(AN23-AV23,"")</f>
-        <v/>
-      </c>
-      <c r="CU23" s="4">
         <f>IFERROR(BD23-BL23,"")</f>
         <v/>
       </c>
-      <c r="CV23" s="6">
-        <f>BY23/CF23</f>
-        <v/>
-      </c>
-      <c r="CW23" s="4">
+      <c r="CR23" s="6">
+        <f>BY23/CD23</f>
+        <v/>
+      </c>
+      <c r="CS23" s="4">
         <f>IFERROR(P23-BT23,"")</f>
         <v/>
       </c>
@@ -3951,82 +3827,70 @@
       <c r="BY24" s="3" t="n">
         <v>18.21</v>
       </c>
-      <c r="BZ24" s="3" t="n">
-        <v>18.21</v>
-      </c>
+      <c r="BZ24" s="3" t="n"/>
       <c r="CA24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB24" s="3" t="n"/>
+        <v>4.63</v>
+      </c>
+      <c r="CB24" s="3" t="n">
+        <v>4.635</v>
+      </c>
       <c r="CC24" s="3" t="n">
-        <v>4.63</v>
+        <v>4.588</v>
       </c>
       <c r="CD24" s="3" t="n">
-        <v>4.635</v>
-      </c>
-      <c r="CE24" s="3" t="n">
-        <v>4.588</v>
-      </c>
-      <c r="CF24" s="3" t="n">
         <v>4.604</v>
       </c>
-      <c r="CG24" s="3" t="n">
-        <v>4.604</v>
-      </c>
-      <c r="CH24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI24" s="3" t="n"/>
+      <c r="CE24" s="3" t="n"/>
+      <c r="CF24" s="4">
+        <f>IF(COUNT(BY24:BY25)=2,ROUND((BY24/BY25-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG24" s="4">
+        <f>IF(COUNT(BY24:BY25)=2,ROUND((BY24/BY25-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH24" s="4">
+        <f>IF(COUNT(BY24:BY29)=6,ROUND((BY24/BY29-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI24" s="4">
+        <f>IF(COUNT(CG24:CG43)=20,IFERROR(ROUND(STDEV(CG24:CG43),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ24" s="4">
-        <f>IF(COUNT(BY24:BY25)=2,ROUND((BY24/BY25-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK24" s="4">
-        <f>IF(COUNT(BY24:BY25)=2,ROUND((BY24/BY25-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL24" s="4">
-        <f>IF(COUNT(BY24:BY29)=6,ROUND((BY24/BY29-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD24:CD25)=2,ROUND((CD24/CD25-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK24" s="5">
+        <f>IF(COUNT(CD24:CD25)=2,(CD24-CD25)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL24" s="3" t="n"/>
       <c r="CM24" s="4">
-        <f>IF(COUNT(CK24:CK43)=20,IFERROR(ROUND(STDEV(CK24:CK43),4),""),"")</f>
+        <f>IFERROR(X24-P24,"")</f>
         <v/>
       </c>
       <c r="CN24" s="4">
-        <f>IF(COUNT(CF24:CF25)=2,ROUND((CF24/CF25-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO24" s="5">
-        <f>IF(COUNT(CF24:CF25)=2,(CF24-CF25)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP24" s="3" t="n"/>
+        <f>IFERROR(AF24-P24,"")</f>
+        <v/>
+      </c>
+      <c r="CO24" s="6">
+        <f>IF(COUNT(H24:H43)=20,IFERROR(CORREL(H24:H43,P24:P43),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP24" s="4">
+        <f>IFERROR(AN24-AV24,"")</f>
+        <v/>
+      </c>
       <c r="CQ24" s="4">
-        <f>IFERROR(X24-P24,"")</f>
-        <v/>
-      </c>
-      <c r="CR24" s="4">
-        <f>IFERROR(AF24-P24,"")</f>
-        <v/>
-      </c>
-      <c r="CS24" s="6">
-        <f>IF(COUNT(H24:H43)=20,IFERROR(CORREL(H24:H43,P24:P43),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT24" s="4">
-        <f>IFERROR(AN24-AV24,"")</f>
-        <v/>
-      </c>
-      <c r="CU24" s="4">
         <f>IFERROR(BD24-BL24,"")</f>
         <v/>
       </c>
-      <c r="CV24" s="6">
-        <f>BY24/CF24</f>
-        <v/>
-      </c>
-      <c r="CW24" s="4">
+      <c r="CR24" s="6">
+        <f>BY24/CD24</f>
+        <v/>
+      </c>
+      <c r="CS24" s="4">
         <f>IFERROR(P24-BT24,"")</f>
         <v/>
       </c>
@@ -4256,82 +4120,70 @@
       <c r="BY25" s="3" t="n">
         <v>18.67</v>
       </c>
-      <c r="BZ25" s="3" t="n">
-        <v>18.67</v>
-      </c>
+      <c r="BZ25" s="3" t="n"/>
       <c r="CA25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB25" s="3" t="n"/>
+        <v>4.647</v>
+      </c>
+      <c r="CB25" s="3" t="n">
+        <v>4.665</v>
+      </c>
       <c r="CC25" s="3" t="n">
-        <v>4.647</v>
+        <v>4.63</v>
       </c>
       <c r="CD25" s="3" t="n">
-        <v>4.665</v>
-      </c>
-      <c r="CE25" s="3" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="CF25" s="3" t="n">
         <v>4.641</v>
       </c>
-      <c r="CG25" s="3" t="n">
-        <v>4.641</v>
-      </c>
-      <c r="CH25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI25" s="3" t="n"/>
+      <c r="CE25" s="3" t="n"/>
+      <c r="CF25" s="4">
+        <f>IF(COUNT(BY25:BY26)=2,ROUND((BY25/BY26-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG25" s="4">
+        <f>IF(COUNT(BY25:BY26)=2,ROUND((BY25/BY26-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH25" s="4">
+        <f>IF(COUNT(BY25:BY30)=6,ROUND((BY25/BY30-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI25" s="4">
+        <f>IF(COUNT(CG25:CG44)=20,IFERROR(ROUND(STDEV(CG25:CG44),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ25" s="4">
-        <f>IF(COUNT(BY25:BY26)=2,ROUND((BY25/BY26-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK25" s="4">
-        <f>IF(COUNT(BY25:BY26)=2,ROUND((BY25/BY26-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL25" s="4">
-        <f>IF(COUNT(BY25:BY30)=6,ROUND((BY25/BY30-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD25:CD26)=2,ROUND((CD25/CD26-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK25" s="5">
+        <f>IF(COUNT(CD25:CD26)=2,(CD25-CD26)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL25" s="3" t="n"/>
       <c r="CM25" s="4">
-        <f>IF(COUNT(CK25:CK44)=20,IFERROR(ROUND(STDEV(CK25:CK44),4),""),"")</f>
+        <f>IFERROR(X25-P25,"")</f>
         <v/>
       </c>
       <c r="CN25" s="4">
-        <f>IF(COUNT(CF25:CF26)=2,ROUND((CF25/CF26-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO25" s="5">
-        <f>IF(COUNT(CF25:CF26)=2,(CF25-CF26)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP25" s="3" t="n"/>
+        <f>IFERROR(AF25-P25,"")</f>
+        <v/>
+      </c>
+      <c r="CO25" s="6">
+        <f>IF(COUNT(H25:H44)=20,IFERROR(CORREL(H25:H44,P25:P44),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP25" s="4">
+        <f>IFERROR(AN25-AV25,"")</f>
+        <v/>
+      </c>
       <c r="CQ25" s="4">
-        <f>IFERROR(X25-P25,"")</f>
-        <v/>
-      </c>
-      <c r="CR25" s="4">
-        <f>IFERROR(AF25-P25,"")</f>
-        <v/>
-      </c>
-      <c r="CS25" s="6">
-        <f>IF(COUNT(H25:H44)=20,IFERROR(CORREL(H25:H44,P25:P44),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT25" s="4">
-        <f>IFERROR(AN25-AV25,"")</f>
-        <v/>
-      </c>
-      <c r="CU25" s="4">
         <f>IFERROR(BD25-BL25,"")</f>
         <v/>
       </c>
-      <c r="CV25" s="6">
-        <f>BY25/CF25</f>
-        <v/>
-      </c>
-      <c r="CW25" s="4">
+      <c r="CR25" s="6">
+        <f>BY25/CD25</f>
+        <v/>
+      </c>
+      <c r="CS25" s="4">
         <f>IFERROR(P25-BT25,"")</f>
         <v/>
       </c>
@@ -4561,82 +4413,70 @@
       <c r="BY26" s="3" t="n">
         <v>18.58</v>
       </c>
-      <c r="BZ26" s="3" t="n">
-        <v>18.58</v>
-      </c>
+      <c r="BZ26" s="3" t="n"/>
       <c r="CA26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB26" s="3" t="n"/>
+        <v>4.683</v>
+      </c>
+      <c r="CB26" s="3" t="n">
+        <v>4.691</v>
+      </c>
       <c r="CC26" s="3" t="n">
-        <v>4.683</v>
+        <v>4.651</v>
       </c>
       <c r="CD26" s="3" t="n">
-        <v>4.691</v>
-      </c>
-      <c r="CE26" s="3" t="n">
-        <v>4.651</v>
-      </c>
-      <c r="CF26" s="3" t="n">
         <v>4.679</v>
       </c>
-      <c r="CG26" s="3" t="n">
-        <v>4.679</v>
-      </c>
-      <c r="CH26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI26" s="3" t="n"/>
+      <c r="CE26" s="3" t="n"/>
+      <c r="CF26" s="4">
+        <f>IF(COUNT(BY26:BY27)=2,ROUND((BY26/BY27-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG26" s="4">
+        <f>IF(COUNT(BY26:BY27)=2,ROUND((BY26/BY27-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH26" s="4">
+        <f>IF(COUNT(BY26:BY31)=6,ROUND((BY26/BY31-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI26" s="4">
+        <f>IF(COUNT(CG26:CG45)=20,IFERROR(ROUND(STDEV(CG26:CG45),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ26" s="4">
-        <f>IF(COUNT(BY26:BY27)=2,ROUND((BY26/BY27-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK26" s="4">
-        <f>IF(COUNT(BY26:BY27)=2,ROUND((BY26/BY27-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL26" s="4">
-        <f>IF(COUNT(BY26:BY31)=6,ROUND((BY26/BY31-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD26:CD27)=2,ROUND((CD26/CD27-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK26" s="5">
+        <f>IF(COUNT(CD26:CD27)=2,(CD26-CD27)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL26" s="3" t="n"/>
       <c r="CM26" s="4">
-        <f>IF(COUNT(CK26:CK45)=20,IFERROR(ROUND(STDEV(CK26:CK45),4),""),"")</f>
+        <f>IFERROR(X26-P26,"")</f>
         <v/>
       </c>
       <c r="CN26" s="4">
-        <f>IF(COUNT(CF26:CF27)=2,ROUND((CF26/CF27-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO26" s="5">
-        <f>IF(COUNT(CF26:CF27)=2,(CF26-CF27)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP26" s="3" t="n"/>
+        <f>IFERROR(AF26-P26,"")</f>
+        <v/>
+      </c>
+      <c r="CO26" s="6">
+        <f>IF(COUNT(H26:H45)=20,IFERROR(CORREL(H26:H45,P26:P45),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP26" s="4">
+        <f>IFERROR(AN26-AV26,"")</f>
+        <v/>
+      </c>
       <c r="CQ26" s="4">
-        <f>IFERROR(X26-P26,"")</f>
-        <v/>
-      </c>
-      <c r="CR26" s="4">
-        <f>IFERROR(AF26-P26,"")</f>
-        <v/>
-      </c>
-      <c r="CS26" s="6">
-        <f>IF(COUNT(H26:H45)=20,IFERROR(CORREL(H26:H45,P26:P45),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT26" s="4">
-        <f>IFERROR(AN26-AV26,"")</f>
-        <v/>
-      </c>
-      <c r="CU26" s="4">
         <f>IFERROR(BD26-BL26,"")</f>
         <v/>
       </c>
-      <c r="CV26" s="6">
-        <f>BY26/CF26</f>
-        <v/>
-      </c>
-      <c r="CW26" s="4">
+      <c r="CR26" s="6">
+        <f>BY26/CD26</f>
+        <v/>
+      </c>
+      <c r="CS26" s="4">
         <f>IFERROR(P26-BT26,"")</f>
         <v/>
       </c>
@@ -4866,82 +4706,70 @@
       <c r="BY27" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="BZ27" s="3" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="BZ27" s="3" t="n"/>
       <c r="CA27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB27" s="3" t="n"/>
+        <v>4.699</v>
+      </c>
+      <c r="CB27" s="3" t="n">
+        <v>4.714</v>
+      </c>
       <c r="CC27" s="3" t="n">
-        <v>4.699</v>
+        <v>4.693</v>
       </c>
       <c r="CD27" s="3" t="n">
-        <v>4.714</v>
-      </c>
-      <c r="CE27" s="3" t="n">
-        <v>4.693</v>
-      </c>
-      <c r="CF27" s="3" t="n">
         <v>4.703</v>
       </c>
-      <c r="CG27" s="3" t="n">
-        <v>4.703</v>
-      </c>
-      <c r="CH27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI27" s="3" t="n"/>
+      <c r="CE27" s="3" t="n"/>
+      <c r="CF27" s="4">
+        <f>IF(COUNT(BY27:BY28)=2,ROUND((BY27/BY28-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG27" s="4">
+        <f>IF(COUNT(BY27:BY28)=2,ROUND((BY27/BY28-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH27" s="4">
+        <f>IF(COUNT(BY27:BY32)=6,ROUND((BY27/BY32-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI27" s="4">
+        <f>IF(COUNT(CG27:CG46)=20,IFERROR(ROUND(STDEV(CG27:CG46),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ27" s="4">
-        <f>IF(COUNT(BY27:BY28)=2,ROUND((BY27/BY28-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK27" s="4">
-        <f>IF(COUNT(BY27:BY28)=2,ROUND((BY27/BY28-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL27" s="4">
-        <f>IF(COUNT(BY27:BY32)=6,ROUND((BY27/BY32-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD27:CD28)=2,ROUND((CD27/CD28-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK27" s="5">
+        <f>IF(COUNT(CD27:CD28)=2,(CD27-CD28)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL27" s="3" t="n"/>
       <c r="CM27" s="4">
-        <f>IF(COUNT(CK27:CK46)=20,IFERROR(ROUND(STDEV(CK27:CK46),4),""),"")</f>
+        <f>IFERROR(X27-P27,"")</f>
         <v/>
       </c>
       <c r="CN27" s="4">
-        <f>IF(COUNT(CF27:CF28)=2,ROUND((CF27/CF28-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO27" s="5">
-        <f>IF(COUNT(CF27:CF28)=2,(CF27-CF28)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP27" s="3" t="n"/>
+        <f>IFERROR(AF27-P27,"")</f>
+        <v/>
+      </c>
+      <c r="CO27" s="6">
+        <f>IF(COUNT(H27:H46)=20,IFERROR(CORREL(H27:H46,P27:P46),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP27" s="4">
+        <f>IFERROR(AN27-AV27,"")</f>
+        <v/>
+      </c>
       <c r="CQ27" s="4">
-        <f>IFERROR(X27-P27,"")</f>
-        <v/>
-      </c>
-      <c r="CR27" s="4">
-        <f>IFERROR(AF27-P27,"")</f>
-        <v/>
-      </c>
-      <c r="CS27" s="6">
-        <f>IF(COUNT(H27:H46)=20,IFERROR(CORREL(H27:H46,P27:P46),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT27" s="4">
-        <f>IFERROR(AN27-AV27,"")</f>
-        <v/>
-      </c>
-      <c r="CU27" s="4">
         <f>IFERROR(BD27-BL27,"")</f>
         <v/>
       </c>
-      <c r="CV27" s="6">
-        <f>BY27/CF27</f>
-        <v/>
-      </c>
-      <c r="CW27" s="4">
+      <c r="CR27" s="6">
+        <f>BY27/CD27</f>
+        <v/>
+      </c>
+      <c r="CS27" s="4">
         <f>IFERROR(P27-BT27,"")</f>
         <v/>
       </c>
@@ -5171,82 +4999,70 @@
       <c r="BY28" s="3" t="n">
         <v>16.64</v>
       </c>
-      <c r="BZ28" s="3" t="n">
-        <v>16.64</v>
-      </c>
+      <c r="BZ28" s="3" t="n"/>
       <c r="CA28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB28" s="3" t="n"/>
+        <v>4.64</v>
+      </c>
+      <c r="CB28" s="3" t="n">
+        <v>4.661</v>
+      </c>
       <c r="CC28" s="3" t="n">
-        <v>4.64</v>
+        <v>4.632</v>
       </c>
       <c r="CD28" s="3" t="n">
-        <v>4.661</v>
-      </c>
-      <c r="CE28" s="3" t="n">
-        <v>4.632</v>
-      </c>
-      <c r="CF28" s="3" t="n">
         <v>4.657</v>
       </c>
-      <c r="CG28" s="3" t="n">
-        <v>4.657</v>
-      </c>
-      <c r="CH28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI28" s="3" t="n"/>
+      <c r="CE28" s="3" t="n"/>
+      <c r="CF28" s="4">
+        <f>IF(COUNT(BY28:BY29)=2,ROUND((BY28/BY29-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG28" s="4">
+        <f>IF(COUNT(BY28:BY29)=2,ROUND((BY28/BY29-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH28" s="4">
+        <f>IF(COUNT(BY28:BY33)=6,ROUND((BY28/BY33-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI28" s="4">
+        <f>IF(COUNT(CG28:CG47)=20,IFERROR(ROUND(STDEV(CG28:CG47),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ28" s="4">
-        <f>IF(COUNT(BY28:BY29)=2,ROUND((BY28/BY29-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK28" s="4">
-        <f>IF(COUNT(BY28:BY29)=2,ROUND((BY28/BY29-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL28" s="4">
-        <f>IF(COUNT(BY28:BY33)=6,ROUND((BY28/BY33-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD28:CD29)=2,ROUND((CD28/CD29-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK28" s="5">
+        <f>IF(COUNT(CD28:CD29)=2,(CD28-CD29)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL28" s="3" t="n"/>
       <c r="CM28" s="4">
-        <f>IF(COUNT(CK28:CK47)=20,IFERROR(ROUND(STDEV(CK28:CK47),4),""),"")</f>
+        <f>IFERROR(X28-P28,"")</f>
         <v/>
       </c>
       <c r="CN28" s="4">
-        <f>IF(COUNT(CF28:CF29)=2,ROUND((CF28/CF29-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO28" s="5">
-        <f>IF(COUNT(CF28:CF29)=2,(CF28-CF29)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP28" s="3" t="n"/>
+        <f>IFERROR(AF28-P28,"")</f>
+        <v/>
+      </c>
+      <c r="CO28" s="6">
+        <f>IF(COUNT(H28:H47)=20,IFERROR(CORREL(H28:H47,P28:P47),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP28" s="4">
+        <f>IFERROR(AN28-AV28,"")</f>
+        <v/>
+      </c>
       <c r="CQ28" s="4">
-        <f>IFERROR(X28-P28,"")</f>
-        <v/>
-      </c>
-      <c r="CR28" s="4">
-        <f>IFERROR(AF28-P28,"")</f>
-        <v/>
-      </c>
-      <c r="CS28" s="6">
-        <f>IF(COUNT(H28:H47)=20,IFERROR(CORREL(H28:H47,P28:P47),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT28" s="4">
-        <f>IFERROR(AN28-AV28,"")</f>
-        <v/>
-      </c>
-      <c r="CU28" s="4">
         <f>IFERROR(BD28-BL28,"")</f>
         <v/>
       </c>
-      <c r="CV28" s="6">
-        <f>BY28/CF28</f>
-        <v/>
-      </c>
-      <c r="CW28" s="4">
+      <c r="CR28" s="6">
+        <f>BY28/CD28</f>
+        <v/>
+      </c>
+      <c r="CS28" s="4">
         <f>IFERROR(P28-BT28,"")</f>
         <v/>
       </c>
@@ -5476,82 +5292,70 @@
       <c r="BY29" s="3" t="n">
         <v>17.05</v>
       </c>
-      <c r="BZ29" s="3" t="n">
-        <v>17.05</v>
-      </c>
+      <c r="BZ29" s="3" t="n"/>
       <c r="CA29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB29" s="3" t="n"/>
+        <v>4.6</v>
+      </c>
+      <c r="CB29" s="3" t="n">
+        <v>4.64</v>
+      </c>
       <c r="CC29" s="3" t="n">
-        <v>4.6</v>
+        <v>4.598</v>
       </c>
       <c r="CD29" s="3" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="CE29" s="3" t="n">
-        <v>4.598</v>
-      </c>
-      <c r="CF29" s="3" t="n">
         <v>4.628</v>
       </c>
-      <c r="CG29" s="3" t="n">
-        <v>4.628</v>
-      </c>
-      <c r="CH29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI29" s="3" t="n"/>
+      <c r="CE29" s="3" t="n"/>
+      <c r="CF29" s="4">
+        <f>IF(COUNT(BY29:BY30)=2,ROUND((BY29/BY30-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG29" s="4">
+        <f>IF(COUNT(BY29:BY30)=2,ROUND((BY29/BY30-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH29" s="4">
+        <f>IF(COUNT(BY29:BY34)=6,ROUND((BY29/BY34-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI29" s="4">
+        <f>IF(COUNT(CG29:CG48)=20,IFERROR(ROUND(STDEV(CG29:CG48),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ29" s="4">
-        <f>IF(COUNT(BY29:BY30)=2,ROUND((BY29/BY30-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK29" s="4">
-        <f>IF(COUNT(BY29:BY30)=2,ROUND((BY29/BY30-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL29" s="4">
-        <f>IF(COUNT(BY29:BY34)=6,ROUND((BY29/BY34-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD29:CD30)=2,ROUND((CD29/CD30-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK29" s="5">
+        <f>IF(COUNT(CD29:CD30)=2,(CD29-CD30)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL29" s="3" t="n"/>
       <c r="CM29" s="4">
-        <f>IF(COUNT(CK29:CK48)=20,IFERROR(ROUND(STDEV(CK29:CK48),4),""),"")</f>
+        <f>IFERROR(X29-P29,"")</f>
         <v/>
       </c>
       <c r="CN29" s="4">
-        <f>IF(COUNT(CF29:CF30)=2,ROUND((CF29/CF30-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO29" s="5">
-        <f>IF(COUNT(CF29:CF30)=2,(CF29-CF30)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP29" s="3" t="n"/>
+        <f>IFERROR(AF29-P29,"")</f>
+        <v/>
+      </c>
+      <c r="CO29" s="6">
+        <f>IF(COUNT(H29:H48)=20,IFERROR(CORREL(H29:H48,P29:P48),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP29" s="4">
+        <f>IFERROR(AN29-AV29,"")</f>
+        <v/>
+      </c>
       <c r="CQ29" s="4">
-        <f>IFERROR(X29-P29,"")</f>
-        <v/>
-      </c>
-      <c r="CR29" s="4">
-        <f>IFERROR(AF29-P29,"")</f>
-        <v/>
-      </c>
-      <c r="CS29" s="6">
-        <f>IF(COUNT(H29:H48)=20,IFERROR(CORREL(H29:H48,P29:P48),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT29" s="4">
-        <f>IFERROR(AN29-AV29,"")</f>
-        <v/>
-      </c>
-      <c r="CU29" s="4">
         <f>IFERROR(BD29-BL29,"")</f>
         <v/>
       </c>
-      <c r="CV29" s="6">
-        <f>BY29/CF29</f>
-        <v/>
-      </c>
-      <c r="CW29" s="4">
+      <c r="CR29" s="6">
+        <f>BY29/CD29</f>
+        <v/>
+      </c>
+      <c r="CS29" s="4">
         <f>IFERROR(P29-BT29,"")</f>
         <v/>
       </c>
@@ -5781,82 +5585,70 @@
       <c r="BY30" s="3" t="n">
         <v>18.65</v>
       </c>
-      <c r="BZ30" s="3" t="n">
-        <v>18.65</v>
-      </c>
+      <c r="BZ30" s="3" t="n"/>
       <c r="CA30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB30" s="3" t="n"/>
+        <v>4.566</v>
+      </c>
+      <c r="CB30" s="3" t="n">
+        <v>4.608</v>
+      </c>
       <c r="CC30" s="3" t="n">
-        <v>4.566</v>
+        <v>4.56</v>
       </c>
       <c r="CD30" s="3" t="n">
-        <v>4.608</v>
-      </c>
-      <c r="CE30" s="3" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="CF30" s="3" t="n">
         <v>4.598</v>
       </c>
-      <c r="CG30" s="3" t="n">
-        <v>4.598</v>
-      </c>
-      <c r="CH30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI30" s="3" t="n"/>
+      <c r="CE30" s="3" t="n"/>
+      <c r="CF30" s="4">
+        <f>IF(COUNT(BY30:BY31)=2,ROUND((BY30/BY31-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG30" s="4">
+        <f>IF(COUNT(BY30:BY31)=2,ROUND((BY30/BY31-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH30" s="4">
+        <f>IF(COUNT(BY30:BY35)=6,ROUND((BY30/BY35-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI30" s="4">
+        <f>IF(COUNT(CG30:CG49)=20,IFERROR(ROUND(STDEV(CG30:CG49),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ30" s="4">
-        <f>IF(COUNT(BY30:BY31)=2,ROUND((BY30/BY31-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK30" s="4">
-        <f>IF(COUNT(BY30:BY31)=2,ROUND((BY30/BY31-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL30" s="4">
-        <f>IF(COUNT(BY30:BY35)=6,ROUND((BY30/BY35-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD30:CD31)=2,ROUND((CD30/CD31-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK30" s="5">
+        <f>IF(COUNT(CD30:CD31)=2,(CD30-CD31)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL30" s="3" t="n"/>
       <c r="CM30" s="4">
-        <f>IF(COUNT(CK30:CK49)=20,IFERROR(ROUND(STDEV(CK30:CK49),4),""),"")</f>
+        <f>IFERROR(X30-P30,"")</f>
         <v/>
       </c>
       <c r="CN30" s="4">
-        <f>IF(COUNT(CF30:CF31)=2,ROUND((CF30/CF31-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO30" s="5">
-        <f>IF(COUNT(CF30:CF31)=2,(CF30-CF31)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP30" s="3" t="n"/>
+        <f>IFERROR(AF30-P30,"")</f>
+        <v/>
+      </c>
+      <c r="CO30" s="6">
+        <f>IF(COUNT(H30:H49)=20,IFERROR(CORREL(H30:H49,P30:P49),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP30" s="4">
+        <f>IFERROR(AN30-AV30,"")</f>
+        <v/>
+      </c>
       <c r="CQ30" s="4">
-        <f>IFERROR(X30-P30,"")</f>
-        <v/>
-      </c>
-      <c r="CR30" s="4">
-        <f>IFERROR(AF30-P30,"")</f>
-        <v/>
-      </c>
-      <c r="CS30" s="6">
-        <f>IF(COUNT(H30:H49)=20,IFERROR(CORREL(H30:H49,P30:P49),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT30" s="4">
-        <f>IFERROR(AN30-AV30,"")</f>
-        <v/>
-      </c>
-      <c r="CU30" s="4">
         <f>IFERROR(BD30-BL30,"")</f>
         <v/>
       </c>
-      <c r="CV30" s="6">
-        <f>BY30/CF30</f>
-        <v/>
-      </c>
-      <c r="CW30" s="4">
+      <c r="CR30" s="6">
+        <f>BY30/CD30</f>
+        <v/>
+      </c>
+      <c r="CS30" s="4">
         <f>IFERROR(P30-BT30,"")</f>
         <v/>
       </c>
@@ -6086,82 +5878,70 @@
       <c r="BY31" s="3" t="n">
         <v>18.77</v>
       </c>
-      <c r="BZ31" s="3" t="n">
-        <v>18.77</v>
-      </c>
+      <c r="BZ31" s="3" t="n"/>
       <c r="CA31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB31" s="3" t="n"/>
+        <v>4.521</v>
+      </c>
+      <c r="CB31" s="3" t="n">
+        <v>4.55</v>
+      </c>
       <c r="CC31" s="3" t="n">
-        <v>4.521</v>
+        <v>4.511</v>
       </c>
       <c r="CD31" s="3" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="CE31" s="3" t="n">
-        <v>4.511</v>
-      </c>
-      <c r="CF31" s="3" t="n">
         <v>4.541</v>
       </c>
-      <c r="CG31" s="3" t="n">
-        <v>4.541</v>
-      </c>
-      <c r="CH31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI31" s="3" t="n"/>
+      <c r="CE31" s="3" t="n"/>
+      <c r="CF31" s="4">
+        <f>IF(COUNT(BY31:BY32)=2,ROUND((BY31/BY32-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG31" s="4">
+        <f>IF(COUNT(BY31:BY32)=2,ROUND((BY31/BY32-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH31" s="4">
+        <f>IF(COUNT(BY31:BY36)=6,ROUND((BY31/BY36-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI31" s="4">
+        <f>IF(COUNT(CG31:CG50)=20,IFERROR(ROUND(STDEV(CG31:CG50),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ31" s="4">
-        <f>IF(COUNT(BY31:BY32)=2,ROUND((BY31/BY32-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK31" s="4">
-        <f>IF(COUNT(BY31:BY32)=2,ROUND((BY31/BY32-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL31" s="4">
-        <f>IF(COUNT(BY31:BY36)=6,ROUND((BY31/BY36-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD31:CD32)=2,ROUND((CD31/CD32-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK31" s="5">
+        <f>IF(COUNT(CD31:CD32)=2,(CD31-CD32)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL31" s="3" t="n"/>
       <c r="CM31" s="4">
-        <f>IF(COUNT(CK31:CK50)=20,IFERROR(ROUND(STDEV(CK31:CK50),4),""),"")</f>
+        <f>IFERROR(X31-P31,"")</f>
         <v/>
       </c>
       <c r="CN31" s="4">
-        <f>IF(COUNT(CF31:CF32)=2,ROUND((CF31/CF32-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO31" s="5">
-        <f>IF(COUNT(CF31:CF32)=2,(CF31-CF32)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP31" s="3" t="n"/>
+        <f>IFERROR(AF31-P31,"")</f>
+        <v/>
+      </c>
+      <c r="CO31" s="6">
+        <f>IF(COUNT(H31:H50)=20,IFERROR(CORREL(H31:H50,P31:P50),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP31" s="4">
+        <f>IFERROR(AN31-AV31,"")</f>
+        <v/>
+      </c>
       <c r="CQ31" s="4">
-        <f>IFERROR(X31-P31,"")</f>
-        <v/>
-      </c>
-      <c r="CR31" s="4">
-        <f>IFERROR(AF31-P31,"")</f>
-        <v/>
-      </c>
-      <c r="CS31" s="6">
-        <f>IF(COUNT(H31:H50)=20,IFERROR(CORREL(H31:H50,P31:P50),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT31" s="4">
-        <f>IFERROR(AN31-AV31,"")</f>
-        <v/>
-      </c>
-      <c r="CU31" s="4">
         <f>IFERROR(BD31-BL31,"")</f>
         <v/>
       </c>
-      <c r="CV31" s="6">
-        <f>BY31/CF31</f>
-        <v/>
-      </c>
-      <c r="CW31" s="4">
+      <c r="CR31" s="6">
+        <f>BY31/CD31</f>
+        <v/>
+      </c>
+      <c r="CS31" s="4">
         <f>IFERROR(P31-BT31,"")</f>
         <v/>
       </c>
@@ -6391,82 +6171,70 @@
       <c r="BY32" s="3" t="n">
         <v>16.73</v>
       </c>
-      <c r="BZ32" s="3" t="n">
-        <v>16.73</v>
-      </c>
+      <c r="BZ32" s="3" t="n"/>
       <c r="CA32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB32" s="3" t="n"/>
+        <v>4.582</v>
+      </c>
+      <c r="CB32" s="3" t="n">
+        <v>4.596</v>
+      </c>
       <c r="CC32" s="3" t="n">
-        <v>4.582</v>
+        <v>4.561</v>
       </c>
       <c r="CD32" s="3" t="n">
-        <v>4.596</v>
-      </c>
-      <c r="CE32" s="3" t="n">
-        <v>4.561</v>
-      </c>
-      <c r="CF32" s="3" t="n">
         <v>4.569</v>
       </c>
-      <c r="CG32" s="3" t="n">
-        <v>4.569</v>
-      </c>
-      <c r="CH32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI32" s="3" t="n"/>
+      <c r="CE32" s="3" t="n"/>
+      <c r="CF32" s="4">
+        <f>IF(COUNT(BY32:BY33)=2,ROUND((BY32/BY33-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG32" s="4">
+        <f>IF(COUNT(BY32:BY33)=2,ROUND((BY32/BY33-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH32" s="4">
+        <f>IF(COUNT(BY32:BY37)=6,ROUND((BY32/BY37-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI32" s="4">
+        <f>IF(COUNT(CG32:CG51)=20,IFERROR(ROUND(STDEV(CG32:CG51),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ32" s="4">
-        <f>IF(COUNT(BY32:BY33)=2,ROUND((BY32/BY33-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK32" s="4">
-        <f>IF(COUNT(BY32:BY33)=2,ROUND((BY32/BY33-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL32" s="4">
-        <f>IF(COUNT(BY32:BY37)=6,ROUND((BY32/BY37-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD32:CD33)=2,ROUND((CD32/CD33-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK32" s="5">
+        <f>IF(COUNT(CD32:CD33)=2,(CD32-CD33)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL32" s="3" t="n"/>
       <c r="CM32" s="4">
-        <f>IF(COUNT(CK32:CK51)=20,IFERROR(ROUND(STDEV(CK32:CK51),4),""),"")</f>
+        <f>IFERROR(X32-P32,"")</f>
         <v/>
       </c>
       <c r="CN32" s="4">
-        <f>IF(COUNT(CF32:CF33)=2,ROUND((CF32/CF33-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO32" s="5">
-        <f>IF(COUNT(CF32:CF33)=2,(CF32-CF33)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP32" s="3" t="n"/>
+        <f>IFERROR(AF32-P32,"")</f>
+        <v/>
+      </c>
+      <c r="CO32" s="6">
+        <f>IF(COUNT(H32:H51)=20,IFERROR(CORREL(H32:H51,P32:P51),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP32" s="4">
+        <f>IFERROR(AN32-AV32,"")</f>
+        <v/>
+      </c>
       <c r="CQ32" s="4">
-        <f>IFERROR(X32-P32,"")</f>
-        <v/>
-      </c>
-      <c r="CR32" s="4">
-        <f>IFERROR(AF32-P32,"")</f>
-        <v/>
-      </c>
-      <c r="CS32" s="6">
-        <f>IF(COUNT(H32:H51)=20,IFERROR(CORREL(H32:H51,P32:P51),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT32" s="4">
-        <f>IFERROR(AN32-AV32,"")</f>
-        <v/>
-      </c>
-      <c r="CU32" s="4">
         <f>IFERROR(BD32-BL32,"")</f>
         <v/>
       </c>
-      <c r="CV32" s="6">
-        <f>BY32/CF32</f>
-        <v/>
-      </c>
-      <c r="CW32" s="4">
+      <c r="CR32" s="6">
+        <f>BY32/CD32</f>
+        <v/>
+      </c>
+      <c r="CS32" s="4">
         <f>IFERROR(P32-BT32,"")</f>
         <v/>
       </c>
@@ -6696,82 +6464,70 @@
       <c r="BY33" s="3" t="n">
         <v>15.67</v>
       </c>
-      <c r="BZ33" s="3" t="n">
-        <v>15.67</v>
-      </c>
+      <c r="BZ33" s="3" t="n"/>
       <c r="CA33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB33" s="3" t="n"/>
+        <v>4.608</v>
+      </c>
+      <c r="CB33" s="3" t="n">
+        <v>4.61</v>
+      </c>
       <c r="CC33" s="3" t="n">
-        <v>4.608</v>
+        <v>4.539</v>
       </c>
       <c r="CD33" s="3" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="CE33" s="3" t="n">
-        <v>4.539</v>
-      </c>
-      <c r="CF33" s="3" t="n">
         <v>4.545</v>
       </c>
-      <c r="CG33" s="3" t="n">
-        <v>4.545</v>
-      </c>
-      <c r="CH33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI33" s="3" t="n"/>
+      <c r="CE33" s="3" t="n"/>
+      <c r="CF33" s="4">
+        <f>IF(COUNT(BY33:BY34)=2,ROUND((BY33/BY34-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG33" s="4">
+        <f>IF(COUNT(BY33:BY34)=2,ROUND((BY33/BY34-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH33" s="4">
+        <f>IF(COUNT(BY33:BY38)=6,ROUND((BY33/BY38-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI33" s="4">
+        <f>IF(COUNT(CG33:CG52)=20,IFERROR(ROUND(STDEV(CG33:CG52),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ33" s="4">
-        <f>IF(COUNT(BY33:BY34)=2,ROUND((BY33/BY34-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK33" s="4">
-        <f>IF(COUNT(BY33:BY34)=2,ROUND((BY33/BY34-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL33" s="4">
-        <f>IF(COUNT(BY33:BY38)=6,ROUND((BY33/BY38-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD33:CD34)=2,ROUND((CD33/CD34-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK33" s="5">
+        <f>IF(COUNT(CD33:CD34)=2,(CD33-CD34)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL33" s="3" t="n"/>
       <c r="CM33" s="4">
-        <f>IF(COUNT(CK33:CK52)=20,IFERROR(ROUND(STDEV(CK33:CK52),4),""),"")</f>
+        <f>IFERROR(X33-P33,"")</f>
         <v/>
       </c>
       <c r="CN33" s="4">
-        <f>IF(COUNT(CF33:CF34)=2,ROUND((CF33/CF34-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO33" s="5">
-        <f>IF(COUNT(CF33:CF34)=2,(CF33-CF34)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP33" s="3" t="n"/>
+        <f>IFERROR(AF33-P33,"")</f>
+        <v/>
+      </c>
+      <c r="CO33" s="6">
+        <f>IF(COUNT(H33:H52)=20,IFERROR(CORREL(H33:H52,P33:P52),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP33" s="4">
+        <f>IFERROR(AN33-AV33,"")</f>
+        <v/>
+      </c>
       <c r="CQ33" s="4">
-        <f>IFERROR(X33-P33,"")</f>
-        <v/>
-      </c>
-      <c r="CR33" s="4">
-        <f>IFERROR(AF33-P33,"")</f>
-        <v/>
-      </c>
-      <c r="CS33" s="6">
-        <f>IF(COUNT(H33:H52)=20,IFERROR(CORREL(H33:H52,P33:P52),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT33" s="4">
-        <f>IFERROR(AN33-AV33,"")</f>
-        <v/>
-      </c>
-      <c r="CU33" s="4">
         <f>IFERROR(BD33-BL33,"")</f>
         <v/>
       </c>
-      <c r="CV33" s="6">
-        <f>BY33/CF33</f>
-        <v/>
-      </c>
-      <c r="CW33" s="4">
+      <c r="CR33" s="6">
+        <f>BY33/CD33</f>
+        <v/>
+      </c>
+      <c r="CS33" s="4">
         <f>IFERROR(P33-BT33,"")</f>
         <v/>
       </c>
@@ -7001,82 +6757,70 @@
       <c r="BY34" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="BZ34" s="3" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="BZ34" s="3" t="n"/>
       <c r="CA34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB34" s="3" t="n"/>
+        <v>4.614</v>
+      </c>
+      <c r="CB34" s="3" t="n">
+        <v>4.614</v>
+      </c>
       <c r="CC34" s="3" t="n">
-        <v>4.614</v>
+        <v>4.525</v>
       </c>
       <c r="CD34" s="3" t="n">
-        <v>4.614</v>
-      </c>
-      <c r="CE34" s="3" t="n">
-        <v>4.525</v>
-      </c>
-      <c r="CF34" s="3" t="n">
         <v>4.585</v>
       </c>
-      <c r="CG34" s="3" t="n">
-        <v>4.585</v>
-      </c>
-      <c r="CH34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI34" s="3" t="n"/>
+      <c r="CE34" s="3" t="n"/>
+      <c r="CF34" s="4">
+        <f>IF(COUNT(BY34:BY35)=2,ROUND((BY34/BY35-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG34" s="4">
+        <f>IF(COUNT(BY34:BY35)=2,ROUND((BY34/BY35-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH34" s="4">
+        <f>IF(COUNT(BY34:BY39)=6,ROUND((BY34/BY39-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI34" s="4">
+        <f>IF(COUNT(CG34:CG53)=20,IFERROR(ROUND(STDEV(CG34:CG53),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ34" s="4">
-        <f>IF(COUNT(BY34:BY35)=2,ROUND((BY34/BY35-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK34" s="4">
-        <f>IF(COUNT(BY34:BY35)=2,ROUND((BY34/BY35-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL34" s="4">
-        <f>IF(COUNT(BY34:BY39)=6,ROUND((BY34/BY39-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD34:CD35)=2,ROUND((CD34/CD35-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK34" s="5">
+        <f>IF(COUNT(CD34:CD35)=2,(CD34-CD35)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL34" s="3" t="n"/>
       <c r="CM34" s="4">
-        <f>IF(COUNT(CK34:CK53)=20,IFERROR(ROUND(STDEV(CK34:CK53),4),""),"")</f>
+        <f>IFERROR(X34-P34,"")</f>
         <v/>
       </c>
       <c r="CN34" s="4">
-        <f>IF(COUNT(CF34:CF35)=2,ROUND((CF34/CF35-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO34" s="5">
-        <f>IF(COUNT(CF34:CF35)=2,(CF34-CF35)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP34" s="3" t="n"/>
+        <f>IFERROR(AF34-P34,"")</f>
+        <v/>
+      </c>
+      <c r="CO34" s="6">
+        <f>IF(COUNT(H34:H53)=20,IFERROR(CORREL(H34:H53,P34:P53),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP34" s="4">
+        <f>IFERROR(AN34-AV34,"")</f>
+        <v/>
+      </c>
       <c r="CQ34" s="4">
-        <f>IFERROR(X34-P34,"")</f>
-        <v/>
-      </c>
-      <c r="CR34" s="4">
-        <f>IFERROR(AF34-P34,"")</f>
-        <v/>
-      </c>
-      <c r="CS34" s="6">
-        <f>IF(COUNT(H34:H53)=20,IFERROR(CORREL(H34:H53,P34:P53),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT34" s="4">
-        <f>IFERROR(AN34-AV34,"")</f>
-        <v/>
-      </c>
-      <c r="CU34" s="4">
         <f>IFERROR(BD34-BL34,"")</f>
         <v/>
       </c>
-      <c r="CV34" s="6">
-        <f>BY34/CF34</f>
-        <v/>
-      </c>
-      <c r="CW34" s="4">
+      <c r="CR34" s="6">
+        <f>BY34/CD34</f>
+        <v/>
+      </c>
+      <c r="CS34" s="4">
         <f>IFERROR(P34-BT34,"")</f>
         <v/>
       </c>
@@ -7306,82 +7050,70 @@
       <c r="BY35" s="3" t="n">
         <v>17.16</v>
       </c>
-      <c r="BZ35" s="3" t="n">
-        <v>17.16</v>
-      </c>
+      <c r="BZ35" s="3" t="n"/>
       <c r="CA35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB35" s="3" t="n"/>
+        <v>4.585</v>
+      </c>
+      <c r="CB35" s="3" t="n">
+        <v>4.618</v>
+      </c>
       <c r="CC35" s="3" t="n">
-        <v>4.585</v>
+        <v>4.573</v>
       </c>
       <c r="CD35" s="3" t="n">
-        <v>4.618</v>
-      </c>
-      <c r="CE35" s="3" t="n">
-        <v>4.573</v>
-      </c>
-      <c r="CF35" s="3" t="n">
         <v>4.609</v>
       </c>
-      <c r="CG35" s="3" t="n">
-        <v>4.609</v>
-      </c>
-      <c r="CH35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI35" s="3" t="n"/>
+      <c r="CE35" s="3" t="n"/>
+      <c r="CF35" s="4">
+        <f>IF(COUNT(BY35:BY36)=2,ROUND((BY35/BY36-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG35" s="4">
+        <f>IF(COUNT(BY35:BY36)=2,ROUND((BY35/BY36-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH35" s="4">
+        <f>IF(COUNT(BY35:BY40)=6,ROUND((BY35/BY40-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CI35" s="4">
+        <f>IF(COUNT(CG35:CG54)=20,IFERROR(ROUND(STDEV(CG35:CG54),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ35" s="4">
-        <f>IF(COUNT(BY35:BY36)=2,ROUND((BY35/BY36-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK35" s="4">
-        <f>IF(COUNT(BY35:BY36)=2,ROUND((BY35/BY36-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL35" s="4">
-        <f>IF(COUNT(BY35:BY40)=6,ROUND((BY35/BY40-1)*100,4),"")</f>
-        <v/>
-      </c>
+        <f>IF(COUNT(CD35:CD36)=2,ROUND((CD35/CD36-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK35" s="5">
+        <f>IF(COUNT(CD35:CD36)=2,(CD35-CD36)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL35" s="3" t="n"/>
       <c r="CM35" s="4">
-        <f>IF(COUNT(CK35:CK54)=20,IFERROR(ROUND(STDEV(CK35:CK54),4),""),"")</f>
+        <f>IFERROR(X35-P35,"")</f>
         <v/>
       </c>
       <c r="CN35" s="4">
-        <f>IF(COUNT(CF35:CF36)=2,ROUND((CF35/CF36-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO35" s="5">
-        <f>IF(COUNT(CF35:CF36)=2,(CF35-CF36)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP35" s="3" t="n"/>
+        <f>IFERROR(AF35-P35,"")</f>
+        <v/>
+      </c>
+      <c r="CO35" s="6">
+        <f>IF(COUNT(H35:H54)=20,IFERROR(CORREL(H35:H54,P35:P54),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP35" s="4">
+        <f>IFERROR(AN35-AV35,"")</f>
+        <v/>
+      </c>
       <c r="CQ35" s="4">
-        <f>IFERROR(X35-P35,"")</f>
-        <v/>
-      </c>
-      <c r="CR35" s="4">
-        <f>IFERROR(AF35-P35,"")</f>
-        <v/>
-      </c>
-      <c r="CS35" s="6">
-        <f>IF(COUNT(H35:H54)=20,IFERROR(CORREL(H35:H54,P35:P54),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT35" s="4">
-        <f>IFERROR(AN35-AV35,"")</f>
-        <v/>
-      </c>
-      <c r="CU35" s="4">
         <f>IFERROR(BD35-BL35,"")</f>
         <v/>
       </c>
-      <c r="CV35" s="6">
-        <f>BY35/CF35</f>
-        <v/>
-      </c>
-      <c r="CW35" s="4">
+      <c r="CR35" s="6">
+        <f>BY35/CD35</f>
+        <v/>
+      </c>
+      <c r="CS35" s="4">
         <f>IFERROR(P35-BT35,"")</f>
         <v/>
       </c>
@@ -7611,79 +7343,67 @@
       <c r="BY36" s="3" t="n">
         <v>15.03</v>
       </c>
-      <c r="BZ36" s="3" t="n">
-        <v>15.03</v>
-      </c>
+      <c r="BZ36" s="3" t="n"/>
       <c r="CA36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB36" s="3" t="n"/>
+        <v>4.541</v>
+      </c>
+      <c r="CB36" s="3" t="n">
+        <v>4.571</v>
+      </c>
       <c r="CC36" s="3" t="n">
-        <v>4.541</v>
+        <v>4.539</v>
       </c>
       <c r="CD36" s="3" t="n">
-        <v>4.571</v>
-      </c>
-      <c r="CE36" s="3" t="n">
-        <v>4.539</v>
-      </c>
-      <c r="CF36" s="3" t="n">
         <v>4.569</v>
       </c>
-      <c r="CG36" s="3" t="n">
-        <v>4.569</v>
-      </c>
-      <c r="CH36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI36" s="3" t="n"/>
+      <c r="CE36" s="3" t="n"/>
+      <c r="CF36" s="4">
+        <f>IF(COUNT(BY36:BY37)=2,ROUND((BY36/BY37-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG36" s="4">
+        <f>IF(COUNT(BY36:BY37)=2,ROUND((BY36/BY37-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH36" s="4" t="n"/>
+      <c r="CI36" s="4">
+        <f>IF(COUNT(CG36:CG55)=20,IFERROR(ROUND(STDEV(CG36:CG55),4),""),"")</f>
+        <v/>
+      </c>
       <c r="CJ36" s="4">
-        <f>IF(COUNT(BY36:BY37)=2,ROUND((BY36/BY37-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK36" s="4">
-        <f>IF(COUNT(BY36:BY37)=2,ROUND((BY36/BY37-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL36" s="4" t="n"/>
+        <f>IF(COUNT(CD36:CD37)=2,ROUND((CD36/CD37-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK36" s="5">
+        <f>IF(COUNT(CD36:CD37)=2,(CD36-CD37)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL36" s="3" t="n"/>
       <c r="CM36" s="4">
-        <f>IF(COUNT(CK36:CK55)=20,IFERROR(ROUND(STDEV(CK36:CK55),4),""),"")</f>
+        <f>IFERROR(X36-P36,"")</f>
         <v/>
       </c>
       <c r="CN36" s="4">
-        <f>IF(COUNT(CF36:CF37)=2,ROUND((CF36/CF37-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO36" s="5">
-        <f>IF(COUNT(CF36:CF37)=2,(CF36-CF37)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP36" s="3" t="n"/>
+        <f>IFERROR(AF36-P36,"")</f>
+        <v/>
+      </c>
+      <c r="CO36" s="6">
+        <f>IF(COUNT(H36:H55)=20,IFERROR(CORREL(H36:H55,P36:P55),""),"")</f>
+        <v/>
+      </c>
+      <c r="CP36" s="4">
+        <f>IFERROR(AN36-AV36,"")</f>
+        <v/>
+      </c>
       <c r="CQ36" s="4">
-        <f>IFERROR(X36-P36,"")</f>
-        <v/>
-      </c>
-      <c r="CR36" s="4">
-        <f>IFERROR(AF36-P36,"")</f>
-        <v/>
-      </c>
-      <c r="CS36" s="6">
-        <f>IF(COUNT(H36:H55)=20,IFERROR(CORREL(H36:H55,P36:P55),""),"")</f>
-        <v/>
-      </c>
-      <c r="CT36" s="4">
-        <f>IFERROR(AN36-AV36,"")</f>
-        <v/>
-      </c>
-      <c r="CU36" s="4">
         <f>IFERROR(BD36-BL36,"")</f>
         <v/>
       </c>
-      <c r="CV36" s="6">
-        <f>BY36/CF36</f>
-        <v/>
-      </c>
-      <c r="CW36" s="4">
+      <c r="CR36" s="6">
+        <f>BY36/CD36</f>
+        <v/>
+      </c>
+      <c r="CS36" s="4">
         <f>IFERROR(P36-BT36,"")</f>
         <v/>
       </c>
@@ -7913,73 +7633,61 @@
       <c r="BY37" s="3" t="n">
         <v>15.84</v>
       </c>
-      <c r="BZ37" s="3" t="n">
-        <v>15.84</v>
-      </c>
+      <c r="BZ37" s="3" t="n"/>
       <c r="CA37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB37" s="3" t="n"/>
+        <v>4.577</v>
+      </c>
+      <c r="CB37" s="3" t="n">
+        <v>4.581</v>
+      </c>
       <c r="CC37" s="3" t="n">
-        <v>4.577</v>
+        <v>4.529</v>
       </c>
       <c r="CD37" s="3" t="n">
-        <v>4.581</v>
-      </c>
-      <c r="CE37" s="3" t="n">
-        <v>4.529</v>
-      </c>
-      <c r="CF37" s="3" t="n">
         <v>4.539</v>
       </c>
-      <c r="CG37" s="3" t="n">
-        <v>4.539</v>
-      </c>
-      <c r="CH37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI37" s="3" t="n"/>
+      <c r="CE37" s="3" t="n"/>
+      <c r="CF37" s="4">
+        <f>IF(COUNT(BY37:BY38)=2,ROUND((BY37/BY38-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG37" s="4">
+        <f>IF(COUNT(BY37:BY38)=2,ROUND((BY37/BY38-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH37" s="4" t="n"/>
+      <c r="CI37" s="4" t="n"/>
       <c r="CJ37" s="4">
-        <f>IF(COUNT(BY37:BY38)=2,ROUND((BY37/BY38-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK37" s="4">
-        <f>IF(COUNT(BY37:BY38)=2,ROUND((BY37/BY38-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL37" s="4" t="n"/>
-      <c r="CM37" s="4" t="n"/>
+        <f>IF(COUNT(CD37:CD38)=2,ROUND((CD37/CD38-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK37" s="5">
+        <f>IF(COUNT(CD37:CD38)=2,(CD37-CD38)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL37" s="3" t="n"/>
+      <c r="CM37" s="4">
+        <f>IFERROR(X37-P37,"")</f>
+        <v/>
+      </c>
       <c r="CN37" s="4">
-        <f>IF(COUNT(CF37:CF38)=2,ROUND((CF37/CF38-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO37" s="5">
-        <f>IF(COUNT(CF37:CF38)=2,(CF37-CF38)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP37" s="3" t="n"/>
+        <f>IFERROR(AF37-P37,"")</f>
+        <v/>
+      </c>
+      <c r="CO37" s="6" t="n"/>
+      <c r="CP37" s="4">
+        <f>IFERROR(AN37-AV37,"")</f>
+        <v/>
+      </c>
       <c r="CQ37" s="4">
-        <f>IFERROR(X37-P37,"")</f>
-        <v/>
-      </c>
-      <c r="CR37" s="4">
-        <f>IFERROR(AF37-P37,"")</f>
-        <v/>
-      </c>
-      <c r="CS37" s="6" t="n"/>
-      <c r="CT37" s="4">
-        <f>IFERROR(AN37-AV37,"")</f>
-        <v/>
-      </c>
-      <c r="CU37" s="4">
         <f>IFERROR(BD37-BL37,"")</f>
         <v/>
       </c>
-      <c r="CV37" s="6">
-        <f>BY37/CF37</f>
-        <v/>
-      </c>
-      <c r="CW37" s="4">
+      <c r="CR37" s="6">
+        <f>BY37/CD37</f>
+        <v/>
+      </c>
+      <c r="CS37" s="4">
         <f>IFERROR(P37-BT37,"")</f>
         <v/>
       </c>
@@ -8209,73 +7917,61 @@
       <c r="BY38" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="BZ38" s="3" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="BZ38" s="3" t="n"/>
       <c r="CA38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB38" s="3" t="n"/>
+        <v>4.561</v>
+      </c>
+      <c r="CB38" s="3" t="n">
+        <v>4.597</v>
+      </c>
       <c r="CC38" s="3" t="n">
-        <v>4.561</v>
+        <v>4.557</v>
       </c>
       <c r="CD38" s="3" t="n">
-        <v>4.597</v>
-      </c>
-      <c r="CE38" s="3" t="n">
-        <v>4.557</v>
-      </c>
-      <c r="CF38" s="3" t="n">
         <v>4.569</v>
       </c>
-      <c r="CG38" s="3" t="n">
-        <v>4.569</v>
-      </c>
-      <c r="CH38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI38" s="3" t="n"/>
+      <c r="CE38" s="3" t="n"/>
+      <c r="CF38" s="4">
+        <f>IF(COUNT(BY38:BY39)=2,ROUND((BY38/BY39-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG38" s="4">
+        <f>IF(COUNT(BY38:BY39)=2,ROUND((BY38/BY39-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH38" s="4" t="n"/>
+      <c r="CI38" s="4" t="n"/>
       <c r="CJ38" s="4">
-        <f>IF(COUNT(BY38:BY39)=2,ROUND((BY38/BY39-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK38" s="4">
-        <f>IF(COUNT(BY38:BY39)=2,ROUND((BY38/BY39-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL38" s="4" t="n"/>
-      <c r="CM38" s="4" t="n"/>
+        <f>IF(COUNT(CD38:CD39)=2,ROUND((CD38/CD39-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK38" s="5">
+        <f>IF(COUNT(CD38:CD39)=2,(CD38-CD39)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL38" s="3" t="n"/>
+      <c r="CM38" s="4">
+        <f>IFERROR(X38-P38,"")</f>
+        <v/>
+      </c>
       <c r="CN38" s="4">
-        <f>IF(COUNT(CF38:CF39)=2,ROUND((CF38/CF39-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO38" s="5">
-        <f>IF(COUNT(CF38:CF39)=2,(CF38-CF39)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP38" s="3" t="n"/>
+        <f>IFERROR(AF38-P38,"")</f>
+        <v/>
+      </c>
+      <c r="CO38" s="6" t="n"/>
+      <c r="CP38" s="4">
+        <f>IFERROR(AN38-AV38,"")</f>
+        <v/>
+      </c>
       <c r="CQ38" s="4">
-        <f>IFERROR(X38-P38,"")</f>
-        <v/>
-      </c>
-      <c r="CR38" s="4">
-        <f>IFERROR(AF38-P38,"")</f>
-        <v/>
-      </c>
-      <c r="CS38" s="6" t="n"/>
-      <c r="CT38" s="4">
-        <f>IFERROR(AN38-AV38,"")</f>
-        <v/>
-      </c>
-      <c r="CU38" s="4">
         <f>IFERROR(BD38-BL38,"")</f>
         <v/>
       </c>
-      <c r="CV38" s="6">
-        <f>BY38/CF38</f>
-        <v/>
-      </c>
-      <c r="CW38" s="4">
+      <c r="CR38" s="6">
+        <f>BY38/CD38</f>
+        <v/>
+      </c>
+      <c r="CS38" s="4">
         <f>IFERROR(P38-BT38,"")</f>
         <v/>
       </c>
@@ -8505,73 +8201,61 @@
       <c r="BY39" s="3" t="n">
         <v>16.13</v>
       </c>
-      <c r="BZ39" s="3" t="n">
-        <v>16.13</v>
-      </c>
+      <c r="BZ39" s="3" t="n"/>
       <c r="CA39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB39" s="3" t="n"/>
+        <v>4.497</v>
+      </c>
+      <c r="CB39" s="3" t="n">
+        <v>4.533</v>
+      </c>
       <c r="CC39" s="3" t="n">
-        <v>4.497</v>
+        <v>4.485</v>
       </c>
       <c r="CD39" s="3" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="CE39" s="3" t="n">
-        <v>4.485</v>
-      </c>
-      <c r="CF39" s="3" t="n">
         <v>4.529</v>
       </c>
-      <c r="CG39" s="3" t="n">
-        <v>4.529</v>
-      </c>
-      <c r="CH39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI39" s="3" t="n"/>
+      <c r="CE39" s="3" t="n"/>
+      <c r="CF39" s="4">
+        <f>IF(COUNT(BY39:BY40)=2,ROUND((BY39/BY40-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG39" s="4">
+        <f>IF(COUNT(BY39:BY40)=2,ROUND((BY39/BY40-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH39" s="4" t="n"/>
+      <c r="CI39" s="4" t="n"/>
       <c r="CJ39" s="4">
-        <f>IF(COUNT(BY39:BY40)=2,ROUND((BY39/BY40-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK39" s="4">
-        <f>IF(COUNT(BY39:BY40)=2,ROUND((BY39/BY40-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL39" s="4" t="n"/>
-      <c r="CM39" s="4" t="n"/>
+        <f>IF(COUNT(CD39:CD40)=2,ROUND((CD39/CD40-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK39" s="5">
+        <f>IF(COUNT(CD39:CD40)=2,(CD39-CD40)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL39" s="3" t="n"/>
+      <c r="CM39" s="4">
+        <f>IFERROR(X39-P39,"")</f>
+        <v/>
+      </c>
       <c r="CN39" s="4">
-        <f>IF(COUNT(CF39:CF40)=2,ROUND((CF39/CF40-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO39" s="5">
-        <f>IF(COUNT(CF39:CF40)=2,(CF39-CF40)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP39" s="3" t="n"/>
+        <f>IFERROR(AF39-P39,"")</f>
+        <v/>
+      </c>
+      <c r="CO39" s="6" t="n"/>
+      <c r="CP39" s="4">
+        <f>IFERROR(AN39-AV39,"")</f>
+        <v/>
+      </c>
       <c r="CQ39" s="4">
-        <f>IFERROR(X39-P39,"")</f>
-        <v/>
-      </c>
-      <c r="CR39" s="4">
-        <f>IFERROR(AF39-P39,"")</f>
-        <v/>
-      </c>
-      <c r="CS39" s="6" t="n"/>
-      <c r="CT39" s="4">
-        <f>IFERROR(AN39-AV39,"")</f>
-        <v/>
-      </c>
-      <c r="CU39" s="4">
         <f>IFERROR(BD39-BL39,"")</f>
         <v/>
       </c>
-      <c r="CV39" s="6">
-        <f>BY39/CF39</f>
-        <v/>
-      </c>
-      <c r="CW39" s="4">
+      <c r="CR39" s="6">
+        <f>BY39/CD39</f>
+        <v/>
+      </c>
+      <c r="CS39" s="4">
         <f>IFERROR(P39-BT39,"")</f>
         <v/>
       </c>
@@ -8774,73 +8458,61 @@
       <c r="BY40" s="3" t="n">
         <v>15.57</v>
       </c>
-      <c r="BZ40" s="3" t="n">
-        <v>15.57</v>
-      </c>
+      <c r="BZ40" s="3" t="n"/>
       <c r="CA40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB40" s="3" t="n"/>
+        <v>4.457</v>
+      </c>
+      <c r="CB40" s="3" t="n">
+        <v>4.491</v>
+      </c>
       <c r="CC40" s="3" t="n">
         <v>4.457</v>
       </c>
       <c r="CD40" s="3" t="n">
-        <v>4.491</v>
-      </c>
-      <c r="CE40" s="3" t="n">
-        <v>4.457</v>
-      </c>
-      <c r="CF40" s="3" t="n">
         <v>4.479</v>
       </c>
-      <c r="CG40" s="3" t="n">
-        <v>4.479</v>
-      </c>
-      <c r="CH40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI40" s="3" t="n"/>
+      <c r="CE40" s="3" t="n"/>
+      <c r="CF40" s="4">
+        <f>IF(COUNT(BY40:BY41)=2,ROUND((BY40/BY41-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CG40" s="4">
+        <f>IF(COUNT(BY40:BY41)=2,ROUND((BY40/BY41-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CH40" s="4" t="n"/>
+      <c r="CI40" s="4" t="n"/>
       <c r="CJ40" s="4">
-        <f>IF(COUNT(BY40:BY41)=2,ROUND((BY40/BY41-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CK40" s="4">
-        <f>IF(COUNT(BY40:BY41)=2,ROUND((BY40/BY41-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CL40" s="4" t="n"/>
-      <c r="CM40" s="4" t="n"/>
+        <f>IF(COUNT(CD40:CD41)=2,ROUND((CD40/CD41-1)*100,4),"")</f>
+        <v/>
+      </c>
+      <c r="CK40" s="5">
+        <f>IF(COUNT(CD40:CD41)=2,(CD40-CD41)*100,"")</f>
+        <v/>
+      </c>
+      <c r="CL40" s="3" t="n"/>
+      <c r="CM40" s="4">
+        <f>IFERROR(X40-P40,"")</f>
+        <v/>
+      </c>
       <c r="CN40" s="4">
-        <f>IF(COUNT(CF40:CF41)=2,ROUND((CF40/CF41-1)*100,4),"")</f>
-        <v/>
-      </c>
-      <c r="CO40" s="5">
-        <f>IF(COUNT(CF40:CF41)=2,(CF40-CF41)*100,"")</f>
-        <v/>
-      </c>
-      <c r="CP40" s="3" t="n"/>
+        <f>IFERROR(AF40-P40,"")</f>
+        <v/>
+      </c>
+      <c r="CO40" s="6" t="n"/>
+      <c r="CP40" s="4">
+        <f>IFERROR(AN40-AV40,"")</f>
+        <v/>
+      </c>
       <c r="CQ40" s="4">
-        <f>IFERROR(X40-P40,"")</f>
-        <v/>
-      </c>
-      <c r="CR40" s="4">
-        <f>IFERROR(AF40-P40,"")</f>
-        <v/>
-      </c>
-      <c r="CS40" s="6" t="n"/>
-      <c r="CT40" s="4">
-        <f>IFERROR(AN40-AV40,"")</f>
-        <v/>
-      </c>
-      <c r="CU40" s="4">
         <f>IFERROR(BD40-BL40,"")</f>
         <v/>
       </c>
-      <c r="CV40" s="6">
-        <f>BY40/CF40</f>
-        <v/>
-      </c>
-      <c r="CW40" s="4">
+      <c r="CR40" s="6">
+        <f>BY40/CD40</f>
+        <v/>
+      </c>
+      <c r="CS40" s="4">
         <f>IFERROR(P40-BT40,"")</f>
         <v/>
       </c>
